--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49C2AF23-DCD6-4741-A475-52EC723F0867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71944921-81FA-41FA-BA47-12406B240C39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -200,74 +200,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -287,7 +219,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="CCE8CF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -542,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C285"/>
+  <dimension ref="A1:C296"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -630,7 +562,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -718,7 +650,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -806,7 +738,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -894,7 +826,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -963,6 +895,9 @@
       <c r="B54" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C54" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B55" s="3" t="s">
@@ -979,7 +914,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -1040,7 +975,9 @@
       <c r="B64" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C64" s="6"/>
+      <c r="C64" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B65" s="3" t="s">
@@ -1056,10 +993,13 @@
       <c r="B67" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C67" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1120,17 +1060,12 @@
       <c r="B75" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C75" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C75" s="6"/>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B76" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C76" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B77" s="3" t="s">
@@ -1141,13 +1076,10 @@
       <c r="B78" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C78" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1235,7 +1167,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1323,7 +1255,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1392,6 +1324,9 @@
       <c r="B109" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C109" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B110" s="3" t="s">
@@ -1408,7 +1343,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1493,7 +1428,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1567,9 +1502,6 @@
       <c r="B132" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C132" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B133" s="3" t="s">
@@ -1581,7 +1513,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1642,7 +1574,9 @@
       <c r="B141" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C141" s="6"/>
+      <c r="C141" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B142" s="3" t="s">
@@ -1653,15 +1587,21 @@
       <c r="B143" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C143" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B144" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C144" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1722,9 +1662,7 @@
       <c r="B152" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C152" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C152" s="6"/>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B153" s="3" t="s">
@@ -1740,13 +1678,10 @@
       <c r="B155" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C155" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1815,9 +1750,6 @@
       <c r="B164" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C164" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B165" s="3" t="s">
@@ -1834,7 +1766,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1903,6 +1835,9 @@
       <c r="B175" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C175" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B176" s="3" t="s">
@@ -1919,7 +1854,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1998,10 +1933,13 @@
       <c r="B188" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C188" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2080,13 +2018,10 @@
       <c r="B199" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C199" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2155,9 +2090,6 @@
       <c r="B208" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C208" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B209" s="3" t="s">
@@ -2174,7 +2106,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2195,19 +2127,25 @@
       <c r="B213" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C213" s="6"/>
+      <c r="C213" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B214" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C214" s="6"/>
+      <c r="C214" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B215" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C215" s="6"/>
+      <c r="C215" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B216" s="3" t="s">
@@ -2229,12 +2167,17 @@
       <c r="B218" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C218" s="6"/>
+      <c r="C218" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B219" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C219" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B220" s="3" t="s">
@@ -2245,10 +2188,13 @@
       <c r="B221" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C221" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2269,25 +2215,19 @@
       <c r="B224" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C224" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C224" s="6"/>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B225" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C225" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C225" s="6"/>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B226" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C226" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C226" s="6"/>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B227" s="3" t="s">
@@ -2309,17 +2249,12 @@
       <c r="B229" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C229" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C229" s="6"/>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B230" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C230" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B231" s="3" t="s">
@@ -2330,13 +2265,10 @@
       <c r="B232" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C232" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2424,7 +2356,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2493,6 +2425,9 @@
       <c r="B252" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C252" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B253" s="3" t="s">
@@ -2509,7 +2444,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2578,9 +2513,6 @@
       <c r="B263" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C263" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B264" s="3" t="s">
@@ -2588,19 +2520,19 @@
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A265" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B265" s="7" t="s">
+      <c r="B265" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C265" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A266" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B266" s="7" t="s">
         <v>3</v>
-      </c>
-      <c r="C265" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B266" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="C266" s="5" t="s">
         <v>13</v>
@@ -2608,7 +2540,7 @@
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B267" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C267" s="5" t="s">
         <v>13</v>
@@ -2616,7 +2548,7 @@
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B268" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C268" s="5" t="s">
         <v>13</v>
@@ -2624,7 +2556,7 @@
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B269" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C269" s="5" t="s">
         <v>13</v>
@@ -2632,7 +2564,7 @@
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B270" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C270" s="5" t="s">
         <v>13</v>
@@ -2640,7 +2572,7 @@
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B271" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C271" s="5" t="s">
         <v>13</v>
@@ -2648,7 +2580,7 @@
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B272" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C272" s="5" t="s">
         <v>13</v>
@@ -2656,7 +2588,7 @@
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B273" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C273" s="5" t="s">
         <v>13</v>
@@ -2664,23 +2596,23 @@
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B274" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C274" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B275" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A275" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B275" s="7" t="s">
+    <row r="276" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A276" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B276" s="7" t="s">
         <v>3</v>
-      </c>
-      <c r="C275" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B276" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="C276" s="5" t="s">
         <v>13</v>
@@ -2688,7 +2620,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B277" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C277" s="5" t="s">
         <v>13</v>
@@ -2696,7 +2628,7 @@
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B278" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C278" s="5" t="s">
         <v>13</v>
@@ -2704,7 +2636,7 @@
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B279" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C279" s="5" t="s">
         <v>13</v>
@@ -2712,7 +2644,7 @@
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B280" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C280" s="5" t="s">
         <v>13</v>
@@ -2720,7 +2652,7 @@
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B281" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C281" s="5" t="s">
         <v>13</v>
@@ -2728,7 +2660,7 @@
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B282" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C282" s="5" t="s">
         <v>13</v>
@@ -2736,16 +2668,104 @@
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B283" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C283" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B284" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C284" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B285" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B285" s="3">
+    <row r="286" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A286" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B286" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C286" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B287" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C287" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B288" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C288" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="289" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B289" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C289" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="290" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B290" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C290" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="291" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B291" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C291" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="292" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B292" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C292" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="293" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B293" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C293" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="294" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B294" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="295" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B295" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="296" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B296" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71944921-81FA-41FA-BA47-12406B240C39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC819D27-532E-4955-8B0E-86D9F3C0F389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -474,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C296"/>
+  <dimension ref="A1:C307"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -562,7 +562,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -650,7 +650,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -738,7 +738,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -826,7 +826,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -914,7 +914,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -983,6 +983,9 @@
       <c r="B65" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C65" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B66" s="3" t="s">
@@ -999,7 +1002,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1060,7 +1063,9 @@
       <c r="B75" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C75" s="6"/>
+      <c r="C75" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B76" s="3" t="s">
@@ -1076,10 +1081,13 @@
       <c r="B78" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C78" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1140,17 +1148,12 @@
       <c r="B86" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C86" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C86" s="6"/>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B87" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C87" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B88" s="3" t="s">
@@ -1161,13 +1164,10 @@
       <c r="B89" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C89" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1255,7 +1255,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1343,7 +1343,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1412,6 +1412,9 @@
       <c r="B120" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C120" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B121" s="3" t="s">
@@ -1428,7 +1431,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1513,7 +1516,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1587,9 +1590,6 @@
       <c r="B143" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C143" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B144" s="3" t="s">
@@ -1601,7 +1601,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1662,7 +1662,9 @@
       <c r="B152" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C152" s="6"/>
+      <c r="C152" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B153" s="3" t="s">
@@ -1673,15 +1675,21 @@
       <c r="B154" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C154" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B155" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C155" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1742,9 +1750,7 @@
       <c r="B163" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C163" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C163" s="6"/>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B164" s="3" t="s">
@@ -1760,13 +1766,10 @@
       <c r="B166" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C166" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1835,9 +1838,6 @@
       <c r="B175" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C175" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B176" s="3" t="s">
@@ -1854,7 +1854,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1923,6 +1923,9 @@
       <c r="B186" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C186" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B187" s="3" t="s">
@@ -1939,7 +1942,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2018,10 +2021,13 @@
       <c r="B199" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C199" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2100,13 +2106,10 @@
       <c r="B210" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C210" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2175,9 +2178,6 @@
       <c r="B219" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C219" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B220" s="3" t="s">
@@ -2194,7 +2194,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2215,19 +2215,25 @@
       <c r="B224" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C224" s="6"/>
+      <c r="C224" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B225" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C225" s="6"/>
+      <c r="C225" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B226" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C226" s="6"/>
+      <c r="C226" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B227" s="3" t="s">
@@ -2249,12 +2255,17 @@
       <c r="B229" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C229" s="6"/>
+      <c r="C229" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B230" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C230" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B231" s="3" t="s">
@@ -2265,10 +2276,13 @@
       <c r="B232" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C232" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2289,25 +2303,19 @@
       <c r="B235" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C235" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C235" s="6"/>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B236" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C236" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C236" s="6"/>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B237" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C237" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C237" s="6"/>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B238" s="3" t="s">
@@ -2329,17 +2337,12 @@
       <c r="B240" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C240" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C240" s="6"/>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B241" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C241" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B242" s="3" t="s">
@@ -2350,13 +2353,10 @@
       <c r="B243" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C243" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2444,7 +2444,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2513,6 +2513,9 @@
       <c r="B263" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C263" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B264" s="3" t="s">
@@ -2529,7 +2532,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2598,9 +2601,6 @@
       <c r="B274" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C274" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B275" s="3" t="s">
@@ -2608,19 +2608,19 @@
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A276" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B276" s="7" t="s">
+      <c r="B276" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C276" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A277" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B277" s="7" t="s">
         <v>3</v>
-      </c>
-      <c r="C276" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B277" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="C277" s="5" t="s">
         <v>13</v>
@@ -2628,7 +2628,7 @@
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B278" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C278" s="5" t="s">
         <v>13</v>
@@ -2636,7 +2636,7 @@
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B279" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C279" s="5" t="s">
         <v>13</v>
@@ -2644,7 +2644,7 @@
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B280" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C280" s="5" t="s">
         <v>13</v>
@@ -2652,7 +2652,7 @@
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B281" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C281" s="5" t="s">
         <v>13</v>
@@ -2660,7 +2660,7 @@
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B282" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C282" s="5" t="s">
         <v>13</v>
@@ -2668,7 +2668,7 @@
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B283" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C283" s="5" t="s">
         <v>13</v>
@@ -2676,7 +2676,7 @@
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B284" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C284" s="5" t="s">
         <v>13</v>
@@ -2684,23 +2684,23 @@
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B285" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C285" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B286" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A286" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B286" s="7" t="s">
+    <row r="287" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A287" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B287" s="7" t="s">
         <v>3</v>
-      </c>
-      <c r="C286" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B287" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="C287" s="5" t="s">
         <v>13</v>
@@ -2708,64 +2708,152 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B288" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C288" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B289" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C288" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="289" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B289" s="3" t="s">
+      <c r="C289" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B290" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C289" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="290" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B290" s="3" t="s">
+      <c r="C290" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B291" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C290" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="291" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B291" s="3" t="s">
+      <c r="C291" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B292" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C291" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="292" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B292" s="3" t="s">
+      <c r="C292" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B293" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C292" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="293" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B293" s="3" t="s">
+      <c r="C293" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B294" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C293" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="294" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B294" s="3" t="s">
+      <c r="C294" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B295" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="295" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B295" s="3" t="s">
+      <c r="C295" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B296" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="296" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B296" s="3">
+    <row r="297" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A297" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B297" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C297" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B298" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C298" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B299" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C299" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B300" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C300" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B301" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C301" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B302" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C302" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B303" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C303" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B304" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C304" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="305" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B305" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="306" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B306" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="307" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B307" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC819D27-532E-4955-8B0E-86D9F3C0F389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBAA1F3B-41F9-4103-9515-711A1C19E331}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -200,6 +200,74 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -219,7 +287,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window" lastClr="CCE8CF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -474,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C307"/>
+  <dimension ref="A1:C318"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -562,7 +630,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -639,6 +707,9 @@
       <c r="B22" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C22" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B23" s="3" t="s">
@@ -650,7 +721,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -738,7 +809,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -826,7 +897,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -914,7 +985,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -1002,7 +1073,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1071,6 +1142,9 @@
       <c r="B76" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C76" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B77" s="3" t="s">
@@ -1087,7 +1161,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1148,7 +1222,9 @@
       <c r="B86" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C86" s="6"/>
+      <c r="C86" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B87" s="3" t="s">
@@ -1164,10 +1240,13 @@
       <c r="B89" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C89" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1228,17 +1307,12 @@
       <c r="B97" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C97" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C97" s="6"/>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B98" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C98" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B99" s="3" t="s">
@@ -1249,13 +1323,10 @@
       <c r="B100" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C100" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1343,7 +1414,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1431,7 +1502,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1500,6 +1571,9 @@
       <c r="B131" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C131" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B132" s="3" t="s">
@@ -1516,7 +1590,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1601,7 +1675,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1675,9 +1749,6 @@
       <c r="B154" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C154" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B155" s="3" t="s">
@@ -1689,7 +1760,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1750,7 +1821,9 @@
       <c r="B163" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C163" s="6"/>
+      <c r="C163" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B164" s="3" t="s">
@@ -1761,15 +1834,21 @@
       <c r="B165" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C165" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B166" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C166" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1830,9 +1909,7 @@
       <c r="B174" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C174" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C174" s="6"/>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B175" s="3" t="s">
@@ -1848,13 +1925,10 @@
       <c r="B177" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C177" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1923,9 +1997,6 @@
       <c r="B186" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C186" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B187" s="3" t="s">
@@ -1942,7 +2013,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2011,6 +2082,9 @@
       <c r="B197" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C197" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B198" s="3" t="s">
@@ -2027,7 +2101,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2106,10 +2180,13 @@
       <c r="B210" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C210" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2188,13 +2265,10 @@
       <c r="B221" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C221" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2263,9 +2337,6 @@
       <c r="B230" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C230" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B231" s="3" t="s">
@@ -2282,7 +2353,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2303,19 +2374,25 @@
       <c r="B235" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C235" s="6"/>
+      <c r="C235" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B236" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C236" s="6"/>
+      <c r="C236" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B237" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C237" s="6"/>
+      <c r="C237" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B238" s="3" t="s">
@@ -2337,12 +2414,17 @@
       <c r="B240" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C240" s="6"/>
+      <c r="C240" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B241" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C241" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B242" s="3" t="s">
@@ -2353,10 +2435,13 @@
       <c r="B243" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C243" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2377,25 +2462,19 @@
       <c r="B246" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C246" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C246" s="6"/>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B247" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C247" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C247" s="6"/>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B248" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C248" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C248" s="6"/>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B249" s="3" t="s">
@@ -2417,17 +2496,12 @@
       <c r="B251" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C251" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C251" s="6"/>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B252" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C252" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B253" s="3" t="s">
@@ -2438,13 +2512,10 @@
       <c r="B254" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C254" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2532,7 +2603,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2601,6 +2672,9 @@
       <c r="B274" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C274" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B275" s="3" t="s">
@@ -2617,7 +2691,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2686,9 +2760,6 @@
       <c r="B285" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C285" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B286" s="3" t="s">
@@ -2696,19 +2767,19 @@
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A287" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B287" s="7" t="s">
+      <c r="B287" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C287" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A288" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B288" s="7" t="s">
         <v>3</v>
-      </c>
-      <c r="C287" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B288" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="C288" s="5" t="s">
         <v>13</v>
@@ -2716,7 +2787,7 @@
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B289" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C289" s="5" t="s">
         <v>13</v>
@@ -2724,7 +2795,7 @@
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B290" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C290" s="5" t="s">
         <v>13</v>
@@ -2732,7 +2803,7 @@
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B291" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C291" s="5" t="s">
         <v>13</v>
@@ -2740,7 +2811,7 @@
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B292" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C292" s="5" t="s">
         <v>13</v>
@@ -2748,7 +2819,7 @@
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B293" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C293" s="5" t="s">
         <v>13</v>
@@ -2756,7 +2827,7 @@
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B294" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C294" s="5" t="s">
         <v>13</v>
@@ -2764,7 +2835,7 @@
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B295" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C295" s="5" t="s">
         <v>13</v>
@@ -2772,23 +2843,23 @@
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B296" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C296" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B297" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A297" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B297" s="7" t="s">
+    <row r="298" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A298" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B298" s="7" t="s">
         <v>3</v>
-      </c>
-      <c r="C297" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B298" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="C298" s="5" t="s">
         <v>13</v>
@@ -2796,7 +2867,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B299" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C299" s="5" t="s">
         <v>13</v>
@@ -2804,7 +2875,7 @@
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B300" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C300" s="5" t="s">
         <v>13</v>
@@ -2812,7 +2883,7 @@
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B301" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C301" s="5" t="s">
         <v>13</v>
@@ -2820,7 +2891,7 @@
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B302" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C302" s="5" t="s">
         <v>13</v>
@@ -2828,7 +2899,7 @@
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B303" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C303" s="5" t="s">
         <v>13</v>
@@ -2836,24 +2907,112 @@
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B304" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C304" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B305" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C304" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="305" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B305" s="3" t="s">
+      <c r="C305" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B306" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="306" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B306" s="3" t="s">
+      <c r="C306" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B307" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="307" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B307" s="3">
+    <row r="308" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A308" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B308" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C308" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B309" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C309" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B310" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C310" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B311" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C311" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B312" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C312" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B313" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C313" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B314" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C314" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B315" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C315" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B316" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B317" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B318" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\WinnerTakeAll\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\03aioveu-Day\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBAA1F3B-41F9-4103-9515-711A1C19E331}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6F03925-02CD-48DA-A6EB-E719A893CA46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -200,74 +200,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -287,7 +219,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="CCE8CF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -542,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C318"/>
+  <dimension ref="A1:C329"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -630,7 +562,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -707,9 +639,6 @@
       <c r="B22" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B23" s="3" t="s">
@@ -721,7 +650,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -798,6 +727,9 @@
       <c r="B33" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C33" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B34" s="3" t="s">
@@ -809,7 +741,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -897,7 +829,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -985,7 +917,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -1073,7 +1005,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1161,7 +1093,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1230,6 +1162,9 @@
       <c r="B87" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C87" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B88" s="3" t="s">
@@ -1246,7 +1181,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1307,7 +1242,9 @@
       <c r="B97" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C97" s="6"/>
+      <c r="C97" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B98" s="3" t="s">
@@ -1323,10 +1260,13 @@
       <c r="B100" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C100" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1387,17 +1327,12 @@
       <c r="B108" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C108" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C108" s="6"/>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B109" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C109" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B110" s="3" t="s">
@@ -1408,13 +1343,10 @@
       <c r="B111" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C111" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1502,7 +1434,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1590,7 +1522,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1659,6 +1591,9 @@
       <c r="B142" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C142" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B143" s="3" t="s">
@@ -1675,7 +1610,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1760,7 +1695,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1834,9 +1769,6 @@
       <c r="B165" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C165" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B166" s="3" t="s">
@@ -1848,7 +1780,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1909,7 +1841,9 @@
       <c r="B174" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C174" s="6"/>
+      <c r="C174" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B175" s="3" t="s">
@@ -1920,15 +1854,21 @@
       <c r="B176" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C176" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B177" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C177" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1989,9 +1929,7 @@
       <c r="B185" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C185" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C185" s="6"/>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B186" s="3" t="s">
@@ -2007,13 +1945,10 @@
       <c r="B188" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C188" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2082,9 +2017,6 @@
       <c r="B197" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C197" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B198" s="3" t="s">
@@ -2101,7 +2033,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2170,6 +2102,9 @@
       <c r="B208" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C208" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B209" s="3" t="s">
@@ -2186,7 +2121,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2265,10 +2200,13 @@
       <c r="B221" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C221" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2347,13 +2285,10 @@
       <c r="B232" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C232" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2422,9 +2357,6 @@
       <c r="B241" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C241" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B242" s="3" t="s">
@@ -2441,7 +2373,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2462,19 +2394,25 @@
       <c r="B246" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C246" s="6"/>
+      <c r="C246" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B247" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C247" s="6"/>
+      <c r="C247" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B248" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C248" s="6"/>
+      <c r="C248" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B249" s="3" t="s">
@@ -2496,12 +2434,17 @@
       <c r="B251" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C251" s="6"/>
+      <c r="C251" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B252" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C252" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B253" s="3" t="s">
@@ -2512,10 +2455,13 @@
       <c r="B254" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C254" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2536,25 +2482,19 @@
       <c r="B257" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C257" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C257" s="6"/>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B258" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C258" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C258" s="6"/>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B259" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C259" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C259" s="6"/>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B260" s="3" t="s">
@@ -2576,17 +2516,12 @@
       <c r="B262" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C262" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C262" s="6"/>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B263" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C263" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B264" s="3" t="s">
@@ -2597,13 +2532,10 @@
       <c r="B265" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C265" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2691,7 +2623,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2760,6 +2692,9 @@
       <c r="B285" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C285" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B286" s="3" t="s">
@@ -2776,7 +2711,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2845,9 +2780,6 @@
       <c r="B296" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C296" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B297" s="3" t="s">
@@ -2855,19 +2787,19 @@
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A298" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B298" s="7" t="s">
+      <c r="B298" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C298" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A299" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B299" s="7" t="s">
         <v>3</v>
-      </c>
-      <c r="C298" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B299" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="C299" s="5" t="s">
         <v>13</v>
@@ -2875,7 +2807,7 @@
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B300" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C300" s="5" t="s">
         <v>13</v>
@@ -2883,7 +2815,7 @@
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B301" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C301" s="5" t="s">
         <v>13</v>
@@ -2891,7 +2823,7 @@
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B302" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C302" s="5" t="s">
         <v>13</v>
@@ -2899,7 +2831,7 @@
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B303" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C303" s="5" t="s">
         <v>13</v>
@@ -2907,7 +2839,7 @@
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B304" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C304" s="5" t="s">
         <v>13</v>
@@ -2915,7 +2847,7 @@
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B305" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C305" s="5" t="s">
         <v>13</v>
@@ -2923,7 +2855,7 @@
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B306" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C306" s="5" t="s">
         <v>13</v>
@@ -2931,23 +2863,23 @@
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B307" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C307" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B308" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A308" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B308" s="7" t="s">
+    <row r="309" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A309" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B309" s="7" t="s">
         <v>3</v>
-      </c>
-      <c r="C308" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B309" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="C309" s="5" t="s">
         <v>13</v>
@@ -2955,7 +2887,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B310" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C310" s="5" t="s">
         <v>13</v>
@@ -2963,7 +2895,7 @@
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B311" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C311" s="5" t="s">
         <v>13</v>
@@ -2971,7 +2903,7 @@
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B312" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C312" s="5" t="s">
         <v>13</v>
@@ -2979,7 +2911,7 @@
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B313" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C313" s="5" t="s">
         <v>13</v>
@@ -2987,7 +2919,7 @@
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B314" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C314" s="5" t="s">
         <v>13</v>
@@ -2995,7 +2927,7 @@
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B315" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C315" s="5" t="s">
         <v>13</v>
@@ -3003,16 +2935,104 @@
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B316" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C316" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B317" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C317" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B318" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B318" s="3">
+    <row r="319" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A319" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B319" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C319" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B320" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C320" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="321" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B321" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C321" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="322" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B322" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C322" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="323" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B323" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C323" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="324" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B324" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C324" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="325" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B325" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C325" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="326" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B326" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C326" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="327" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B327" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="328" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B328" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="329" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B329" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\03aioveu-Day\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6F03925-02CD-48DA-A6EB-E719A893CA46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86F7A736-C480-4317-9379-2F131FE78F64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -200,6 +200,74 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -219,7 +287,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window" lastClr="CCE8CF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -474,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C329"/>
+  <dimension ref="A1:C340"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -562,7 +630,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -650,7 +718,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -727,9 +795,6 @@
       <c r="B33" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C33" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B34" s="3" t="s">
@@ -741,7 +806,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -818,6 +883,9 @@
       <c r="B44" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C44" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B45" s="3" t="s">
@@ -829,7 +897,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -917,7 +985,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -1005,7 +1073,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1093,7 +1161,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1181,7 +1249,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1250,6 +1318,9 @@
       <c r="B98" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C98" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B99" s="3" t="s">
@@ -1266,7 +1337,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1327,7 +1398,9 @@
       <c r="B108" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C108" s="6"/>
+      <c r="C108" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B109" s="3" t="s">
@@ -1343,10 +1416,13 @@
       <c r="B111" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C111" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1407,17 +1483,12 @@
       <c r="B119" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C119" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C119" s="6"/>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B120" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C120" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B121" s="3" t="s">
@@ -1428,13 +1499,10 @@
       <c r="B122" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C122" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1522,7 +1590,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1610,7 +1678,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1679,6 +1747,9 @@
       <c r="B153" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C153" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B154" s="3" t="s">
@@ -1695,7 +1766,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1780,7 +1851,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1854,9 +1925,6 @@
       <c r="B176" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C176" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B177" s="3" t="s">
@@ -1868,7 +1936,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1929,7 +1997,9 @@
       <c r="B185" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C185" s="6"/>
+      <c r="C185" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B186" s="3" t="s">
@@ -1940,15 +2010,21 @@
       <c r="B187" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C187" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B188" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C188" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2009,9 +2085,7 @@
       <c r="B196" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C196" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C196" s="6"/>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B197" s="3" t="s">
@@ -2027,13 +2101,10 @@
       <c r="B199" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C199" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2102,9 +2173,6 @@
       <c r="B208" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C208" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B209" s="3" t="s">
@@ -2121,7 +2189,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2190,6 +2258,9 @@
       <c r="B219" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C219" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B220" s="3" t="s">
@@ -2206,7 +2277,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2285,10 +2356,13 @@
       <c r="B232" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C232" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2367,13 +2441,10 @@
       <c r="B243" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C243" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2442,9 +2513,6 @@
       <c r="B252" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C252" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B253" s="3" t="s">
@@ -2461,7 +2529,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2482,19 +2550,25 @@
       <c r="B257" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C257" s="6"/>
+      <c r="C257" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B258" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C258" s="6"/>
+      <c r="C258" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B259" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C259" s="6"/>
+      <c r="C259" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B260" s="3" t="s">
@@ -2516,12 +2590,17 @@
       <c r="B262" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C262" s="6"/>
+      <c r="C262" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B263" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C263" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B264" s="3" t="s">
@@ -2532,10 +2611,13 @@
       <c r="B265" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C265" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2556,25 +2638,19 @@
       <c r="B268" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C268" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C268" s="6"/>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B269" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C269" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C269" s="6"/>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B270" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C270" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C270" s="6"/>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B271" s="3" t="s">
@@ -2596,17 +2672,12 @@
       <c r="B273" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C273" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C273" s="6"/>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B274" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C274" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B275" s="3" t="s">
@@ -2617,13 +2688,10 @@
       <c r="B276" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C276" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2711,7 +2779,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2780,6 +2848,9 @@
       <c r="B296" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C296" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B297" s="3" t="s">
@@ -2796,7 +2867,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2865,9 +2936,6 @@
       <c r="B307" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C307" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B308" s="3" t="s">
@@ -2875,19 +2943,19 @@
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A309" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B309" s="7" t="s">
+      <c r="B309" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C309" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A310" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B310" s="7" t="s">
         <v>3</v>
-      </c>
-      <c r="C309" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B310" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="C310" s="5" t="s">
         <v>13</v>
@@ -2895,7 +2963,7 @@
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B311" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C311" s="5" t="s">
         <v>13</v>
@@ -2903,7 +2971,7 @@
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B312" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C312" s="5" t="s">
         <v>13</v>
@@ -2911,7 +2979,7 @@
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B313" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C313" s="5" t="s">
         <v>13</v>
@@ -2919,7 +2987,7 @@
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B314" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C314" s="5" t="s">
         <v>13</v>
@@ -2927,7 +2995,7 @@
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B315" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C315" s="5" t="s">
         <v>13</v>
@@ -2935,7 +3003,7 @@
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B316" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C316" s="5" t="s">
         <v>13</v>
@@ -2943,7 +3011,7 @@
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B317" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C317" s="5" t="s">
         <v>13</v>
@@ -2951,88 +3019,176 @@
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B318" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C318" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B319" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A319" s="4">
+    <row r="320" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A320" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B320" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C320" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B321" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C321" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B322" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C322" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B323" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C323" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B324" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C324" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B325" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C325" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B326" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C326" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B327" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C327" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B328" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C328" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B329" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A330" s="4">
         <v>46042</v>
       </c>
-      <c r="B319" s="7" t="s">
+      <c r="B330" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C319" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B320" s="3" t="s">
+      <c r="C330" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B331" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C320" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="321" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B321" s="3" t="s">
+      <c r="C331" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B332" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C321" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="322" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B322" s="3" t="s">
+      <c r="C332" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B333" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C322" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="323" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B323" s="3" t="s">
+      <c r="C333" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B334" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C323" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="324" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B324" s="3" t="s">
+      <c r="C334" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B335" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C324" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="325" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B325" s="3" t="s">
+      <c r="C335" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B336" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C325" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="326" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B326" s="3" t="s">
+      <c r="C336" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="337" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B337" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C326" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="327" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B327" s="3" t="s">
+      <c r="C337" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="338" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B338" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="328" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B328" s="3" t="s">
+    <row r="339" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B339" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="329" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B329" s="3">
+    <row r="340" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B340" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\03aioveu-Day\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86F7A736-C480-4317-9379-2F131FE78F64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76D59EE1-C49D-482E-84A2-1550A5345249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -542,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C340"/>
+  <dimension ref="A1:C351"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -630,7 +630,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -699,9 +699,6 @@
       <c r="B21" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B22" s="3" t="s">
@@ -718,7 +715,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -806,7 +803,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -883,9 +880,6 @@
       <c r="B44" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C44" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B45" s="3" t="s">
@@ -897,7 +891,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -974,6 +968,9 @@
       <c r="B55" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C55" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B56" s="3" t="s">
@@ -985,7 +982,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -1073,7 +1070,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1161,7 +1158,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1249,7 +1246,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1337,7 +1334,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1406,6 +1403,9 @@
       <c r="B109" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C109" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B110" s="3" t="s">
@@ -1422,7 +1422,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1483,7 +1483,9 @@
       <c r="B119" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C119" s="6"/>
+      <c r="C119" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B120" s="3" t="s">
@@ -1499,10 +1501,13 @@
       <c r="B122" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C122" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1563,17 +1568,12 @@
       <c r="B130" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C130" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C130" s="6"/>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B131" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C131" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B132" s="3" t="s">
@@ -1584,13 +1584,10 @@
       <c r="B133" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C133" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1678,7 +1675,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1766,7 +1763,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1835,6 +1832,9 @@
       <c r="B164" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C164" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B165" s="3" t="s">
@@ -1851,7 +1851,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1936,7 +1936,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -2010,9 +2010,6 @@
       <c r="B187" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C187" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B188" s="3" t="s">
@@ -2024,7 +2021,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2085,7 +2082,9 @@
       <c r="B196" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C196" s="6"/>
+      <c r="C196" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B197" s="3" t="s">
@@ -2096,15 +2095,21 @@
       <c r="B198" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C198" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B199" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C199" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2165,9 +2170,7 @@
       <c r="B207" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C207" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C207" s="6"/>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B208" s="3" t="s">
@@ -2183,13 +2186,10 @@
       <c r="B210" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C210" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2258,9 +2258,6 @@
       <c r="B219" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C219" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B220" s="3" t="s">
@@ -2277,7 +2274,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2346,6 +2343,9 @@
       <c r="B230" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C230" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B231" s="3" t="s">
@@ -2362,7 +2362,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2441,10 +2441,13 @@
       <c r="B243" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C243" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2523,13 +2526,10 @@
       <c r="B254" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C254" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2598,9 +2598,6 @@
       <c r="B263" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C263" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B264" s="3" t="s">
@@ -2617,7 +2614,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2638,19 +2635,25 @@
       <c r="B268" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C268" s="6"/>
+      <c r="C268" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B269" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C269" s="6"/>
+      <c r="C269" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B270" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C270" s="6"/>
+      <c r="C270" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B271" s="3" t="s">
@@ -2672,12 +2675,17 @@
       <c r="B273" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C273" s="6"/>
+      <c r="C273" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B274" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C274" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B275" s="3" t="s">
@@ -2688,10 +2696,13 @@
       <c r="B276" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C276" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2712,25 +2723,19 @@
       <c r="B279" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C279" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C279" s="6"/>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B280" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C280" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C280" s="6"/>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B281" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C281" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C281" s="6"/>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B282" s="3" t="s">
@@ -2752,17 +2757,12 @@
       <c r="B284" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C284" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C284" s="6"/>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B285" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C285" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B286" s="3" t="s">
@@ -2773,13 +2773,10 @@
       <c r="B287" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C287" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2867,7 +2864,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2936,6 +2933,9 @@
       <c r="B307" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C307" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B308" s="3" t="s">
@@ -2952,7 +2952,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3021,9 +3021,6 @@
       <c r="B318" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C318" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B319" s="3" t="s">
@@ -3031,19 +3028,19 @@
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A320" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B320" s="7" t="s">
+      <c r="B320" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C320" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A321" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B321" s="7" t="s">
         <v>3</v>
-      </c>
-      <c r="C320" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B321" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="C321" s="5" t="s">
         <v>13</v>
@@ -3051,7 +3048,7 @@
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B322" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C322" s="5" t="s">
         <v>13</v>
@@ -3059,7 +3056,7 @@
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B323" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C323" s="5" t="s">
         <v>13</v>
@@ -3067,7 +3064,7 @@
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B324" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C324" s="5" t="s">
         <v>13</v>
@@ -3075,7 +3072,7 @@
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B325" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C325" s="5" t="s">
         <v>13</v>
@@ -3083,7 +3080,7 @@
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B326" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C326" s="5" t="s">
         <v>13</v>
@@ -3091,7 +3088,7 @@
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B327" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C327" s="5" t="s">
         <v>13</v>
@@ -3099,7 +3096,7 @@
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B328" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C328" s="5" t="s">
         <v>13</v>
@@ -3107,23 +3104,23 @@
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B329" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C329" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B330" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A330" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B330" s="7" t="s">
+    <row r="331" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A331" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B331" s="7" t="s">
         <v>3</v>
-      </c>
-      <c r="C330" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B331" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="C331" s="5" t="s">
         <v>13</v>
@@ -3131,7 +3128,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B332" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C332" s="5" t="s">
         <v>13</v>
@@ -3139,7 +3136,7 @@
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B333" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C333" s="5" t="s">
         <v>13</v>
@@ -3147,7 +3144,7 @@
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B334" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C334" s="5" t="s">
         <v>13</v>
@@ -3155,7 +3152,7 @@
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B335" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C335" s="5" t="s">
         <v>13</v>
@@ -3163,32 +3160,120 @@
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B336" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C336" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B337" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C336" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="337" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B337" s="3" t="s">
+      <c r="C337" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B338" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C337" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="338" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B338" s="3" t="s">
+      <c r="C338" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B339" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="339" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B339" s="3" t="s">
+      <c r="C339" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B340" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="340" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B340" s="3">
+    <row r="341" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A341" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B341" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C341" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B342" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C342" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B343" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C343" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B344" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C344" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B345" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C345" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B346" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C346" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B347" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C347" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B348" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C348" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B349" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B350" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B351" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\03aioveu-Day\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76D59EE1-C49D-482E-84A2-1550A5345249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6C1B7B4-607E-493E-944A-F39F5D3D9D51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -542,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C351"/>
+  <dimension ref="A1:C362"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -630,7 +630,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -715,7 +715,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -784,9 +784,6 @@
       <c r="B32" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C32" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B33" s="3" t="s">
@@ -803,7 +800,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -891,7 +888,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -968,9 +965,6 @@
       <c r="B55" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C55" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B56" s="3" t="s">
@@ -982,7 +976,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -1059,6 +1053,9 @@
       <c r="B66" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C66" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B67" s="3" t="s">
@@ -1070,7 +1067,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1158,7 +1155,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1246,7 +1243,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1334,7 +1331,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1422,7 +1419,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1491,6 +1488,9 @@
       <c r="B120" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C120" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B121" s="3" t="s">
@@ -1507,7 +1507,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1568,7 +1568,9 @@
       <c r="B130" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C130" s="6"/>
+      <c r="C130" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B131" s="3" t="s">
@@ -1584,10 +1586,13 @@
       <c r="B133" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C133" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1648,17 +1653,12 @@
       <c r="B141" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C141" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C141" s="6"/>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B142" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C142" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B143" s="3" t="s">
@@ -1669,13 +1669,10 @@
       <c r="B144" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C144" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1763,7 +1760,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1851,7 +1848,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1920,6 +1917,9 @@
       <c r="B175" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C175" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B176" s="3" t="s">
@@ -1936,7 +1936,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -2021,7 +2021,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2095,9 +2095,6 @@
       <c r="B198" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C198" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B199" s="3" t="s">
@@ -2109,7 +2106,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2170,7 +2167,9 @@
       <c r="B207" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C207" s="6"/>
+      <c r="C207" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B208" s="3" t="s">
@@ -2181,15 +2180,21 @@
       <c r="B209" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C209" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B210" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C210" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2250,9 +2255,7 @@
       <c r="B218" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C218" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C218" s="6"/>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B219" s="3" t="s">
@@ -2268,13 +2271,10 @@
       <c r="B221" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C221" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2343,9 +2343,6 @@
       <c r="B230" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C230" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B231" s="3" t="s">
@@ -2362,7 +2359,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2431,6 +2428,9 @@
       <c r="B241" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C241" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B242" s="3" t="s">
@@ -2447,7 +2447,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2526,10 +2526,13 @@
       <c r="B254" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C254" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2608,13 +2611,10 @@
       <c r="B265" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C265" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2683,9 +2683,6 @@
       <c r="B274" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C274" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B275" s="3" t="s">
@@ -2702,7 +2699,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2723,19 +2720,25 @@
       <c r="B279" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C279" s="6"/>
+      <c r="C279" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B280" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C280" s="6"/>
+      <c r="C280" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B281" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C281" s="6"/>
+      <c r="C281" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B282" s="3" t="s">
@@ -2757,12 +2760,17 @@
       <c r="B284" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C284" s="6"/>
+      <c r="C284" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B285" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C285" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B286" s="3" t="s">
@@ -2773,10 +2781,13 @@
       <c r="B287" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C287" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2797,25 +2808,19 @@
       <c r="B290" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C290" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C290" s="6"/>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B291" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C291" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C291" s="6"/>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B292" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C292" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C292" s="6"/>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B293" s="3" t="s">
@@ -2837,17 +2842,12 @@
       <c r="B295" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C295" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C295" s="6"/>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B296" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C296" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B297" s="3" t="s">
@@ -2858,13 +2858,10 @@
       <c r="B298" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C298" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2952,7 +2949,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3021,6 +3018,9 @@
       <c r="B318" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C318" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B319" s="3" t="s">
@@ -3037,7 +3037,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3106,9 +3106,6 @@
       <c r="B329" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C329" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B330" s="3" t="s">
@@ -3116,19 +3113,19 @@
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A331" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B331" s="7" t="s">
+      <c r="B331" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C331" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A332" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B332" s="7" t="s">
         <v>3</v>
-      </c>
-      <c r="C331" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B332" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="C332" s="5" t="s">
         <v>13</v>
@@ -3136,7 +3133,7 @@
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B333" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C333" s="5" t="s">
         <v>13</v>
@@ -3144,7 +3141,7 @@
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B334" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C334" s="5" t="s">
         <v>13</v>
@@ -3152,7 +3149,7 @@
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B335" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C335" s="5" t="s">
         <v>13</v>
@@ -3160,7 +3157,7 @@
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B336" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C336" s="5" t="s">
         <v>13</v>
@@ -3168,7 +3165,7 @@
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B337" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C337" s="5" t="s">
         <v>13</v>
@@ -3176,7 +3173,7 @@
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B338" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C338" s="5" t="s">
         <v>13</v>
@@ -3184,7 +3181,7 @@
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B339" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C339" s="5" t="s">
         <v>13</v>
@@ -3192,23 +3189,23 @@
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B340" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C340" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B341" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A341" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B341" s="7" t="s">
+    <row r="342" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A342" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B342" s="7" t="s">
         <v>3</v>
-      </c>
-      <c r="C341" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B342" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="C342" s="5" t="s">
         <v>13</v>
@@ -3216,7 +3213,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B343" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C343" s="5" t="s">
         <v>13</v>
@@ -3224,7 +3221,7 @@
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B344" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C344" s="5" t="s">
         <v>13</v>
@@ -3232,7 +3229,7 @@
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B345" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C345" s="5" t="s">
         <v>13</v>
@@ -3240,7 +3237,7 @@
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B346" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C346" s="5" t="s">
         <v>13</v>
@@ -3248,7 +3245,7 @@
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B347" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C347" s="5" t="s">
         <v>13</v>
@@ -3256,7 +3253,7 @@
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B348" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C348" s="5" t="s">
         <v>13</v>
@@ -3264,16 +3261,104 @@
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B349" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C349" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B350" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C350" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B351" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B351" s="3">
+    <row r="352" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A352" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B352" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C352" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="353" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B353" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C353" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="354" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B354" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C354" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="355" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B355" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C355" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="356" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B356" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C356" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="357" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B357" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C357" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="358" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B358" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C358" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="359" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B359" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C359" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="360" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B360" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="361" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B361" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="362" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B362" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\03aioveu-Day\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6C1B7B4-607E-493E-944A-F39F5D3D9D51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D7F6F18-6F5F-4FE6-99BF-2E052B097E24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -542,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C362"/>
+  <dimension ref="A1:C373"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -630,7 +630,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -715,7 +715,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -800,7 +800,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -869,9 +869,6 @@
       <c r="B43" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C43" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B44" s="3" t="s">
@@ -888,7 +885,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -976,7 +973,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -1053,9 +1050,6 @@
       <c r="B66" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C66" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B67" s="3" t="s">
@@ -1067,7 +1061,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1144,6 +1138,9 @@
       <c r="B77" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C77" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B78" s="3" t="s">
@@ -1155,7 +1152,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1243,7 +1240,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1331,7 +1328,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1419,7 +1416,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1507,7 +1504,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1576,6 +1573,9 @@
       <c r="B131" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C131" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B132" s="3" t="s">
@@ -1592,7 +1592,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1653,7 +1653,9 @@
       <c r="B141" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C141" s="6"/>
+      <c r="C141" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B142" s="3" t="s">
@@ -1669,10 +1671,13 @@
       <c r="B144" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C144" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1733,17 +1738,12 @@
       <c r="B152" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C152" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C152" s="6"/>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B153" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C153" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B154" s="3" t="s">
@@ -1754,13 +1754,10 @@
       <c r="B155" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C155" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1848,7 +1845,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1936,7 +1933,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -2005,6 +2002,9 @@
       <c r="B186" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C186" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B187" s="3" t="s">
@@ -2021,7 +2021,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2106,7 +2106,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2180,9 +2180,6 @@
       <c r="B209" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C209" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B210" s="3" t="s">
@@ -2194,7 +2191,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2255,7 +2252,9 @@
       <c r="B218" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C218" s="6"/>
+      <c r="C218" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B219" s="3" t="s">
@@ -2266,15 +2265,21 @@
       <c r="B220" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C220" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B221" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C221" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2335,9 +2340,7 @@
       <c r="B229" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C229" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C229" s="6"/>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B230" s="3" t="s">
@@ -2353,13 +2356,10 @@
       <c r="B232" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C232" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2428,9 +2428,6 @@
       <c r="B241" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C241" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B242" s="3" t="s">
@@ -2447,7 +2444,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2516,6 +2513,9 @@
       <c r="B252" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C252" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B253" s="3" t="s">
@@ -2532,7 +2532,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2611,10 +2611,13 @@
       <c r="B265" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C265" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2693,13 +2696,10 @@
       <c r="B276" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C276" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2768,9 +2768,6 @@
       <c r="B285" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C285" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B286" s="3" t="s">
@@ -2787,7 +2784,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2808,19 +2805,25 @@
       <c r="B290" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C290" s="6"/>
+      <c r="C290" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B291" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C291" s="6"/>
+      <c r="C291" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B292" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C292" s="6"/>
+      <c r="C292" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B293" s="3" t="s">
@@ -2842,12 +2845,17 @@
       <c r="B295" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C295" s="6"/>
+      <c r="C295" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B296" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C296" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B297" s="3" t="s">
@@ -2858,10 +2866,13 @@
       <c r="B298" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C298" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2882,25 +2893,19 @@
       <c r="B301" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C301" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C301" s="6"/>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B302" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C302" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C302" s="6"/>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B303" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C303" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C303" s="6"/>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B304" s="3" t="s">
@@ -2922,17 +2927,12 @@
       <c r="B306" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C306" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C306" s="6"/>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B307" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C307" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B308" s="3" t="s">
@@ -2943,13 +2943,10 @@
       <c r="B309" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C309" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3037,7 +3034,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3106,6 +3103,9 @@
       <c r="B329" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C329" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B330" s="3" t="s">
@@ -3122,7 +3122,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3191,9 +3191,6 @@
       <c r="B340" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C340" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B341" s="3" t="s">
@@ -3201,19 +3198,19 @@
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A342" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B342" s="7" t="s">
+      <c r="B342" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C342" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A343" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B343" s="7" t="s">
         <v>3</v>
-      </c>
-      <c r="C342" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B343" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="C343" s="5" t="s">
         <v>13</v>
@@ -3221,7 +3218,7 @@
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B344" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C344" s="5" t="s">
         <v>13</v>
@@ -3229,7 +3226,7 @@
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B345" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C345" s="5" t="s">
         <v>13</v>
@@ -3237,7 +3234,7 @@
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B346" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C346" s="5" t="s">
         <v>13</v>
@@ -3245,7 +3242,7 @@
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B347" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C347" s="5" t="s">
         <v>13</v>
@@ -3253,7 +3250,7 @@
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B348" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C348" s="5" t="s">
         <v>13</v>
@@ -3261,7 +3258,7 @@
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B349" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C349" s="5" t="s">
         <v>13</v>
@@ -3269,7 +3266,7 @@
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B350" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C350" s="5" t="s">
         <v>13</v>
@@ -3277,88 +3274,176 @@
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B351" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C351" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B352" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="352" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A352" s="4">
+    <row r="353" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A353" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B353" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C353" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B354" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C354" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B355" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C355" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B356" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C356" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B357" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C357" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B358" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C358" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B359" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C359" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B360" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C360" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B361" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C361" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="362" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B362" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A363" s="4">
         <v>46042</v>
       </c>
-      <c r="B352" s="7" t="s">
+      <c r="B363" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C352" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="353" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B353" s="3" t="s">
+      <c r="C363" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B364" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C353" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="354" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B354" s="3" t="s">
+      <c r="C364" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B365" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C354" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="355" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B355" s="3" t="s">
+      <c r="C365" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="366" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B366" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C355" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="356" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B356" s="3" t="s">
+      <c r="C366" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B367" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C356" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="357" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B357" s="3" t="s">
+      <c r="C367" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="368" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B368" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C357" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="358" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B358" s="3" t="s">
+      <c r="C368" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="369" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B369" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C358" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="359" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B359" s="3" t="s">
+      <c r="C369" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="370" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B370" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C359" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="360" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B360" s="3" t="s">
+      <c r="C370" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="371" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B371" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="361" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B361" s="3" t="s">
+    <row r="372" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B372" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="362" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B362" s="3">
+    <row r="373" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B373" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\03aioveu-Day\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D7F6F18-6F5F-4FE6-99BF-2E052B097E24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1756CBCD-D63A-4FE6-B560-8A886CC26557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -200,74 +200,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -287,7 +219,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="CCE8CF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -542,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C373"/>
+  <dimension ref="A1:C384"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -564,7 +496,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
-        <v>46054</v>
+        <v>46120</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>3</v>
@@ -630,7 +562,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -715,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -800,7 +732,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -885,7 +817,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -954,9 +886,6 @@
       <c r="B54" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C54" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B55" s="3" t="s">
@@ -973,7 +902,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -1061,7 +990,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1138,9 +1067,6 @@
       <c r="B77" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C77" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B78" s="3" t="s">
@@ -1152,7 +1078,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1229,6 +1155,9 @@
       <c r="B88" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C88" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B89" s="3" t="s">
@@ -1240,7 +1169,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1328,7 +1257,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1416,7 +1345,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1504,7 +1433,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1592,7 +1521,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1661,6 +1590,9 @@
       <c r="B142" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C142" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B143" s="3" t="s">
@@ -1677,7 +1609,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1738,7 +1670,9 @@
       <c r="B152" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C152" s="6"/>
+      <c r="C152" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B153" s="3" t="s">
@@ -1754,10 +1688,13 @@
       <c r="B155" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C155" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1818,16 +1755,11 @@
       <c r="B163" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C163" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C163" s="6"/>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B164" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C164" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.2">
@@ -1839,13 +1771,10 @@
       <c r="B166" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C166" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1933,7 +1862,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -2021,7 +1950,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2090,6 +2019,9 @@
       <c r="B197" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C197" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B198" s="3" t="s">
@@ -2106,7 +2038,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2191,7 +2123,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2265,9 +2197,6 @@
       <c r="B220" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C220" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B221" s="3" t="s">
@@ -2279,7 +2208,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2340,7 +2269,9 @@
       <c r="B229" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C229" s="6"/>
+      <c r="C229" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B230" s="3" t="s">
@@ -2351,15 +2282,21 @@
       <c r="B231" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C231" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B232" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C232" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2420,9 +2357,7 @@
       <c r="B240" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C240" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C240" s="6"/>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B241" s="3" t="s">
@@ -2438,13 +2373,10 @@
       <c r="B243" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C243" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2513,9 +2445,6 @@
       <c r="B252" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C252" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B253" s="3" t="s">
@@ -2532,7 +2461,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2601,6 +2530,9 @@
       <c r="B263" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C263" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B264" s="3" t="s">
@@ -2617,7 +2549,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2696,10 +2628,13 @@
       <c r="B276" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C276" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2778,13 +2713,10 @@
       <c r="B287" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C287" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2853,9 +2785,6 @@
       <c r="B296" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C296" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B297" s="3" t="s">
@@ -2872,7 +2801,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2893,19 +2822,25 @@
       <c r="B301" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C301" s="6"/>
+      <c r="C301" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B302" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C302" s="6"/>
+      <c r="C302" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B303" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C303" s="6"/>
+      <c r="C303" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B304" s="3" t="s">
@@ -2927,11 +2862,16 @@
       <c r="B306" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C306" s="6"/>
+      <c r="C306" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B307" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C307" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.2">
@@ -2943,10 +2883,13 @@
       <c r="B309" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C309" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -2967,25 +2910,19 @@
       <c r="B312" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C312" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C312" s="6"/>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B313" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C313" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C313" s="6"/>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B314" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C314" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C314" s="6"/>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B315" s="3" t="s">
@@ -3007,16 +2944,11 @@
       <c r="B317" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C317" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C317" s="6"/>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B318" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C318" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.2">
@@ -3028,13 +2960,10 @@
       <c r="B320" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C320" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3122,7 +3051,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3191,6 +3120,9 @@
       <c r="B340" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C340" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B341" s="3" t="s">
@@ -3207,7 +3139,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3276,9 +3208,6 @@
       <c r="B351" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C351" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B352" s="3" t="s">
@@ -3286,19 +3215,19 @@
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A353" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B353" s="7" t="s">
+      <c r="B353" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C353" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A354" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B354" s="7" t="s">
         <v>3</v>
-      </c>
-      <c r="C353" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="354" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B354" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="C354" s="5" t="s">
         <v>13</v>
@@ -3306,7 +3235,7 @@
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B355" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C355" s="5" t="s">
         <v>13</v>
@@ -3314,7 +3243,7 @@
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B356" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C356" s="5" t="s">
         <v>13</v>
@@ -3322,7 +3251,7 @@
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B357" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C357" s="5" t="s">
         <v>13</v>
@@ -3330,7 +3259,7 @@
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B358" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C358" s="5" t="s">
         <v>13</v>
@@ -3338,7 +3267,7 @@
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B359" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C359" s="5" t="s">
         <v>13</v>
@@ -3346,7 +3275,7 @@
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B360" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C360" s="5" t="s">
         <v>13</v>
@@ -3354,7 +3283,7 @@
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B361" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C361" s="5" t="s">
         <v>13</v>
@@ -3362,23 +3291,23 @@
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B362" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C362" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B363" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="363" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A363" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B363" s="7" t="s">
+    <row r="364" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A364" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B364" s="7" t="s">
         <v>3</v>
-      </c>
-      <c r="C363" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="364" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B364" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="C364" s="5" t="s">
         <v>13</v>
@@ -3386,7 +3315,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B365" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C365" s="5" t="s">
         <v>13</v>
@@ -3394,7 +3323,7 @@
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B366" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C366" s="5" t="s">
         <v>13</v>
@@ -3402,7 +3331,7 @@
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B367" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C367" s="5" t="s">
         <v>13</v>
@@ -3410,40 +3339,128 @@
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B368" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C368" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B369" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C368" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="369" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B369" s="3" t="s">
+      <c r="C369" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B370" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C369" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="370" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B370" s="3" t="s">
+      <c r="C370" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B371" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C370" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="371" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B371" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="372" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C371" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B372" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C372" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B373" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="373" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B373" s="3">
+    <row r="374" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A374" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B374" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C374" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B375" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C375" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B376" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C376" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B377" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C377" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B378" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C378" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B379" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C379" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="380" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B380" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C380" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="381" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B381" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C381" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B382" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="383" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B383" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B384" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\03aioveu-Day\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1756CBCD-D63A-4FE6-B560-8A886CC26557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11BAA13D-2F14-468F-83A0-34B9D7A36EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -474,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C384"/>
+  <dimension ref="A1:C395"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -562,7 +562,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -631,6 +631,9 @@
       <c r="B21" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C21" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B22" s="3" t="s">
@@ -647,7 +650,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -732,7 +735,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -817,7 +820,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -902,7 +905,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -971,9 +974,6 @@
       <c r="B65" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C65" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B66" s="3" t="s">
@@ -990,7 +990,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1078,7 +1078,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1155,9 +1155,6 @@
       <c r="B88" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C88" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B89" s="3" t="s">
@@ -1169,7 +1166,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1246,6 +1243,9 @@
       <c r="B99" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C99" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B100" s="3" t="s">
@@ -1257,7 +1257,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1345,7 +1345,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1433,7 +1433,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1521,7 +1521,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1609,7 +1609,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1678,6 +1678,9 @@
       <c r="B153" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C153" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B154" s="3" t="s">
@@ -1694,7 +1697,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1755,7 +1758,9 @@
       <c r="B163" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C163" s="6"/>
+      <c r="C163" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B164" s="3" t="s">
@@ -1771,10 +1776,13 @@
       <c r="B166" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C166" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1835,16 +1843,11 @@
       <c r="B174" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C174" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C174" s="6"/>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B175" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C175" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.2">
@@ -1856,13 +1859,10 @@
       <c r="B177" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C177" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1950,7 +1950,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2038,7 +2038,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2107,6 +2107,9 @@
       <c r="B208" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C208" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B209" s="3" t="s">
@@ -2123,7 +2126,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2208,7 +2211,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2282,9 +2285,6 @@
       <c r="B231" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C231" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B232" s="3" t="s">
@@ -2296,7 +2296,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2357,7 +2357,9 @@
       <c r="B240" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C240" s="6"/>
+      <c r="C240" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B241" s="3" t="s">
@@ -2368,15 +2370,21 @@
       <c r="B242" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C242" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B243" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C243" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2437,9 +2445,7 @@
       <c r="B251" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C251" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C251" s="6"/>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B252" s="3" t="s">
@@ -2455,13 +2461,10 @@
       <c r="B254" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C254" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2530,9 +2533,6 @@
       <c r="B263" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C263" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B264" s="3" t="s">
@@ -2549,7 +2549,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2618,6 +2618,9 @@
       <c r="B274" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C274" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B275" s="3" t="s">
@@ -2634,7 +2637,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2713,10 +2716,13 @@
       <c r="B287" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C287" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2795,13 +2801,10 @@
       <c r="B298" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C298" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2870,9 +2873,6 @@
       <c r="B307" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C307" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B308" s="3" t="s">
@@ -2889,7 +2889,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -2910,19 +2910,25 @@
       <c r="B312" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C312" s="6"/>
+      <c r="C312" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B313" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C313" s="6"/>
+      <c r="C313" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B314" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C314" s="6"/>
+      <c r="C314" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B315" s="3" t="s">
@@ -2944,11 +2950,16 @@
       <c r="B317" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C317" s="6"/>
+      <c r="C317" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B318" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C318" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.2">
@@ -2960,10 +2971,13 @@
       <c r="B320" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C320" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -2984,25 +2998,19 @@
       <c r="B323" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C323" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C323" s="6"/>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B324" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C324" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C324" s="6"/>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B325" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C325" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C325" s="6"/>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B326" s="3" t="s">
@@ -3024,16 +3032,11 @@
       <c r="B328" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C328" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C328" s="6"/>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B329" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C329" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.2">
@@ -3045,13 +3048,10 @@
       <c r="B331" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C331" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3139,7 +3139,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3208,6 +3208,9 @@
       <c r="B351" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C351" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B352" s="3" t="s">
@@ -3224,7 +3227,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3293,9 +3296,6 @@
       <c r="B362" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C362" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B363" s="3" t="s">
@@ -3303,19 +3303,19 @@
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A364" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B364" s="7" t="s">
+      <c r="B364" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C364" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A365" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B365" s="7" t="s">
         <v>3</v>
-      </c>
-      <c r="C364" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="365" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B365" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="C365" s="5" t="s">
         <v>13</v>
@@ -3323,7 +3323,7 @@
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B366" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C366" s="5" t="s">
         <v>13</v>
@@ -3331,7 +3331,7 @@
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B367" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C367" s="5" t="s">
         <v>13</v>
@@ -3339,7 +3339,7 @@
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B368" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C368" s="5" t="s">
         <v>13</v>
@@ -3347,7 +3347,7 @@
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B369" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C369" s="5" t="s">
         <v>13</v>
@@ -3355,7 +3355,7 @@
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B370" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C370" s="5" t="s">
         <v>13</v>
@@ -3363,7 +3363,7 @@
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B371" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C371" s="5" t="s">
         <v>13</v>
@@ -3371,7 +3371,7 @@
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B372" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C372" s="5" t="s">
         <v>13</v>
@@ -3379,23 +3379,23 @@
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B373" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C373" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="374" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B374" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="374" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A374" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B374" s="7" t="s">
+    <row r="375" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A375" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B375" s="7" t="s">
         <v>3</v>
-      </c>
-      <c r="C374" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="375" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B375" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="C375" s="5" t="s">
         <v>13</v>
@@ -3403,7 +3403,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B376" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C376" s="5" t="s">
         <v>13</v>
@@ -3411,7 +3411,7 @@
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B377" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C377" s="5" t="s">
         <v>13</v>
@@ -3419,7 +3419,7 @@
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B378" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C378" s="5" t="s">
         <v>13</v>
@@ -3427,7 +3427,7 @@
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B379" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C379" s="5" t="s">
         <v>13</v>
@@ -3435,7 +3435,7 @@
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B380" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C380" s="5" t="s">
         <v>13</v>
@@ -3443,7 +3443,7 @@
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B381" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C381" s="5" t="s">
         <v>13</v>
@@ -3451,16 +3451,104 @@
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B382" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C382" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B383" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C383" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B384" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="384" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B384" s="3">
+    <row r="385" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A385" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B385" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C385" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="386" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B386" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C386" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="387" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B387" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C387" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="388" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B388" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C388" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B389" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C389" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B390" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C390" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="391" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B391" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C391" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B392" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C392" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="393" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B393" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="394" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B394" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="395" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B395" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\03aioveu-Day\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11BAA13D-2F14-468F-83A0-34B9D7A36EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1A0E4F4-3E6C-409A-A506-33CA2394EE1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -200,6 +200,74 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -219,7 +287,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window" lastClr="CCE8CF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -474,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C395"/>
+  <dimension ref="A1:C406"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -562,7 +630,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -650,7 +718,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -719,6 +787,9 @@
       <c r="B32" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C32" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B33" s="3" t="s">
@@ -735,7 +806,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -820,7 +891,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -905,7 +976,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -990,7 +1061,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1059,9 +1130,6 @@
       <c r="B76" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C76" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B77" s="3" t="s">
@@ -1078,7 +1146,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1166,7 +1234,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1243,9 +1311,6 @@
       <c r="B99" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C99" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B100" s="3" t="s">
@@ -1257,7 +1322,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1334,6 +1399,9 @@
       <c r="B110" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C110" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B111" s="3" t="s">
@@ -1345,7 +1413,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1433,7 +1501,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1521,7 +1589,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1609,7 +1677,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1697,7 +1765,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1766,6 +1834,9 @@
       <c r="B164" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C164" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B165" s="3" t="s">
@@ -1782,7 +1853,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1843,7 +1914,9 @@
       <c r="B174" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C174" s="6"/>
+      <c r="C174" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B175" s="3" t="s">
@@ -1859,10 +1932,13 @@
       <c r="B177" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C177" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1923,17 +1999,12 @@
       <c r="B185" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C185" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C185" s="6"/>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B186" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C186" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B187" s="3" t="s">
@@ -1944,13 +2015,10 @@
       <c r="B188" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C188" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2038,7 +2106,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2126,7 +2194,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2195,6 +2263,9 @@
       <c r="B219" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C219" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B220" s="3" t="s">
@@ -2211,7 +2282,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2296,7 +2367,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2370,9 +2441,6 @@
       <c r="B242" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C242" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B243" s="3" t="s">
@@ -2384,7 +2452,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2445,7 +2513,9 @@
       <c r="B251" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C251" s="6"/>
+      <c r="C251" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B252" s="3" t="s">
@@ -2456,15 +2526,21 @@
       <c r="B253" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C253" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B254" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C254" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2525,9 +2601,7 @@
       <c r="B262" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C262" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C262" s="6"/>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B263" s="3" t="s">
@@ -2543,13 +2617,10 @@
       <c r="B265" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C265" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2618,9 +2689,6 @@
       <c r="B274" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C274" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B275" s="3" t="s">
@@ -2637,7 +2705,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2706,6 +2774,9 @@
       <c r="B285" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C285" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B286" s="3" t="s">
@@ -2722,7 +2793,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2801,10 +2872,13 @@
       <c r="B298" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C298" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2883,13 +2957,10 @@
       <c r="B309" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C309" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -2958,9 +3029,6 @@
       <c r="B318" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C318" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B319" s="3" t="s">
@@ -2977,7 +3045,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -2998,19 +3066,25 @@
       <c r="B323" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C323" s="6"/>
+      <c r="C323" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B324" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C324" s="6"/>
+      <c r="C324" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B325" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C325" s="6"/>
+      <c r="C325" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B326" s="3" t="s">
@@ -3032,12 +3106,17 @@
       <c r="B328" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C328" s="6"/>
+      <c r="C328" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B329" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C329" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B330" s="3" t="s">
@@ -3048,10 +3127,13 @@
       <c r="B331" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C331" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3072,25 +3154,19 @@
       <c r="B334" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C334" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C334" s="6"/>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B335" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C335" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C335" s="6"/>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B336" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C336" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C336" s="6"/>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B337" s="3" t="s">
@@ -3112,17 +3188,12 @@
       <c r="B339" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C339" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C339" s="6"/>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B340" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C340" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B341" s="3" t="s">
@@ -3133,13 +3204,10 @@
       <c r="B342" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C342" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3227,7 +3295,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3296,6 +3364,9 @@
       <c r="B362" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C362" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B363" s="3" t="s">
@@ -3312,7 +3383,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3381,9 +3452,6 @@
       <c r="B373" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C373" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B374" s="3" t="s">
@@ -3391,19 +3459,19 @@
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A375" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B375" s="7" t="s">
+      <c r="B375" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C375" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A376" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B376" s="7" t="s">
         <v>3</v>
-      </c>
-      <c r="C375" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="376" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B376" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="C376" s="5" t="s">
         <v>13</v>
@@ -3411,7 +3479,7 @@
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B377" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C377" s="5" t="s">
         <v>13</v>
@@ -3419,7 +3487,7 @@
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B378" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C378" s="5" t="s">
         <v>13</v>
@@ -3427,7 +3495,7 @@
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B379" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C379" s="5" t="s">
         <v>13</v>
@@ -3435,7 +3503,7 @@
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B380" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C380" s="5" t="s">
         <v>13</v>
@@ -3443,7 +3511,7 @@
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B381" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C381" s="5" t="s">
         <v>13</v>
@@ -3451,7 +3519,7 @@
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B382" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C382" s="5" t="s">
         <v>13</v>
@@ -3459,7 +3527,7 @@
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B383" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C383" s="5" t="s">
         <v>13</v>
@@ -3467,23 +3535,23 @@
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B384" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C384" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="385" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B385" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="385" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A385" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B385" s="7" t="s">
+    <row r="386" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A386" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B386" s="7" t="s">
         <v>3</v>
-      </c>
-      <c r="C385" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="386" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B386" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="C386" s="5" t="s">
         <v>13</v>
@@ -3491,7 +3559,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B387" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C387" s="5" t="s">
         <v>13</v>
@@ -3499,7 +3567,7 @@
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B388" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C388" s="5" t="s">
         <v>13</v>
@@ -3507,7 +3575,7 @@
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B389" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C389" s="5" t="s">
         <v>13</v>
@@ -3515,7 +3583,7 @@
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B390" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C390" s="5" t="s">
         <v>13</v>
@@ -3523,7 +3591,7 @@
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B391" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C391" s="5" t="s">
         <v>13</v>
@@ -3531,7 +3599,7 @@
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B392" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C392" s="5" t="s">
         <v>13</v>
@@ -3539,16 +3607,104 @@
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B393" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C393" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B394" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C394" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="395" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B395" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="395" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B395" s="3">
+    <row r="396" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A396" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B396" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C396" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="397" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B397" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C397" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="398" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B398" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C398" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="399" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B399" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C399" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="400" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B400" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C400" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="401" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B401" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C401" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="402" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B402" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C402" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="403" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B403" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C403" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="404" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B404" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="405" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B405" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="406" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B406" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\03aioveu-Day\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1A0E4F4-3E6C-409A-A506-33CA2394EE1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F05FC4C-02CF-46FC-8E6A-8625F8210D6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -200,74 +200,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -287,7 +219,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="CCE8CF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -542,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C406"/>
+  <dimension ref="A1:C417"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -630,7 +562,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -699,9 +631,6 @@
       <c r="B21" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B22" s="3" t="s">
@@ -718,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -806,7 +735,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -875,6 +804,9 @@
       <c r="B43" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C43" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B44" s="3" t="s">
@@ -891,7 +823,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -976,7 +908,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -1061,7 +993,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1146,7 +1078,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1215,9 +1147,6 @@
       <c r="B87" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C87" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B88" s="3" t="s">
@@ -1234,7 +1163,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1322,7 +1251,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1399,9 +1328,6 @@
       <c r="B110" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C110" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B111" s="3" t="s">
@@ -1413,7 +1339,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1490,6 +1416,9 @@
       <c r="B121" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C121" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B122" s="3" t="s">
@@ -1501,7 +1430,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1589,7 +1518,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1677,7 +1606,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1765,7 +1694,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1853,7 +1782,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1922,6 +1851,9 @@
       <c r="B175" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C175" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B176" s="3" t="s">
@@ -1938,7 +1870,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1999,7 +1931,9 @@
       <c r="B185" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C185" s="6"/>
+      <c r="C185" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B186" s="3" t="s">
@@ -2015,10 +1949,13 @@
       <c r="B188" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C188" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2079,16 +2016,11 @@
       <c r="B196" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C196" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C196" s="6"/>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B197" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C197" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.2">
@@ -2100,13 +2032,10 @@
       <c r="B199" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C199" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2194,7 +2123,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2282,7 +2211,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2351,6 +2280,9 @@
       <c r="B230" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C230" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B231" s="3" t="s">
@@ -2367,7 +2299,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2452,7 +2384,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2526,9 +2458,6 @@
       <c r="B253" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C253" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B254" s="3" t="s">
@@ -2540,7 +2469,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2601,7 +2530,9 @@
       <c r="B262" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C262" s="6"/>
+      <c r="C262" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B263" s="3" t="s">
@@ -2612,15 +2543,21 @@
       <c r="B264" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C264" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B265" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C265" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2681,9 +2618,7 @@
       <c r="B273" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C273" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C273" s="6"/>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B274" s="3" t="s">
@@ -2699,13 +2634,10 @@
       <c r="B276" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C276" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2774,9 +2706,6 @@
       <c r="B285" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C285" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B286" s="3" t="s">
@@ -2793,7 +2722,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2862,6 +2791,9 @@
       <c r="B296" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C296" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B297" s="3" t="s">
@@ -2878,7 +2810,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2957,10 +2889,13 @@
       <c r="B309" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C309" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3039,13 +2974,10 @@
       <c r="B320" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C320" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3114,9 +3046,6 @@
       <c r="B329" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C329" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B330" s="3" t="s">
@@ -3133,7 +3062,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3154,19 +3083,25 @@
       <c r="B334" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C334" s="6"/>
+      <c r="C334" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B335" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C335" s="6"/>
+      <c r="C335" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B336" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C336" s="6"/>
+      <c r="C336" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B337" s="3" t="s">
@@ -3188,11 +3123,16 @@
       <c r="B339" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C339" s="6"/>
+      <c r="C339" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B340" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C340" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.2">
@@ -3204,10 +3144,13 @@
       <c r="B342" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C342" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3228,25 +3171,19 @@
       <c r="B345" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C345" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C345" s="6"/>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B346" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C346" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C346" s="6"/>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B347" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C347" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C347" s="6"/>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B348" s="3" t="s">
@@ -3268,16 +3205,11 @@
       <c r="B350" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C350" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C350" s="6"/>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B351" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C351" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.2">
@@ -3289,13 +3221,10 @@
       <c r="B353" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C353" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3383,7 +3312,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3452,6 +3381,9 @@
       <c r="B373" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C373" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B374" s="3" t="s">
@@ -3468,7 +3400,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3537,9 +3469,6 @@
       <c r="B384" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C384" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B385" s="3" t="s">
@@ -3547,19 +3476,19 @@
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A386" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B386" s="7" t="s">
+      <c r="B386" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C386" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="387" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A387" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B387" s="7" t="s">
         <v>3</v>
-      </c>
-      <c r="C386" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="387" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B387" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="C387" s="5" t="s">
         <v>13</v>
@@ -3567,7 +3496,7 @@
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B388" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C388" s="5" t="s">
         <v>13</v>
@@ -3575,7 +3504,7 @@
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B389" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C389" s="5" t="s">
         <v>13</v>
@@ -3583,7 +3512,7 @@
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B390" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C390" s="5" t="s">
         <v>13</v>
@@ -3591,7 +3520,7 @@
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B391" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C391" s="5" t="s">
         <v>13</v>
@@ -3599,7 +3528,7 @@
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B392" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C392" s="5" t="s">
         <v>13</v>
@@ -3607,7 +3536,7 @@
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B393" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C393" s="5" t="s">
         <v>13</v>
@@ -3615,7 +3544,7 @@
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B394" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C394" s="5" t="s">
         <v>13</v>
@@ -3623,23 +3552,23 @@
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B395" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C395" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="396" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B396" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="396" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A396" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B396" s="7" t="s">
+    <row r="397" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A397" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B397" s="7" t="s">
         <v>3</v>
-      </c>
-      <c r="C396" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="397" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B397" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="C397" s="5" t="s">
         <v>13</v>
@@ -3647,7 +3576,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B398" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C398" s="5" t="s">
         <v>13</v>
@@ -3655,7 +3584,7 @@
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B399" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C399" s="5" t="s">
         <v>13</v>
@@ -3663,48 +3592,136 @@
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B400" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C400" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="401" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B401" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C400" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="401" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B401" s="3" t="s">
+      <c r="C401" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="402" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B402" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C401" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="402" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B402" s="3" t="s">
+      <c r="C402" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="403" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B403" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C402" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="403" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B403" s="3" t="s">
+      <c r="C403" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="404" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B404" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C403" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="404" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B404" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="405" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C404" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="405" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B405" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C405" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="406" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B406" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="406" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B406" s="3">
+    <row r="407" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A407" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B407" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C407" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="408" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B408" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C408" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="409" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B409" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C409" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="410" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B410" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C410" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="411" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B411" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C411" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="412" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B412" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C412" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="413" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B413" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C413" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="414" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B414" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C414" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="415" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B415" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="416" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B416" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="417" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B417" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\03aioveu-Day\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F05FC4C-02CF-46FC-8E6A-8625F8210D6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50B9CD21-0D27-496D-A208-6EB6458B6E2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -474,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C417"/>
+  <dimension ref="A1:C428"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -562,7 +562,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -716,9 +716,6 @@
       <c r="B32" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C32" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B33" s="3" t="s">
@@ -735,7 +732,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -823,7 +820,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -892,6 +889,9 @@
       <c r="B54" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C54" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B55" s="3" t="s">
@@ -908,7 +908,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1078,7 +1078,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1163,7 +1163,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1232,9 +1232,6 @@
       <c r="B98" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C98" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B99" s="3" t="s">
@@ -1251,7 +1248,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1339,7 +1336,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1416,9 +1413,6 @@
       <c r="B121" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C121" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B122" s="3" t="s">
@@ -1430,7 +1424,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1507,6 +1501,9 @@
       <c r="B132" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C132" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B133" s="3" t="s">
@@ -1518,7 +1515,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1606,7 +1603,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1694,7 +1691,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1782,7 +1779,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1870,7 +1867,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1939,6 +1936,9 @@
       <c r="B186" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C186" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B187" s="3" t="s">
@@ -1955,7 +1955,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2016,7 +2016,9 @@
       <c r="B196" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C196" s="6"/>
+      <c r="C196" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B197" s="3" t="s">
@@ -2032,10 +2034,13 @@
       <c r="B199" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C199" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2096,16 +2101,11 @@
       <c r="B207" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C207" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C207" s="6"/>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B208" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C208" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.2">
@@ -2117,13 +2117,10 @@
       <c r="B210" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C210" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2211,7 +2208,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2299,7 +2296,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2368,6 +2365,9 @@
       <c r="B241" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C241" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B242" s="3" t="s">
@@ -2384,7 +2384,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2469,7 +2469,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2543,9 +2543,6 @@
       <c r="B264" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C264" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B265" s="3" t="s">
@@ -2557,7 +2554,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2618,7 +2615,9 @@
       <c r="B273" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C273" s="6"/>
+      <c r="C273" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B274" s="3" t="s">
@@ -2629,15 +2628,21 @@
       <c r="B275" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C275" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B276" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C276" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2698,9 +2703,7 @@
       <c r="B284" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C284" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C284" s="6"/>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B285" s="3" t="s">
@@ -2716,13 +2719,10 @@
       <c r="B287" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C287" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2791,9 +2791,6 @@
       <c r="B296" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C296" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B297" s="3" t="s">
@@ -2810,7 +2807,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2879,6 +2876,9 @@
       <c r="B307" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C307" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B308" s="3" t="s">
@@ -2895,7 +2895,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -2974,10 +2974,13 @@
       <c r="B320" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C320" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3056,13 +3059,10 @@
       <c r="B331" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C331" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3131,9 +3131,6 @@
       <c r="B340" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C340" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B341" s="3" t="s">
@@ -3150,7 +3147,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3171,19 +3168,25 @@
       <c r="B345" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C345" s="6"/>
+      <c r="C345" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B346" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C346" s="6"/>
+      <c r="C346" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B347" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C347" s="6"/>
+      <c r="C347" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B348" s="3" t="s">
@@ -3205,11 +3208,16 @@
       <c r="B350" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C350" s="6"/>
+      <c r="C350" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B351" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C351" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.2">
@@ -3221,10 +3229,13 @@
       <c r="B353" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C353" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3245,25 +3256,19 @@
       <c r="B356" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C356" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C356" s="6"/>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B357" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C357" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C357" s="6"/>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B358" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C358" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C358" s="6"/>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B359" s="3" t="s">
@@ -3285,16 +3290,11 @@
       <c r="B361" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C361" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C361" s="6"/>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B362" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C362" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.2">
@@ -3306,13 +3306,10 @@
       <c r="B364" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C364" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3400,7 +3397,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3469,6 +3466,9 @@
       <c r="B384" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C384" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B385" s="3" t="s">
@@ -3485,7 +3485,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3554,9 +3554,6 @@
       <c r="B395" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C395" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B396" s="3" t="s">
@@ -3564,19 +3561,19 @@
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A397" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B397" s="7" t="s">
+      <c r="B397" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C397" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="398" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A398" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B398" s="7" t="s">
         <v>3</v>
-      </c>
-      <c r="C397" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="398" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B398" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="C398" s="5" t="s">
         <v>13</v>
@@ -3584,7 +3581,7 @@
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B399" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C399" s="5" t="s">
         <v>13</v>
@@ -3592,7 +3589,7 @@
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B400" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C400" s="5" t="s">
         <v>13</v>
@@ -3600,7 +3597,7 @@
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B401" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C401" s="5" t="s">
         <v>13</v>
@@ -3608,7 +3605,7 @@
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B402" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C402" s="5" t="s">
         <v>13</v>
@@ -3616,7 +3613,7 @@
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B403" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C403" s="5" t="s">
         <v>13</v>
@@ -3624,7 +3621,7 @@
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B404" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C404" s="5" t="s">
         <v>13</v>
@@ -3632,7 +3629,7 @@
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B405" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C405" s="5" t="s">
         <v>13</v>
@@ -3640,23 +3637,23 @@
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B406" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C406" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="407" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B407" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="407" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A407" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B407" s="7" t="s">
+    <row r="408" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A408" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B408" s="7" t="s">
         <v>3</v>
-      </c>
-      <c r="C407" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="408" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B408" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="C408" s="5" t="s">
         <v>13</v>
@@ -3664,7 +3661,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B409" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C409" s="5" t="s">
         <v>13</v>
@@ -3672,7 +3669,7 @@
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B410" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C410" s="5" t="s">
         <v>13</v>
@@ -3680,7 +3677,7 @@
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B411" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C411" s="5" t="s">
         <v>13</v>
@@ -3688,7 +3685,7 @@
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B412" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C412" s="5" t="s">
         <v>13</v>
@@ -3696,7 +3693,7 @@
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B413" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C413" s="5" t="s">
         <v>13</v>
@@ -3704,7 +3701,7 @@
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B414" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C414" s="5" t="s">
         <v>13</v>
@@ -3712,16 +3709,104 @@
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B415" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C415" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B416" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C416" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="417" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B417" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="417" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B417" s="3">
+    <row r="418" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A418" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B418" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C418" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="419" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B419" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C419" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="420" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B420" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C420" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="421" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B421" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C421" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="422" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B422" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C422" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="423" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B423" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C423" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="424" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B424" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C424" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="425" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B425" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C425" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="426" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B426" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="427" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B427" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="428" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B428" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\03aioveu-Day\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50B9CD21-0D27-496D-A208-6EB6458B6E2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7091A55C-F223-44F3-A4D7-EC3FBC14B4CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -200,6 +200,74 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -219,7 +287,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window" lastClr="CCE8CF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -474,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C428"/>
+  <dimension ref="A1:C439"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -562,7 +630,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -647,7 +715,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -732,7 +800,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -801,9 +869,6 @@
       <c r="B43" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C43" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B44" s="3" t="s">
@@ -820,7 +885,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -908,7 +973,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -977,6 +1042,9 @@
       <c r="B65" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C65" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B66" s="3" t="s">
@@ -993,7 +1061,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1078,7 +1146,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1163,7 +1231,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1248,7 +1316,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1317,9 +1385,6 @@
       <c r="B109" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C109" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B110" s="3" t="s">
@@ -1336,7 +1401,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1424,7 +1489,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1501,9 +1566,6 @@
       <c r="B132" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C132" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B133" s="3" t="s">
@@ -1515,7 +1577,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1592,6 +1654,9 @@
       <c r="B143" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C143" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B144" s="3" t="s">
@@ -1603,7 +1668,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1691,7 +1756,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1779,7 +1844,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1867,7 +1932,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1955,7 +2020,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2024,6 +2089,9 @@
       <c r="B197" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C197" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B198" s="3" t="s">
@@ -2040,7 +2108,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2101,7 +2169,9 @@
       <c r="B207" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C207" s="6"/>
+      <c r="C207" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B208" s="3" t="s">
@@ -2117,10 +2187,13 @@
       <c r="B210" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C210" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2181,16 +2254,11 @@
       <c r="B218" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C218" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C218" s="6"/>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B219" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C219" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.2">
@@ -2202,13 +2270,10 @@
       <c r="B221" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C221" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2296,7 +2361,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2384,7 +2449,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2453,6 +2518,9 @@
       <c r="B252" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C252" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B253" s="3" t="s">
@@ -2469,7 +2537,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2554,7 +2622,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2628,9 +2696,6 @@
       <c r="B275" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C275" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B276" s="3" t="s">
@@ -2642,7 +2707,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2703,7 +2768,9 @@
       <c r="B284" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C284" s="6"/>
+      <c r="C284" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B285" s="3" t="s">
@@ -2714,15 +2781,21 @@
       <c r="B286" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C286" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B287" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C287" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2783,9 +2856,7 @@
       <c r="B295" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C295" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C295" s="6"/>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B296" s="3" t="s">
@@ -2801,13 +2872,10 @@
       <c r="B298" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C298" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2876,9 +2944,6 @@
       <c r="B307" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C307" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B308" s="3" t="s">
@@ -2895,7 +2960,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -2964,6 +3029,9 @@
       <c r="B318" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C318" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B319" s="3" t="s">
@@ -2980,7 +3048,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3059,10 +3127,13 @@
       <c r="B331" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C331" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3141,13 +3212,10 @@
       <c r="B342" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C342" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3216,9 +3284,6 @@
       <c r="B351" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C351" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B352" s="3" t="s">
@@ -3235,7 +3300,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3256,19 +3321,25 @@
       <c r="B356" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C356" s="6"/>
+      <c r="C356" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B357" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C357" s="6"/>
+      <c r="C357" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B358" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C358" s="6"/>
+      <c r="C358" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B359" s="3" t="s">
@@ -3290,11 +3361,16 @@
       <c r="B361" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C361" s="6"/>
+      <c r="C361" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B362" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C362" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.2">
@@ -3306,10 +3382,13 @@
       <c r="B364" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C364" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3330,25 +3409,19 @@
       <c r="B367" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C367" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C367" s="6"/>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B368" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C368" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C368" s="6"/>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B369" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C369" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C369" s="6"/>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B370" s="3" t="s">
@@ -3370,16 +3443,11 @@
       <c r="B372" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C372" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C372" s="6"/>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B373" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C373" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.2">
@@ -3391,13 +3459,10 @@
       <c r="B375" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C375" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3485,7 +3550,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3554,6 +3619,9 @@
       <c r="B395" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C395" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B396" s="3" t="s">
@@ -3570,7 +3638,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3639,9 +3707,6 @@
       <c r="B406" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C406" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B407" s="3" t="s">
@@ -3649,19 +3714,19 @@
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A408" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B408" s="7" t="s">
+      <c r="B408" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C408" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="409" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A409" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B409" s="7" t="s">
         <v>3</v>
-      </c>
-      <c r="C408" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="409" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B409" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="C409" s="5" t="s">
         <v>13</v>
@@ -3669,7 +3734,7 @@
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B410" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C410" s="5" t="s">
         <v>13</v>
@@ -3677,7 +3742,7 @@
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B411" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C411" s="5" t="s">
         <v>13</v>
@@ -3685,7 +3750,7 @@
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B412" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C412" s="5" t="s">
         <v>13</v>
@@ -3693,7 +3758,7 @@
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B413" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C413" s="5" t="s">
         <v>13</v>
@@ -3701,7 +3766,7 @@
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B414" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C414" s="5" t="s">
         <v>13</v>
@@ -3709,7 +3774,7 @@
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B415" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C415" s="5" t="s">
         <v>13</v>
@@ -3717,7 +3782,7 @@
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B416" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C416" s="5" t="s">
         <v>13</v>
@@ -3725,23 +3790,23 @@
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B417" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C417" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="418" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B418" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="418" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A418" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B418" s="7" t="s">
+    <row r="419" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A419" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B419" s="7" t="s">
         <v>3</v>
-      </c>
-      <c r="C418" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="419" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B419" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="C419" s="5" t="s">
         <v>13</v>
@@ -3749,7 +3814,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B420" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C420" s="5" t="s">
         <v>13</v>
@@ -3757,7 +3822,7 @@
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B421" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C421" s="5" t="s">
         <v>13</v>
@@ -3765,7 +3830,7 @@
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B422" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C422" s="5" t="s">
         <v>13</v>
@@ -3773,7 +3838,7 @@
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B423" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C423" s="5" t="s">
         <v>13</v>
@@ -3781,7 +3846,7 @@
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B424" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C424" s="5" t="s">
         <v>13</v>
@@ -3789,7 +3854,7 @@
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B425" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C425" s="5" t="s">
         <v>13</v>
@@ -3797,16 +3862,104 @@
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B426" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C426" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B427" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C427" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="428" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B428" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="428" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B428" s="3">
+    <row r="429" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A429" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B429" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C429" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="430" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B430" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C430" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="431" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B431" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C431" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="432" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B432" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C432" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="433" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B433" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C433" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="434" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B434" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C434" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="435" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B435" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C435" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="436" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B436" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C436" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="437" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B437" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="438" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B438" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="439" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B439" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\03aioveu-Day\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7091A55C-F223-44F3-A4D7-EC3FBC14B4CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A5868B8-47E2-4E8C-AFA4-E16B2260C8AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -200,74 +200,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -287,7 +219,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="CCE8CF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -542,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C439"/>
+  <dimension ref="A1:C450"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -630,7 +562,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -698,6 +630,9 @@
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B21" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -715,7 +650,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -800,7 +735,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -885,7 +820,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -953,9 +888,6 @@
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B54" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
@@ -973,7 +905,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -1061,7 +993,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1129,6 +1061,9 @@
     <row r="76" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B76" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
@@ -1146,7 +1081,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1231,7 +1166,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1316,7 +1251,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1401,7 +1336,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1469,9 +1404,6 @@
     <row r="120" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B120" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C120" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.2">
@@ -1489,7 +1421,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1577,7 +1509,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1653,9 +1585,6 @@
     <row r="143" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B143" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="C143" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.2">
@@ -1668,7 +1597,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1744,6 +1673,9 @@
     <row r="154" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B154" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="C154" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.2">
@@ -1756,7 +1688,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1844,7 +1776,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1932,7 +1864,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -2020,7 +1952,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2108,7 +2040,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2176,6 +2108,9 @@
     <row r="208" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B208" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C208" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.2">
@@ -2193,7 +2128,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2254,7 +2189,9 @@
       <c r="B218" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C218" s="6"/>
+      <c r="C218" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B219" s="3" t="s">
@@ -2270,10 +2207,13 @@
       <c r="B221" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C221" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2334,16 +2274,11 @@
       <c r="B229" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C229" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C229" s="6"/>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B230" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C230" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.2">
@@ -2355,13 +2290,10 @@
       <c r="B232" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C232" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2449,7 +2381,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2537,7 +2469,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2605,6 +2537,9 @@
     <row r="263" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B263" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C263" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.2">
@@ -2622,7 +2557,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2707,7 +2642,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2780,9 +2715,6 @@
     <row r="286" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B286" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="C286" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.2">
@@ -2795,7 +2727,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2856,7 +2788,9 @@
       <c r="B295" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C295" s="6"/>
+      <c r="C295" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B296" s="3" t="s">
@@ -2866,16 +2800,22 @@
     <row r="297" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B297" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="C297" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B298" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C298" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2936,9 +2876,7 @@
       <c r="B306" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C306" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C306" s="6"/>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B307" s="3" t="s">
@@ -2954,13 +2892,10 @@
       <c r="B309" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C309" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3028,9 +2963,6 @@
     <row r="318" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B318" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C318" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.2">
@@ -3048,7 +2980,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3116,6 +3048,9 @@
     <row r="329" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B329" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C329" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.2">
@@ -3133,7 +3068,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3212,10 +3147,13 @@
       <c r="B342" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C342" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3294,13 +3232,10 @@
       <c r="B353" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C353" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3368,9 +3303,6 @@
     <row r="362" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B362" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C362" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.2">
@@ -3388,7 +3320,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3409,19 +3341,25 @@
       <c r="B367" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C367" s="6"/>
+      <c r="C367" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B368" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C368" s="6"/>
+      <c r="C368" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B369" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C369" s="6"/>
+      <c r="C369" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B370" s="3" t="s">
@@ -3443,11 +3381,16 @@
       <c r="B372" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C372" s="6"/>
+      <c r="C372" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B373" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C373" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.2">
@@ -3459,10 +3402,13 @@
       <c r="B375" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C375" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3483,25 +3429,19 @@
       <c r="B378" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C378" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C378" s="6"/>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B379" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C379" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C379" s="6"/>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B380" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C380" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C380" s="6"/>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B381" s="3" t="s">
@@ -3523,16 +3463,11 @@
       <c r="B383" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C383" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C383" s="6"/>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B384" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C384" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.2">
@@ -3544,13 +3479,10 @@
       <c r="B386" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C386" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3638,7 +3570,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3706,6 +3638,9 @@
     <row r="406" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B406" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C406" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.2">
@@ -3723,7 +3658,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3792,9 +3727,6 @@
       <c r="B417" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C417" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B418" s="3" t="s">
@@ -3802,19 +3734,19 @@
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A419" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B419" s="7" t="s">
-        <v>3</v>
+      <c r="B419" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C419" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B420" s="3" t="s">
-        <v>4</v>
+      <c r="A420" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B420" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C420" s="5" t="s">
         <v>13</v>
@@ -3822,7 +3754,7 @@
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B421" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C421" s="5" t="s">
         <v>13</v>
@@ -3830,7 +3762,7 @@
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B422" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C422" s="5" t="s">
         <v>13</v>
@@ -3838,7 +3770,7 @@
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B423" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C423" s="5" t="s">
         <v>13</v>
@@ -3846,7 +3778,7 @@
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B424" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C424" s="5" t="s">
         <v>13</v>
@@ -3854,7 +3786,7 @@
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B425" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C425" s="5" t="s">
         <v>13</v>
@@ -3862,7 +3794,7 @@
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B426" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C426" s="5" t="s">
         <v>13</v>
@@ -3870,7 +3802,7 @@
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B427" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C427" s="5" t="s">
         <v>13</v>
@@ -3878,23 +3810,23 @@
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B428" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C428" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A429" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B429" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C429" s="5" t="s">
-        <v>13</v>
+      <c r="B429" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B430" s="3" t="s">
-        <v>4</v>
+      <c r="A430" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B430" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C430" s="5" t="s">
         <v>13</v>
@@ -3902,7 +3834,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B431" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C431" s="5" t="s">
         <v>13</v>
@@ -3910,56 +3842,144 @@
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B432" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C432" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="433" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B433" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C433" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="434" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B434" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C434" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="435" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B435" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C435" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="436" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B436" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C436" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="437" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B437" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="438" spans="2:3" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="C437" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="438" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B438" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="439" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B439" s="3">
+        <v>11</v>
+      </c>
+      <c r="C438" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="439" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B439" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="440" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A440" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B440" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C440" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="441" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B441" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C441" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="442" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B442" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C442" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="443" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B443" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C443" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="444" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B444" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C444" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="445" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B445" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C445" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="446" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B446" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C446" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="447" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B447" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C447" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="448" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B448" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="449" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B449" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="450" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B450" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\03aioveu-Day\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A5868B8-47E2-4E8C-AFA4-E16B2260C8AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E504CFB-2A7E-4A27-A5F8-979F1C3992A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -474,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C450"/>
+  <dimension ref="A1:C461"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -562,7 +562,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -630,9 +630,6 @@
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B21" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -650,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -718,6 +715,9 @@
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B32" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -735,7 +735,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -820,7 +820,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -905,7 +905,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -973,9 +973,6 @@
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B65" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C65" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
@@ -993,7 +990,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1081,7 +1078,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1149,6 +1146,9 @@
     <row r="87" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B87" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.2">
@@ -1166,7 +1166,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1251,7 +1251,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1336,7 +1336,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1421,7 +1421,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1489,9 +1489,6 @@
     <row r="131" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B131" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C131" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.2">
@@ -1509,7 +1506,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1597,7 +1594,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1673,9 +1670,6 @@
     <row r="154" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B154" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="C154" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.2">
@@ -1688,7 +1682,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1764,6 +1758,9 @@
     <row r="165" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B165" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="C165" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.2">
@@ -1776,7 +1773,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1864,7 +1861,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1952,7 +1949,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2040,7 +2037,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2128,7 +2125,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2196,6 +2193,9 @@
     <row r="219" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B219" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C219" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.2">
@@ -2213,7 +2213,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2274,7 +2274,9 @@
       <c r="B229" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C229" s="6"/>
+      <c r="C229" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B230" s="3" t="s">
@@ -2290,10 +2292,13 @@
       <c r="B232" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C232" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2354,16 +2359,11 @@
       <c r="B240" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C240" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C240" s="6"/>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B241" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C241" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.2">
@@ -2375,13 +2375,10 @@
       <c r="B243" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C243" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2469,7 +2466,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2557,7 +2554,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2625,6 +2622,9 @@
     <row r="274" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B274" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C274" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.2">
@@ -2642,7 +2642,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2727,7 +2727,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2800,9 +2800,6 @@
     <row r="297" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B297" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="C297" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.2">
@@ -2815,7 +2812,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2876,7 +2873,9 @@
       <c r="B306" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C306" s="6"/>
+      <c r="C306" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B307" s="3" t="s">
@@ -2886,16 +2885,22 @@
     <row r="308" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B308" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="C308" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B309" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C309" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -2956,9 +2961,7 @@
       <c r="B317" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C317" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C317" s="6"/>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B318" s="3" t="s">
@@ -2974,13 +2977,10 @@
       <c r="B320" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C320" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3048,9 +3048,6 @@
     <row r="329" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B329" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C329" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.2">
@@ -3068,7 +3065,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3136,6 +3133,9 @@
     <row r="340" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B340" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C340" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.2">
@@ -3153,7 +3153,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3232,10 +3232,13 @@
       <c r="B353" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C353" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3314,13 +3317,10 @@
       <c r="B364" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C364" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3388,9 +3388,6 @@
     <row r="373" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B373" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C373" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.2">
@@ -3408,7 +3405,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3429,19 +3426,25 @@
       <c r="B378" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C378" s="6"/>
+      <c r="C378" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B379" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C379" s="6"/>
+      <c r="C379" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B380" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C380" s="6"/>
+      <c r="C380" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B381" s="3" t="s">
@@ -3463,11 +3466,16 @@
       <c r="B383" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C383" s="6"/>
+      <c r="C383" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B384" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C384" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.2">
@@ -3479,10 +3487,13 @@
       <c r="B386" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C386" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3503,25 +3514,19 @@
       <c r="B389" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C389" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C389" s="6"/>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B390" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C390" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C390" s="6"/>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B391" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C391" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C391" s="6"/>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B392" s="3" t="s">
@@ -3543,16 +3548,11 @@
       <c r="B394" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C394" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C394" s="6"/>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B395" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C395" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.2">
@@ -3564,13 +3564,10 @@
       <c r="B397" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C397" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3658,7 +3655,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3726,6 +3723,9 @@
     <row r="417" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B417" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C417" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.2">
@@ -3743,7 +3743,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3812,9 +3812,6 @@
       <c r="B428" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C428" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B429" s="3" t="s">
@@ -3822,19 +3819,19 @@
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A430" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B430" s="7" t="s">
-        <v>3</v>
+      <c r="B430" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C430" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B431" s="3" t="s">
-        <v>4</v>
+      <c r="A431" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B431" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C431" s="5" t="s">
         <v>13</v>
@@ -3842,7 +3839,7 @@
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B432" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C432" s="5" t="s">
         <v>13</v>
@@ -3850,7 +3847,7 @@
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B433" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C433" s="5" t="s">
         <v>13</v>
@@ -3858,7 +3855,7 @@
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B434" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C434" s="5" t="s">
         <v>13</v>
@@ -3866,7 +3863,7 @@
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B435" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C435" s="5" t="s">
         <v>13</v>
@@ -3874,7 +3871,7 @@
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B436" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C436" s="5" t="s">
         <v>13</v>
@@ -3882,7 +3879,7 @@
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B437" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C437" s="5" t="s">
         <v>13</v>
@@ -3890,7 +3887,7 @@
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B438" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C438" s="5" t="s">
         <v>13</v>
@@ -3898,23 +3895,23 @@
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B439" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C439" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A440" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B440" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C440" s="5" t="s">
-        <v>13</v>
+      <c r="B440" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B441" s="3" t="s">
-        <v>4</v>
+      <c r="A441" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B441" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C441" s="5" t="s">
         <v>13</v>
@@ -3922,7 +3919,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B442" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C442" s="5" t="s">
         <v>13</v>
@@ -3930,7 +3927,7 @@
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B443" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C443" s="5" t="s">
         <v>13</v>
@@ -3938,7 +3935,7 @@
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B444" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C444" s="5" t="s">
         <v>13</v>
@@ -3946,7 +3943,7 @@
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B445" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C445" s="5" t="s">
         <v>13</v>
@@ -3954,7 +3951,7 @@
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B446" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C446" s="5" t="s">
         <v>13</v>
@@ -3962,7 +3959,7 @@
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B447" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C447" s="5" t="s">
         <v>13</v>
@@ -3970,16 +3967,104 @@
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B448" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="449" spans="2:2" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="C448" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="449" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B449" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="450" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B450" s="3">
+        <v>11</v>
+      </c>
+      <c r="C449" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="450" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B450" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="451" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A451" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B451" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C451" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="452" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B452" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C452" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="453" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B453" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C453" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="454" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B454" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C454" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="455" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B455" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C455" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="456" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B456" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C456" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="457" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B457" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C457" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="458" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B458" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C458" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="459" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B459" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="460" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B460" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="461" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B461" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\03aioveu-Day\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E504CFB-2A7E-4A27-A5F8-979F1C3992A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FD0B3FF-30F3-4891-B4D5-90C481CFC312}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -474,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C461"/>
+  <dimension ref="A1:C472"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -562,7 +562,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -715,9 +715,6 @@
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B32" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -735,7 +732,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -803,6 +800,9 @@
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B43" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
@@ -820,7 +820,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -905,7 +905,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -990,7 +990,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1058,9 +1058,6 @@
     <row r="76" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B76" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C76" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
@@ -1078,7 +1075,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1166,7 +1163,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1234,6 +1231,9 @@
     <row r="98" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B98" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.2">
@@ -1251,7 +1251,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1336,7 +1336,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1421,7 +1421,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1506,7 +1506,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1574,9 +1574,6 @@
     <row r="142" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B142" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C142" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.2">
@@ -1594,7 +1591,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1682,7 +1679,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1758,9 +1755,6 @@
     <row r="165" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B165" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="C165" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.2">
@@ -1773,7 +1767,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1849,6 +1843,9 @@
     <row r="176" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B176" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="C176" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.2">
@@ -1861,7 +1858,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1949,7 +1946,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2037,7 +2034,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2125,7 +2122,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2213,7 +2210,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2281,6 +2278,9 @@
     <row r="230" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B230" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C230" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.2">
@@ -2298,7 +2298,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2359,7 +2359,9 @@
       <c r="B240" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C240" s="6"/>
+      <c r="C240" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B241" s="3" t="s">
@@ -2375,10 +2377,13 @@
       <c r="B243" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C243" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2439,16 +2444,11 @@
       <c r="B251" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C251" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C251" s="6"/>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B252" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C252" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.2">
@@ -2460,13 +2460,10 @@
       <c r="B254" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C254" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2554,7 +2551,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2642,7 +2639,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2710,6 +2707,9 @@
     <row r="285" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B285" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C285" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.2">
@@ -2727,7 +2727,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2812,7 +2812,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2885,9 +2885,6 @@
     <row r="308" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B308" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="C308" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.2">
@@ -2900,7 +2897,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -2961,7 +2958,9 @@
       <c r="B317" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C317" s="6"/>
+      <c r="C317" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B318" s="3" t="s">
@@ -2971,16 +2970,22 @@
     <row r="319" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B319" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="C319" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B320" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C320" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3041,9 +3046,7 @@
       <c r="B328" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C328" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C328" s="6"/>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B329" s="3" t="s">
@@ -3059,13 +3062,10 @@
       <c r="B331" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C331" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3133,9 +3133,6 @@
     <row r="340" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B340" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C340" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.2">
@@ -3153,7 +3150,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3221,6 +3218,9 @@
     <row r="351" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B351" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C351" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.2">
@@ -3238,7 +3238,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3317,10 +3317,13 @@
       <c r="B364" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C364" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3399,13 +3402,10 @@
       <c r="B375" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C375" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3473,9 +3473,6 @@
     <row r="384" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B384" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C384" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.2">
@@ -3493,7 +3490,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3514,19 +3511,25 @@
       <c r="B389" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C389" s="6"/>
+      <c r="C389" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B390" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C390" s="6"/>
+      <c r="C390" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B391" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C391" s="6"/>
+      <c r="C391" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B392" s="3" t="s">
@@ -3548,11 +3551,16 @@
       <c r="B394" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C394" s="6"/>
+      <c r="C394" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B395" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C395" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.2">
@@ -3564,10 +3572,13 @@
       <c r="B397" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C397" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3588,25 +3599,19 @@
       <c r="B400" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C400" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C400" s="6"/>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B401" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C401" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C401" s="6"/>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B402" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C402" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C402" s="6"/>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B403" s="3" t="s">
@@ -3628,16 +3633,11 @@
       <c r="B405" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C405" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C405" s="6"/>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B406" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C406" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.2">
@@ -3649,13 +3649,10 @@
       <c r="B408" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C408" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3743,7 +3740,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3811,6 +3808,9 @@
     <row r="428" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B428" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C428" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.2">
@@ -3828,7 +3828,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3897,9 +3897,6 @@
       <c r="B439" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C439" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B440" s="3" t="s">
@@ -3907,19 +3904,19 @@
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A441" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B441" s="7" t="s">
-        <v>3</v>
+      <c r="B441" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C441" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B442" s="3" t="s">
-        <v>4</v>
+      <c r="A442" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B442" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C442" s="5" t="s">
         <v>13</v>
@@ -3927,7 +3924,7 @@
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B443" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C443" s="5" t="s">
         <v>13</v>
@@ -3935,7 +3932,7 @@
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B444" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C444" s="5" t="s">
         <v>13</v>
@@ -3943,7 +3940,7 @@
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B445" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C445" s="5" t="s">
         <v>13</v>
@@ -3951,7 +3948,7 @@
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B446" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C446" s="5" t="s">
         <v>13</v>
@@ -3959,7 +3956,7 @@
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B447" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C447" s="5" t="s">
         <v>13</v>
@@ -3967,7 +3964,7 @@
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B448" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C448" s="5" t="s">
         <v>13</v>
@@ -3975,7 +3972,7 @@
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B449" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C449" s="5" t="s">
         <v>13</v>
@@ -3983,23 +3980,23 @@
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B450" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C450" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A451" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B451" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C451" s="5" t="s">
-        <v>13</v>
+      <c r="B451" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B452" s="3" t="s">
-        <v>4</v>
+      <c r="A452" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B452" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C452" s="5" t="s">
         <v>13</v>
@@ -4007,7 +4004,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B453" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C453" s="5" t="s">
         <v>13</v>
@@ -4015,7 +4012,7 @@
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B454" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C454" s="5" t="s">
         <v>13</v>
@@ -4023,7 +4020,7 @@
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B455" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C455" s="5" t="s">
         <v>13</v>
@@ -4031,7 +4028,7 @@
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B456" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C456" s="5" t="s">
         <v>13</v>
@@ -4039,7 +4036,7 @@
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B457" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C457" s="5" t="s">
         <v>13</v>
@@ -4047,7 +4044,7 @@
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B458" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C458" s="5" t="s">
         <v>13</v>
@@ -4055,16 +4052,104 @@
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B459" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C459" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B460" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C460" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B461" s="3">
+      <c r="B461" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="462" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A462" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B462" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C462" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="463" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B463" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C463" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="464" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B464" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C464" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="465" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B465" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C465" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="466" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B466" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C466" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="467" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B467" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C467" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="468" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B468" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C468" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="469" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B469" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C469" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="470" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B470" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="471" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B471" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="472" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B472" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\03aioveu-Day\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FD0B3FF-30F3-4891-B4D5-90C481CFC312}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6B4B7AA-CBD0-4798-A592-7843D86016F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -474,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C472"/>
+  <dimension ref="A1:C483"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -562,7 +562,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -732,7 +732,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -800,9 +800,6 @@
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B43" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
@@ -820,7 +817,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -888,6 +885,9 @@
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B54" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
@@ -905,7 +905,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -990,7 +990,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1075,7 +1075,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1143,9 +1143,6 @@
     <row r="87" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B87" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C87" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.2">
@@ -1163,7 +1160,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1251,7 +1248,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1319,6 +1316,9 @@
     <row r="109" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B109" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.2">
@@ -1336,7 +1336,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1421,7 +1421,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1506,7 +1506,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1591,7 +1591,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1659,9 +1659,6 @@
     <row r="153" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B153" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C153" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.2">
@@ -1679,7 +1676,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1767,7 +1764,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1843,9 +1840,6 @@
     <row r="176" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B176" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="C176" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.2">
@@ -1858,7 +1852,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1934,6 +1928,9 @@
     <row r="187" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B187" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="C187" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.2">
@@ -1946,7 +1943,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2034,7 +2031,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2122,7 +2119,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2210,7 +2207,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2298,7 +2295,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2366,6 +2363,9 @@
     <row r="241" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B241" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C241" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.2">
@@ -2383,7 +2383,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2444,7 +2444,9 @@
       <c r="B251" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C251" s="6"/>
+      <c r="C251" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B252" s="3" t="s">
@@ -2460,10 +2462,13 @@
       <c r="B254" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C254" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2524,16 +2529,11 @@
       <c r="B262" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C262" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C262" s="6"/>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B263" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C263" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.2">
@@ -2545,13 +2545,10 @@
       <c r="B265" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C265" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2639,7 +2636,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2727,7 +2724,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2795,6 +2792,9 @@
     <row r="296" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B296" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C296" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.2">
@@ -2812,7 +2812,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2897,7 +2897,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -2970,9 +2970,6 @@
     <row r="319" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B319" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="C319" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.2">
@@ -2985,7 +2982,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3046,7 +3043,9 @@
       <c r="B328" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C328" s="6"/>
+      <c r="C328" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B329" s="3" t="s">
@@ -3056,16 +3055,22 @@
     <row r="330" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B330" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="C330" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B331" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C331" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3126,9 +3131,7 @@
       <c r="B339" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C339" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C339" s="6"/>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B340" s="3" t="s">
@@ -3144,13 +3147,10 @@
       <c r="B342" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C342" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3218,9 +3218,6 @@
     <row r="351" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B351" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C351" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.2">
@@ -3238,7 +3235,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3306,6 +3303,9 @@
     <row r="362" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B362" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C362" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.2">
@@ -3323,7 +3323,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3402,10 +3402,13 @@
       <c r="B375" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C375" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3484,13 +3487,10 @@
       <c r="B386" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C386" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3558,9 +3558,6 @@
     <row r="395" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B395" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C395" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.2">
@@ -3578,7 +3575,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3599,19 +3596,25 @@
       <c r="B400" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C400" s="6"/>
+      <c r="C400" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B401" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C401" s="6"/>
+      <c r="C401" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B402" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C402" s="6"/>
+      <c r="C402" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B403" s="3" t="s">
@@ -3633,11 +3636,16 @@
       <c r="B405" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C405" s="6"/>
+      <c r="C405" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B406" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C406" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.2">
@@ -3649,10 +3657,13 @@
       <c r="B408" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C408" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3673,25 +3684,19 @@
       <c r="B411" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C411" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C411" s="6"/>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B412" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C412" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C412" s="6"/>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B413" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C413" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C413" s="6"/>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B414" s="3" t="s">
@@ -3713,16 +3718,11 @@
       <c r="B416" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C416" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C416" s="6"/>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B417" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C417" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.2">
@@ -3734,13 +3734,10 @@
       <c r="B419" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C419" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3828,7 +3825,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3896,6 +3893,9 @@
     <row r="439" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B439" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C439" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.2">
@@ -3913,7 +3913,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -3982,9 +3982,6 @@
       <c r="B450" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C450" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B451" s="3" t="s">
@@ -3992,19 +3989,19 @@
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A452" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B452" s="7" t="s">
-        <v>3</v>
+      <c r="B452" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C452" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B453" s="3" t="s">
-        <v>4</v>
+      <c r="A453" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B453" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C453" s="5" t="s">
         <v>13</v>
@@ -4012,7 +4009,7 @@
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B454" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C454" s="5" t="s">
         <v>13</v>
@@ -4020,7 +4017,7 @@
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B455" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C455" s="5" t="s">
         <v>13</v>
@@ -4028,7 +4025,7 @@
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B456" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C456" s="5" t="s">
         <v>13</v>
@@ -4036,7 +4033,7 @@
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B457" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C457" s="5" t="s">
         <v>13</v>
@@ -4044,7 +4041,7 @@
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B458" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C458" s="5" t="s">
         <v>13</v>
@@ -4052,7 +4049,7 @@
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B459" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C459" s="5" t="s">
         <v>13</v>
@@ -4060,7 +4057,7 @@
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B460" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C460" s="5" t="s">
         <v>13</v>
@@ -4068,23 +4065,23 @@
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B461" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C461" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A462" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B462" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C462" s="5" t="s">
-        <v>13</v>
+      <c r="B462" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B463" s="3" t="s">
-        <v>4</v>
+      <c r="A463" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B463" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C463" s="5" t="s">
         <v>13</v>
@@ -4092,64 +4089,152 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B464" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C464" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="465" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B465" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C465" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="466" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B466" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C466" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="467" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B467" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C467" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="468" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B468" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C468" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="469" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B469" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C469" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="470" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B470" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="471" spans="2:3" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="C470" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="471" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B471" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="472" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B472" s="3">
+        <v>11</v>
+      </c>
+      <c r="C471" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="472" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B472" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="473" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A473" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B473" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C473" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="474" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B474" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C474" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="475" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B475" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C475" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="476" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B476" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C476" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="477" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B477" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C477" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="478" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B478" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C478" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="479" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B479" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C479" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="480" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B480" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C480" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="481" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B481" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="482" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B482" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="483" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B483" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\03aioveu-Day\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6B4B7AA-CBD0-4798-A592-7843D86016F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A20C538-3A47-42B5-A8E4-7F699C958E1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -474,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C483"/>
+  <dimension ref="A1:C494"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -562,7 +562,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -732,7 +732,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -817,7 +817,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -885,9 +885,6 @@
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B54" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
@@ -905,7 +902,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -973,6 +970,9 @@
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B65" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
@@ -990,7 +990,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1075,7 +1075,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1160,7 +1160,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1228,9 +1228,6 @@
     <row r="98" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B98" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C98" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.2">
@@ -1248,7 +1245,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1336,7 +1333,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1404,6 +1401,9 @@
     <row r="120" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B120" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C120" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.2">
@@ -1421,7 +1421,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1506,7 +1506,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1591,7 +1591,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1676,7 +1676,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1744,9 +1744,6 @@
     <row r="164" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B164" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C164" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.2">
@@ -1764,7 +1761,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1852,7 +1849,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1928,9 +1925,6 @@
     <row r="187" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B187" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="C187" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.2">
@@ -1943,7 +1937,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2019,6 +2013,9 @@
     <row r="198" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B198" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="C198" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.2">
@@ -2031,7 +2028,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2119,7 +2116,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2207,7 +2204,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2295,7 +2292,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2383,7 +2380,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2451,6 +2448,9 @@
     <row r="252" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B252" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C252" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.2">
@@ -2468,7 +2468,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2529,7 +2529,9 @@
       <c r="B262" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C262" s="6"/>
+      <c r="C262" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B263" s="3" t="s">
@@ -2545,10 +2547,13 @@
       <c r="B265" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C265" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2609,16 +2614,11 @@
       <c r="B273" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C273" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C273" s="6"/>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B274" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C274" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.2">
@@ -2630,13 +2630,10 @@
       <c r="B276" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C276" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2724,7 +2721,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2812,7 +2809,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2880,6 +2877,9 @@
     <row r="307" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B307" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C307" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.2">
@@ -2897,7 +2897,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -2982,7 +2982,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3055,9 +3055,6 @@
     <row r="330" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B330" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="C330" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.2">
@@ -3070,7 +3067,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3131,7 +3128,9 @@
       <c r="B339" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C339" s="6"/>
+      <c r="C339" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B340" s="3" t="s">
@@ -3141,16 +3140,22 @@
     <row r="341" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B341" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="C341" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B342" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C342" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3211,9 +3216,7 @@
       <c r="B350" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C350" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C350" s="6"/>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B351" s="3" t="s">
@@ -3229,13 +3232,10 @@
       <c r="B353" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C353" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3303,9 +3303,6 @@
     <row r="362" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B362" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C362" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.2">
@@ -3323,7 +3320,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3391,6 +3388,9 @@
     <row r="373" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B373" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C373" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.2">
@@ -3408,7 +3408,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3487,10 +3487,13 @@
       <c r="B386" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C386" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3569,13 +3572,10 @@
       <c r="B397" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C397" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3643,9 +3643,6 @@
     <row r="406" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B406" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C406" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.2">
@@ -3663,7 +3660,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3684,19 +3681,25 @@
       <c r="B411" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C411" s="6"/>
+      <c r="C411" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B412" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C412" s="6"/>
+      <c r="C412" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B413" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C413" s="6"/>
+      <c r="C413" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B414" s="3" t="s">
@@ -3718,11 +3721,16 @@
       <c r="B416" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C416" s="6"/>
+      <c r="C416" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B417" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C417" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.2">
@@ -3734,10 +3742,13 @@
       <c r="B419" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C419" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3758,25 +3769,19 @@
       <c r="B422" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C422" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C422" s="6"/>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B423" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C423" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C423" s="6"/>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B424" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C424" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C424" s="6"/>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B425" s="3" t="s">
@@ -3798,16 +3803,11 @@
       <c r="B427" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C427" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C427" s="6"/>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B428" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C428" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.2">
@@ -3819,13 +3819,10 @@
       <c r="B430" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C430" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3913,7 +3910,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -3981,6 +3978,9 @@
     <row r="450" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B450" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C450" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.2">
@@ -3998,7 +3998,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4067,9 +4067,6 @@
       <c r="B461" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C461" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B462" s="3" t="s">
@@ -4077,19 +4074,19 @@
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A463" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B463" s="7" t="s">
-        <v>3</v>
+      <c r="B463" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C463" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B464" s="3" t="s">
-        <v>4</v>
+      <c r="A464" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B464" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C464" s="5" t="s">
         <v>13</v>
@@ -4097,7 +4094,7 @@
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B465" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C465" s="5" t="s">
         <v>13</v>
@@ -4105,7 +4102,7 @@
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B466" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C466" s="5" t="s">
         <v>13</v>
@@ -4113,7 +4110,7 @@
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B467" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C467" s="5" t="s">
         <v>13</v>
@@ -4121,7 +4118,7 @@
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B468" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C468" s="5" t="s">
         <v>13</v>
@@ -4129,7 +4126,7 @@
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B469" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C469" s="5" t="s">
         <v>13</v>
@@ -4137,7 +4134,7 @@
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B470" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C470" s="5" t="s">
         <v>13</v>
@@ -4145,7 +4142,7 @@
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B471" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C471" s="5" t="s">
         <v>13</v>
@@ -4153,23 +4150,23 @@
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B472" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C472" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A473" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B473" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C473" s="5" t="s">
-        <v>13</v>
+      <c r="B473" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B474" s="3" t="s">
-        <v>4</v>
+      <c r="A474" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B474" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C474" s="5" t="s">
         <v>13</v>
@@ -4177,7 +4174,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B475" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C475" s="5" t="s">
         <v>13</v>
@@ -4185,7 +4182,7 @@
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B476" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C476" s="5" t="s">
         <v>13</v>
@@ -4193,7 +4190,7 @@
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B477" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C477" s="5" t="s">
         <v>13</v>
@@ -4201,7 +4198,7 @@
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B478" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C478" s="5" t="s">
         <v>13</v>
@@ -4209,7 +4206,7 @@
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B479" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C479" s="5" t="s">
         <v>13</v>
@@ -4217,24 +4214,112 @@
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B480" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C480" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="481" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B481" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="482" spans="2:2" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="C481" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="482" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B482" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="483" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B483" s="3">
+        <v>11</v>
+      </c>
+      <c r="C482" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="483" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B483" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="484" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A484" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B484" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C484" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="485" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B485" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C485" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="486" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B486" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C486" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="487" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B487" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C487" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="488" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B488" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C488" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="489" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B489" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C489" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="490" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B490" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C490" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="491" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B491" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C491" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="492" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B492" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="493" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B493" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="494" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B494" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\03aioveu-Day\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A20C538-3A47-42B5-A8E4-7F699C958E1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C1B7CB8-49A8-450A-9CD6-9F0213664532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -474,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C494"/>
+  <dimension ref="A1:C505"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -562,7 +562,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -732,7 +732,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -817,7 +817,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -902,7 +902,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -970,9 +970,6 @@
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B65" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C65" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
@@ -990,7 +987,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1058,6 +1055,9 @@
     <row r="76" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B76" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
@@ -1075,7 +1075,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1160,7 +1160,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1245,7 +1245,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1313,9 +1313,6 @@
     <row r="109" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B109" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C109" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.2">
@@ -1333,7 +1330,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1421,7 +1418,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1489,6 +1486,9 @@
     <row r="131" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B131" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.2">
@@ -1506,7 +1506,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1591,7 +1591,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1676,7 +1676,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1761,7 +1761,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1829,9 +1829,6 @@
     <row r="175" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B175" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C175" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.2">
@@ -1849,7 +1846,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1937,7 +1934,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2013,9 +2010,6 @@
     <row r="198" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B198" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="C198" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.2">
@@ -2028,7 +2022,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2104,6 +2098,9 @@
     <row r="209" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B209" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="C209" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.2">
@@ -2116,7 +2113,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2204,7 +2201,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2292,7 +2289,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2380,7 +2377,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2468,7 +2465,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2536,6 +2533,9 @@
     <row r="263" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B263" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C263" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.2">
@@ -2553,7 +2553,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2614,7 +2614,9 @@
       <c r="B273" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C273" s="6"/>
+      <c r="C273" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B274" s="3" t="s">
@@ -2630,10 +2632,13 @@
       <c r="B276" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C276" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2694,16 +2699,11 @@
       <c r="B284" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C284" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C284" s="6"/>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B285" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C285" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.2">
@@ -2715,13 +2715,10 @@
       <c r="B287" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C287" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2809,7 +2806,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2897,7 +2894,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -2965,6 +2962,9 @@
     <row r="318" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B318" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C318" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.2">
@@ -2982,7 +2982,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3067,7 +3067,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3140,9 +3140,6 @@
     <row r="341" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B341" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="C341" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.2">
@@ -3155,7 +3152,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3216,7 +3213,9 @@
       <c r="B350" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C350" s="6"/>
+      <c r="C350" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B351" s="3" t="s">
@@ -3226,16 +3225,22 @@
     <row r="352" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B352" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="C352" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B353" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C353" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3296,9 +3301,7 @@
       <c r="B361" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C361" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C361" s="6"/>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B362" s="3" t="s">
@@ -3314,13 +3317,10 @@
       <c r="B364" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C364" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3388,9 +3388,6 @@
     <row r="373" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B373" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C373" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.2">
@@ -3408,7 +3405,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3476,6 +3473,9 @@
     <row r="384" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B384" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C384" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.2">
@@ -3493,7 +3493,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3572,10 +3572,13 @@
       <c r="B397" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C397" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3654,13 +3657,10 @@
       <c r="B408" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C408" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3728,9 +3728,6 @@
     <row r="417" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B417" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C417" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.2">
@@ -3748,7 +3745,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3769,19 +3766,25 @@
       <c r="B422" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C422" s="6"/>
+      <c r="C422" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B423" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C423" s="6"/>
+      <c r="C423" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B424" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C424" s="6"/>
+      <c r="C424" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B425" s="3" t="s">
@@ -3803,11 +3806,16 @@
       <c r="B427" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C427" s="6"/>
+      <c r="C427" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B428" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C428" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.2">
@@ -3819,10 +3827,13 @@
       <c r="B430" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C430" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3843,25 +3854,19 @@
       <c r="B433" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C433" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C433" s="6"/>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B434" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C434" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C434" s="6"/>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B435" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C435" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C435" s="6"/>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B436" s="3" t="s">
@@ -3883,16 +3888,11 @@
       <c r="B438" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C438" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C438" s="6"/>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B439" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C439" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.2">
@@ -3904,13 +3904,10 @@
       <c r="B441" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C441" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -3998,7 +3995,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4066,6 +4063,9 @@
     <row r="461" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B461" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C461" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.2">
@@ -4083,7 +4083,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4152,9 +4152,6 @@
       <c r="B472" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C472" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B473" s="3" t="s">
@@ -4162,19 +4159,19 @@
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A474" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B474" s="7" t="s">
-        <v>3</v>
+      <c r="B474" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C474" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B475" s="3" t="s">
-        <v>4</v>
+      <c r="A475" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B475" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C475" s="5" t="s">
         <v>13</v>
@@ -4182,7 +4179,7 @@
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B476" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C476" s="5" t="s">
         <v>13</v>
@@ -4190,7 +4187,7 @@
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B477" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C477" s="5" t="s">
         <v>13</v>
@@ -4198,7 +4195,7 @@
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B478" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C478" s="5" t="s">
         <v>13</v>
@@ -4206,7 +4203,7 @@
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B479" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C479" s="5" t="s">
         <v>13</v>
@@ -4214,7 +4211,7 @@
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B480" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C480" s="5" t="s">
         <v>13</v>
@@ -4222,7 +4219,7 @@
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B481" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C481" s="5" t="s">
         <v>13</v>
@@ -4230,7 +4227,7 @@
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B482" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C482" s="5" t="s">
         <v>13</v>
@@ -4238,23 +4235,23 @@
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B483" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C483" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A484" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B484" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C484" s="5" t="s">
-        <v>13</v>
+      <c r="B484" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B485" s="3" t="s">
-        <v>4</v>
+      <c r="A485" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B485" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C485" s="5" t="s">
         <v>13</v>
@@ -4262,7 +4259,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B486" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C486" s="5" t="s">
         <v>13</v>
@@ -4270,7 +4267,7 @@
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B487" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C487" s="5" t="s">
         <v>13</v>
@@ -4278,7 +4275,7 @@
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B488" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C488" s="5" t="s">
         <v>13</v>
@@ -4286,7 +4283,7 @@
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B489" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C489" s="5" t="s">
         <v>13</v>
@@ -4294,7 +4291,7 @@
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B490" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C490" s="5" t="s">
         <v>13</v>
@@ -4302,7 +4299,7 @@
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B491" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C491" s="5" t="s">
         <v>13</v>
@@ -4310,16 +4307,104 @@
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B492" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C492" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B493" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C493" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B494" s="3">
+      <c r="B494" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="495" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A495" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B495" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C495" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="496" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B496" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C496" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="497" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B497" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C497" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="498" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B498" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C498" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="499" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B499" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C499" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="500" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B500" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C500" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="501" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B501" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C501" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="502" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B502" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C502" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="503" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B503" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="504" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B504" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="505" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B505" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\03aioveu-Day\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C1B7CB8-49A8-450A-9CD6-9F0213664532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9B7D914-1CB5-4694-B7F7-9474B4A49054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -474,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C505"/>
+  <dimension ref="A1:C516"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -562,7 +562,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -732,7 +732,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -817,7 +817,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -902,7 +902,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -987,7 +987,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1055,9 +1055,6 @@
     <row r="76" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B76" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C76" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
@@ -1075,7 +1072,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1143,6 +1140,9 @@
     <row r="87" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B87" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.2">
@@ -1160,7 +1160,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1245,7 +1245,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1330,7 +1330,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1398,9 +1398,6 @@
     <row r="120" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B120" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C120" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.2">
@@ -1418,7 +1415,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1506,7 +1503,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1574,6 +1571,9 @@
     <row r="142" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B142" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C142" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.2">
@@ -1591,7 +1591,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1676,7 +1676,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1761,7 +1761,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1846,7 +1846,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1914,9 +1914,6 @@
     <row r="186" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B186" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C186" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.2">
@@ -1934,7 +1931,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2022,7 +2019,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2098,9 +2095,6 @@
     <row r="209" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B209" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="C209" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.2">
@@ -2113,7 +2107,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2189,6 +2183,9 @@
     <row r="220" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B220" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="C220" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.2">
@@ -2201,7 +2198,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2289,7 +2286,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2377,7 +2374,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2465,7 +2462,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2553,7 +2550,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2621,6 +2618,9 @@
     <row r="274" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B274" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C274" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.2">
@@ -2638,7 +2638,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2699,7 +2699,9 @@
       <c r="B284" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C284" s="6"/>
+      <c r="C284" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B285" s="3" t="s">
@@ -2715,10 +2717,13 @@
       <c r="B287" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C287" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2779,16 +2784,11 @@
       <c r="B295" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C295" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C295" s="6"/>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B296" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C296" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.2">
@@ -2800,13 +2800,10 @@
       <c r="B298" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C298" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2894,7 +2891,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -2982,7 +2979,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3050,6 +3047,9 @@
     <row r="329" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B329" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C329" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.2">
@@ -3067,7 +3067,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3152,7 +3152,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3225,9 +3225,6 @@
     <row r="352" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B352" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="C352" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.2">
@@ -3240,7 +3237,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3301,7 +3298,9 @@
       <c r="B361" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C361" s="6"/>
+      <c r="C361" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B362" s="3" t="s">
@@ -3311,16 +3310,22 @@
     <row r="363" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B363" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="C363" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B364" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C364" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3381,9 +3386,7 @@
       <c r="B372" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C372" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C372" s="6"/>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B373" s="3" t="s">
@@ -3399,13 +3402,10 @@
       <c r="B375" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C375" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3473,9 +3473,6 @@
     <row r="384" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B384" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C384" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.2">
@@ -3493,7 +3490,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3561,6 +3558,9 @@
     <row r="395" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B395" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C395" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.2">
@@ -3578,7 +3578,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3657,10 +3657,13 @@
       <c r="B408" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C408" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3739,13 +3742,10 @@
       <c r="B419" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C419" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3813,9 +3813,6 @@
     <row r="428" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B428" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C428" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.2">
@@ -3833,7 +3830,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3854,19 +3851,25 @@
       <c r="B433" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C433" s="6"/>
+      <c r="C433" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B434" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C434" s="6"/>
+      <c r="C434" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B435" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C435" s="6"/>
+      <c r="C435" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B436" s="3" t="s">
@@ -3888,11 +3891,16 @@
       <c r="B438" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C438" s="6"/>
+      <c r="C438" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B439" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C439" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.2">
@@ -3904,10 +3912,13 @@
       <c r="B441" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C441" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -3928,25 +3939,19 @@
       <c r="B444" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C444" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C444" s="6"/>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B445" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C445" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C445" s="6"/>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B446" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C446" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C446" s="6"/>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B447" s="3" t="s">
@@ -3968,16 +3973,11 @@
       <c r="B449" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C449" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C449" s="6"/>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B450" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C450" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.2">
@@ -3989,13 +3989,10 @@
       <c r="B452" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C452" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4083,7 +4080,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4151,6 +4148,9 @@
     <row r="472" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B472" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C472" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.2">
@@ -4168,7 +4168,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4237,9 +4237,6 @@
       <c r="B483" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C483" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B484" s="3" t="s">
@@ -4247,19 +4244,19 @@
       </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A485" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B485" s="7" t="s">
-        <v>3</v>
+      <c r="B485" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C485" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B486" s="3" t="s">
-        <v>4</v>
+      <c r="A486" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B486" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C486" s="5" t="s">
         <v>13</v>
@@ -4267,7 +4264,7 @@
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B487" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C487" s="5" t="s">
         <v>13</v>
@@ -4275,7 +4272,7 @@
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B488" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C488" s="5" t="s">
         <v>13</v>
@@ -4283,7 +4280,7 @@
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B489" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C489" s="5" t="s">
         <v>13</v>
@@ -4291,7 +4288,7 @@
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B490" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C490" s="5" t="s">
         <v>13</v>
@@ -4299,7 +4296,7 @@
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B491" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C491" s="5" t="s">
         <v>13</v>
@@ -4307,7 +4304,7 @@
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B492" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C492" s="5" t="s">
         <v>13</v>
@@ -4315,7 +4312,7 @@
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B493" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C493" s="5" t="s">
         <v>13</v>
@@ -4323,88 +4320,176 @@
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B494" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C494" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A495" s="4">
+      <c r="B495" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="496" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A496" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B496" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C496" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="497" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B497" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C497" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="498" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B498" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C498" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="499" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B499" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C499" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="500" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B500" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C500" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="501" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B501" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C501" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="502" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B502" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C502" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="503" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B503" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C503" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="504" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B504" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C504" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="505" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B505" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="506" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A506" s="4">
         <v>46042</v>
       </c>
-      <c r="B495" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C495" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="496" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B496" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C496" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="497" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B497" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C497" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="498" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B498" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C498" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="499" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B499" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C499" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="500" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B500" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C500" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="501" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B501" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C501" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="502" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B502" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C502" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="503" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B503" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="504" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B504" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="505" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B505" s="3">
+      <c r="B506" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C506" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="507" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B507" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C507" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="508" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B508" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C508" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="509" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B509" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C509" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="510" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B510" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C510" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="511" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B511" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C511" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="512" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B512" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C512" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="513" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B513" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C513" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="514" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B514" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="515" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B515" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="516" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B516" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\03aioveu-Day\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9B7D914-1CB5-4694-B7F7-9474B4A49054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FC53BA8-AAB8-4924-AAC0-22E8DFA8CC8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -474,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C516"/>
+  <dimension ref="A1:C527"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -562,7 +562,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -732,7 +732,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -817,7 +817,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -902,7 +902,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -987,7 +987,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1072,7 +1072,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1140,9 +1140,6 @@
     <row r="87" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B87" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C87" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.2">
@@ -1160,7 +1157,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1228,6 +1225,9 @@
     <row r="98" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B98" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.2">
@@ -1245,7 +1245,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1330,7 +1330,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1415,7 +1415,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1483,9 +1483,6 @@
     <row r="131" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B131" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C131" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.2">
@@ -1503,7 +1500,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1591,7 +1588,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1659,6 +1656,9 @@
     <row r="153" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B153" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C153" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.2">
@@ -1676,7 +1676,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1761,7 +1761,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1846,7 +1846,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1931,7 +1931,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -1999,9 +1999,6 @@
     <row r="197" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B197" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C197" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.2">
@@ -2019,7 +2016,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2107,7 +2104,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2183,9 +2180,6 @@
     <row r="220" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B220" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="C220" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.2">
@@ -2198,7 +2192,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2274,6 +2268,9 @@
     <row r="231" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B231" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="C231" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.2">
@@ -2286,7 +2283,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2374,7 +2371,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2462,7 +2459,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2550,7 +2547,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2638,7 +2635,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2706,6 +2703,9 @@
     <row r="285" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B285" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C285" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.2">
@@ -2723,7 +2723,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2784,7 +2784,9 @@
       <c r="B295" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C295" s="6"/>
+      <c r="C295" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B296" s="3" t="s">
@@ -2800,10 +2802,13 @@
       <c r="B298" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C298" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2864,16 +2869,11 @@
       <c r="B306" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C306" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C306" s="6"/>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B307" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C307" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.2">
@@ -2885,13 +2885,10 @@
       <c r="B309" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C309" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -2979,7 +2976,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3067,7 +3064,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3135,6 +3132,9 @@
     <row r="340" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B340" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C340" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.2">
@@ -3152,7 +3152,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3237,7 +3237,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3310,9 +3310,6 @@
     <row r="363" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B363" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="C363" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.2">
@@ -3325,7 +3322,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3386,7 +3383,9 @@
       <c r="B372" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C372" s="6"/>
+      <c r="C372" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B373" s="3" t="s">
@@ -3396,16 +3395,22 @@
     <row r="374" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B374" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="C374" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B375" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C375" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3466,9 +3471,7 @@
       <c r="B383" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C383" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C383" s="6"/>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B384" s="3" t="s">
@@ -3484,13 +3487,10 @@
       <c r="B386" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C386" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3558,9 +3558,6 @@
     <row r="395" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B395" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C395" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.2">
@@ -3578,7 +3575,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3646,6 +3643,9 @@
     <row r="406" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B406" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C406" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.2">
@@ -3663,7 +3663,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3742,10 +3742,13 @@
       <c r="B419" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C419" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3824,13 +3827,10 @@
       <c r="B430" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C430" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3898,9 +3898,6 @@
     <row r="439" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B439" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C439" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.2">
@@ -3918,7 +3915,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -3939,19 +3936,25 @@
       <c r="B444" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C444" s="6"/>
+      <c r="C444" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B445" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C445" s="6"/>
+      <c r="C445" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B446" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C446" s="6"/>
+      <c r="C446" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B447" s="3" t="s">
@@ -3973,11 +3976,16 @@
       <c r="B449" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C449" s="6"/>
+      <c r="C449" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B450" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C450" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.2">
@@ -3989,10 +3997,13 @@
       <c r="B452" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C452" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4013,25 +4024,19 @@
       <c r="B455" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C455" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C455" s="6"/>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B456" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C456" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C456" s="6"/>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B457" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C457" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C457" s="6"/>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B458" s="3" t="s">
@@ -4053,16 +4058,11 @@
       <c r="B460" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C460" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C460" s="6"/>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B461" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C461" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.2">
@@ -4074,13 +4074,10 @@
       <c r="B463" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C463" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4168,7 +4165,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4236,6 +4233,9 @@
     <row r="483" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B483" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C483" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.2">
@@ -4253,7 +4253,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4322,9 +4322,6 @@
       <c r="B494" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C494" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B495" s="3" t="s">
@@ -4332,19 +4329,19 @@
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A496" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B496" s="7" t="s">
-        <v>3</v>
+      <c r="B496" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C496" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B497" s="3" t="s">
-        <v>4</v>
+      <c r="A497" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B497" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C497" s="5" t="s">
         <v>13</v>
@@ -4352,7 +4349,7 @@
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B498" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C498" s="5" t="s">
         <v>13</v>
@@ -4360,7 +4357,7 @@
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B499" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C499" s="5" t="s">
         <v>13</v>
@@ -4368,7 +4365,7 @@
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B500" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C500" s="5" t="s">
         <v>13</v>
@@ -4376,7 +4373,7 @@
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B501" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C501" s="5" t="s">
         <v>13</v>
@@ -4384,7 +4381,7 @@
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B502" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C502" s="5" t="s">
         <v>13</v>
@@ -4392,7 +4389,7 @@
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B503" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C503" s="5" t="s">
         <v>13</v>
@@ -4400,7 +4397,7 @@
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B504" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C504" s="5" t="s">
         <v>13</v>
@@ -4408,23 +4405,23 @@
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B505" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C505" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A506" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B506" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C506" s="5" t="s">
-        <v>13</v>
+      <c r="B506" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B507" s="3" t="s">
-        <v>4</v>
+      <c r="A507" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B507" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C507" s="5" t="s">
         <v>13</v>
@@ -4432,7 +4429,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B508" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C508" s="5" t="s">
         <v>13</v>
@@ -4440,7 +4437,7 @@
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B509" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C509" s="5" t="s">
         <v>13</v>
@@ -4448,7 +4445,7 @@
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B510" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C510" s="5" t="s">
         <v>13</v>
@@ -4456,7 +4453,7 @@
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B511" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C511" s="5" t="s">
         <v>13</v>
@@ -4464,32 +4461,120 @@
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B512" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C512" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="513" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B513" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C513" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="514" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B514" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="515" spans="2:3" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="C514" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="515" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B515" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="516" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B516" s="3">
+        <v>11</v>
+      </c>
+      <c r="C515" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="516" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B516" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="517" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A517" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B517" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C517" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="518" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B518" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C518" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="519" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B519" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C519" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="520" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B520" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C520" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="521" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B521" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C521" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="522" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B522" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C522" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="523" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B523" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C523" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="524" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B524" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C524" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="525" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B525" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="526" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B526" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="527" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B527" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\03aioveu-Day\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FC53BA8-AAB8-4924-AAC0-22E8DFA8CC8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BB8609F-732F-4D92-B5EB-6A7FB54113DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -474,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C527"/>
+  <dimension ref="A1:C538"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -562,7 +562,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -732,7 +732,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -817,7 +817,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -902,7 +902,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -987,7 +987,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1072,7 +1072,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1157,7 +1157,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1225,9 +1225,6 @@
     <row r="98" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B98" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C98" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.2">
@@ -1245,7 +1242,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1313,6 +1310,9 @@
     <row r="109" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B109" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.2">
@@ -1330,7 +1330,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1415,7 +1415,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1500,7 +1500,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1568,9 +1568,6 @@
     <row r="142" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B142" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C142" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.2">
@@ -1588,7 +1585,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1676,7 +1673,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1744,6 +1741,9 @@
     <row r="164" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B164" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C164" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.2">
@@ -1761,7 +1761,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1846,7 +1846,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1931,7 +1931,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2016,7 +2016,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2084,9 +2084,6 @@
     <row r="208" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B208" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C208" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.2">
@@ -2104,7 +2101,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2192,7 +2189,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2268,9 +2265,6 @@
     <row r="231" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B231" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="C231" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.2">
@@ -2283,7 +2277,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2359,6 +2353,9 @@
     <row r="242" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B242" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="C242" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.2">
@@ -2371,7 +2368,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2459,7 +2456,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2547,7 +2544,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2635,7 +2632,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2723,7 +2720,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2791,6 +2788,9 @@
     <row r="296" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B296" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C296" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.2">
@@ -2808,7 +2808,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2869,7 +2869,9 @@
       <c r="B306" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C306" s="6"/>
+      <c r="C306" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B307" s="3" t="s">
@@ -2885,10 +2887,13 @@
       <c r="B309" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C309" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -2949,16 +2954,11 @@
       <c r="B317" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C317" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C317" s="6"/>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B318" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C318" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.2">
@@ -2970,13 +2970,10 @@
       <c r="B320" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C320" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3064,7 +3061,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3152,7 +3149,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3220,6 +3217,9 @@
     <row r="351" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B351" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C351" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.2">
@@ -3237,7 +3237,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3322,7 +3322,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3395,9 +3395,6 @@
     <row r="374" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B374" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="C374" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.2">
@@ -3410,7 +3407,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3471,7 +3468,9 @@
       <c r="B383" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C383" s="6"/>
+      <c r="C383" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B384" s="3" t="s">
@@ -3481,16 +3480,22 @@
     <row r="385" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B385" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="C385" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B386" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C386" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3551,9 +3556,7 @@
       <c r="B394" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C394" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C394" s="6"/>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B395" s="3" t="s">
@@ -3569,13 +3572,10 @@
       <c r="B397" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C397" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3643,9 +3643,6 @@
     <row r="406" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B406" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C406" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.2">
@@ -3663,7 +3660,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3731,6 +3728,9 @@
     <row r="417" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B417" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C417" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.2">
@@ -3748,7 +3748,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3827,10 +3827,13 @@
       <c r="B430" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C430" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3909,13 +3912,10 @@
       <c r="B441" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C441" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -3983,9 +3983,6 @@
     <row r="450" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B450" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C450" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.2">
@@ -4003,7 +4000,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4024,19 +4021,25 @@
       <c r="B455" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C455" s="6"/>
+      <c r="C455" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B456" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C456" s="6"/>
+      <c r="C456" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B457" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C457" s="6"/>
+      <c r="C457" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B458" s="3" t="s">
@@ -4058,11 +4061,16 @@
       <c r="B460" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C460" s="6"/>
+      <c r="C460" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B461" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C461" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.2">
@@ -4074,10 +4082,13 @@
       <c r="B463" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C463" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4098,25 +4109,19 @@
       <c r="B466" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C466" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C466" s="6"/>
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B467" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C467" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C467" s="6"/>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B468" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C468" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C468" s="6"/>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B469" s="3" t="s">
@@ -4138,16 +4143,11 @@
       <c r="B471" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C471" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C471" s="6"/>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B472" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C472" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.2">
@@ -4159,13 +4159,10 @@
       <c r="B474" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C474" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4253,7 +4250,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4321,6 +4318,9 @@
     <row r="494" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B494" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C494" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.2">
@@ -4338,7 +4338,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4407,9 +4407,6 @@
       <c r="B505" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C505" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B506" s="3" t="s">
@@ -4417,19 +4414,19 @@
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A507" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B507" s="7" t="s">
-        <v>3</v>
+      <c r="B507" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C507" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B508" s="3" t="s">
-        <v>4</v>
+      <c r="A508" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B508" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C508" s="5" t="s">
         <v>13</v>
@@ -4437,7 +4434,7 @@
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B509" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C509" s="5" t="s">
         <v>13</v>
@@ -4445,7 +4442,7 @@
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B510" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C510" s="5" t="s">
         <v>13</v>
@@ -4453,7 +4450,7 @@
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B511" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C511" s="5" t="s">
         <v>13</v>
@@ -4461,7 +4458,7 @@
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B512" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C512" s="5" t="s">
         <v>13</v>
@@ -4469,7 +4466,7 @@
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B513" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C513" s="5" t="s">
         <v>13</v>
@@ -4477,7 +4474,7 @@
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B514" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C514" s="5" t="s">
         <v>13</v>
@@ -4485,7 +4482,7 @@
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B515" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C515" s="5" t="s">
         <v>13</v>
@@ -4493,23 +4490,23 @@
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B516" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C516" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A517" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B517" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C517" s="5" t="s">
-        <v>13</v>
+      <c r="B517" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B518" s="3" t="s">
-        <v>4</v>
+      <c r="A518" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B518" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C518" s="5" t="s">
         <v>13</v>
@@ -4517,7 +4514,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B519" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C519" s="5" t="s">
         <v>13</v>
@@ -4525,7 +4522,7 @@
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B520" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C520" s="5" t="s">
         <v>13</v>
@@ -4533,7 +4530,7 @@
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B521" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C521" s="5" t="s">
         <v>13</v>
@@ -4541,7 +4538,7 @@
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B522" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C522" s="5" t="s">
         <v>13</v>
@@ -4549,7 +4546,7 @@
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B523" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C523" s="5" t="s">
         <v>13</v>
@@ -4557,7 +4554,7 @@
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B524" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C524" s="5" t="s">
         <v>13</v>
@@ -4565,16 +4562,104 @@
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B525" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C525" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B526" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C526" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B527" s="3">
+      <c r="B527" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="528" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A528" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B528" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C528" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="529" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B529" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C529" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="530" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B530" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C530" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="531" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B531" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C531" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="532" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B532" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C532" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="533" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B533" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C533" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="534" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B534" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C534" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="535" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B535" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C535" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="536" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B536" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="537" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B537" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="538" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B538" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\03aioveu-Day\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BB8609F-732F-4D92-B5EB-6A7FB54113DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC0F11CF-F945-4A25-B2B4-A06FF744DE92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -474,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C538"/>
+  <dimension ref="A1:C549"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -562,7 +562,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -732,7 +732,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -817,7 +817,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -902,7 +902,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -987,7 +987,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1072,7 +1072,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1157,7 +1157,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1242,7 +1242,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1310,9 +1310,6 @@
     <row r="109" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B109" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C109" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.2">
@@ -1330,7 +1327,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1398,6 +1395,9 @@
     <row r="120" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B120" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C120" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.2">
@@ -1415,7 +1415,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1500,7 +1500,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1585,7 +1585,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1653,9 +1653,6 @@
     <row r="153" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B153" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C153" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.2">
@@ -1673,7 +1670,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1761,7 +1758,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1829,6 +1826,9 @@
     <row r="175" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B175" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C175" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.2">
@@ -1846,7 +1846,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1931,7 +1931,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2016,7 +2016,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2101,7 +2101,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2169,9 +2169,6 @@
     <row r="219" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B219" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C219" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.2">
@@ -2189,7 +2186,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2277,7 +2274,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2353,9 +2350,6 @@
     <row r="242" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B242" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="C242" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.2">
@@ -2368,7 +2362,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2444,6 +2438,9 @@
     <row r="253" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B253" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="C253" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.2">
@@ -2456,7 +2453,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2544,7 +2541,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2632,7 +2629,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2720,7 +2717,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2808,7 +2805,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2876,6 +2873,9 @@
     <row r="307" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B307" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C307" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.2">
@@ -2893,7 +2893,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -2954,7 +2954,9 @@
       <c r="B317" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C317" s="6"/>
+      <c r="C317" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B318" s="3" t="s">
@@ -2970,10 +2972,13 @@
       <c r="B320" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C320" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3034,16 +3039,11 @@
       <c r="B328" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C328" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C328" s="6"/>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B329" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C329" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.2">
@@ -3055,13 +3055,10 @@
       <c r="B331" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C331" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3149,7 +3146,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3237,7 +3234,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3305,6 +3302,9 @@
     <row r="362" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B362" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C362" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.2">
@@ -3322,7 +3322,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3407,7 +3407,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3480,9 +3480,6 @@
     <row r="385" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B385" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="C385" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.2">
@@ -3495,7 +3492,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3556,7 +3553,9 @@
       <c r="B394" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C394" s="6"/>
+      <c r="C394" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B395" s="3" t="s">
@@ -3566,16 +3565,22 @@
     <row r="396" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B396" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="C396" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B397" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C397" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3636,9 +3641,7 @@
       <c r="B405" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C405" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C405" s="6"/>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B406" s="3" t="s">
@@ -3654,13 +3657,10 @@
       <c r="B408" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C408" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3728,9 +3728,6 @@
     <row r="417" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B417" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C417" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.2">
@@ -3748,7 +3745,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3816,6 +3813,9 @@
     <row r="428" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B428" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C428" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.2">
@@ -3833,7 +3833,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3912,10 +3912,13 @@
       <c r="B441" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C441" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -3994,13 +3997,10 @@
       <c r="B452" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C452" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4068,9 +4068,6 @@
     <row r="461" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B461" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C461" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.2">
@@ -4088,7 +4085,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4109,19 +4106,25 @@
       <c r="B466" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C466" s="6"/>
+      <c r="C466" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B467" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C467" s="6"/>
+      <c r="C467" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B468" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C468" s="6"/>
+      <c r="C468" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B469" s="3" t="s">
@@ -4143,11 +4146,16 @@
       <c r="B471" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C471" s="6"/>
+      <c r="C471" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B472" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C472" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.2">
@@ -4159,10 +4167,13 @@
       <c r="B474" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C474" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4183,25 +4194,19 @@
       <c r="B477" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C477" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C477" s="6"/>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B478" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C478" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C478" s="6"/>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B479" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C479" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C479" s="6"/>
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B480" s="3" t="s">
@@ -4223,16 +4228,11 @@
       <c r="B482" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C482" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C482" s="6"/>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B483" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C483" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.2">
@@ -4244,13 +4244,10 @@
       <c r="B485" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C485" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4338,7 +4335,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4406,6 +4403,9 @@
     <row r="505" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B505" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C505" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.2">
@@ -4423,7 +4423,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4492,9 +4492,6 @@
       <c r="B516" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C516" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B517" s="3" t="s">
@@ -4502,19 +4499,19 @@
       </c>
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A518" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B518" s="7" t="s">
-        <v>3</v>
+      <c r="B518" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C518" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B519" s="3" t="s">
-        <v>4</v>
+      <c r="A519" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B519" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C519" s="5" t="s">
         <v>13</v>
@@ -4522,7 +4519,7 @@
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B520" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C520" s="5" t="s">
         <v>13</v>
@@ -4530,7 +4527,7 @@
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B521" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C521" s="5" t="s">
         <v>13</v>
@@ -4538,7 +4535,7 @@
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B522" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C522" s="5" t="s">
         <v>13</v>
@@ -4546,7 +4543,7 @@
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B523" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C523" s="5" t="s">
         <v>13</v>
@@ -4554,7 +4551,7 @@
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B524" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C524" s="5" t="s">
         <v>13</v>
@@ -4562,7 +4559,7 @@
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B525" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C525" s="5" t="s">
         <v>13</v>
@@ -4570,7 +4567,7 @@
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B526" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C526" s="5" t="s">
         <v>13</v>
@@ -4578,88 +4575,176 @@
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B527" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C527" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A528" s="4">
+      <c r="B528" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="529" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A529" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B529" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C529" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="530" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B530" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C530" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="531" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B531" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C531" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="532" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B532" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C532" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="533" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B533" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C533" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="534" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B534" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C534" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="535" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B535" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C535" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="536" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B536" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C536" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="537" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B537" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C537" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="538" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B538" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="539" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A539" s="4">
         <v>46042</v>
       </c>
-      <c r="B528" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C528" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="529" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B529" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C529" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="530" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B530" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C530" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="531" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B531" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C531" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="532" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B532" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C532" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="533" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B533" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C533" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="534" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B534" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C534" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="535" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B535" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C535" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="536" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B536" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="537" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B537" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="538" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B538" s="3">
+      <c r="B539" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C539" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="540" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B540" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C540" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="541" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B541" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C541" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="542" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B542" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C542" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="543" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B543" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C543" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="544" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B544" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C544" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="545" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B545" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C545" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="546" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B546" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C546" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="547" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B547" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="548" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B548" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="549" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B549" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\Github\03aioveu-Day\WinnerTakeAll\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC0F11CF-F945-4A25-B2B4-A06FF744DE92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3299508-F17F-43C1-BC95-3788205447D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,15 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1020" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -474,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C549"/>
+  <dimension ref="A1:C560"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -562,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -647,7 +644,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -732,7 +729,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -817,7 +814,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -902,7 +899,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -987,7 +984,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1072,7 +1069,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1157,7 +1154,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1242,7 +1239,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1327,7 +1324,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1395,9 +1392,6 @@
     <row r="120" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B120" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C120" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.2">
@@ -1415,7 +1409,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1483,6 +1477,9 @@
     <row r="131" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B131" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.2">
@@ -1500,7 +1497,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1585,7 +1582,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1670,7 +1667,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1738,9 +1735,6 @@
     <row r="164" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B164" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C164" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.2">
@@ -1758,7 +1752,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1846,7 +1840,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1914,6 +1908,9 @@
     <row r="186" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B186" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C186" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.2">
@@ -1931,7 +1928,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2016,7 +2013,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2101,7 +2098,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2186,7 +2183,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2254,9 +2251,6 @@
     <row r="230" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B230" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C230" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.2">
@@ -2274,7 +2268,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2362,7 +2356,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2438,9 +2432,6 @@
     <row r="253" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B253" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="C253" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.2">
@@ -2453,7 +2444,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2529,6 +2520,9 @@
     <row r="264" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B264" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="C264" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.2">
@@ -2541,7 +2535,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2629,7 +2623,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2717,7 +2711,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2805,7 +2799,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2893,7 +2887,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -2961,6 +2955,9 @@
     <row r="318" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B318" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C318" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.2">
@@ -2978,7 +2975,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3039,7 +3036,9 @@
       <c r="B328" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C328" s="6"/>
+      <c r="C328" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B329" s="3" t="s">
@@ -3055,10 +3054,13 @@
       <c r="B331" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C331" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3119,16 +3121,11 @@
       <c r="B339" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C339" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C339" s="6"/>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B340" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C340" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.2">
@@ -3140,13 +3137,10 @@
       <c r="B342" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C342" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3234,7 +3228,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3322,7 +3316,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3390,6 +3384,9 @@
     <row r="373" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B373" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C373" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.2">
@@ -3407,7 +3404,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3492,7 +3489,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3565,9 +3562,6 @@
     <row r="396" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B396" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="C396" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.2">
@@ -3580,7 +3574,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3641,7 +3635,9 @@
       <c r="B405" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C405" s="6"/>
+      <c r="C405" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B406" s="3" t="s">
@@ -3651,16 +3647,22 @@
     <row r="407" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B407" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="C407" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B408" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C408" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3721,9 +3723,7 @@
       <c r="B416" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C416" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C416" s="6"/>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B417" s="3" t="s">
@@ -3739,13 +3739,10 @@
       <c r="B419" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C419" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3813,9 +3810,6 @@
     <row r="428" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B428" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C428" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.2">
@@ -3833,7 +3827,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3901,6 +3895,9 @@
     <row r="439" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B439" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C439" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.2">
@@ -3918,7 +3915,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -3997,10 +3994,13 @@
       <c r="B452" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C452" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4079,13 +4079,10 @@
       <c r="B463" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C463" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4153,9 +4150,6 @@
     <row r="472" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B472" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C472" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.2">
@@ -4173,7 +4167,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4194,19 +4188,25 @@
       <c r="B477" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C477" s="6"/>
+      <c r="C477" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B478" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C478" s="6"/>
+      <c r="C478" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B479" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C479" s="6"/>
+      <c r="C479" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B480" s="3" t="s">
@@ -4228,11 +4228,16 @@
       <c r="B482" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C482" s="6"/>
+      <c r="C482" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B483" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C483" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.2">
@@ -4244,10 +4249,13 @@
       <c r="B485" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C485" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4268,25 +4276,19 @@
       <c r="B488" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C488" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C488" s="6"/>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B489" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C489" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C489" s="6"/>
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B490" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C490" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C490" s="6"/>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B491" s="3" t="s">
@@ -4308,16 +4310,11 @@
       <c r="B493" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C493" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C493" s="6"/>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B494" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C494" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.2">
@@ -4329,13 +4326,10 @@
       <c r="B496" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C496" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4423,7 +4417,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4491,6 +4485,9 @@
     <row r="516" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B516" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C516" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.2">
@@ -4508,7 +4505,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4577,9 +4574,6 @@
       <c r="B527" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C527" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B528" s="3" t="s">
@@ -4587,19 +4581,19 @@
       </c>
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A529" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B529" s="7" t="s">
-        <v>3</v>
+      <c r="B529" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C529" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B530" s="3" t="s">
-        <v>4</v>
+      <c r="A530" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B530" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C530" s="5" t="s">
         <v>13</v>
@@ -4607,7 +4601,7 @@
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B531" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C531" s="5" t="s">
         <v>13</v>
@@ -4615,7 +4609,7 @@
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B532" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C532" s="5" t="s">
         <v>13</v>
@@ -4623,7 +4617,7 @@
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B533" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C533" s="5" t="s">
         <v>13</v>
@@ -4631,7 +4625,7 @@
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B534" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C534" s="5" t="s">
         <v>13</v>
@@ -4639,7 +4633,7 @@
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B535" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C535" s="5" t="s">
         <v>13</v>
@@ -4647,7 +4641,7 @@
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B536" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C536" s="5" t="s">
         <v>13</v>
@@ -4655,7 +4649,7 @@
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B537" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C537" s="5" t="s">
         <v>13</v>
@@ -4663,23 +4657,23 @@
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B538" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C538" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A539" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B539" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C539" s="5" t="s">
-        <v>13</v>
+      <c r="B539" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B540" s="3" t="s">
-        <v>4</v>
+      <c r="A540" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B540" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C540" s="5" t="s">
         <v>13</v>
@@ -4687,7 +4681,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B541" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C541" s="5" t="s">
         <v>13</v>
@@ -4695,7 +4689,7 @@
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B542" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C542" s="5" t="s">
         <v>13</v>
@@ -4703,7 +4697,7 @@
     </row>
     <row r="543" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B543" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C543" s="5" t="s">
         <v>13</v>
@@ -4711,40 +4705,128 @@
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B544" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C544" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="545" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B545" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C545" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="546" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B546" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C546" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="547" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B547" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="548" spans="2:3" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="C547" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="548" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B548" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="549" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B549" s="3">
+        <v>11</v>
+      </c>
+      <c r="C548" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="549" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B549" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="550" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A550" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B550" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C550" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="551" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B551" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C551" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="552" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B552" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C552" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="553" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B553" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C553" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="554" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B554" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C554" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="555" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B555" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C555" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="556" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B556" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C556" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="557" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B557" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C557" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="558" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B558" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="559" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B559" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="560" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B560" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3299508-F17F-43C1-BC95-3788205447D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8C3469F-238D-475E-95AB-8FA1C058D4B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1020" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C560"/>
+  <dimension ref="A1:C571"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -493,7 +493,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
-        <v>46120</v>
+        <v>46143</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>3</v>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -644,7 +644,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -729,7 +729,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -814,7 +814,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -899,7 +899,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -984,7 +984,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1069,7 +1069,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1239,7 +1239,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1324,7 +1324,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1409,7 +1409,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1477,9 +1477,6 @@
     <row r="131" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B131" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C131" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.2">
@@ -1497,7 +1494,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1565,6 +1562,9 @@
     <row r="142" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B142" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C142" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.2">
@@ -1582,7 +1582,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1667,7 +1667,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1752,7 +1752,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1820,9 +1820,6 @@
     <row r="175" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B175" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C175" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.2">
@@ -1840,7 +1837,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1928,7 +1925,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -1996,6 +1993,9 @@
     <row r="197" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B197" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C197" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.2">
@@ -2013,7 +2013,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2098,7 +2098,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2183,7 +2183,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2268,7 +2268,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2336,9 +2336,6 @@
     <row r="241" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B241" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C241" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.2">
@@ -2356,7 +2353,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2444,7 +2441,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2520,9 +2517,6 @@
     <row r="264" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B264" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="C264" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.2">
@@ -2535,7 +2529,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2611,6 +2605,9 @@
     <row r="275" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B275" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="C275" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.2">
@@ -2623,7 +2620,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2711,7 +2708,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2799,7 +2796,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2887,7 +2884,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -2975,7 +2972,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3043,6 +3040,9 @@
     <row r="329" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B329" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C329" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.2">
@@ -3060,7 +3060,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3121,7 +3121,9 @@
       <c r="B339" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C339" s="6"/>
+      <c r="C339" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B340" s="3" t="s">
@@ -3137,10 +3139,13 @@
       <c r="B342" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C342" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3201,16 +3206,11 @@
       <c r="B350" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C350" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C350" s="6"/>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B351" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C351" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.2">
@@ -3222,13 +3222,10 @@
       <c r="B353" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C353" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3316,7 +3313,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3404,7 +3401,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3472,6 +3469,9 @@
     <row r="384" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B384" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C384" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.2">
@@ -3489,7 +3489,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3574,7 +3574,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3647,9 +3647,6 @@
     <row r="407" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B407" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="C407" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.2">
@@ -3662,7 +3659,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3723,7 +3720,9 @@
       <c r="B416" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C416" s="6"/>
+      <c r="C416" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B417" s="3" t="s">
@@ -3733,16 +3732,22 @@
     <row r="418" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B418" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="C418" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B419" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C419" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3803,9 +3808,7 @@
       <c r="B427" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C427" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C427" s="6"/>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B428" s="3" t="s">
@@ -3821,13 +3824,10 @@
       <c r="B430" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C430" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3895,9 +3895,6 @@
     <row r="439" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B439" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C439" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.2">
@@ -3915,7 +3912,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -3983,6 +3980,9 @@
     <row r="450" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B450" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C450" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.2">
@@ -4000,7 +4000,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4079,10 +4079,13 @@
       <c r="B463" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C463" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4161,13 +4164,10 @@
       <c r="B474" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C474" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4235,9 +4235,6 @@
     <row r="483" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B483" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C483" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.2">
@@ -4255,7 +4252,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4276,19 +4273,25 @@
       <c r="B488" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C488" s="6"/>
+      <c r="C488" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B489" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C489" s="6"/>
+      <c r="C489" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B490" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C490" s="6"/>
+      <c r="C490" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B491" s="3" t="s">
@@ -4310,11 +4313,16 @@
       <c r="B493" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C493" s="6"/>
+      <c r="C493" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B494" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C494" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.2">
@@ -4326,10 +4334,13 @@
       <c r="B496" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C496" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4350,25 +4361,19 @@
       <c r="B499" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C499" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C499" s="6"/>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B500" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C500" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C500" s="6"/>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B501" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C501" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C501" s="6"/>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B502" s="3" t="s">
@@ -4390,16 +4395,11 @@
       <c r="B504" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C504" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C504" s="6"/>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B505" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C505" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.2">
@@ -4411,13 +4411,10 @@
       <c r="B507" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C507" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4505,7 +4502,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4573,6 +4570,9 @@
     <row r="527" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B527" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C527" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.2">
@@ -4590,7 +4590,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4659,9 +4659,6 @@
       <c r="B538" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C538" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B539" s="3" t="s">
@@ -4669,19 +4666,19 @@
       </c>
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A540" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B540" s="7" t="s">
-        <v>3</v>
+      <c r="B540" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C540" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B541" s="3" t="s">
-        <v>4</v>
+      <c r="A541" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B541" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C541" s="5" t="s">
         <v>13</v>
@@ -4689,7 +4686,7 @@
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B542" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C542" s="5" t="s">
         <v>13</v>
@@ -4697,7 +4694,7 @@
     </row>
     <row r="543" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B543" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C543" s="5" t="s">
         <v>13</v>
@@ -4705,7 +4702,7 @@
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B544" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C544" s="5" t="s">
         <v>13</v>
@@ -4713,7 +4710,7 @@
     </row>
     <row r="545" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B545" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C545" s="5" t="s">
         <v>13</v>
@@ -4721,7 +4718,7 @@
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B546" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C546" s="5" t="s">
         <v>13</v>
@@ -4729,7 +4726,7 @@
     </row>
     <row r="547" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B547" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C547" s="5" t="s">
         <v>13</v>
@@ -4737,7 +4734,7 @@
     </row>
     <row r="548" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B548" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C548" s="5" t="s">
         <v>13</v>
@@ -4745,23 +4742,23 @@
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B549" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C549" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A550" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B550" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C550" s="5" t="s">
-        <v>13</v>
+      <c r="B550" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B551" s="3" t="s">
-        <v>4</v>
+      <c r="A551" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B551" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C551" s="5" t="s">
         <v>13</v>
@@ -4769,7 +4766,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B552" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C552" s="5" t="s">
         <v>13</v>
@@ -4777,7 +4774,7 @@
     </row>
     <row r="553" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B553" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C553" s="5" t="s">
         <v>13</v>
@@ -4785,7 +4782,7 @@
     </row>
     <row r="554" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B554" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C554" s="5" t="s">
         <v>13</v>
@@ -4793,7 +4790,7 @@
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B555" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C555" s="5" t="s">
         <v>13</v>
@@ -4801,7 +4798,7 @@
     </row>
     <row r="556" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B556" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C556" s="5" t="s">
         <v>13</v>
@@ -4809,7 +4806,7 @@
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B557" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C557" s="5" t="s">
         <v>13</v>
@@ -4817,16 +4814,104 @@
     </row>
     <row r="558" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B558" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C558" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="559" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B559" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C559" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B560" s="3">
+      <c r="B560" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="561" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A561" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B561" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C561" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="562" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B562" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C562" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="563" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B563" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C563" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="564" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B564" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C564" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="565" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B565" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C565" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="566" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B566" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C566" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="567" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B567" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C567" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="568" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B568" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C568" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="569" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B569" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="570" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B570" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="571" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B571" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8C3469F-238D-475E-95AB-8FA1C058D4B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{951E21F3-9035-4AD2-B7A4-83AE65BB0364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1060" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C571"/>
+  <dimension ref="A1:C582"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -644,7 +644,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -729,7 +729,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -814,7 +814,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -899,7 +899,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -984,7 +984,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1069,7 +1069,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1239,7 +1239,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1324,7 +1324,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1409,7 +1409,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1494,7 +1494,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1562,9 +1562,6 @@
     <row r="142" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B142" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C142" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.2">
@@ -1582,7 +1579,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1650,6 +1647,9 @@
     <row r="153" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B153" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C153" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.2">
@@ -1667,7 +1667,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1752,7 +1752,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1837,7 +1837,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1905,9 +1905,6 @@
     <row r="186" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B186" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C186" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.2">
@@ -1925,7 +1922,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2013,7 +2010,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2081,6 +2078,9 @@
     <row r="208" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B208" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C208" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.2">
@@ -2098,7 +2098,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2183,7 +2183,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2268,7 +2268,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2353,7 +2353,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2421,9 +2421,6 @@
     <row r="252" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B252" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C252" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.2">
@@ -2441,7 +2438,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2529,7 +2526,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2605,9 +2602,6 @@
     <row r="275" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B275" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="C275" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.2">
@@ -2620,7 +2614,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2696,6 +2690,9 @@
     <row r="286" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B286" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="C286" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.2">
@@ -2708,7 +2705,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2796,7 +2793,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2884,7 +2881,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -2972,7 +2969,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3060,7 +3057,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3128,6 +3125,9 @@
     <row r="340" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B340" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C340" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.2">
@@ -3145,7 +3145,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3206,7 +3206,9 @@
       <c r="B350" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C350" s="6"/>
+      <c r="C350" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B351" s="3" t="s">
@@ -3222,10 +3224,13 @@
       <c r="B353" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C353" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3286,16 +3291,11 @@
       <c r="B361" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C361" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C361" s="6"/>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B362" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C362" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.2">
@@ -3307,13 +3307,10 @@
       <c r="B364" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C364" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3401,7 +3398,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3489,7 +3486,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3557,6 +3554,9 @@
     <row r="395" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B395" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C395" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.2">
@@ -3574,7 +3574,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3659,7 +3659,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3732,9 +3732,6 @@
     <row r="418" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B418" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="C418" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.2">
@@ -3747,7 +3744,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3808,7 +3805,9 @@
       <c r="B427" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C427" s="6"/>
+      <c r="C427" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B428" s="3" t="s">
@@ -3818,16 +3817,22 @@
     <row r="429" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B429" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="C429" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B430" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C430" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3888,9 +3893,7 @@
       <c r="B438" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C438" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C438" s="6"/>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B439" s="3" t="s">
@@ -3906,13 +3909,10 @@
       <c r="B441" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C441" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -3980,9 +3980,6 @@
     <row r="450" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B450" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C450" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.2">
@@ -4000,7 +3997,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4068,6 +4065,9 @@
     <row r="461" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B461" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C461" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.2">
@@ -4085,7 +4085,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4164,10 +4164,13 @@
       <c r="B474" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C474" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4246,13 +4249,10 @@
       <c r="B485" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C485" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4320,9 +4320,6 @@
     <row r="494" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B494" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C494" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.2">
@@ -4340,7 +4337,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4361,19 +4358,25 @@
       <c r="B499" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C499" s="6"/>
+      <c r="C499" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B500" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C500" s="6"/>
+      <c r="C500" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B501" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C501" s="6"/>
+      <c r="C501" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B502" s="3" t="s">
@@ -4395,11 +4398,16 @@
       <c r="B504" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C504" s="6"/>
+      <c r="C504" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B505" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C505" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.2">
@@ -4411,10 +4419,13 @@
       <c r="B507" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C507" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4435,25 +4446,19 @@
       <c r="B510" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C510" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C510" s="6"/>
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B511" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C511" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C511" s="6"/>
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B512" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C512" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C512" s="6"/>
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B513" s="3" t="s">
@@ -4475,16 +4480,11 @@
       <c r="B515" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C515" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C515" s="6"/>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B516" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C516" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.2">
@@ -4496,13 +4496,10 @@
       <c r="B518" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C518" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4590,7 +4587,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4658,6 +4655,9 @@
     <row r="538" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B538" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C538" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.2">
@@ -4675,7 +4675,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4744,9 +4744,6 @@
       <c r="B549" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C549" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B550" s="3" t="s">
@@ -4754,19 +4751,19 @@
       </c>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A551" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B551" s="7" t="s">
-        <v>3</v>
+      <c r="B551" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C551" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B552" s="3" t="s">
-        <v>4</v>
+      <c r="A552" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B552" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C552" s="5" t="s">
         <v>13</v>
@@ -4774,7 +4771,7 @@
     </row>
     <row r="553" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B553" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C553" s="5" t="s">
         <v>13</v>
@@ -4782,7 +4779,7 @@
     </row>
     <row r="554" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B554" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C554" s="5" t="s">
         <v>13</v>
@@ -4790,7 +4787,7 @@
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B555" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C555" s="5" t="s">
         <v>13</v>
@@ -4798,7 +4795,7 @@
     </row>
     <row r="556" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B556" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C556" s="5" t="s">
         <v>13</v>
@@ -4806,7 +4803,7 @@
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B557" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C557" s="5" t="s">
         <v>13</v>
@@ -4814,7 +4811,7 @@
     </row>
     <row r="558" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B558" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C558" s="5" t="s">
         <v>13</v>
@@ -4822,7 +4819,7 @@
     </row>
     <row r="559" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B559" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C559" s="5" t="s">
         <v>13</v>
@@ -4830,23 +4827,23 @@
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B560" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C560" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A561" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B561" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C561" s="5" t="s">
-        <v>13</v>
+      <c r="B561" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="562" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B562" s="3" t="s">
-        <v>4</v>
+      <c r="A562" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B562" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C562" s="5" t="s">
         <v>13</v>
@@ -4854,7 +4851,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B563" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C563" s="5" t="s">
         <v>13</v>
@@ -4862,7 +4859,7 @@
     </row>
     <row r="564" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B564" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C564" s="5" t="s">
         <v>13</v>
@@ -4870,7 +4867,7 @@
     </row>
     <row r="565" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B565" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C565" s="5" t="s">
         <v>13</v>
@@ -4878,7 +4875,7 @@
     </row>
     <row r="566" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B566" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C566" s="5" t="s">
         <v>13</v>
@@ -4886,7 +4883,7 @@
     </row>
     <row r="567" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B567" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C567" s="5" t="s">
         <v>13</v>
@@ -4894,7 +4891,7 @@
     </row>
     <row r="568" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B568" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C568" s="5" t="s">
         <v>13</v>
@@ -4902,16 +4899,104 @@
     </row>
     <row r="569" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B569" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C569" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="570" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B570" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C570" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="571" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B571" s="3">
+      <c r="B571" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="572" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A572" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B572" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C572" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="573" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B573" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C573" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="574" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B574" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C574" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="575" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B575" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C575" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="576" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B576" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C576" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="577" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B577" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C577" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="578" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B578" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C578" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="579" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B579" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C579" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="580" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B580" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="581" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B581" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="582" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B582" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{951E21F3-9035-4AD2-B7A4-83AE65BB0364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A042375-9280-4ED6-8A29-465D7778FF66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1060" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1081" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C582"/>
+  <dimension ref="A1:C593"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -627,6 +627,9 @@
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B21" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -644,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -729,7 +732,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -814,7 +817,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -899,7 +902,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -984,7 +987,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1069,7 +1072,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1154,7 +1157,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1239,7 +1242,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1324,7 +1327,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1409,7 +1412,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1494,7 +1497,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1579,7 +1582,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1647,9 +1650,6 @@
     <row r="153" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B153" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C153" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.2">
@@ -1667,7 +1667,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1735,6 +1735,9 @@
     <row r="164" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B164" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C164" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.2">
@@ -1752,7 +1755,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1837,7 +1840,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1922,7 +1925,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -1990,9 +1993,6 @@
     <row r="197" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B197" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C197" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.2">
@@ -2010,7 +2010,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2098,7 +2098,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2166,6 +2166,9 @@
     <row r="219" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B219" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C219" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.2">
@@ -2183,7 +2186,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2268,7 +2271,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2353,7 +2356,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2438,7 +2441,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2506,9 +2509,6 @@
     <row r="263" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B263" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C263" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.2">
@@ -2526,7 +2526,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2614,7 +2614,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2690,9 +2690,6 @@
     <row r="286" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B286" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="C286" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.2">
@@ -2705,7 +2702,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2781,6 +2778,9 @@
     <row r="297" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B297" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="C297" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.2">
@@ -2793,7 +2793,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2881,7 +2881,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -2969,7 +2969,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3057,7 +3057,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3145,7 +3145,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3213,6 +3213,9 @@
     <row r="351" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B351" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C351" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.2">
@@ -3230,7 +3233,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3291,7 +3294,9 @@
       <c r="B361" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C361" s="6"/>
+      <c r="C361" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B362" s="3" t="s">
@@ -3307,10 +3312,13 @@
       <c r="B364" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C364" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3371,16 +3379,11 @@
       <c r="B372" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C372" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C372" s="6"/>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B373" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C373" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.2">
@@ -3392,13 +3395,10 @@
       <c r="B375" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C375" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3486,7 +3486,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3574,7 +3574,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3642,6 +3642,9 @@
     <row r="406" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B406" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C406" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.2">
@@ -3659,7 +3662,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3744,7 +3747,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3817,9 +3820,6 @@
     <row r="429" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B429" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="C429" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.2">
@@ -3832,7 +3832,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3893,7 +3893,9 @@
       <c r="B438" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C438" s="6"/>
+      <c r="C438" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B439" s="3" t="s">
@@ -3903,16 +3905,22 @@
     <row r="440" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B440" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="C440" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B441" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C441" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -3973,9 +3981,7 @@
       <c r="B449" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C449" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C449" s="6"/>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B450" s="3" t="s">
@@ -3991,13 +3997,10 @@
       <c r="B452" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C452" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4065,9 +4068,6 @@
     <row r="461" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B461" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C461" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.2">
@@ -4085,7 +4085,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4153,6 +4153,9 @@
     <row r="472" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B472" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C472" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.2">
@@ -4170,7 +4173,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4249,10 +4252,13 @@
       <c r="B485" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C485" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4331,13 +4337,10 @@
       <c r="B496" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C496" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4405,9 +4408,6 @@
     <row r="505" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B505" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C505" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.2">
@@ -4425,7 +4425,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4446,19 +4446,25 @@
       <c r="B510" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C510" s="6"/>
+      <c r="C510" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B511" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C511" s="6"/>
+      <c r="C511" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B512" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C512" s="6"/>
+      <c r="C512" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B513" s="3" t="s">
@@ -4480,11 +4486,16 @@
       <c r="B515" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C515" s="6"/>
+      <c r="C515" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B516" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C516" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.2">
@@ -4496,10 +4507,13 @@
       <c r="B518" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C518" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4520,25 +4534,19 @@
       <c r="B521" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C521" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C521" s="6"/>
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B522" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C522" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C522" s="6"/>
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B523" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C523" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C523" s="6"/>
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B524" s="3" t="s">
@@ -4560,16 +4568,11 @@
       <c r="B526" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C526" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C526" s="6"/>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B527" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C527" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.2">
@@ -4581,13 +4584,10 @@
       <c r="B529" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C529" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4675,7 +4675,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4743,6 +4743,9 @@
     <row r="549" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B549" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C549" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.2">
@@ -4760,7 +4763,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4829,9 +4832,6 @@
       <c r="B560" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C560" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B561" s="3" t="s">
@@ -4839,19 +4839,19 @@
       </c>
     </row>
     <row r="562" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A562" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B562" s="7" t="s">
-        <v>3</v>
+      <c r="B562" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C562" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B563" s="3" t="s">
-        <v>4</v>
+      <c r="A563" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B563" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C563" s="5" t="s">
         <v>13</v>
@@ -4859,7 +4859,7 @@
     </row>
     <row r="564" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B564" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C564" s="5" t="s">
         <v>13</v>
@@ -4867,7 +4867,7 @@
     </row>
     <row r="565" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B565" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C565" s="5" t="s">
         <v>13</v>
@@ -4875,7 +4875,7 @@
     </row>
     <row r="566" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B566" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C566" s="5" t="s">
         <v>13</v>
@@ -4883,7 +4883,7 @@
     </row>
     <row r="567" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B567" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C567" s="5" t="s">
         <v>13</v>
@@ -4891,7 +4891,7 @@
     </row>
     <row r="568" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B568" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C568" s="5" t="s">
         <v>13</v>
@@ -4899,7 +4899,7 @@
     </row>
     <row r="569" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B569" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C569" s="5" t="s">
         <v>13</v>
@@ -4907,7 +4907,7 @@
     </row>
     <row r="570" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B570" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C570" s="5" t="s">
         <v>13</v>
@@ -4915,23 +4915,23 @@
     </row>
     <row r="571" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B571" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C571" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A572" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B572" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C572" s="5" t="s">
-        <v>13</v>
+      <c r="B572" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="573" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B573" s="3" t="s">
-        <v>4</v>
+      <c r="A573" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B573" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C573" s="5" t="s">
         <v>13</v>
@@ -4939,7 +4939,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B574" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C574" s="5" t="s">
         <v>13</v>
@@ -4947,7 +4947,7 @@
     </row>
     <row r="575" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B575" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C575" s="5" t="s">
         <v>13</v>
@@ -4955,48 +4955,136 @@
     </row>
     <row r="576" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B576" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C576" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="577" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B577" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C577" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="578" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B578" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C578" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="579" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B579" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C579" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="580" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B580" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="581" spans="2:3" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="C580" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="581" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B581" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="582" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B582" s="3">
+        <v>11</v>
+      </c>
+      <c r="C581" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="582" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B582" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="583" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A583" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B583" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C583" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="584" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B584" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C584" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="585" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B585" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C585" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="586" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B586" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C586" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="587" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B587" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C587" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="588" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B588" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C588" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="589" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B589" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C589" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="590" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B590" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C590" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="591" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B591" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="592" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B592" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="593" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B593" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A042375-9280-4ED6-8A29-465D7778FF66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A220858A-98F7-42C6-B4EA-43BC64860DF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1081" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1102" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C593"/>
+  <dimension ref="A1:C604"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -715,6 +715,9 @@
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B32" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -732,7 +735,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -817,7 +820,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -902,7 +905,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -987,7 +990,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1072,7 +1075,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1157,7 +1160,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1242,7 +1245,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1327,7 +1330,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1412,7 +1415,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1497,7 +1500,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1582,7 +1585,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1667,7 +1670,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1735,9 +1738,6 @@
     <row r="164" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B164" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C164" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.2">
@@ -1755,7 +1755,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1823,6 +1823,9 @@
     <row r="175" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B175" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C175" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.2">
@@ -1840,7 +1843,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1925,7 +1928,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2010,7 +2013,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2078,9 +2081,6 @@
     <row r="208" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B208" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C208" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.2">
@@ -2098,7 +2098,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2186,7 +2186,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2254,6 +2254,9 @@
     <row r="230" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B230" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C230" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.2">
@@ -2271,7 +2274,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2356,7 +2359,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2441,7 +2444,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2526,7 +2529,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2594,9 +2597,6 @@
     <row r="274" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B274" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C274" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.2">
@@ -2614,7 +2614,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2702,7 +2702,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2778,9 +2778,6 @@
     <row r="297" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B297" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="C297" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.2">
@@ -2793,7 +2790,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2869,6 +2866,9 @@
     <row r="308" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B308" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="C308" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.2">
@@ -2881,7 +2881,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -2969,7 +2969,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3057,7 +3057,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3145,7 +3145,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3233,7 +3233,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3301,6 +3301,9 @@
     <row r="362" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B362" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C362" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.2">
@@ -3318,7 +3321,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3379,7 +3382,9 @@
       <c r="B372" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C372" s="6"/>
+      <c r="C372" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B373" s="3" t="s">
@@ -3395,10 +3400,13 @@
       <c r="B375" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C375" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3459,16 +3467,11 @@
       <c r="B383" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C383" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C383" s="6"/>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B384" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C384" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.2">
@@ -3480,13 +3483,10 @@
       <c r="B386" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C386" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3574,7 +3574,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3662,7 +3662,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3730,6 +3730,9 @@
     <row r="417" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B417" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C417" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.2">
@@ -3747,7 +3750,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3832,7 +3835,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3905,9 +3908,6 @@
     <row r="440" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B440" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="C440" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.2">
@@ -3920,7 +3920,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -3981,7 +3981,9 @@
       <c r="B449" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C449" s="6"/>
+      <c r="C449" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B450" s="3" t="s">
@@ -3991,16 +3993,22 @@
     <row r="451" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B451" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="C451" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B452" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C452" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4061,9 +4069,7 @@
       <c r="B460" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C460" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C460" s="6"/>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B461" s="3" t="s">
@@ -4079,13 +4085,10 @@
       <c r="B463" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C463" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4153,9 +4156,6 @@
     <row r="472" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B472" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C472" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.2">
@@ -4173,7 +4173,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4241,6 +4241,9 @@
     <row r="483" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B483" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C483" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.2">
@@ -4258,7 +4261,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4337,10 +4340,13 @@
       <c r="B496" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C496" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4419,13 +4425,10 @@
       <c r="B507" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C507" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4493,9 +4496,6 @@
     <row r="516" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B516" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C516" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.2">
@@ -4513,7 +4513,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4534,19 +4534,25 @@
       <c r="B521" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C521" s="6"/>
+      <c r="C521" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B522" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C522" s="6"/>
+      <c r="C522" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B523" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C523" s="6"/>
+      <c r="C523" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B524" s="3" t="s">
@@ -4568,11 +4574,16 @@
       <c r="B526" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C526" s="6"/>
+      <c r="C526" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B527" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C527" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.2">
@@ -4584,10 +4595,13 @@
       <c r="B529" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C529" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4608,25 +4622,19 @@
       <c r="B532" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C532" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C532" s="6"/>
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B533" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C533" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C533" s="6"/>
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B534" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C534" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C534" s="6"/>
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B535" s="3" t="s">
@@ -4648,16 +4656,11 @@
       <c r="B537" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C537" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C537" s="6"/>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B538" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C538" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.2">
@@ -4669,13 +4672,10 @@
       <c r="B540" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C540" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4763,7 +4763,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4831,6 +4831,9 @@
     <row r="560" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B560" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C560" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.2">
@@ -4848,7 +4851,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -4917,9 +4920,6 @@
       <c r="B571" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C571" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B572" s="3" t="s">
@@ -4927,19 +4927,19 @@
       </c>
     </row>
     <row r="573" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A573" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B573" s="7" t="s">
-        <v>3</v>
+      <c r="B573" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C573" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B574" s="3" t="s">
-        <v>4</v>
+      <c r="A574" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B574" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C574" s="5" t="s">
         <v>13</v>
@@ -4947,7 +4947,7 @@
     </row>
     <row r="575" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B575" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C575" s="5" t="s">
         <v>13</v>
@@ -4955,7 +4955,7 @@
     </row>
     <row r="576" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B576" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C576" s="5" t="s">
         <v>13</v>
@@ -4963,7 +4963,7 @@
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B577" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C577" s="5" t="s">
         <v>13</v>
@@ -4971,7 +4971,7 @@
     </row>
     <row r="578" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B578" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C578" s="5" t="s">
         <v>13</v>
@@ -4979,7 +4979,7 @@
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B579" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C579" s="5" t="s">
         <v>13</v>
@@ -4987,7 +4987,7 @@
     </row>
     <row r="580" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B580" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C580" s="5" t="s">
         <v>13</v>
@@ -4995,7 +4995,7 @@
     </row>
     <row r="581" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B581" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C581" s="5" t="s">
         <v>13</v>
@@ -5003,23 +5003,23 @@
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B582" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C582" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A583" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B583" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C583" s="5" t="s">
-        <v>13</v>
+      <c r="B583" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B584" s="3" t="s">
-        <v>4</v>
+      <c r="A584" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B584" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C584" s="5" t="s">
         <v>13</v>
@@ -5027,7 +5027,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B585" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C585" s="5" t="s">
         <v>13</v>
@@ -5035,7 +5035,7 @@
     </row>
     <row r="586" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B586" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C586" s="5" t="s">
         <v>13</v>
@@ -5043,7 +5043,7 @@
     </row>
     <row r="587" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B587" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C587" s="5" t="s">
         <v>13</v>
@@ -5051,7 +5051,7 @@
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B588" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C588" s="5" t="s">
         <v>13</v>
@@ -5059,7 +5059,7 @@
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B589" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C589" s="5" t="s">
         <v>13</v>
@@ -5067,7 +5067,7 @@
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B590" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C590" s="5" t="s">
         <v>13</v>
@@ -5075,16 +5075,104 @@
     </row>
     <row r="591" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B591" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C591" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="592" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B592" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="593" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B593" s="3">
+        <v>11</v>
+      </c>
+      <c r="C592" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="593" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B593" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="594" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A594" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B594" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C594" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="595" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B595" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C595" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="596" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B596" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C596" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="597" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B597" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C597" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="598" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B598" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C598" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="599" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B599" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C599" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="600" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B600" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C600" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="601" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B601" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C601" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="602" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B602" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="603" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B603" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="604" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B604" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A220858A-98F7-42C6-B4EA-43BC64860DF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F42EBB3-37EE-47AC-BD5E-2B95079473A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1102" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1123" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C604"/>
+  <dimension ref="A1:C615"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -735,7 +735,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -803,6 +803,9 @@
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B43" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
@@ -820,7 +823,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -905,7 +908,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -990,7 +993,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1075,7 +1078,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1160,7 +1163,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1245,7 +1248,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1330,7 +1333,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1415,7 +1418,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1500,7 +1503,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1585,7 +1588,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1670,7 +1673,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1755,7 +1758,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1823,9 +1826,6 @@
     <row r="175" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B175" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C175" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.2">
@@ -1843,7 +1843,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1911,6 +1911,9 @@
     <row r="186" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B186" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C186" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.2">
@@ -1928,7 +1931,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2013,7 +2016,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2098,7 +2101,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2166,9 +2169,6 @@
     <row r="219" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B219" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C219" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.2">
@@ -2186,7 +2186,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2274,7 +2274,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2342,6 +2342,9 @@
     <row r="241" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B241" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C241" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.2">
@@ -2359,7 +2362,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2444,7 +2447,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2529,7 +2532,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2614,7 +2617,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2682,9 +2685,6 @@
     <row r="285" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B285" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C285" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.2">
@@ -2702,7 +2702,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2790,7 +2790,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2866,9 +2866,6 @@
     <row r="308" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B308" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="C308" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.2">
@@ -2881,7 +2878,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -2957,6 +2954,9 @@
     <row r="319" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B319" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="C319" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.2">
@@ -2969,7 +2969,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3057,7 +3057,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3145,7 +3145,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3233,7 +3233,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3321,7 +3321,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3389,6 +3389,9 @@
     <row r="373" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B373" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C373" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.2">
@@ -3406,7 +3409,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3467,7 +3470,9 @@
       <c r="B383" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C383" s="6"/>
+      <c r="C383" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B384" s="3" t="s">
@@ -3483,10 +3488,13 @@
       <c r="B386" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C386" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3547,16 +3555,11 @@
       <c r="B394" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C394" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C394" s="6"/>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B395" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C395" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.2">
@@ -3568,13 +3571,10 @@
       <c r="B397" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C397" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3662,7 +3662,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3750,7 +3750,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3818,6 +3818,9 @@
     <row r="428" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B428" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C428" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.2">
@@ -3835,7 +3838,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3920,7 +3923,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -3993,9 +3996,6 @@
     <row r="451" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B451" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="C451" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.2">
@@ -4008,7 +4008,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4069,7 +4069,9 @@
       <c r="B460" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C460" s="6"/>
+      <c r="C460" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B461" s="3" t="s">
@@ -4079,16 +4081,22 @@
     <row r="462" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B462" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="C462" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B463" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C463" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4149,9 +4157,7 @@
       <c r="B471" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C471" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C471" s="6"/>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B472" s="3" t="s">
@@ -4167,13 +4173,10 @@
       <c r="B474" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C474" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4241,9 +4244,6 @@
     <row r="483" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B483" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C483" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.2">
@@ -4261,7 +4261,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4329,6 +4329,9 @@
     <row r="494" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B494" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C494" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.2">
@@ -4346,7 +4349,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4425,10 +4428,13 @@
       <c r="B507" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C507" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4507,13 +4513,10 @@
       <c r="B518" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C518" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4581,9 +4584,6 @@
     <row r="527" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B527" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C527" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.2">
@@ -4601,7 +4601,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4622,19 +4622,25 @@
       <c r="B532" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C532" s="6"/>
+      <c r="C532" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B533" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C533" s="6"/>
+      <c r="C533" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B534" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C534" s="6"/>
+      <c r="C534" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B535" s="3" t="s">
@@ -4656,11 +4662,16 @@
       <c r="B537" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C537" s="6"/>
+      <c r="C537" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B538" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C538" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.2">
@@ -4672,10 +4683,13 @@
       <c r="B540" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C540" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4696,25 +4710,19 @@
       <c r="B543" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C543" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C543" s="6"/>
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B544" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C544" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C544" s="6"/>
     </row>
     <row r="545" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B545" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C545" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C545" s="6"/>
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B546" s="3" t="s">
@@ -4736,16 +4744,11 @@
       <c r="B548" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C548" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C548" s="6"/>
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B549" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C549" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.2">
@@ -4757,13 +4760,10 @@
       <c r="B551" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C551" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4851,7 +4851,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -4919,6 +4919,9 @@
     <row r="571" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B571" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C571" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.2">
@@ -4936,7 +4939,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5005,9 +5008,6 @@
       <c r="B582" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C582" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B583" s="3" t="s">
@@ -5015,19 +5015,19 @@
       </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A584" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B584" s="7" t="s">
-        <v>3</v>
+      <c r="B584" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C584" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B585" s="3" t="s">
-        <v>4</v>
+      <c r="A585" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B585" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C585" s="5" t="s">
         <v>13</v>
@@ -5035,7 +5035,7 @@
     </row>
     <row r="586" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B586" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C586" s="5" t="s">
         <v>13</v>
@@ -5043,7 +5043,7 @@
     </row>
     <row r="587" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B587" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C587" s="5" t="s">
         <v>13</v>
@@ -5051,7 +5051,7 @@
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B588" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C588" s="5" t="s">
         <v>13</v>
@@ -5059,7 +5059,7 @@
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B589" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C589" s="5" t="s">
         <v>13</v>
@@ -5067,7 +5067,7 @@
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B590" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C590" s="5" t="s">
         <v>13</v>
@@ -5075,7 +5075,7 @@
     </row>
     <row r="591" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B591" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C591" s="5" t="s">
         <v>13</v>
@@ -5083,7 +5083,7 @@
     </row>
     <row r="592" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B592" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C592" s="5" t="s">
         <v>13</v>
@@ -5091,23 +5091,23 @@
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B593" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C593" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A594" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B594" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C594" s="5" t="s">
-        <v>13</v>
+      <c r="B594" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B595" s="3" t="s">
-        <v>4</v>
+      <c r="A595" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B595" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C595" s="5" t="s">
         <v>13</v>
@@ -5115,7 +5115,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B596" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C596" s="5" t="s">
         <v>13</v>
@@ -5123,7 +5123,7 @@
     </row>
     <row r="597" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B597" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C597" s="5" t="s">
         <v>13</v>
@@ -5131,7 +5131,7 @@
     </row>
     <row r="598" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B598" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C598" s="5" t="s">
         <v>13</v>
@@ -5139,7 +5139,7 @@
     </row>
     <row r="599" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B599" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C599" s="5" t="s">
         <v>13</v>
@@ -5147,7 +5147,7 @@
     </row>
     <row r="600" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B600" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C600" s="5" t="s">
         <v>13</v>
@@ -5155,7 +5155,7 @@
     </row>
     <row r="601" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B601" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C601" s="5" t="s">
         <v>13</v>
@@ -5163,16 +5163,104 @@
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B602" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C602" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="603" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B603" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C603" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B604" s="3">
+      <c r="B604" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="605" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A605" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B605" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C605" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="606" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B606" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C606" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="607" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B607" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C607" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="608" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B608" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C608" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="609" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B609" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C609" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="610" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B610" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C610" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="611" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B611" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C611" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="612" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B612" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C612" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="613" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B613" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="614" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B614" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="615" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B615" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F42EBB3-37EE-47AC-BD5E-2B95079473A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F9DC739-AFF0-4E7C-94D2-51939ABF7AAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1123" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1143" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C615"/>
+  <dimension ref="A1:C626"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -627,9 +627,6 @@
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B21" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -647,7 +644,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -735,7 +732,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -823,7 +820,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -891,6 +888,9 @@
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B54" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
@@ -908,7 +908,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1078,7 +1078,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1163,7 +1163,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1248,7 +1248,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1333,7 +1333,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1418,7 +1418,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1503,7 +1503,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1588,7 +1588,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1673,7 +1673,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1758,7 +1758,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1843,7 +1843,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1911,9 +1911,6 @@
     <row r="186" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B186" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C186" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.2">
@@ -1931,7 +1928,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -1999,6 +1996,9 @@
     <row r="197" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B197" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C197" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.2">
@@ -2016,7 +2016,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2101,7 +2101,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2186,7 +2186,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2254,9 +2254,6 @@
     <row r="230" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B230" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C230" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.2">
@@ -2274,7 +2271,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2362,7 +2359,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2430,6 +2427,9 @@
     <row r="252" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B252" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C252" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.2">
@@ -2447,7 +2447,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2532,7 +2532,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2617,7 +2617,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2702,7 +2702,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2770,9 +2770,6 @@
     <row r="296" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B296" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C296" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.2">
@@ -2790,7 +2787,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2878,7 +2875,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -2954,9 +2951,6 @@
     <row r="319" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B319" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="C319" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.2">
@@ -2969,7 +2963,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3045,6 +3039,9 @@
     <row r="330" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B330" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="C330" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.2">
@@ -3057,7 +3054,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3145,7 +3142,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3233,7 +3230,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3321,7 +3318,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3409,7 +3406,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3477,6 +3474,9 @@
     <row r="384" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B384" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C384" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.2">
@@ -3494,7 +3494,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3555,7 +3555,9 @@
       <c r="B394" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C394" s="6"/>
+      <c r="C394" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B395" s="3" t="s">
@@ -3571,10 +3573,13 @@
       <c r="B397" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C397" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3635,16 +3640,11 @@
       <c r="B405" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C405" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C405" s="6"/>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B406" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C406" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.2">
@@ -3656,13 +3656,10 @@
       <c r="B408" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C408" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3750,7 +3747,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3838,7 +3835,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3906,6 +3903,9 @@
     <row r="439" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B439" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C439" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.2">
@@ -3923,7 +3923,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4008,7 +4008,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4081,9 +4081,6 @@
     <row r="462" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B462" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="C462" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.2">
@@ -4096,7 +4093,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4157,7 +4154,9 @@
       <c r="B471" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C471" s="6"/>
+      <c r="C471" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B472" s="3" t="s">
@@ -4167,16 +4166,22 @@
     <row r="473" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B473" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="C473" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B474" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C474" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4237,9 +4242,7 @@
       <c r="B482" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C482" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C482" s="6"/>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B483" s="3" t="s">
@@ -4255,13 +4258,10 @@
       <c r="B485" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C485" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4329,9 +4329,6 @@
     <row r="494" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B494" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C494" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.2">
@@ -4349,7 +4346,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4417,6 +4414,9 @@
     <row r="505" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B505" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C505" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.2">
@@ -4434,7 +4434,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4513,10 +4513,13 @@
       <c r="B518" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C518" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4595,13 +4598,10 @@
       <c r="B529" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C529" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4669,9 +4669,6 @@
     <row r="538" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B538" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C538" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.2">
@@ -4689,7 +4686,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4710,19 +4707,25 @@
       <c r="B543" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C543" s="6"/>
+      <c r="C543" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B544" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C544" s="6"/>
+      <c r="C544" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="545" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B545" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C545" s="6"/>
+      <c r="C545" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B546" s="3" t="s">
@@ -4744,11 +4747,16 @@
       <c r="B548" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C548" s="6"/>
+      <c r="C548" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B549" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C549" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.2">
@@ -4760,10 +4768,13 @@
       <c r="B551" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C551" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4784,25 +4795,19 @@
       <c r="B554" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C554" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C554" s="6"/>
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B555" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C555" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C555" s="6"/>
     </row>
     <row r="556" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B556" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C556" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C556" s="6"/>
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B557" s="3" t="s">
@@ -4824,16 +4829,11 @@
       <c r="B559" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C559" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C559" s="6"/>
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B560" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C560" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.2">
@@ -4845,13 +4845,10 @@
       <c r="B562" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C562" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -4939,7 +4936,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5007,6 +5004,9 @@
     <row r="582" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B582" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C582" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.2">
@@ -5024,7 +5024,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5093,9 +5093,6 @@
       <c r="B593" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C593" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B594" s="3" t="s">
@@ -5103,19 +5100,19 @@
       </c>
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A595" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B595" s="7" t="s">
-        <v>3</v>
+      <c r="B595" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C595" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B596" s="3" t="s">
-        <v>4</v>
+      <c r="A596" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B596" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C596" s="5" t="s">
         <v>13</v>
@@ -5123,7 +5120,7 @@
     </row>
     <row r="597" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B597" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C597" s="5" t="s">
         <v>13</v>
@@ -5131,7 +5128,7 @@
     </row>
     <row r="598" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B598" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C598" s="5" t="s">
         <v>13</v>
@@ -5139,7 +5136,7 @@
     </row>
     <row r="599" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B599" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C599" s="5" t="s">
         <v>13</v>
@@ -5147,7 +5144,7 @@
     </row>
     <row r="600" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B600" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C600" s="5" t="s">
         <v>13</v>
@@ -5155,7 +5152,7 @@
     </row>
     <row r="601" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B601" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C601" s="5" t="s">
         <v>13</v>
@@ -5163,7 +5160,7 @@
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B602" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C602" s="5" t="s">
         <v>13</v>
@@ -5171,7 +5168,7 @@
     </row>
     <row r="603" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B603" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C603" s="5" t="s">
         <v>13</v>
@@ -5179,23 +5176,23 @@
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B604" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C604" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A605" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B605" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C605" s="5" t="s">
-        <v>13</v>
+      <c r="B605" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B606" s="3" t="s">
-        <v>4</v>
+      <c r="A606" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B606" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C606" s="5" t="s">
         <v>13</v>
@@ -5203,7 +5200,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B607" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C607" s="5" t="s">
         <v>13</v>
@@ -5211,56 +5208,144 @@
     </row>
     <row r="608" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B608" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C608" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="609" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B609" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C609" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="610" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B610" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C610" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="611" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B611" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C611" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="612" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B612" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C612" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="613" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B613" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="614" spans="2:3" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="C613" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="614" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B614" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="615" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B615" s="3">
+        <v>11</v>
+      </c>
+      <c r="C614" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="615" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B615" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="616" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A616" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B616" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C616" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="617" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B617" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C617" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="618" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B618" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C618" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="619" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B619" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C619" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="620" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B620" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C620" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="621" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B621" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C621" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="622" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B622" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C622" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="623" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B623" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C623" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="624" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B624" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="625" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B625" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="626" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B626" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F9DC739-AFF0-4E7C-94D2-51939ABF7AAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42D01126-94DF-4399-8B0C-799C2522F6F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1143" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1164" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C626"/>
+  <dimension ref="A1:C637"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -627,6 +627,9 @@
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B21" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -644,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -712,9 +715,6 @@
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B32" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -732,7 +732,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -820,7 +820,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -908,7 +908,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -976,6 +976,9 @@
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B65" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
@@ -993,7 +996,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1078,7 +1081,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1163,7 +1166,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1248,7 +1251,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1333,7 +1336,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1418,7 +1421,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1503,7 +1506,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1588,7 +1591,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1673,7 +1676,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1758,7 +1761,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1843,7 +1846,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1928,7 +1931,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -1996,9 +1999,6 @@
     <row r="197" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B197" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C197" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.2">
@@ -2016,7 +2016,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2084,6 +2084,9 @@
     <row r="208" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B208" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C208" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.2">
@@ -2101,7 +2104,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2186,7 +2189,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2271,7 +2274,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2339,9 +2342,6 @@
     <row r="241" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B241" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C241" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.2">
@@ -2359,7 +2359,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2447,7 +2447,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2515,6 +2515,9 @@
     <row r="263" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B263" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C263" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.2">
@@ -2532,7 +2535,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2617,7 +2620,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2702,7 +2705,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2787,7 +2790,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2855,9 +2858,6 @@
     <row r="307" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B307" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C307" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.2">
@@ -2875,7 +2875,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -2963,7 +2963,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3039,9 +3039,6 @@
     <row r="330" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B330" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="C330" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.2">
@@ -3054,7 +3051,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3130,6 +3127,9 @@
     <row r="341" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B341" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="C341" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.2">
@@ -3142,7 +3142,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3230,7 +3230,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3318,7 +3318,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3406,7 +3406,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3494,7 +3494,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3562,6 +3562,9 @@
     <row r="395" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B395" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C395" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.2">
@@ -3579,7 +3582,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3640,7 +3643,9 @@
       <c r="B405" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C405" s="6"/>
+      <c r="C405" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B406" s="3" t="s">
@@ -3656,10 +3661,13 @@
       <c r="B408" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C408" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3720,16 +3728,11 @@
       <c r="B416" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C416" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C416" s="6"/>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B417" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C417" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.2">
@@ -3741,13 +3744,10 @@
       <c r="B419" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C419" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3835,7 +3835,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3923,7 +3923,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -3991,6 +3991,9 @@
     <row r="450" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B450" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C450" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.2">
@@ -4008,7 +4011,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4093,7 +4096,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4166,9 +4169,6 @@
     <row r="473" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B473" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="C473" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.2">
@@ -4181,7 +4181,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4242,7 +4242,9 @@
       <c r="B482" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C482" s="6"/>
+      <c r="C482" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B483" s="3" t="s">
@@ -4252,16 +4254,22 @@
     <row r="484" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B484" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="C484" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B485" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C485" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4322,9 +4330,7 @@
       <c r="B493" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C493" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C493" s="6"/>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B494" s="3" t="s">
@@ -4340,13 +4346,10 @@
       <c r="B496" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C496" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4414,9 +4417,6 @@
     <row r="505" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B505" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C505" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.2">
@@ -4434,7 +4434,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4502,6 +4502,9 @@
     <row r="516" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B516" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C516" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.2">
@@ -4519,7 +4522,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4598,10 +4601,13 @@
       <c r="B529" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C529" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4680,13 +4686,10 @@
       <c r="B540" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C540" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4754,9 +4757,6 @@
     <row r="549" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B549" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C549" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.2">
@@ -4774,7 +4774,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4795,19 +4795,25 @@
       <c r="B554" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C554" s="6"/>
+      <c r="C554" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B555" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C555" s="6"/>
+      <c r="C555" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="556" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B556" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C556" s="6"/>
+      <c r="C556" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B557" s="3" t="s">
@@ -4829,11 +4835,16 @@
       <c r="B559" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C559" s="6"/>
+      <c r="C559" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B560" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C560" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.2">
@@ -4845,10 +4856,13 @@
       <c r="B562" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C562" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -4869,25 +4883,19 @@
       <c r="B565" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C565" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C565" s="6"/>
     </row>
     <row r="566" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B566" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C566" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C566" s="6"/>
     </row>
     <row r="567" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B567" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C567" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C567" s="6"/>
     </row>
     <row r="568" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B568" s="3" t="s">
@@ -4909,16 +4917,11 @@
       <c r="B570" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C570" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C570" s="6"/>
     </row>
     <row r="571" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B571" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C571" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.2">
@@ -4930,13 +4933,10 @@
       <c r="B573" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C573" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5024,7 +5024,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5092,6 +5092,9 @@
     <row r="593" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B593" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C593" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.2">
@@ -5109,7 +5112,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5178,9 +5181,6 @@
       <c r="B604" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C604" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B605" s="3" t="s">
@@ -5188,19 +5188,19 @@
       </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A606" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B606" s="7" t="s">
-        <v>3</v>
+      <c r="B606" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C606" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B607" s="3" t="s">
-        <v>4</v>
+      <c r="A607" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B607" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C607" s="5" t="s">
         <v>13</v>
@@ -5208,7 +5208,7 @@
     </row>
     <row r="608" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B608" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C608" s="5" t="s">
         <v>13</v>
@@ -5216,7 +5216,7 @@
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B609" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C609" s="5" t="s">
         <v>13</v>
@@ -5224,7 +5224,7 @@
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B610" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C610" s="5" t="s">
         <v>13</v>
@@ -5232,7 +5232,7 @@
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B611" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C611" s="5" t="s">
         <v>13</v>
@@ -5240,7 +5240,7 @@
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B612" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C612" s="5" t="s">
         <v>13</v>
@@ -5248,7 +5248,7 @@
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B613" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C613" s="5" t="s">
         <v>13</v>
@@ -5256,7 +5256,7 @@
     </row>
     <row r="614" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B614" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C614" s="5" t="s">
         <v>13</v>
@@ -5264,23 +5264,23 @@
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B615" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C615" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A616" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B616" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C616" s="5" t="s">
-        <v>13</v>
+      <c r="B616" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B617" s="3" t="s">
-        <v>4</v>
+      <c r="A617" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B617" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C617" s="5" t="s">
         <v>13</v>
@@ -5288,7 +5288,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B618" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C618" s="5" t="s">
         <v>13</v>
@@ -5296,7 +5296,7 @@
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B619" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C619" s="5" t="s">
         <v>13</v>
@@ -5304,7 +5304,7 @@
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B620" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C620" s="5" t="s">
         <v>13</v>
@@ -5312,7 +5312,7 @@
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B621" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C621" s="5" t="s">
         <v>13</v>
@@ -5320,7 +5320,7 @@
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B622" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C622" s="5" t="s">
         <v>13</v>
@@ -5328,7 +5328,7 @@
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B623" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C623" s="5" t="s">
         <v>13</v>
@@ -5336,16 +5336,104 @@
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B624" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="625" spans="2:2" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="C624" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="625" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B625" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="626" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B626" s="3">
+        <v>11</v>
+      </c>
+      <c r="C625" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="626" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B626" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="627" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A627" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B627" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C627" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="628" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B628" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C628" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="629" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B629" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C629" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="630" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B630" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C630" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="631" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B631" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C631" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="632" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B632" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C632" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="633" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B633" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C633" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="634" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B634" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C634" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="635" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B635" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="636" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B636" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="637" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B637" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42D01126-94DF-4399-8B0C-799C2522F6F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA9B5F16-9DD1-4298-BE22-4FD0D30CDE31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1164" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C637"/>
+  <dimension ref="A1:C648"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -627,9 +627,6 @@
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B21" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -647,7 +644,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -715,6 +712,9 @@
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B32" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -732,7 +732,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -800,9 +800,6 @@
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B43" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
@@ -820,7 +817,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -908,7 +905,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -996,7 +993,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1064,6 +1061,9 @@
     <row r="76" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B76" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
@@ -1081,7 +1081,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1166,7 +1166,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1251,7 +1251,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1336,7 +1336,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1421,7 +1421,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1506,7 +1506,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1591,7 +1591,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1676,7 +1676,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1761,7 +1761,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1846,7 +1846,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1931,7 +1931,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2016,7 +2016,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2084,9 +2084,6 @@
     <row r="208" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B208" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C208" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.2">
@@ -2104,7 +2101,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2172,6 +2169,9 @@
     <row r="219" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B219" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C219" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.2">
@@ -2189,7 +2189,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2274,7 +2274,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2359,7 +2359,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2427,9 +2427,6 @@
     <row r="252" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B252" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C252" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.2">
@@ -2447,7 +2444,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2535,7 +2532,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2603,6 +2600,9 @@
     <row r="274" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B274" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C274" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.2">
@@ -2620,7 +2620,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2705,7 +2705,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2790,7 +2790,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2875,7 +2875,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -2943,9 +2943,6 @@
     <row r="318" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B318" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C318" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.2">
@@ -2963,7 +2960,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3051,7 +3048,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3127,9 +3124,6 @@
     <row r="341" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B341" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="C341" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.2">
@@ -3142,7 +3136,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3218,6 +3212,9 @@
     <row r="352" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B352" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="C352" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.2">
@@ -3230,7 +3227,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3318,7 +3315,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3406,7 +3403,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3494,7 +3491,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3582,7 +3579,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3650,6 +3647,9 @@
     <row r="406" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B406" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C406" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.2">
@@ -3667,7 +3667,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3728,7 +3728,9 @@
       <c r="B416" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C416" s="6"/>
+      <c r="C416" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B417" s="3" t="s">
@@ -3744,10 +3746,13 @@
       <c r="B419" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C419" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3808,16 +3813,11 @@
       <c r="B427" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C427" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C427" s="6"/>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B428" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C428" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.2">
@@ -3829,13 +3829,10 @@
       <c r="B430" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C430" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3923,7 +3920,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4011,7 +4008,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4079,6 +4076,9 @@
     <row r="461" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B461" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C461" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.2">
@@ -4096,7 +4096,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4181,7 +4181,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4254,9 +4254,6 @@
     <row r="484" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B484" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="C484" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.2">
@@ -4269,7 +4266,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4330,7 +4327,9 @@
       <c r="B493" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C493" s="6"/>
+      <c r="C493" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B494" s="3" t="s">
@@ -4340,16 +4339,22 @@
     <row r="495" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B495" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="C495" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B496" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C496" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4410,9 +4415,7 @@
       <c r="B504" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C504" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C504" s="6"/>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B505" s="3" t="s">
@@ -4428,13 +4431,10 @@
       <c r="B507" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C507" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4502,9 +4502,6 @@
     <row r="516" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B516" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C516" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.2">
@@ -4522,7 +4519,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4590,6 +4587,9 @@
     <row r="527" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B527" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C527" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.2">
@@ -4607,7 +4607,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4686,10 +4686,13 @@
       <c r="B540" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C540" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4768,13 +4771,10 @@
       <c r="B551" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C551" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4842,9 +4842,6 @@
     <row r="560" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B560" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C560" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.2">
@@ -4862,7 +4859,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -4883,19 +4880,25 @@
       <c r="B565" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C565" s="6"/>
+      <c r="C565" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="566" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B566" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C566" s="6"/>
+      <c r="C566" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="567" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B567" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C567" s="6"/>
+      <c r="C567" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="568" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B568" s="3" t="s">
@@ -4917,11 +4920,16 @@
       <c r="B570" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C570" s="6"/>
+      <c r="C570" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="571" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B571" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C571" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.2">
@@ -4933,10 +4941,13 @@
       <c r="B573" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C573" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -4957,25 +4968,19 @@
       <c r="B576" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C576" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C576" s="6"/>
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B577" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C577" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C577" s="6"/>
     </row>
     <row r="578" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B578" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C578" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C578" s="6"/>
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B579" s="3" t="s">
@@ -4997,16 +5002,11 @@
       <c r="B581" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C581" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C581" s="6"/>
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B582" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C582" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.2">
@@ -5018,13 +5018,10 @@
       <c r="B584" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C584" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5112,7 +5109,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5180,6 +5177,9 @@
     <row r="604" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B604" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C604" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.2">
@@ -5197,7 +5197,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5266,9 +5266,6 @@
       <c r="B615" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C615" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B616" s="3" t="s">
@@ -5276,19 +5273,19 @@
       </c>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A617" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B617" s="7" t="s">
-        <v>3</v>
+      <c r="B617" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C617" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B618" s="3" t="s">
-        <v>4</v>
+      <c r="A618" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B618" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C618" s="5" t="s">
         <v>13</v>
@@ -5296,7 +5293,7 @@
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B619" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C619" s="5" t="s">
         <v>13</v>
@@ -5304,7 +5301,7 @@
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B620" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C620" s="5" t="s">
         <v>13</v>
@@ -5312,7 +5309,7 @@
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B621" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C621" s="5" t="s">
         <v>13</v>
@@ -5320,7 +5317,7 @@
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B622" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C622" s="5" t="s">
         <v>13</v>
@@ -5328,7 +5325,7 @@
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B623" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C623" s="5" t="s">
         <v>13</v>
@@ -5336,7 +5333,7 @@
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B624" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C624" s="5" t="s">
         <v>13</v>
@@ -5344,7 +5341,7 @@
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B625" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C625" s="5" t="s">
         <v>13</v>
@@ -5352,23 +5349,23 @@
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B626" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C626" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A627" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B627" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C627" s="5" t="s">
-        <v>13</v>
+      <c r="B627" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B628" s="3" t="s">
-        <v>4</v>
+      <c r="A628" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B628" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C628" s="5" t="s">
         <v>13</v>
@@ -5376,7 +5373,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B629" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C629" s="5" t="s">
         <v>13</v>
@@ -5384,7 +5381,7 @@
     </row>
     <row r="630" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B630" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C630" s="5" t="s">
         <v>13</v>
@@ -5392,7 +5389,7 @@
     </row>
     <row r="631" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B631" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C631" s="5" t="s">
         <v>13</v>
@@ -5400,7 +5397,7 @@
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B632" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C632" s="5" t="s">
         <v>13</v>
@@ -5408,7 +5405,7 @@
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B633" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C633" s="5" t="s">
         <v>13</v>
@@ -5416,7 +5413,7 @@
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B634" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C634" s="5" t="s">
         <v>13</v>
@@ -5424,16 +5421,104 @@
     </row>
     <row r="635" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B635" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C635" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="636" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B636" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C636" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B637" s="3">
+      <c r="B637" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="638" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A638" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B638" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C638" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="639" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B639" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C639" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="640" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B640" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C640" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="641" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B641" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C641" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="642" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B642" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C642" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="643" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B643" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C643" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="644" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B644" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C644" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="645" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B645" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C645" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="646" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B646" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="647" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B647" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="648" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B648" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA9B5F16-9DD1-4298-BE22-4FD0D30CDE31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DB3F7DA-62EC-4105-9CC9-5978519C3C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1205" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C648"/>
+  <dimension ref="A1:C659"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -627,6 +627,9 @@
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B21" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -644,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -712,9 +715,6 @@
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B32" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -732,7 +732,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -800,6 +800,9 @@
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B43" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
@@ -817,7 +820,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -885,9 +888,6 @@
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B54" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
@@ -905,7 +905,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1081,7 +1081,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1149,6 +1149,9 @@
     <row r="87" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B87" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.2">
@@ -1166,7 +1169,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1251,7 +1254,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1336,7 +1339,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1421,7 +1424,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1506,7 +1509,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1591,7 +1594,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1676,7 +1679,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1761,7 +1764,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1846,7 +1849,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1931,7 +1934,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2016,7 +2019,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2101,7 +2104,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2169,9 +2172,6 @@
     <row r="219" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B219" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C219" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.2">
@@ -2189,7 +2189,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2257,6 +2257,9 @@
     <row r="230" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B230" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C230" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.2">
@@ -2274,7 +2277,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2359,7 +2362,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2444,7 +2447,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2512,9 +2515,6 @@
     <row r="263" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B263" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C263" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.2">
@@ -2532,7 +2532,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2620,7 +2620,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2688,6 +2688,9 @@
     <row r="285" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B285" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C285" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.2">
@@ -2705,7 +2708,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2790,7 +2793,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2875,7 +2878,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -2960,7 +2963,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3028,9 +3031,6 @@
     <row r="329" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B329" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C329" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.2">
@@ -3048,7 +3048,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3136,7 +3136,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3212,9 +3212,6 @@
     <row r="352" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B352" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="C352" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.2">
@@ -3227,7 +3224,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3303,6 +3300,9 @@
     <row r="363" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B363" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="C363" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.2">
@@ -3315,7 +3315,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3403,7 +3403,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3491,7 +3491,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3579,7 +3579,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3667,7 +3667,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3735,6 +3735,9 @@
     <row r="417" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B417" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C417" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.2">
@@ -3752,7 +3755,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3813,7 +3816,9 @@
       <c r="B427" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C427" s="6"/>
+      <c r="C427" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B428" s="3" t="s">
@@ -3829,10 +3834,13 @@
       <c r="B430" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C430" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3893,16 +3901,11 @@
       <c r="B438" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C438" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C438" s="6"/>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B439" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C439" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.2">
@@ -3914,13 +3917,10 @@
       <c r="B441" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C441" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4008,7 +4008,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4096,7 +4096,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4164,6 +4164,9 @@
     <row r="472" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B472" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C472" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.2">
@@ -4181,7 +4184,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4266,7 +4269,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4339,9 +4342,6 @@
     <row r="495" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B495" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="C495" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.2">
@@ -4354,7 +4354,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4415,7 +4415,9 @@
       <c r="B504" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C504" s="6"/>
+      <c r="C504" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B505" s="3" t="s">
@@ -4425,16 +4427,22 @@
     <row r="506" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B506" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="C506" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B507" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C507" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4495,9 +4503,7 @@
       <c r="B515" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C515" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C515" s="6"/>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B516" s="3" t="s">
@@ -4513,13 +4519,10 @@
       <c r="B518" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C518" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4587,9 +4590,6 @@
     <row r="527" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B527" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C527" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.2">
@@ -4607,7 +4607,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4675,6 +4675,9 @@
     <row r="538" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B538" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C538" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.2">
@@ -4692,7 +4695,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4771,10 +4774,13 @@
       <c r="B551" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C551" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4853,13 +4859,10 @@
       <c r="B562" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C562" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -4927,9 +4930,6 @@
     <row r="571" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B571" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C571" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.2">
@@ -4947,7 +4947,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -4968,19 +4968,25 @@
       <c r="B576" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C576" s="6"/>
+      <c r="C576" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B577" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C577" s="6"/>
+      <c r="C577" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="578" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B578" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C578" s="6"/>
+      <c r="C578" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B579" s="3" t="s">
@@ -5002,11 +5008,16 @@
       <c r="B581" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C581" s="6"/>
+      <c r="C581" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B582" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C582" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.2">
@@ -5018,10 +5029,13 @@
       <c r="B584" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C584" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5042,25 +5056,19 @@
       <c r="B587" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C587" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C587" s="6"/>
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B588" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C588" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C588" s="6"/>
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B589" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C589" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C589" s="6"/>
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B590" s="3" t="s">
@@ -5082,16 +5090,11 @@
       <c r="B592" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C592" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C592" s="6"/>
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B593" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C593" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.2">
@@ -5103,13 +5106,10 @@
       <c r="B595" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C595" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5197,7 +5197,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5265,6 +5265,9 @@
     <row r="615" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B615" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C615" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.2">
@@ -5282,7 +5285,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5351,9 +5354,6 @@
       <c r="B626" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C626" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B627" s="3" t="s">
@@ -5361,19 +5361,19 @@
       </c>
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A628" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B628" s="7" t="s">
-        <v>3</v>
+      <c r="B628" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C628" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B629" s="3" t="s">
-        <v>4</v>
+      <c r="A629" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B629" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C629" s="5" t="s">
         <v>13</v>
@@ -5381,7 +5381,7 @@
     </row>
     <row r="630" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B630" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C630" s="5" t="s">
         <v>13</v>
@@ -5389,7 +5389,7 @@
     </row>
     <row r="631" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B631" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C631" s="5" t="s">
         <v>13</v>
@@ -5397,7 +5397,7 @@
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B632" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C632" s="5" t="s">
         <v>13</v>
@@ -5405,7 +5405,7 @@
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B633" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C633" s="5" t="s">
         <v>13</v>
@@ -5413,7 +5413,7 @@
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B634" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C634" s="5" t="s">
         <v>13</v>
@@ -5421,7 +5421,7 @@
     </row>
     <row r="635" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B635" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C635" s="5" t="s">
         <v>13</v>
@@ -5429,7 +5429,7 @@
     </row>
     <row r="636" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B636" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C636" s="5" t="s">
         <v>13</v>
@@ -5437,23 +5437,23 @@
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B637" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C637" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A638" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B638" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C638" s="5" t="s">
-        <v>13</v>
+      <c r="B638" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B639" s="3" t="s">
-        <v>4</v>
+      <c r="A639" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B639" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C639" s="5" t="s">
         <v>13</v>
@@ -5461,64 +5461,152 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B640" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C640" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="641" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B641" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C641" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="642" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B642" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C642" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="643" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B643" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C643" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="644" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B644" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C644" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="645" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B645" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C645" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="646" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B646" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="647" spans="2:3" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="C646" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="647" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B647" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="648" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B648" s="3">
+        <v>11</v>
+      </c>
+      <c r="C647" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="648" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B648" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="649" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A649" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B649" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C649" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="650" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B650" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C650" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="651" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B651" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C651" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="652" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B652" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C652" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="653" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B653" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C653" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="654" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B654" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C654" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="655" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B655" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C655" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="656" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B656" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C656" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="657" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B657" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="658" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B658" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="659" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B659" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DB3F7DA-62EC-4105-9CC9-5978519C3C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CDD5F2E-5635-4B50-8681-6751B0FAB0D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1205" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C659"/>
+  <dimension ref="A1:C670"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -635,6 +635,9 @@
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B22" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -647,7 +650,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -715,6 +718,9 @@
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B32" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -732,7 +738,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -800,9 +806,6 @@
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B43" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
@@ -820,7 +823,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -888,6 +891,9 @@
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B54" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
@@ -905,7 +911,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -973,9 +979,6 @@
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B65" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C65" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
@@ -993,7 +996,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1081,7 +1084,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1169,7 +1172,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1237,6 +1240,9 @@
     <row r="98" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B98" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.2">
@@ -1254,7 +1260,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1339,7 +1345,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1424,7 +1430,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1509,7 +1515,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1594,7 +1600,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1679,7 +1685,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1764,7 +1770,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1849,7 +1855,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1934,7 +1940,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2019,7 +2025,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2104,7 +2110,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2189,7 +2195,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2257,9 +2263,6 @@
     <row r="230" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B230" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C230" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.2">
@@ -2277,7 +2280,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2345,6 +2348,9 @@
     <row r="241" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B241" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C241" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.2">
@@ -2362,7 +2368,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2447,7 +2453,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2532,7 +2538,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2600,9 +2606,6 @@
     <row r="274" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B274" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C274" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.2">
@@ -2620,7 +2623,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2708,7 +2711,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2776,6 +2779,9 @@
     <row r="296" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B296" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C296" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.2">
@@ -2793,7 +2799,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2878,7 +2884,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -2963,7 +2969,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3048,7 +3054,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3116,9 +3122,6 @@
     <row r="340" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B340" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C340" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.2">
@@ -3136,7 +3139,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3224,7 +3227,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3300,9 +3303,6 @@
     <row r="363" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B363" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="C363" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.2">
@@ -3315,7 +3315,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3391,6 +3391,9 @@
     <row r="374" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B374" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="C374" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.2">
@@ -3403,7 +3406,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3491,7 +3494,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3579,7 +3582,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3667,7 +3670,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3755,7 +3758,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3823,6 +3826,9 @@
     <row r="428" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B428" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C428" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.2">
@@ -3840,7 +3846,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3901,7 +3907,9 @@
       <c r="B438" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C438" s="6"/>
+      <c r="C438" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B439" s="3" t="s">
@@ -3917,10 +3925,13 @@
       <c r="B441" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C441" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -3981,16 +3992,11 @@
       <c r="B449" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C449" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C449" s="6"/>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B450" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C450" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.2">
@@ -4002,13 +4008,10 @@
       <c r="B452" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C452" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4096,7 +4099,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4184,7 +4187,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4252,6 +4255,9 @@
     <row r="483" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B483" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C483" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.2">
@@ -4269,7 +4275,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4354,7 +4360,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4427,9 +4433,6 @@
     <row r="506" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B506" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="C506" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.2">
@@ -4442,7 +4445,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4503,7 +4506,9 @@
       <c r="B515" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C515" s="6"/>
+      <c r="C515" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B516" s="3" t="s">
@@ -4513,16 +4518,22 @@
     <row r="517" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B517" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="C517" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B518" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C518" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4583,9 +4594,7 @@
       <c r="B526" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C526" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C526" s="6"/>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B527" s="3" t="s">
@@ -4601,13 +4610,10 @@
       <c r="B529" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C529" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4675,9 +4681,6 @@
     <row r="538" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B538" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C538" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.2">
@@ -4695,7 +4698,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4763,6 +4766,9 @@
     <row r="549" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B549" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C549" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.2">
@@ -4780,7 +4786,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4859,10 +4865,13 @@
       <c r="B562" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C562" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -4941,13 +4950,10 @@
       <c r="B573" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C573" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5015,9 +5021,6 @@
     <row r="582" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B582" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C582" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.2">
@@ -5035,7 +5038,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5056,19 +5059,25 @@
       <c r="B587" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C587" s="6"/>
+      <c r="C587" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B588" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C588" s="6"/>
+      <c r="C588" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B589" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C589" s="6"/>
+      <c r="C589" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B590" s="3" t="s">
@@ -5090,11 +5099,16 @@
       <c r="B592" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C592" s="6"/>
+      <c r="C592" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B593" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C593" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.2">
@@ -5106,10 +5120,13 @@
       <c r="B595" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C595" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5130,25 +5147,19 @@
       <c r="B598" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C598" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C598" s="6"/>
     </row>
     <row r="599" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B599" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C599" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C599" s="6"/>
     </row>
     <row r="600" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B600" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C600" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C600" s="6"/>
     </row>
     <row r="601" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B601" s="3" t="s">
@@ -5170,16 +5181,11 @@
       <c r="B603" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C603" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C603" s="6"/>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B604" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C604" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.2">
@@ -5191,13 +5197,10 @@
       <c r="B606" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C606" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5285,7 +5288,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5353,6 +5356,9 @@
     <row r="626" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B626" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C626" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.2">
@@ -5370,7 +5376,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5439,9 +5445,6 @@
       <c r="B637" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C637" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B638" s="3" t="s">
@@ -5449,19 +5452,19 @@
       </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A639" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B639" s="7" t="s">
-        <v>3</v>
+      <c r="B639" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C639" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B640" s="3" t="s">
-        <v>4</v>
+      <c r="A640" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B640" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C640" s="5" t="s">
         <v>13</v>
@@ -5469,7 +5472,7 @@
     </row>
     <row r="641" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B641" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C641" s="5" t="s">
         <v>13</v>
@@ -5477,7 +5480,7 @@
     </row>
     <row r="642" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B642" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C642" s="5" t="s">
         <v>13</v>
@@ -5485,7 +5488,7 @@
     </row>
     <row r="643" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B643" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C643" s="5" t="s">
         <v>13</v>
@@ -5493,7 +5496,7 @@
     </row>
     <row r="644" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B644" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C644" s="5" t="s">
         <v>13</v>
@@ -5501,7 +5504,7 @@
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B645" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C645" s="5" t="s">
         <v>13</v>
@@ -5509,7 +5512,7 @@
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B646" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C646" s="5" t="s">
         <v>13</v>
@@ -5517,7 +5520,7 @@
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B647" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C647" s="5" t="s">
         <v>13</v>
@@ -5525,23 +5528,23 @@
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B648" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C648" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A649" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B649" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C649" s="5" t="s">
-        <v>13</v>
+      <c r="B649" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B650" s="3" t="s">
-        <v>4</v>
+      <c r="A650" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B650" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C650" s="5" t="s">
         <v>13</v>
@@ -5549,7 +5552,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B651" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C651" s="5" t="s">
         <v>13</v>
@@ -5557,7 +5560,7 @@
     </row>
     <row r="652" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B652" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C652" s="5" t="s">
         <v>13</v>
@@ -5565,7 +5568,7 @@
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B653" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C653" s="5" t="s">
         <v>13</v>
@@ -5573,7 +5576,7 @@
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B654" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C654" s="5" t="s">
         <v>13</v>
@@ -5581,7 +5584,7 @@
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B655" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C655" s="5" t="s">
         <v>13</v>
@@ -5589,24 +5592,112 @@
     </row>
     <row r="656" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B656" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C656" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="657" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B657" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="658" spans="2:2" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="C657" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="658" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B658" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="659" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B659" s="3">
+        <v>11</v>
+      </c>
+      <c r="C658" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="659" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B659" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="660" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A660" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B660" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C660" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="661" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B661" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C661" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="662" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B662" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C662" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="663" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B663" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C663" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="664" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B664" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C664" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="665" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B665" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C665" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="666" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B666" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C666" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="667" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B667" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C667" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="668" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B668" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="669" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B669" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="670" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B670" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CDD5F2E-5635-4B50-8681-6751B0FAB0D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A8A1868-5396-4141-9BA8-CBF68D816E7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1248" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C670"/>
+  <dimension ref="A1:C681"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -628,9 +628,6 @@
       <c r="B21" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B22" s="3" t="s">
@@ -650,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -727,6 +724,9 @@
       <c r="B33" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C33" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B34" s="3" t="s">
@@ -738,7 +738,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -807,6 +807,9 @@
       <c r="B43" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C43" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B44" s="3" t="s">
@@ -823,7 +826,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -892,9 +895,6 @@
       <c r="B54" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C54" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B55" s="3" t="s">
@@ -911,7 +911,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -980,6 +980,9 @@
       <c r="B65" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C65" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B66" s="3" t="s">
@@ -996,7 +999,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1065,9 +1068,6 @@
       <c r="B76" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C76" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B77" s="3" t="s">
@@ -1084,7 +1084,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1172,7 +1172,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1260,7 +1260,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1329,6 +1329,9 @@
       <c r="B109" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C109" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B110" s="3" t="s">
@@ -1345,7 +1348,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1430,7 +1433,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1515,7 +1518,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1600,7 +1603,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1685,7 +1688,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1770,7 +1773,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1855,7 +1858,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1940,7 +1943,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2025,7 +2028,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2110,7 +2113,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2195,7 +2198,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2280,7 +2283,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2349,9 +2352,6 @@
       <c r="B241" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C241" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B242" s="3" t="s">
@@ -2368,7 +2368,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2437,6 +2437,9 @@
       <c r="B252" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C252" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B253" s="3" t="s">
@@ -2453,7 +2456,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2538,7 +2541,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2623,7 +2626,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2692,9 +2695,6 @@
       <c r="B285" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C285" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B286" s="3" t="s">
@@ -2711,7 +2711,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2799,7 +2799,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2868,6 +2868,9 @@
       <c r="B307" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C307" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B308" s="3" t="s">
@@ -2884,7 +2887,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -2969,7 +2972,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3054,7 +3057,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3139,7 +3142,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3208,9 +3211,6 @@
       <c r="B351" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C351" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B352" s="3" t="s">
@@ -3227,7 +3227,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3315,7 +3315,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3392,9 +3392,6 @@
       <c r="B374" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C374" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B375" s="3" t="s">
@@ -3406,7 +3403,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3483,6 +3480,9 @@
       <c r="B385" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C385" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B386" s="3" t="s">
@@ -3494,7 +3494,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3582,7 +3582,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3670,7 +3670,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3758,7 +3758,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3846,7 +3846,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3915,6 +3915,9 @@
       <c r="B439" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C439" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B440" s="3" t="s">
@@ -3931,7 +3934,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -3992,7 +3995,9 @@
       <c r="B449" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C449" s="6"/>
+      <c r="C449" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B450" s="3" t="s">
@@ -4008,10 +4013,13 @@
       <c r="B452" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C452" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4072,17 +4080,12 @@
       <c r="B460" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C460" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C460" s="6"/>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B461" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C461" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B462" s="3" t="s">
@@ -4093,13 +4096,10 @@
       <c r="B463" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C463" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4187,7 +4187,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4275,7 +4275,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4344,6 +4344,9 @@
       <c r="B494" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C494" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B495" s="3" t="s">
@@ -4360,7 +4363,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4445,7 +4448,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4519,9 +4522,6 @@
       <c r="B517" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C517" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B518" s="3" t="s">
@@ -4533,7 +4533,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4594,7 +4594,9 @@
       <c r="B526" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C526" s="6"/>
+      <c r="C526" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B527" s="3" t="s">
@@ -4605,15 +4607,21 @@
       <c r="B528" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C528" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B529" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C529" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4674,9 +4682,7 @@
       <c r="B537" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C537" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C537" s="6"/>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B538" s="3" t="s">
@@ -4692,13 +4698,10 @@
       <c r="B540" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C540" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4767,9 +4770,6 @@
       <c r="B549" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C549" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B550" s="3" t="s">
@@ -4786,7 +4786,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4855,6 +4855,9 @@
       <c r="B560" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C560" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B561" s="3" t="s">
@@ -4871,7 +4874,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -4950,10 +4953,13 @@
       <c r="B573" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C573" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5032,13 +5038,10 @@
       <c r="B584" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C584" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5107,9 +5110,6 @@
       <c r="B593" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C593" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B594" s="3" t="s">
@@ -5126,7 +5126,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5147,19 +5147,25 @@
       <c r="B598" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C598" s="6"/>
+      <c r="C598" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="599" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B599" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C599" s="6"/>
+      <c r="C599" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="600" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B600" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C600" s="6"/>
+      <c r="C600" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="601" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B601" s="3" t="s">
@@ -5181,12 +5187,17 @@
       <c r="B603" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C603" s="6"/>
+      <c r="C603" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B604" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C604" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B605" s="3" t="s">
@@ -5197,10 +5208,13 @@
       <c r="B606" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C606" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5221,25 +5235,19 @@
       <c r="B609" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C609" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C609" s="6"/>
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B610" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C610" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C610" s="6"/>
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B611" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C611" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C611" s="6"/>
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B612" s="3" t="s">
@@ -5261,17 +5269,12 @@
       <c r="B614" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C614" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C614" s="6"/>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B615" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C615" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B616" s="3" t="s">
@@ -5282,13 +5285,10 @@
       <c r="B617" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C617" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5376,7 +5376,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5445,6 +5445,9 @@
       <c r="B637" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C637" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B638" s="3" t="s">
@@ -5461,7 +5464,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5530,9 +5533,6 @@
       <c r="B648" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C648" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B649" s="3" t="s">
@@ -5540,19 +5540,19 @@
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A650" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B650" s="7" t="s">
-        <v>3</v>
+      <c r="B650" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C650" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B651" s="3" t="s">
-        <v>4</v>
+      <c r="A651" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B651" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C651" s="5" t="s">
         <v>13</v>
@@ -5560,7 +5560,7 @@
     </row>
     <row r="652" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B652" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C652" s="5" t="s">
         <v>13</v>
@@ -5568,7 +5568,7 @@
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B653" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C653" s="5" t="s">
         <v>13</v>
@@ -5576,7 +5576,7 @@
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B654" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C654" s="5" t="s">
         <v>13</v>
@@ -5584,7 +5584,7 @@
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B655" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C655" s="5" t="s">
         <v>13</v>
@@ -5592,7 +5592,7 @@
     </row>
     <row r="656" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B656" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C656" s="5" t="s">
         <v>13</v>
@@ -5600,7 +5600,7 @@
     </row>
     <row r="657" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B657" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C657" s="5" t="s">
         <v>13</v>
@@ -5608,7 +5608,7 @@
     </row>
     <row r="658" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B658" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C658" s="5" t="s">
         <v>13</v>
@@ -5616,23 +5616,23 @@
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B659" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C659" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A660" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B660" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C660" s="5" t="s">
-        <v>13</v>
+      <c r="B660" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B661" s="3" t="s">
-        <v>4</v>
+      <c r="A661" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B661" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C661" s="5" t="s">
         <v>13</v>
@@ -5640,7 +5640,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B662" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C662" s="5" t="s">
         <v>13</v>
@@ -5648,7 +5648,7 @@
     </row>
     <row r="663" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B663" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C663" s="5" t="s">
         <v>13</v>
@@ -5656,7 +5656,7 @@
     </row>
     <row r="664" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B664" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C664" s="5" t="s">
         <v>13</v>
@@ -5664,7 +5664,7 @@
     </row>
     <row r="665" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B665" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C665" s="5" t="s">
         <v>13</v>
@@ -5672,7 +5672,7 @@
     </row>
     <row r="666" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B666" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C666" s="5" t="s">
         <v>13</v>
@@ -5680,7 +5680,7 @@
     </row>
     <row r="667" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B667" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C667" s="5" t="s">
         <v>13</v>
@@ -5688,16 +5688,104 @@
     </row>
     <row r="668" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B668" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C668" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="669" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B669" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C669" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="670" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B670" s="3">
+      <c r="B670" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="671" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A671" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B671" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C671" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="672" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B672" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C672" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="673" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B673" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C673" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="674" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B674" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C674" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="675" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B675" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C675" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="676" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B676" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C676" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="677" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B677" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C677" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="678" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B678" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C678" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="679" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B679" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="680" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B680" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="681" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B681" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A8A1868-5396-4141-9BA8-CBF68D816E7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{217A1B0F-E4F7-4FC8-BDB5-746D93B83EED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1248" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1270" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C681"/>
+  <dimension ref="A1:C692"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -628,6 +628,9 @@
       <c r="B21" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C21" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B22" s="3" t="s">
@@ -647,7 +650,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -716,9 +719,6 @@
       <c r="B32" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C32" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B33" s="3" t="s">
@@ -738,7 +738,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -815,6 +815,9 @@
       <c r="B44" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C44" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B45" s="3" t="s">
@@ -826,7 +829,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -895,6 +898,9 @@
       <c r="B54" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C54" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B55" s="3" t="s">
@@ -911,7 +917,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -980,9 +986,6 @@
       <c r="B65" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C65" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B66" s="3" t="s">
@@ -999,7 +1002,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1068,6 +1071,9 @@
       <c r="B76" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C76" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B77" s="3" t="s">
@@ -1084,7 +1090,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1153,9 +1159,6 @@
       <c r="B87" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C87" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B88" s="3" t="s">
@@ -1172,7 +1175,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1260,7 +1263,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1348,7 +1351,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1417,6 +1420,9 @@
       <c r="B120" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C120" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B121" s="3" t="s">
@@ -1433,7 +1439,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1518,7 +1524,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1603,7 +1609,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1688,7 +1694,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1773,7 +1779,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1858,7 +1864,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1943,7 +1949,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2028,7 +2034,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2113,7 +2119,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2198,7 +2204,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2283,7 +2289,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2368,7 +2374,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2437,9 +2443,6 @@
       <c r="B252" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C252" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B253" s="3" t="s">
@@ -2456,7 +2459,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2525,6 +2528,9 @@
       <c r="B263" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C263" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B264" s="3" t="s">
@@ -2541,7 +2547,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2626,7 +2632,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2711,7 +2717,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2780,9 +2786,6 @@
       <c r="B296" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C296" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B297" s="3" t="s">
@@ -2799,7 +2802,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2887,7 +2890,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -2956,6 +2959,9 @@
       <c r="B318" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C318" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B319" s="3" t="s">
@@ -2972,7 +2978,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3057,7 +3063,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3142,7 +3148,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3227,7 +3233,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3296,9 +3302,6 @@
       <c r="B362" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C362" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B363" s="3" t="s">
@@ -3315,7 +3318,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3403,7 +3406,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3480,9 +3483,6 @@
       <c r="B385" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C385" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B386" s="3" t="s">
@@ -3494,7 +3494,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3571,6 +3571,9 @@
       <c r="B396" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C396" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B397" s="3" t="s">
@@ -3582,7 +3585,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3670,7 +3673,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3758,7 +3761,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3846,7 +3849,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3934,7 +3937,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4003,6 +4006,9 @@
       <c r="B450" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C450" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B451" s="3" t="s">
@@ -4019,7 +4025,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4080,7 +4086,9 @@
       <c r="B460" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C460" s="6"/>
+      <c r="C460" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B461" s="3" t="s">
@@ -4096,10 +4104,13 @@
       <c r="B463" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C463" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4160,17 +4171,12 @@
       <c r="B471" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C471" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C471" s="6"/>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B472" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C472" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B473" s="3" t="s">
@@ -4181,13 +4187,10 @@
       <c r="B474" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C474" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4275,7 +4278,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4363,7 +4366,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4432,6 +4435,9 @@
       <c r="B505" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C505" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B506" s="3" t="s">
@@ -4448,7 +4454,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4533,7 +4539,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4607,9 +4613,6 @@
       <c r="B528" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C528" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B529" s="3" t="s">
@@ -4621,7 +4624,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4682,7 +4685,9 @@
       <c r="B537" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C537" s="6"/>
+      <c r="C537" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B538" s="3" t="s">
@@ -4693,15 +4698,21 @@
       <c r="B539" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C539" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B540" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C540" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4762,9 +4773,7 @@
       <c r="B548" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C548" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C548" s="6"/>
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B549" s="3" t="s">
@@ -4780,13 +4789,10 @@
       <c r="B551" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C551" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4855,9 +4861,6 @@
       <c r="B560" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C560" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B561" s="3" t="s">
@@ -4874,7 +4877,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -4943,6 +4946,9 @@
       <c r="B571" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C571" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B572" s="3" t="s">
@@ -4959,7 +4965,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5038,10 +5044,13 @@
       <c r="B584" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C584" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5120,13 +5129,10 @@
       <c r="B595" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C595" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5195,9 +5201,6 @@
       <c r="B604" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C604" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B605" s="3" t="s">
@@ -5214,7 +5217,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5235,19 +5238,25 @@
       <c r="B609" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C609" s="6"/>
+      <c r="C609" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B610" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C610" s="6"/>
+      <c r="C610" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B611" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C611" s="6"/>
+      <c r="C611" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B612" s="3" t="s">
@@ -5269,12 +5278,17 @@
       <c r="B614" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C614" s="6"/>
+      <c r="C614" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B615" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C615" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B616" s="3" t="s">
@@ -5285,10 +5299,13 @@
       <c r="B617" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C617" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5309,25 +5326,19 @@
       <c r="B620" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C620" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C620" s="6"/>
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B621" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C621" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C621" s="6"/>
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B622" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C622" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C622" s="6"/>
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B623" s="3" t="s">
@@ -5349,17 +5360,12 @@
       <c r="B625" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C625" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C625" s="6"/>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B626" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C626" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B627" s="3" t="s">
@@ -5370,13 +5376,10 @@
       <c r="B628" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C628" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5464,7 +5467,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5533,6 +5536,9 @@
       <c r="B648" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C648" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B649" s="3" t="s">
@@ -5549,7 +5555,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5618,9 +5624,6 @@
       <c r="B659" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C659" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B660" s="3" t="s">
@@ -5628,19 +5631,19 @@
       </c>
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A661" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B661" s="7" t="s">
-        <v>3</v>
+      <c r="B661" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C661" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B662" s="3" t="s">
-        <v>4</v>
+      <c r="A662" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B662" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C662" s="5" t="s">
         <v>13</v>
@@ -5648,7 +5651,7 @@
     </row>
     <row r="663" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B663" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C663" s="5" t="s">
         <v>13</v>
@@ -5656,7 +5659,7 @@
     </row>
     <row r="664" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B664" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C664" s="5" t="s">
         <v>13</v>
@@ -5664,7 +5667,7 @@
     </row>
     <row r="665" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B665" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C665" s="5" t="s">
         <v>13</v>
@@ -5672,7 +5675,7 @@
     </row>
     <row r="666" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B666" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C666" s="5" t="s">
         <v>13</v>
@@ -5680,7 +5683,7 @@
     </row>
     <row r="667" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B667" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C667" s="5" t="s">
         <v>13</v>
@@ -5688,7 +5691,7 @@
     </row>
     <row r="668" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B668" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C668" s="5" t="s">
         <v>13</v>
@@ -5696,7 +5699,7 @@
     </row>
     <row r="669" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B669" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C669" s="5" t="s">
         <v>13</v>
@@ -5704,88 +5707,176 @@
     </row>
     <row r="670" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B670" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C670" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="671" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A671" s="4">
+      <c r="B671" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="672" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A672" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B672" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C672" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="673" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B673" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C673" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="674" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B674" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C674" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="675" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B675" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C675" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="676" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B676" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C676" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="677" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B677" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C677" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="678" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B678" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C678" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="679" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B679" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C679" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="680" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B680" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C680" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="681" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B681" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="682" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A682" s="4">
         <v>46042</v>
       </c>
-      <c r="B671" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C671" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="672" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B672" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C672" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="673" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B673" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C673" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="674" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B674" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C674" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="675" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B675" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C675" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="676" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B676" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C676" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="677" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B677" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C677" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="678" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B678" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C678" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="679" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B679" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="680" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B680" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="681" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B681" s="3">
+      <c r="B682" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C682" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="683" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B683" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C683" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="684" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B684" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C684" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="685" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B685" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C685" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="686" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B686" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C686" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="687" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B687" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C687" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="688" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B688" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C688" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="689" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B689" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C689" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="690" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B690" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="691" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B691" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="692" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B692" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{217A1B0F-E4F7-4FC8-BDB5-746D93B83EED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B8416D5-C551-454A-A5FE-D9DF41A222F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1270" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C692"/>
+  <dimension ref="A1:C703"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -650,7 +650,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -719,6 +719,9 @@
       <c r="B32" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C32" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B33" s="3" t="s">
@@ -738,7 +741,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -807,9 +810,6 @@
       <c r="B43" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C43" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B44" s="3" t="s">
@@ -829,7 +829,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -906,6 +906,9 @@
       <c r="B55" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C55" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B56" s="3" t="s">
@@ -917,7 +920,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -986,6 +989,9 @@
       <c r="B65" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C65" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B66" s="3" t="s">
@@ -1002,7 +1008,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1071,9 +1077,6 @@
       <c r="B76" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C76" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B77" s="3" t="s">
@@ -1090,7 +1093,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1159,6 +1162,9 @@
       <c r="B87" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C87" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B88" s="3" t="s">
@@ -1175,7 +1181,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1244,9 +1250,6 @@
       <c r="B98" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C98" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B99" s="3" t="s">
@@ -1263,7 +1266,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1351,7 +1354,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1439,7 +1442,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1508,6 +1511,9 @@
       <c r="B131" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C131" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B132" s="3" t="s">
@@ -1524,7 +1530,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1609,7 +1615,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1694,7 +1700,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1779,7 +1785,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1864,7 +1870,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1949,7 +1955,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2034,7 +2040,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2119,7 +2125,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2204,7 +2210,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2289,7 +2295,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2374,7 +2380,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2459,7 +2465,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2528,9 +2534,6 @@
       <c r="B263" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C263" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B264" s="3" t="s">
@@ -2547,7 +2550,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2616,6 +2619,9 @@
       <c r="B274" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C274" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B275" s="3" t="s">
@@ -2632,7 +2638,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2717,7 +2723,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2802,7 +2808,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2871,9 +2877,6 @@
       <c r="B307" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C307" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B308" s="3" t="s">
@@ -2890,7 +2893,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -2978,7 +2981,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3047,6 +3050,9 @@
       <c r="B329" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C329" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B330" s="3" t="s">
@@ -3063,7 +3069,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3148,7 +3154,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3233,7 +3239,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3318,7 +3324,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3387,9 +3393,6 @@
       <c r="B373" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C373" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B374" s="3" t="s">
@@ -3406,7 +3409,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3494,7 +3497,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3571,9 +3574,6 @@
       <c r="B396" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C396" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B397" s="3" t="s">
@@ -3585,7 +3585,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3662,6 +3662,9 @@
       <c r="B407" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C407" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B408" s="3" t="s">
@@ -3673,7 +3676,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3761,7 +3764,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3849,7 +3852,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3937,7 +3940,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4025,7 +4028,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4094,6 +4097,9 @@
       <c r="B461" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C461" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B462" s="3" t="s">
@@ -4110,7 +4116,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4171,7 +4177,9 @@
       <c r="B471" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C471" s="6"/>
+      <c r="C471" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B472" s="3" t="s">
@@ -4187,10 +4195,13 @@
       <c r="B474" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C474" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4251,17 +4262,12 @@
       <c r="B482" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C482" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C482" s="6"/>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B483" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C483" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B484" s="3" t="s">
@@ -4272,13 +4278,10 @@
       <c r="B485" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C485" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4366,7 +4369,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4454,7 +4457,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4523,6 +4526,9 @@
       <c r="B516" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C516" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B517" s="3" t="s">
@@ -4539,7 +4545,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4624,7 +4630,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4698,9 +4704,6 @@
       <c r="B539" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C539" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B540" s="3" t="s">
@@ -4712,7 +4715,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4773,7 +4776,9 @@
       <c r="B548" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C548" s="6"/>
+      <c r="C548" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B549" s="3" t="s">
@@ -4784,15 +4789,21 @@
       <c r="B550" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C550" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B551" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C551" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4853,9 +4864,7 @@
       <c r="B559" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C559" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C559" s="6"/>
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B560" s="3" t="s">
@@ -4871,13 +4880,10 @@
       <c r="B562" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C562" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -4946,9 +4952,6 @@
       <c r="B571" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C571" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B572" s="3" t="s">
@@ -4965,7 +4968,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5034,6 +5037,9 @@
       <c r="B582" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C582" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B583" s="3" t="s">
@@ -5050,7 +5056,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5129,10 +5135,13 @@
       <c r="B595" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C595" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5211,13 +5220,10 @@
       <c r="B606" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C606" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5286,9 +5292,6 @@
       <c r="B615" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C615" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B616" s="3" t="s">
@@ -5305,7 +5308,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5326,19 +5329,25 @@
       <c r="B620" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C620" s="6"/>
+      <c r="C620" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B621" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C621" s="6"/>
+      <c r="C621" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B622" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C622" s="6"/>
+      <c r="C622" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B623" s="3" t="s">
@@ -5360,12 +5369,17 @@
       <c r="B625" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C625" s="6"/>
+      <c r="C625" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B626" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C626" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B627" s="3" t="s">
@@ -5376,10 +5390,13 @@
       <c r="B628" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C628" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5400,25 +5417,19 @@
       <c r="B631" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C631" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C631" s="6"/>
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B632" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C632" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C632" s="6"/>
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B633" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C633" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C633" s="6"/>
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B634" s="3" t="s">
@@ -5440,17 +5451,12 @@
       <c r="B636" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C636" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C636" s="6"/>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B637" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C637" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B638" s="3" t="s">
@@ -5461,13 +5467,10 @@
       <c r="B639" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C639" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5555,7 +5558,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5624,6 +5627,9 @@
       <c r="B659" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C659" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B660" s="3" t="s">
@@ -5640,7 +5646,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5709,9 +5715,6 @@
       <c r="B670" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C670" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="671" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B671" s="3" t="s">
@@ -5719,19 +5722,19 @@
       </c>
     </row>
     <row r="672" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A672" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B672" s="7" t="s">
-        <v>3</v>
+      <c r="B672" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C672" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B673" s="3" t="s">
-        <v>4</v>
+      <c r="A673" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B673" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C673" s="5" t="s">
         <v>13</v>
@@ -5739,7 +5742,7 @@
     </row>
     <row r="674" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B674" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C674" s="5" t="s">
         <v>13</v>
@@ -5747,7 +5750,7 @@
     </row>
     <row r="675" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B675" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C675" s="5" t="s">
         <v>13</v>
@@ -5755,7 +5758,7 @@
     </row>
     <row r="676" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B676" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C676" s="5" t="s">
         <v>13</v>
@@ -5763,7 +5766,7 @@
     </row>
     <row r="677" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B677" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C677" s="5" t="s">
         <v>13</v>
@@ -5771,7 +5774,7 @@
     </row>
     <row r="678" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B678" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C678" s="5" t="s">
         <v>13</v>
@@ -5779,7 +5782,7 @@
     </row>
     <row r="679" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B679" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C679" s="5" t="s">
         <v>13</v>
@@ -5787,7 +5790,7 @@
     </row>
     <row r="680" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B680" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C680" s="5" t="s">
         <v>13</v>
@@ -5795,23 +5798,23 @@
     </row>
     <row r="681" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B681" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C681" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="682" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A682" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B682" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C682" s="5" t="s">
-        <v>13</v>
+      <c r="B682" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="683" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B683" s="3" t="s">
-        <v>4</v>
+      <c r="A683" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B683" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C683" s="5" t="s">
         <v>13</v>
@@ -5819,7 +5822,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B684" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C684" s="5" t="s">
         <v>13</v>
@@ -5827,7 +5830,7 @@
     </row>
     <row r="685" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B685" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C685" s="5" t="s">
         <v>13</v>
@@ -5835,7 +5838,7 @@
     </row>
     <row r="686" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B686" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C686" s="5" t="s">
         <v>13</v>
@@ -5843,7 +5846,7 @@
     </row>
     <row r="687" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B687" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C687" s="5" t="s">
         <v>13</v>
@@ -5851,32 +5854,120 @@
     </row>
     <row r="688" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B688" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C688" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="689" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B689" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C689" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="690" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B690" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="691" spans="2:3" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="C690" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="691" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B691" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="692" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B692" s="3">
+        <v>11</v>
+      </c>
+      <c r="C691" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="692" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B692" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="693" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A693" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B693" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C693" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="694" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B694" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C694" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="695" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B695" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C695" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="696" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B696" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C696" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="697" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B697" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C697" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="698" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B698" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C698" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="699" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B699" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C699" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="700" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B700" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C700" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="701" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B701" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="702" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B702" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="703" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B703" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B8416D5-C551-454A-A5FE-D9DF41A222F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5339354-2144-4DAE-A675-8D7ACE82EB8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1314" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C703"/>
+  <dimension ref="A1:C714"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -650,7 +650,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -741,7 +741,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -810,6 +810,9 @@
       <c r="B43" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C43" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B44" s="3" t="s">
@@ -829,7 +832,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -898,9 +901,6 @@
       <c r="B54" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C54" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B55" s="3" t="s">
@@ -920,7 +920,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -997,6 +997,9 @@
       <c r="B66" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C66" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B67" s="3" t="s">
@@ -1008,7 +1011,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1077,6 +1080,9 @@
       <c r="B76" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C76" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B77" s="3" t="s">
@@ -1093,7 +1099,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1162,9 +1168,6 @@
       <c r="B87" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C87" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B88" s="3" t="s">
@@ -1181,7 +1184,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1250,6 +1253,9 @@
       <c r="B98" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C98" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B99" s="3" t="s">
@@ -1266,7 +1272,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1335,9 +1341,6 @@
       <c r="B109" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C109" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B110" s="3" t="s">
@@ -1354,7 +1357,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1442,7 +1445,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1530,7 +1533,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1599,6 +1602,9 @@
       <c r="B142" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C142" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B143" s="3" t="s">
@@ -1615,7 +1621,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1700,7 +1706,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1785,7 +1791,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1870,7 +1876,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1955,7 +1961,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2040,7 +2046,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2125,7 +2131,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2210,7 +2216,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2295,7 +2301,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2380,7 +2386,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2465,7 +2471,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2550,7 +2556,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2619,9 +2625,6 @@
       <c r="B274" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C274" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B275" s="3" t="s">
@@ -2638,7 +2641,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2707,6 +2710,9 @@
       <c r="B285" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C285" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B286" s="3" t="s">
@@ -2723,7 +2729,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2808,7 +2814,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2893,7 +2899,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -2962,9 +2968,6 @@
       <c r="B318" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C318" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B319" s="3" t="s">
@@ -2981,7 +2984,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3069,7 +3072,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3138,6 +3141,9 @@
       <c r="B340" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C340" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B341" s="3" t="s">
@@ -3154,7 +3160,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3239,7 +3245,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3324,7 +3330,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3409,7 +3415,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3478,9 +3484,6 @@
       <c r="B384" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C384" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B385" s="3" t="s">
@@ -3497,7 +3500,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3585,7 +3588,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3662,9 +3665,6 @@
       <c r="B407" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C407" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B408" s="3" t="s">
@@ -3676,7 +3676,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3753,6 +3753,9 @@
       <c r="B418" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C418" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B419" s="3" t="s">
@@ -3764,7 +3767,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3852,7 +3855,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3940,7 +3943,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4028,7 +4031,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4116,7 +4119,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4185,6 +4188,9 @@
       <c r="B472" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C472" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B473" s="3" t="s">
@@ -4201,7 +4207,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4262,7 +4268,9 @@
       <c r="B482" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C482" s="6"/>
+      <c r="C482" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B483" s="3" t="s">
@@ -4278,10 +4286,13 @@
       <c r="B485" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C485" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4342,17 +4353,12 @@
       <c r="B493" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C493" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C493" s="6"/>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B494" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C494" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B495" s="3" t="s">
@@ -4363,13 +4369,10 @@
       <c r="B496" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C496" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4457,7 +4460,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4545,7 +4548,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4614,6 +4617,9 @@
       <c r="B527" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C527" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B528" s="3" t="s">
@@ -4630,7 +4636,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4715,7 +4721,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4789,9 +4795,6 @@
       <c r="B550" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C550" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B551" s="3" t="s">
@@ -4803,7 +4806,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4864,7 +4867,9 @@
       <c r="B559" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C559" s="6"/>
+      <c r="C559" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B560" s="3" t="s">
@@ -4875,15 +4880,21 @@
       <c r="B561" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C561" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="562" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B562" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C562" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -4944,9 +4955,7 @@
       <c r="B570" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C570" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C570" s="6"/>
     </row>
     <row r="571" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B571" s="3" t="s">
@@ -4962,13 +4971,10 @@
       <c r="B573" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C573" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5037,9 +5043,6 @@
       <c r="B582" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C582" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B583" s="3" t="s">
@@ -5056,7 +5059,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5125,6 +5128,9 @@
       <c r="B593" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C593" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B594" s="3" t="s">
@@ -5141,7 +5147,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5220,10 +5226,13 @@
       <c r="B606" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C606" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5302,13 +5311,10 @@
       <c r="B617" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C617" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5377,9 +5383,6 @@
       <c r="B626" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C626" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B627" s="3" t="s">
@@ -5396,7 +5399,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5417,19 +5420,25 @@
       <c r="B631" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C631" s="6"/>
+      <c r="C631" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B632" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C632" s="6"/>
+      <c r="C632" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B633" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C633" s="6"/>
+      <c r="C633" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B634" s="3" t="s">
@@ -5451,12 +5460,17 @@
       <c r="B636" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C636" s="6"/>
+      <c r="C636" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B637" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C637" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B638" s="3" t="s">
@@ -5467,10 +5481,13 @@
       <c r="B639" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C639" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5491,25 +5508,19 @@
       <c r="B642" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C642" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C642" s="6"/>
     </row>
     <row r="643" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B643" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C643" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C643" s="6"/>
     </row>
     <row r="644" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B644" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C644" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C644" s="6"/>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B645" s="3" t="s">
@@ -5531,17 +5542,12 @@
       <c r="B647" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C647" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C647" s="6"/>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B648" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C648" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B649" s="3" t="s">
@@ -5552,13 +5558,10 @@
       <c r="B650" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C650" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5646,7 +5649,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5715,6 +5718,9 @@
       <c r="B670" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C670" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="671" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B671" s="3" t="s">
@@ -5731,7 +5737,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5800,9 +5806,6 @@
       <c r="B681" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C681" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="682" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B682" s="3" t="s">
@@ -5810,19 +5813,19 @@
       </c>
     </row>
     <row r="683" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A683" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B683" s="7" t="s">
-        <v>3</v>
+      <c r="B683" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C683" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B684" s="3" t="s">
-        <v>4</v>
+      <c r="A684" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B684" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C684" s="5" t="s">
         <v>13</v>
@@ -5830,7 +5833,7 @@
     </row>
     <row r="685" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B685" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C685" s="5" t="s">
         <v>13</v>
@@ -5838,7 +5841,7 @@
     </row>
     <row r="686" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B686" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C686" s="5" t="s">
         <v>13</v>
@@ -5846,7 +5849,7 @@
     </row>
     <row r="687" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B687" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C687" s="5" t="s">
         <v>13</v>
@@ -5854,7 +5857,7 @@
     </row>
     <row r="688" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B688" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C688" s="5" t="s">
         <v>13</v>
@@ -5862,7 +5865,7 @@
     </row>
     <row r="689" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B689" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C689" s="5" t="s">
         <v>13</v>
@@ -5870,7 +5873,7 @@
     </row>
     <row r="690" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B690" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C690" s="5" t="s">
         <v>13</v>
@@ -5878,7 +5881,7 @@
     </row>
     <row r="691" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B691" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C691" s="5" t="s">
         <v>13</v>
@@ -5886,23 +5889,23 @@
     </row>
     <row r="692" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B692" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C692" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="693" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A693" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B693" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C693" s="5" t="s">
-        <v>13</v>
+      <c r="B693" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="694" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B694" s="3" t="s">
-        <v>4</v>
+      <c r="A694" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B694" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C694" s="5" t="s">
         <v>13</v>
@@ -5910,7 +5913,7 @@
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B695" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C695" s="5" t="s">
         <v>13</v>
@@ -5918,7 +5921,7 @@
     </row>
     <row r="696" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B696" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C696" s="5" t="s">
         <v>13</v>
@@ -5926,7 +5929,7 @@
     </row>
     <row r="697" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B697" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C697" s="5" t="s">
         <v>13</v>
@@ -5934,7 +5937,7 @@
     </row>
     <row r="698" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B698" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C698" s="5" t="s">
         <v>13</v>
@@ -5942,7 +5945,7 @@
     </row>
     <row r="699" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B699" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C699" s="5" t="s">
         <v>13</v>
@@ -5950,7 +5953,7 @@
     </row>
     <row r="700" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B700" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C700" s="5" t="s">
         <v>13</v>
@@ -5958,16 +5961,104 @@
     </row>
     <row r="701" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B701" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C701" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="702" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B702" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C702" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="703" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B703" s="3">
+      <c r="B703" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="704" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A704" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B704" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C704" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="705" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B705" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C705" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="706" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B706" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C706" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="707" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B707" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C707" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="708" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B708" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C708" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="709" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B709" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C709" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="710" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B710" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C710" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="711" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B711" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C711" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="712" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B712" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="713" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B713" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="714" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B714" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5339354-2144-4DAE-A675-8D7ACE82EB8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DCC5664-46F5-4C19-98E2-1C010D48619E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1314" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1336" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C714"/>
+  <dimension ref="A1:C725"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -650,7 +650,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -741,7 +741,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -832,7 +832,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -901,6 +901,9 @@
       <c r="B54" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C54" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B55" s="3" t="s">
@@ -920,7 +923,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -989,9 +992,6 @@
       <c r="B65" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C65" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B66" s="3" t="s">
@@ -1011,7 +1011,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1088,6 +1088,9 @@
       <c r="B77" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C77" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B78" s="3" t="s">
@@ -1099,7 +1102,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1168,6 +1171,9 @@
       <c r="B87" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C87" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B88" s="3" t="s">
@@ -1184,7 +1190,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1253,9 +1259,6 @@
       <c r="B98" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C98" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B99" s="3" t="s">
@@ -1272,7 +1275,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1341,6 +1344,9 @@
       <c r="B109" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C109" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B110" s="3" t="s">
@@ -1357,7 +1363,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1426,9 +1432,6 @@
       <c r="B120" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C120" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B121" s="3" t="s">
@@ -1445,7 +1448,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1533,7 +1536,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1621,7 +1624,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1690,6 +1693,9 @@
       <c r="B153" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C153" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B154" s="3" t="s">
@@ -1706,7 +1712,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1791,7 +1797,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1876,7 +1882,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1961,7 +1967,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2046,7 +2052,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2131,7 +2137,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2216,7 +2222,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2301,7 +2307,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2386,7 +2392,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2471,7 +2477,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2556,7 +2562,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2641,7 +2647,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2710,9 +2716,6 @@
       <c r="B285" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C285" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B286" s="3" t="s">
@@ -2729,7 +2732,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2798,6 +2801,9 @@
       <c r="B296" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C296" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B297" s="3" t="s">
@@ -2814,7 +2820,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2899,7 +2905,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -2984,7 +2990,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3053,9 +3059,6 @@
       <c r="B329" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C329" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B330" s="3" t="s">
@@ -3072,7 +3075,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3160,7 +3163,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3229,6 +3232,9 @@
       <c r="B351" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C351" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B352" s="3" t="s">
@@ -3245,7 +3251,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3330,7 +3336,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3415,7 +3421,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3500,7 +3506,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3569,9 +3575,6 @@
       <c r="B395" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C395" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B396" s="3" t="s">
@@ -3588,7 +3591,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3676,7 +3679,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3753,9 +3756,6 @@
       <c r="B418" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C418" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B419" s="3" t="s">
@@ -3767,7 +3767,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3844,6 +3844,9 @@
       <c r="B429" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C429" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B430" s="3" t="s">
@@ -3855,7 +3858,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3943,7 +3946,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4031,7 +4034,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4119,7 +4122,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4207,7 +4210,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4276,6 +4279,9 @@
       <c r="B483" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C483" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B484" s="3" t="s">
@@ -4292,7 +4298,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4353,7 +4359,9 @@
       <c r="B493" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C493" s="6"/>
+      <c r="C493" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B494" s="3" t="s">
@@ -4369,10 +4377,13 @@
       <c r="B496" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C496" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4433,17 +4444,12 @@
       <c r="B504" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C504" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C504" s="6"/>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B505" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C505" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B506" s="3" t="s">
@@ -4454,13 +4460,10 @@
       <c r="B507" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C507" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4548,7 +4551,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4636,7 +4639,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4705,6 +4708,9 @@
       <c r="B538" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C538" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B539" s="3" t="s">
@@ -4721,7 +4727,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4806,7 +4812,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4880,9 +4886,6 @@
       <c r="B561" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C561" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="562" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B562" s="3" t="s">
@@ -4894,7 +4897,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -4955,7 +4958,9 @@
       <c r="B570" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C570" s="6"/>
+      <c r="C570" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="571" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B571" s="3" t="s">
@@ -4966,15 +4971,21 @@
       <c r="B572" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C572" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="573" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B573" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C573" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5035,9 +5046,7 @@
       <c r="B581" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C581" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C581" s="6"/>
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B582" s="3" t="s">
@@ -5053,13 +5062,10 @@
       <c r="B584" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C584" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5128,9 +5134,6 @@
       <c r="B593" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C593" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B594" s="3" t="s">
@@ -5147,7 +5150,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5216,6 +5219,9 @@
       <c r="B604" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C604" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B605" s="3" t="s">
@@ -5232,7 +5238,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5311,10 +5317,13 @@
       <c r="B617" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C617" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5393,13 +5402,10 @@
       <c r="B628" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C628" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5468,9 +5474,6 @@
       <c r="B637" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C637" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B638" s="3" t="s">
@@ -5487,7 +5490,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5508,19 +5511,25 @@
       <c r="B642" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C642" s="6"/>
+      <c r="C642" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="643" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B643" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C643" s="6"/>
+      <c r="C643" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="644" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B644" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C644" s="6"/>
+      <c r="C644" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B645" s="3" t="s">
@@ -5542,12 +5551,17 @@
       <c r="B647" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C647" s="6"/>
+      <c r="C647" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B648" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C648" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B649" s="3" t="s">
@@ -5558,10 +5572,13 @@
       <c r="B650" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C650" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5582,25 +5599,19 @@
       <c r="B653" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C653" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C653" s="6"/>
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B654" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C654" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C654" s="6"/>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B655" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C655" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C655" s="6"/>
     </row>
     <row r="656" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B656" s="3" t="s">
@@ -5622,17 +5633,12 @@
       <c r="B658" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C658" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C658" s="6"/>
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B659" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C659" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B660" s="3" t="s">
@@ -5643,13 +5649,10 @@
       <c r="B661" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C661" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5737,7 +5740,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5806,6 +5809,9 @@
       <c r="B681" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C681" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="682" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B682" s="3" t="s">
@@ -5822,7 +5828,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -5891,9 +5897,6 @@
       <c r="B692" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C692" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="693" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B693" s="3" t="s">
@@ -5901,19 +5904,19 @@
       </c>
     </row>
     <row r="694" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A694" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B694" s="7" t="s">
-        <v>3</v>
+      <c r="B694" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C694" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B695" s="3" t="s">
-        <v>4</v>
+      <c r="A695" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B695" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C695" s="5" t="s">
         <v>13</v>
@@ -5921,7 +5924,7 @@
     </row>
     <row r="696" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B696" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C696" s="5" t="s">
         <v>13</v>
@@ -5929,7 +5932,7 @@
     </row>
     <row r="697" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B697" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C697" s="5" t="s">
         <v>13</v>
@@ -5937,7 +5940,7 @@
     </row>
     <row r="698" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B698" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C698" s="5" t="s">
         <v>13</v>
@@ -5945,7 +5948,7 @@
     </row>
     <row r="699" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B699" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C699" s="5" t="s">
         <v>13</v>
@@ -5953,7 +5956,7 @@
     </row>
     <row r="700" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B700" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C700" s="5" t="s">
         <v>13</v>
@@ -5961,7 +5964,7 @@
     </row>
     <row r="701" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B701" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C701" s="5" t="s">
         <v>13</v>
@@ -5969,7 +5972,7 @@
     </row>
     <row r="702" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B702" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C702" s="5" t="s">
         <v>13</v>
@@ -5977,88 +5980,176 @@
     </row>
     <row r="703" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B703" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C703" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="704" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A704" s="4">
+      <c r="B704" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="705" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A705" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B705" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C705" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="706" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B706" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C706" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="707" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B707" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C707" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="708" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B708" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C708" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="709" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B709" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C709" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="710" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B710" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C710" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="711" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B711" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C711" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="712" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B712" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C712" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="713" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B713" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C713" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="714" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B714" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="715" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A715" s="4">
         <v>46042</v>
       </c>
-      <c r="B704" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C704" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="705" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B705" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C705" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="706" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B706" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C706" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="707" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B707" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C707" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="708" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B708" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C708" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="709" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B709" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C709" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="710" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B710" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C710" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="711" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B711" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C711" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="712" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B712" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="713" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B713" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="714" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B714" s="3">
+      <c r="B715" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C715" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="716" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B716" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C716" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="717" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B717" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C717" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="718" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B718" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C718" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="719" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B719" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C719" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="720" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B720" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C720" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="721" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B721" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C721" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="722" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B722" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C722" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="723" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B723" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="724" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B724" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="725" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B725" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DCC5664-46F5-4C19-98E2-1C010D48619E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62AB5C83-1545-40E6-A86B-56452CE49E1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1336" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1358" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C725"/>
+  <dimension ref="A1:C736"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -650,7 +650,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -741,7 +741,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -832,7 +832,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -923,7 +923,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -992,6 +992,9 @@
       <c r="B65" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C65" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B66" s="3" t="s">
@@ -1011,7 +1014,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1080,9 +1083,6 @@
       <c r="B76" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C76" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B77" s="3" t="s">
@@ -1102,7 +1102,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1179,6 +1179,9 @@
       <c r="B88" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C88" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B89" s="3" t="s">
@@ -1190,7 +1193,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1259,6 +1262,9 @@
       <c r="B98" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C98" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B99" s="3" t="s">
@@ -1275,7 +1281,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1344,9 +1350,6 @@
       <c r="B109" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C109" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B110" s="3" t="s">
@@ -1363,7 +1366,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1432,6 +1435,9 @@
       <c r="B120" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C120" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B121" s="3" t="s">
@@ -1448,7 +1454,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1517,9 +1523,6 @@
       <c r="B131" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C131" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B132" s="3" t="s">
@@ -1536,7 +1539,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1624,7 +1627,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1712,7 +1715,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1781,6 +1784,9 @@
       <c r="B164" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C164" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B165" s="3" t="s">
@@ -1797,7 +1803,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1882,7 +1888,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1967,7 +1973,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2052,7 +2058,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2137,7 +2143,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2222,7 +2228,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2307,7 +2313,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2392,7 +2398,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2477,7 +2483,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2562,7 +2568,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2647,7 +2653,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2732,7 +2738,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2801,9 +2807,6 @@
       <c r="B296" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C296" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B297" s="3" t="s">
@@ -2820,7 +2823,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2889,6 +2892,9 @@
       <c r="B307" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C307" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B308" s="3" t="s">
@@ -2905,7 +2911,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -2990,7 +2996,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3075,7 +3081,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3144,9 +3150,6 @@
       <c r="B340" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C340" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B341" s="3" t="s">
@@ -3163,7 +3166,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3251,7 +3254,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3320,6 +3323,9 @@
       <c r="B362" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C362" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B363" s="3" t="s">
@@ -3336,7 +3342,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3421,7 +3427,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3506,7 +3512,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3591,7 +3597,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3660,9 +3666,6 @@
       <c r="B406" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C406" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B407" s="3" t="s">
@@ -3679,7 +3682,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3767,7 +3770,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3844,9 +3847,6 @@
       <c r="B429" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C429" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B430" s="3" t="s">
@@ -3858,7 +3858,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3935,6 +3935,9 @@
       <c r="B440" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C440" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B441" s="3" t="s">
@@ -3946,7 +3949,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4034,7 +4037,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4122,7 +4125,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4210,7 +4213,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4298,7 +4301,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4367,6 +4370,9 @@
       <c r="B494" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C494" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B495" s="3" t="s">
@@ -4383,7 +4389,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4444,7 +4450,9 @@
       <c r="B504" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C504" s="6"/>
+      <c r="C504" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B505" s="3" t="s">
@@ -4460,10 +4468,13 @@
       <c r="B507" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C507" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4524,17 +4535,12 @@
       <c r="B515" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C515" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C515" s="6"/>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B516" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C516" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B517" s="3" t="s">
@@ -4545,13 +4551,10 @@
       <c r="B518" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C518" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4639,7 +4642,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4727,7 +4730,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4796,6 +4799,9 @@
       <c r="B549" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C549" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B550" s="3" t="s">
@@ -4812,7 +4818,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4897,7 +4903,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -4971,9 +4977,6 @@
       <c r="B572" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C572" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="573" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B573" s="3" t="s">
@@ -4985,7 +4988,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5046,7 +5049,9 @@
       <c r="B581" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C581" s="6"/>
+      <c r="C581" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B582" s="3" t="s">
@@ -5057,15 +5062,21 @@
       <c r="B583" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C583" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B584" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C584" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5126,9 +5137,7 @@
       <c r="B592" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C592" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C592" s="6"/>
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B593" s="3" t="s">
@@ -5144,13 +5153,10 @@
       <c r="B595" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C595" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5219,9 +5225,6 @@
       <c r="B604" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C604" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B605" s="3" t="s">
@@ -5238,7 +5241,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5307,6 +5310,9 @@
       <c r="B615" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C615" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B616" s="3" t="s">
@@ -5323,7 +5329,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5402,10 +5408,13 @@
       <c r="B628" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C628" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5484,13 +5493,10 @@
       <c r="B639" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C639" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5559,9 +5565,6 @@
       <c r="B648" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C648" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B649" s="3" t="s">
@@ -5578,7 +5581,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5599,19 +5602,25 @@
       <c r="B653" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C653" s="6"/>
+      <c r="C653" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B654" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C654" s="6"/>
+      <c r="C654" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B655" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C655" s="6"/>
+      <c r="C655" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="656" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B656" s="3" t="s">
@@ -5633,12 +5642,17 @@
       <c r="B658" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C658" s="6"/>
+      <c r="C658" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B659" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C659" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B660" s="3" t="s">
@@ -5649,10 +5663,13 @@
       <c r="B661" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C661" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5673,25 +5690,19 @@
       <c r="B664" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C664" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C664" s="6"/>
     </row>
     <row r="665" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B665" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C665" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C665" s="6"/>
     </row>
     <row r="666" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B666" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C666" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C666" s="6"/>
     </row>
     <row r="667" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B667" s="3" t="s">
@@ -5713,17 +5724,12 @@
       <c r="B669" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C669" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C669" s="6"/>
     </row>
     <row r="670" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B670" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C670" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="671" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B671" s="3" t="s">
@@ -5734,13 +5740,10 @@
       <c r="B672" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C672" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5828,7 +5831,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -5897,6 +5900,9 @@
       <c r="B692" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C692" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="693" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B693" s="3" t="s">
@@ -5913,7 +5919,7 @@
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -5982,9 +5988,6 @@
       <c r="B703" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C703" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="704" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B704" s="3" t="s">
@@ -5992,19 +5995,19 @@
       </c>
     </row>
     <row r="705" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A705" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B705" s="7" t="s">
-        <v>3</v>
+      <c r="B705" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C705" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B706" s="3" t="s">
-        <v>4</v>
+      <c r="A706" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B706" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C706" s="5" t="s">
         <v>13</v>
@@ -6012,7 +6015,7 @@
     </row>
     <row r="707" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B707" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C707" s="5" t="s">
         <v>13</v>
@@ -6020,7 +6023,7 @@
     </row>
     <row r="708" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B708" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C708" s="5" t="s">
         <v>13</v>
@@ -6028,7 +6031,7 @@
     </row>
     <row r="709" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B709" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C709" s="5" t="s">
         <v>13</v>
@@ -6036,7 +6039,7 @@
     </row>
     <row r="710" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B710" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C710" s="5" t="s">
         <v>13</v>
@@ -6044,7 +6047,7 @@
     </row>
     <row r="711" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B711" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C711" s="5" t="s">
         <v>13</v>
@@ -6052,7 +6055,7 @@
     </row>
     <row r="712" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B712" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C712" s="5" t="s">
         <v>13</v>
@@ -6060,7 +6063,7 @@
     </row>
     <row r="713" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B713" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C713" s="5" t="s">
         <v>13</v>
@@ -6068,23 +6071,23 @@
     </row>
     <row r="714" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B714" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C714" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="715" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A715" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B715" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C715" s="5" t="s">
-        <v>13</v>
+      <c r="B715" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="716" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B716" s="3" t="s">
-        <v>4</v>
+      <c r="A716" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B716" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C716" s="5" t="s">
         <v>13</v>
@@ -6092,7 +6095,7 @@
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B717" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C717" s="5" t="s">
         <v>13</v>
@@ -6100,7 +6103,7 @@
     </row>
     <row r="718" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B718" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C718" s="5" t="s">
         <v>13</v>
@@ -6108,7 +6111,7 @@
     </row>
     <row r="719" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B719" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C719" s="5" t="s">
         <v>13</v>
@@ -6116,40 +6119,128 @@
     </row>
     <row r="720" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B720" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C720" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="721" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B721" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C721" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="722" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B722" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C722" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="723" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B723" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="724" spans="2:3" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="C723" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="724" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B724" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="725" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B725" s="3">
+        <v>11</v>
+      </c>
+      <c r="C724" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="725" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B725" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="726" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A726" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B726" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C726" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="727" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B727" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C727" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="728" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B728" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C728" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="729" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B729" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C729" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="730" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B730" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C730" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="731" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B731" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C731" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="732" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B732" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C732" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="733" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B733" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C733" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="734" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B734" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="735" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B735" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="736" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B736" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62AB5C83-1545-40E6-A86B-56452CE49E1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC1A0434-9028-462C-8BA6-1BB242B10017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1358" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1380" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C736"/>
+  <dimension ref="A1:C747"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -650,7 +650,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -741,7 +741,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -832,7 +832,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -923,7 +923,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -1014,7 +1014,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1083,6 +1083,9 @@
       <c r="B76" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C76" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B77" s="3" t="s">
@@ -1102,7 +1105,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1171,9 +1174,6 @@
       <c r="B87" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C87" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B88" s="3" t="s">
@@ -1193,7 +1193,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1270,6 +1270,9 @@
       <c r="B99" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C99" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B100" s="3" t="s">
@@ -1281,7 +1284,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1350,6 +1353,9 @@
       <c r="B109" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C109" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B110" s="3" t="s">
@@ -1366,7 +1372,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1435,9 +1441,6 @@
       <c r="B120" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C120" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B121" s="3" t="s">
@@ -1454,7 +1457,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1523,6 +1526,9 @@
       <c r="B131" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C131" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B132" s="3" t="s">
@@ -1539,7 +1545,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1608,9 +1614,6 @@
       <c r="B142" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C142" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B143" s="3" t="s">
@@ -1627,7 +1630,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1715,7 +1718,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1803,7 +1806,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1872,6 +1875,9 @@
       <c r="B175" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C175" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B176" s="3" t="s">
@@ -1888,7 +1894,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1973,7 +1979,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2058,7 +2064,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2143,7 +2149,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2228,7 +2234,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2313,7 +2319,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2398,7 +2404,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2483,7 +2489,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2568,7 +2574,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2653,7 +2659,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2738,7 +2744,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2823,7 +2829,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2892,9 +2898,6 @@
       <c r="B307" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C307" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B308" s="3" t="s">
@@ -2911,7 +2914,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -2980,6 +2983,9 @@
       <c r="B318" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C318" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B319" s="3" t="s">
@@ -2996,7 +3002,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3081,7 +3087,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3166,7 +3172,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3235,9 +3241,6 @@
       <c r="B351" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C351" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B352" s="3" t="s">
@@ -3254,7 +3257,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3342,7 +3345,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3411,6 +3414,9 @@
       <c r="B373" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C373" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B374" s="3" t="s">
@@ -3427,7 +3433,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3512,7 +3518,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3597,7 +3603,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3682,7 +3688,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3751,9 +3757,6 @@
       <c r="B417" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C417" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B418" s="3" t="s">
@@ -3770,7 +3773,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3858,7 +3861,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3935,9 +3938,6 @@
       <c r="B440" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C440" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B441" s="3" t="s">
@@ -3949,7 +3949,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4026,6 +4026,9 @@
       <c r="B451" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C451" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B452" s="3" t="s">
@@ -4037,7 +4040,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4125,7 +4128,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4213,7 +4216,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4301,7 +4304,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4389,7 +4392,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4458,6 +4461,9 @@
       <c r="B505" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C505" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B506" s="3" t="s">
@@ -4474,7 +4480,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4535,7 +4541,9 @@
       <c r="B515" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C515" s="6"/>
+      <c r="C515" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B516" s="3" t="s">
@@ -4551,10 +4559,13 @@
       <c r="B518" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C518" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4615,17 +4626,12 @@
       <c r="B526" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C526" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C526" s="6"/>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B527" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C527" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B528" s="3" t="s">
@@ -4636,13 +4642,10 @@
       <c r="B529" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C529" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4730,7 +4733,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4818,7 +4821,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4887,6 +4890,9 @@
       <c r="B560" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C560" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B561" s="3" t="s">
@@ -4903,7 +4909,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -4988,7 +4994,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5062,9 +5068,6 @@
       <c r="B583" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C583" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B584" s="3" t="s">
@@ -5076,7 +5079,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5137,7 +5140,9 @@
       <c r="B592" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C592" s="6"/>
+      <c r="C592" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B593" s="3" t="s">
@@ -5148,15 +5153,21 @@
       <c r="B594" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C594" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B595" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C595" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5217,9 +5228,7 @@
       <c r="B603" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C603" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C603" s="6"/>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B604" s="3" t="s">
@@ -5235,13 +5244,10 @@
       <c r="B606" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C606" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5310,9 +5316,6 @@
       <c r="B615" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C615" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B616" s="3" t="s">
@@ -5329,7 +5332,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5398,6 +5401,9 @@
       <c r="B626" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C626" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B627" s="3" t="s">
@@ -5414,7 +5420,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5493,10 +5499,13 @@
       <c r="B639" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C639" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5575,13 +5584,10 @@
       <c r="B650" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C650" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5650,9 +5656,6 @@
       <c r="B659" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C659" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B660" s="3" t="s">
@@ -5669,7 +5672,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5690,19 +5693,25 @@
       <c r="B664" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C664" s="6"/>
+      <c r="C664" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="665" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B665" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C665" s="6"/>
+      <c r="C665" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="666" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B666" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C666" s="6"/>
+      <c r="C666" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="667" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B667" s="3" t="s">
@@ -5724,12 +5733,17 @@
       <c r="B669" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C669" s="6"/>
+      <c r="C669" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="670" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B670" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C670" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="671" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B671" s="3" t="s">
@@ -5740,10 +5754,13 @@
       <c r="B672" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C672" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5764,25 +5781,19 @@
       <c r="B675" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C675" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C675" s="6"/>
     </row>
     <row r="676" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B676" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C676" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C676" s="6"/>
     </row>
     <row r="677" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B677" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C677" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C677" s="6"/>
     </row>
     <row r="678" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B678" s="3" t="s">
@@ -5804,17 +5815,12 @@
       <c r="B680" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C680" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C680" s="6"/>
     </row>
     <row r="681" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B681" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C681" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="682" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B682" s="3" t="s">
@@ -5825,13 +5831,10 @@
       <c r="B683" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C683" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -5919,7 +5922,7 @@
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -5988,6 +5991,9 @@
       <c r="B703" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C703" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="704" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B704" s="3" t="s">
@@ -6004,7 +6010,7 @@
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6073,9 +6079,6 @@
       <c r="B714" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C714" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="715" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B715" s="3" t="s">
@@ -6083,19 +6086,19 @@
       </c>
     </row>
     <row r="716" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A716" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B716" s="7" t="s">
-        <v>3</v>
+      <c r="B716" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C716" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B717" s="3" t="s">
-        <v>4</v>
+      <c r="A717" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B717" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C717" s="5" t="s">
         <v>13</v>
@@ -6103,7 +6106,7 @@
     </row>
     <row r="718" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B718" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C718" s="5" t="s">
         <v>13</v>
@@ -6111,7 +6114,7 @@
     </row>
     <row r="719" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B719" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C719" s="5" t="s">
         <v>13</v>
@@ -6119,7 +6122,7 @@
     </row>
     <row r="720" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B720" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C720" s="5" t="s">
         <v>13</v>
@@ -6127,7 +6130,7 @@
     </row>
     <row r="721" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B721" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C721" s="5" t="s">
         <v>13</v>
@@ -6135,7 +6138,7 @@
     </row>
     <row r="722" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B722" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C722" s="5" t="s">
         <v>13</v>
@@ -6143,7 +6146,7 @@
     </row>
     <row r="723" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B723" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C723" s="5" t="s">
         <v>13</v>
@@ -6151,7 +6154,7 @@
     </row>
     <row r="724" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B724" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C724" s="5" t="s">
         <v>13</v>
@@ -6159,23 +6162,23 @@
     </row>
     <row r="725" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B725" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C725" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="726" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A726" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B726" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C726" s="5" t="s">
-        <v>13</v>
+      <c r="B726" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="727" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B727" s="3" t="s">
-        <v>4</v>
+      <c r="A727" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B727" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C727" s="5" t="s">
         <v>13</v>
@@ -6183,7 +6186,7 @@
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B728" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C728" s="5" t="s">
         <v>13</v>
@@ -6191,7 +6194,7 @@
     </row>
     <row r="729" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B729" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C729" s="5" t="s">
         <v>13</v>
@@ -6199,7 +6202,7 @@
     </row>
     <row r="730" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B730" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C730" s="5" t="s">
         <v>13</v>
@@ -6207,7 +6210,7 @@
     </row>
     <row r="731" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B731" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C731" s="5" t="s">
         <v>13</v>
@@ -6215,7 +6218,7 @@
     </row>
     <row r="732" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B732" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C732" s="5" t="s">
         <v>13</v>
@@ -6223,7 +6226,7 @@
     </row>
     <row r="733" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B733" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C733" s="5" t="s">
         <v>13</v>
@@ -6231,16 +6234,104 @@
     </row>
     <row r="734" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B734" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C734" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="735" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B735" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C735" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="736" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B736" s="3">
+      <c r="B736" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="737" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A737" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B737" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C737" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="738" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B738" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C738" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="739" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B739" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C739" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="740" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B740" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C740" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="741" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B741" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C741" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="742" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B742" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C742" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="743" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B743" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C743" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="744" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B744" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C744" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="745" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B745" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="746" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B746" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="747" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B747" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC1A0434-9028-462C-8BA6-1BB242B10017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47C3F4E0-0138-4282-B329-B5576DF85BEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1380" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1402" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C747"/>
+  <dimension ref="A1:C758"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -650,7 +650,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -741,7 +741,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -832,7 +832,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -923,7 +923,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -1014,7 +1014,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1105,7 +1105,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1174,6 +1174,9 @@
       <c r="B87" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C87" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B88" s="3" t="s">
@@ -1193,7 +1196,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1262,9 +1265,6 @@
       <c r="B98" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C98" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B99" s="3" t="s">
@@ -1284,7 +1284,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1361,6 +1361,9 @@
       <c r="B110" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C110" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B111" s="3" t="s">
@@ -1372,7 +1375,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1441,6 +1444,9 @@
       <c r="B120" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C120" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B121" s="3" t="s">
@@ -1457,7 +1463,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1526,9 +1532,6 @@
       <c r="B131" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C131" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B132" s="3" t="s">
@@ -1545,7 +1548,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1614,6 +1617,9 @@
       <c r="B142" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C142" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B143" s="3" t="s">
@@ -1630,7 +1636,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1699,9 +1705,6 @@
       <c r="B153" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C153" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B154" s="3" t="s">
@@ -1718,7 +1721,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1806,7 +1809,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1894,7 +1897,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1963,6 +1966,9 @@
       <c r="B186" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C186" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B187" s="3" t="s">
@@ -1979,7 +1985,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2064,7 +2070,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2149,7 +2155,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2234,7 +2240,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2319,7 +2325,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2404,7 +2410,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2489,7 +2495,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2574,7 +2580,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2659,7 +2665,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2744,7 +2750,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2829,7 +2835,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2914,7 +2920,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -2983,9 +2989,6 @@
       <c r="B318" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C318" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B319" s="3" t="s">
@@ -3002,7 +3005,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3071,6 +3074,9 @@
       <c r="B329" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C329" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B330" s="3" t="s">
@@ -3087,7 +3093,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3172,7 +3178,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3257,7 +3263,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3326,9 +3332,6 @@
       <c r="B362" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C362" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B363" s="3" t="s">
@@ -3345,7 +3348,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3433,7 +3436,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3502,6 +3505,9 @@
       <c r="B384" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C384" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B385" s="3" t="s">
@@ -3518,7 +3524,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3603,7 +3609,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3688,7 +3694,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3773,7 +3779,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3842,9 +3848,6 @@
       <c r="B428" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C428" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B429" s="3" t="s">
@@ -3861,7 +3864,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3949,7 +3952,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4026,9 +4029,6 @@
       <c r="B451" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C451" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B452" s="3" t="s">
@@ -4040,7 +4040,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4117,6 +4117,9 @@
       <c r="B462" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C462" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B463" s="3" t="s">
@@ -4128,7 +4131,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4216,7 +4219,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4304,7 +4307,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4392,7 +4395,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4480,7 +4483,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4549,6 +4552,9 @@
       <c r="B516" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C516" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B517" s="3" t="s">
@@ -4565,7 +4571,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4626,7 +4632,9 @@
       <c r="B526" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C526" s="6"/>
+      <c r="C526" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B527" s="3" t="s">
@@ -4642,10 +4650,13 @@
       <c r="B529" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C529" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4706,17 +4717,12 @@
       <c r="B537" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C537" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C537" s="6"/>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B538" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C538" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B539" s="3" t="s">
@@ -4727,13 +4733,10 @@
       <c r="B540" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C540" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4821,7 +4824,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4909,7 +4912,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -4978,6 +4981,9 @@
       <c r="B571" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C571" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B572" s="3" t="s">
@@ -4994,7 +5000,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5079,7 +5085,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5153,9 +5159,6 @@
       <c r="B594" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C594" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B595" s="3" t="s">
@@ -5167,7 +5170,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5228,7 +5231,9 @@
       <c r="B603" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C603" s="6"/>
+      <c r="C603" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B604" s="3" t="s">
@@ -5239,15 +5244,21 @@
       <c r="B605" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C605" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B606" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C606" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5308,9 +5319,7 @@
       <c r="B614" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C614" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C614" s="6"/>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B615" s="3" t="s">
@@ -5326,13 +5335,10 @@
       <c r="B617" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C617" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5401,9 +5407,6 @@
       <c r="B626" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C626" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B627" s="3" t="s">
@@ -5420,7 +5423,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5489,6 +5492,9 @@
       <c r="B637" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C637" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B638" s="3" t="s">
@@ -5505,7 +5511,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5584,10 +5590,13 @@
       <c r="B650" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C650" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5666,13 +5675,10 @@
       <c r="B661" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C661" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5741,9 +5747,6 @@
       <c r="B670" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C670" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="671" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B671" s="3" t="s">
@@ -5760,7 +5763,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5781,19 +5784,25 @@
       <c r="B675" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C675" s="6"/>
+      <c r="C675" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="676" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B676" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C676" s="6"/>
+      <c r="C676" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="677" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B677" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C677" s="6"/>
+      <c r="C677" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="678" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B678" s="3" t="s">
@@ -5815,12 +5824,17 @@
       <c r="B680" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C680" s="6"/>
+      <c r="C680" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="681" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B681" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C681" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="682" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B682" s="3" t="s">
@@ -5831,10 +5845,13 @@
       <c r="B683" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C683" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -5855,25 +5872,19 @@
       <c r="B686" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C686" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C686" s="6"/>
     </row>
     <row r="687" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B687" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C687" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C687" s="6"/>
     </row>
     <row r="688" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B688" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C688" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C688" s="6"/>
     </row>
     <row r="689" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B689" s="3" t="s">
@@ -5895,17 +5906,12 @@
       <c r="B691" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C691" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C691" s="6"/>
     </row>
     <row r="692" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B692" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C692" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="693" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B693" s="3" t="s">
@@ -5916,13 +5922,10 @@
       <c r="B694" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C694" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6010,7 +6013,7 @@
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6079,6 +6082,9 @@
       <c r="B714" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C714" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="715" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B715" s="3" t="s">
@@ -6095,7 +6101,7 @@
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6164,9 +6170,6 @@
       <c r="B725" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C725" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="726" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B726" s="3" t="s">
@@ -6174,19 +6177,19 @@
       </c>
     </row>
     <row r="727" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A727" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B727" s="7" t="s">
-        <v>3</v>
+      <c r="B727" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C727" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B728" s="3" t="s">
-        <v>4</v>
+      <c r="A728" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B728" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C728" s="5" t="s">
         <v>13</v>
@@ -6194,7 +6197,7 @@
     </row>
     <row r="729" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B729" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C729" s="5" t="s">
         <v>13</v>
@@ -6202,7 +6205,7 @@
     </row>
     <row r="730" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B730" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C730" s="5" t="s">
         <v>13</v>
@@ -6210,7 +6213,7 @@
     </row>
     <row r="731" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B731" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C731" s="5" t="s">
         <v>13</v>
@@ -6218,7 +6221,7 @@
     </row>
     <row r="732" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B732" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C732" s="5" t="s">
         <v>13</v>
@@ -6226,7 +6229,7 @@
     </row>
     <row r="733" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B733" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C733" s="5" t="s">
         <v>13</v>
@@ -6234,7 +6237,7 @@
     </row>
     <row r="734" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B734" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C734" s="5" t="s">
         <v>13</v>
@@ -6242,7 +6245,7 @@
     </row>
     <row r="735" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B735" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C735" s="5" t="s">
         <v>13</v>
@@ -6250,23 +6253,23 @@
     </row>
     <row r="736" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B736" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C736" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="737" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A737" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B737" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C737" s="5" t="s">
-        <v>13</v>
+      <c r="B737" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="738" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B738" s="3" t="s">
-        <v>4</v>
+      <c r="A738" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B738" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C738" s="5" t="s">
         <v>13</v>
@@ -6274,7 +6277,7 @@
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B739" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C739" s="5" t="s">
         <v>13</v>
@@ -6282,7 +6285,7 @@
     </row>
     <row r="740" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B740" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C740" s="5" t="s">
         <v>13</v>
@@ -6290,7 +6293,7 @@
     </row>
     <row r="741" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B741" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C741" s="5" t="s">
         <v>13</v>
@@ -6298,7 +6301,7 @@
     </row>
     <row r="742" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B742" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C742" s="5" t="s">
         <v>13</v>
@@ -6306,7 +6309,7 @@
     </row>
     <row r="743" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B743" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C743" s="5" t="s">
         <v>13</v>
@@ -6314,7 +6317,7 @@
     </row>
     <row r="744" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B744" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C744" s="5" t="s">
         <v>13</v>
@@ -6322,16 +6325,104 @@
     </row>
     <row r="745" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B745" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C745" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="746" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B746" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C746" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="747" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B747" s="3">
+      <c r="B747" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="748" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A748" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B748" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C748" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="749" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B749" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C749" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="750" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B750" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C750" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="751" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B751" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C751" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="752" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B752" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C752" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="753" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B753" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C753" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="754" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B754" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C754" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="755" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B755" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C755" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="756" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B756" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="757" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B757" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="758" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B758" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47C3F4E0-0138-4282-B329-B5576DF85BEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90807B0C-E821-4BF5-BF49-F79BC0E1B372}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1402" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1424" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C758"/>
+  <dimension ref="A1:C769"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -650,7 +650,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -741,7 +741,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -832,7 +832,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -923,7 +923,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -1014,7 +1014,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1105,7 +1105,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1196,7 +1196,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1265,6 +1265,9 @@
       <c r="B98" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C98" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B99" s="3" t="s">
@@ -1284,7 +1287,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1353,9 +1356,6 @@
       <c r="B109" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C109" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B110" s="3" t="s">
@@ -1375,7 +1375,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1452,6 +1452,9 @@
       <c r="B121" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C121" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B122" s="3" t="s">
@@ -1463,7 +1466,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1532,6 +1535,9 @@
       <c r="B131" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C131" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B132" s="3" t="s">
@@ -1548,7 +1554,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1617,9 +1623,6 @@
       <c r="B142" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C142" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B143" s="3" t="s">
@@ -1636,7 +1639,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1705,6 +1708,9 @@
       <c r="B153" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C153" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B154" s="3" t="s">
@@ -1721,7 +1727,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1790,9 +1796,6 @@
       <c r="B164" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C164" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B165" s="3" t="s">
@@ -1809,7 +1812,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1897,7 +1900,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1985,7 +1988,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2054,6 +2057,9 @@
       <c r="B197" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C197" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B198" s="3" t="s">
@@ -2070,7 +2076,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2155,7 +2161,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2240,7 +2246,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2325,7 +2331,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2410,7 +2416,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2495,7 +2501,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2580,7 +2586,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2665,7 +2671,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2750,7 +2756,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2835,7 +2841,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2920,7 +2926,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3005,7 +3011,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3074,9 +3080,6 @@
       <c r="B329" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C329" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B330" s="3" t="s">
@@ -3093,7 +3096,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3162,6 +3165,9 @@
       <c r="B340" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C340" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B341" s="3" t="s">
@@ -3178,7 +3184,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3263,7 +3269,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3348,7 +3354,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3417,9 +3423,6 @@
       <c r="B373" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C373" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B374" s="3" t="s">
@@ -3436,7 +3439,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3524,7 +3527,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3593,6 +3596,9 @@
       <c r="B395" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C395" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B396" s="3" t="s">
@@ -3609,7 +3615,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3694,7 +3700,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3779,7 +3785,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3864,7 +3870,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3933,9 +3939,6 @@
       <c r="B439" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C439" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B440" s="3" t="s">
@@ -3952,7 +3955,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4040,7 +4043,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4117,9 +4120,6 @@
       <c r="B462" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C462" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B463" s="3" t="s">
@@ -4131,7 +4131,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4208,6 +4208,9 @@
       <c r="B473" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C473" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B474" s="3" t="s">
@@ -4219,7 +4222,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4307,7 +4310,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4395,7 +4398,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4483,7 +4486,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4571,7 +4574,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4640,6 +4643,9 @@
       <c r="B527" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C527" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B528" s="3" t="s">
@@ -4656,7 +4662,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4717,7 +4723,9 @@
       <c r="B537" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C537" s="6"/>
+      <c r="C537" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B538" s="3" t="s">
@@ -4733,10 +4741,13 @@
       <c r="B540" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C540" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4797,17 +4808,12 @@
       <c r="B548" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C548" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C548" s="6"/>
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B549" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C549" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B550" s="3" t="s">
@@ -4818,13 +4824,10 @@
       <c r="B551" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C551" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4912,7 +4915,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5000,7 +5003,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5069,6 +5072,9 @@
       <c r="B582" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C582" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B583" s="3" t="s">
@@ -5085,7 +5091,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5170,7 +5176,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5244,9 +5250,6 @@
       <c r="B605" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C605" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B606" s="3" t="s">
@@ -5258,7 +5261,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5319,7 +5322,9 @@
       <c r="B614" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C614" s="6"/>
+      <c r="C614" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B615" s="3" t="s">
@@ -5330,15 +5335,21 @@
       <c r="B616" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C616" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B617" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C617" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5399,9 +5410,7 @@
       <c r="B625" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C625" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C625" s="6"/>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B626" s="3" t="s">
@@ -5417,13 +5426,10 @@
       <c r="B628" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C628" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5492,9 +5498,6 @@
       <c r="B637" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C637" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B638" s="3" t="s">
@@ -5511,7 +5514,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5580,6 +5583,9 @@
       <c r="B648" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C648" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B649" s="3" t="s">
@@ -5596,7 +5602,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5675,10 +5681,13 @@
       <c r="B661" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C661" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5757,13 +5766,10 @@
       <c r="B672" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C672" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5832,9 +5838,6 @@
       <c r="B681" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C681" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="682" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B682" s="3" t="s">
@@ -5851,7 +5854,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -5872,19 +5875,25 @@
       <c r="B686" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C686" s="6"/>
+      <c r="C686" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="687" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B687" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C687" s="6"/>
+      <c r="C687" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="688" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B688" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C688" s="6"/>
+      <c r="C688" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="689" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B689" s="3" t="s">
@@ -5906,12 +5915,17 @@
       <c r="B691" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C691" s="6"/>
+      <c r="C691" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="692" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B692" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C692" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="693" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B693" s="3" t="s">
@@ -5922,10 +5936,13 @@
       <c r="B694" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C694" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -5946,25 +5963,19 @@
       <c r="B697" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C697" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C697" s="6"/>
     </row>
     <row r="698" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B698" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C698" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C698" s="6"/>
     </row>
     <row r="699" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B699" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C699" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C699" s="6"/>
     </row>
     <row r="700" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B700" s="3" t="s">
@@ -5986,17 +5997,12 @@
       <c r="B702" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C702" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C702" s="6"/>
     </row>
     <row r="703" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B703" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C703" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="704" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B704" s="3" t="s">
@@ -6007,13 +6013,10 @@
       <c r="B705" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C705" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6101,7 +6104,7 @@
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6170,6 +6173,9 @@
       <c r="B725" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C725" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="726" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B726" s="3" t="s">
@@ -6186,7 +6192,7 @@
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6255,9 +6261,6 @@
       <c r="B736" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C736" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="737" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B737" s="3" t="s">
@@ -6265,19 +6268,19 @@
       </c>
     </row>
     <row r="738" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A738" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B738" s="7" t="s">
-        <v>3</v>
+      <c r="B738" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C738" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B739" s="3" t="s">
-        <v>4</v>
+      <c r="A739" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B739" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C739" s="5" t="s">
         <v>13</v>
@@ -6285,7 +6288,7 @@
     </row>
     <row r="740" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B740" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C740" s="5" t="s">
         <v>13</v>
@@ -6293,7 +6296,7 @@
     </row>
     <row r="741" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B741" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C741" s="5" t="s">
         <v>13</v>
@@ -6301,7 +6304,7 @@
     </row>
     <row r="742" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B742" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C742" s="5" t="s">
         <v>13</v>
@@ -6309,7 +6312,7 @@
     </row>
     <row r="743" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B743" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C743" s="5" t="s">
         <v>13</v>
@@ -6317,7 +6320,7 @@
     </row>
     <row r="744" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B744" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C744" s="5" t="s">
         <v>13</v>
@@ -6325,7 +6328,7 @@
     </row>
     <row r="745" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B745" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C745" s="5" t="s">
         <v>13</v>
@@ -6333,7 +6336,7 @@
     </row>
     <row r="746" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B746" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C746" s="5" t="s">
         <v>13</v>
@@ -6341,23 +6344,23 @@
     </row>
     <row r="747" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B747" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C747" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="748" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A748" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B748" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C748" s="5" t="s">
-        <v>13</v>
+      <c r="B748" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="749" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B749" s="3" t="s">
-        <v>4</v>
+      <c r="A749" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B749" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C749" s="5" t="s">
         <v>13</v>
@@ -6365,7 +6368,7 @@
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B750" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C750" s="5" t="s">
         <v>13</v>
@@ -6373,7 +6376,7 @@
     </row>
     <row r="751" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B751" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C751" s="5" t="s">
         <v>13</v>
@@ -6381,48 +6384,136 @@
     </row>
     <row r="752" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B752" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C752" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="753" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="753" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B753" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C753" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="754" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B754" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C754" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="755" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B755" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C755" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="756" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B756" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="757" spans="2:3" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="C756" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="757" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B757" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="758" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B758" s="3">
+        <v>11</v>
+      </c>
+      <c r="C757" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="758" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B758" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="759" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A759" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B759" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C759" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="760" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B760" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C760" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="761" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B761" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C761" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="762" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B762" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C762" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="763" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B763" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C763" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="764" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B764" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C764" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="765" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B765" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C765" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="766" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B766" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C766" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="767" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B767" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="768" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B768" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="769" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B769" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90807B0C-E821-4BF5-BF49-F79BC0E1B372}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0414D08C-9C8A-409C-B51C-155BD2F6076A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1424" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1446" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C769"/>
+  <dimension ref="A1:C780"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -650,7 +650,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -741,7 +741,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -832,7 +832,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -923,7 +923,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -1014,7 +1014,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1105,7 +1105,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1196,7 +1196,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1356,6 +1356,9 @@
       <c r="B109" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C109" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B110" s="3" t="s">
@@ -1375,7 +1378,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1444,9 +1447,6 @@
       <c r="B120" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C120" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B121" s="3" t="s">
@@ -1466,7 +1466,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1543,6 +1543,9 @@
       <c r="B132" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C132" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B133" s="3" t="s">
@@ -1554,7 +1557,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1623,6 +1626,9 @@
       <c r="B142" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C142" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B143" s="3" t="s">
@@ -1639,7 +1645,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1708,9 +1714,6 @@
       <c r="B153" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C153" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B154" s="3" t="s">
@@ -1727,7 +1730,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1796,6 +1799,9 @@
       <c r="B164" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C164" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B165" s="3" t="s">
@@ -1812,7 +1818,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1881,9 +1887,6 @@
       <c r="B175" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C175" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B176" s="3" t="s">
@@ -1900,7 +1903,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1988,7 +1991,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2076,7 +2079,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2145,6 +2148,9 @@
       <c r="B208" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C208" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B209" s="3" t="s">
@@ -2161,7 +2167,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2246,7 +2252,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2331,7 +2337,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2416,7 +2422,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2501,7 +2507,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2586,7 +2592,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2671,7 +2677,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2756,7 +2762,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2841,7 +2847,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2926,7 +2932,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3011,7 +3017,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3096,7 +3102,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3165,9 +3171,6 @@
       <c r="B340" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C340" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B341" s="3" t="s">
@@ -3184,7 +3187,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3253,6 +3256,9 @@
       <c r="B351" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C351" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B352" s="3" t="s">
@@ -3269,7 +3275,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3354,7 +3360,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3439,7 +3445,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3508,9 +3514,6 @@
       <c r="B384" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C384" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B385" s="3" t="s">
@@ -3527,7 +3530,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3615,7 +3618,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3684,6 +3687,9 @@
       <c r="B406" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C406" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B407" s="3" t="s">
@@ -3700,7 +3706,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3785,7 +3791,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3870,7 +3876,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3955,7 +3961,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4024,9 +4030,6 @@
       <c r="B450" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C450" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B451" s="3" t="s">
@@ -4043,7 +4046,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4131,7 +4134,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4208,9 +4211,6 @@
       <c r="B473" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C473" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B474" s="3" t="s">
@@ -4222,7 +4222,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4299,6 +4299,9 @@
       <c r="B484" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C484" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B485" s="3" t="s">
@@ -4310,7 +4313,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4398,7 +4401,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4486,7 +4489,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4574,7 +4577,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4662,7 +4665,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4731,6 +4734,9 @@
       <c r="B538" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C538" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B539" s="3" t="s">
@@ -4747,7 +4753,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4808,7 +4814,9 @@
       <c r="B548" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C548" s="6"/>
+      <c r="C548" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B549" s="3" t="s">
@@ -4824,10 +4832,13 @@
       <c r="B551" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C551" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4888,17 +4899,12 @@
       <c r="B559" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C559" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C559" s="6"/>
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B560" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C560" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B561" s="3" t="s">
@@ -4909,13 +4915,10 @@
       <c r="B562" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C562" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5003,7 +5006,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5091,7 +5094,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5160,6 +5163,9 @@
       <c r="B593" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C593" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B594" s="3" t="s">
@@ -5176,7 +5182,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5261,7 +5267,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5335,9 +5341,6 @@
       <c r="B616" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C616" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B617" s="3" t="s">
@@ -5349,7 +5352,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5410,7 +5413,9 @@
       <c r="B625" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C625" s="6"/>
+      <c r="C625" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B626" s="3" t="s">
@@ -5421,15 +5426,21 @@
       <c r="B627" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C627" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B628" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C628" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5490,9 +5501,7 @@
       <c r="B636" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C636" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C636" s="6"/>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B637" s="3" t="s">
@@ -5508,13 +5517,10 @@
       <c r="B639" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C639" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5583,9 +5589,6 @@
       <c r="B648" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C648" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B649" s="3" t="s">
@@ -5602,7 +5605,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5671,6 +5674,9 @@
       <c r="B659" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C659" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B660" s="3" t="s">
@@ -5687,7 +5693,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5766,10 +5772,13 @@
       <c r="B672" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C672" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5848,13 +5857,10 @@
       <c r="B683" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C683" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -5923,9 +5929,6 @@
       <c r="B692" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C692" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="693" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B693" s="3" t="s">
@@ -5942,7 +5945,7 @@
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -5963,19 +5966,25 @@
       <c r="B697" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C697" s="6"/>
+      <c r="C697" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="698" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B698" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C698" s="6"/>
+      <c r="C698" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="699" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B699" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C699" s="6"/>
+      <c r="C699" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="700" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B700" s="3" t="s">
@@ -5997,12 +6006,17 @@
       <c r="B702" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C702" s="6"/>
+      <c r="C702" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="703" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B703" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C703" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="704" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B704" s="3" t="s">
@@ -6013,10 +6027,13 @@
       <c r="B705" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C705" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6037,25 +6054,19 @@
       <c r="B708" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C708" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C708" s="6"/>
     </row>
     <row r="709" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B709" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C709" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C709" s="6"/>
     </row>
     <row r="710" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B710" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C710" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C710" s="6"/>
     </row>
     <row r="711" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B711" s="3" t="s">
@@ -6077,17 +6088,12 @@
       <c r="B713" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C713" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C713" s="6"/>
     </row>
     <row r="714" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B714" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C714" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="715" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B715" s="3" t="s">
@@ -6098,13 +6104,10 @@
       <c r="B716" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C716" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6192,7 +6195,7 @@
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6261,6 +6264,9 @@
       <c r="B736" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C736" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="737" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B737" s="3" t="s">
@@ -6277,7 +6283,7 @@
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6346,9 +6352,6 @@
       <c r="B747" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C747" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="748" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B748" s="3" t="s">
@@ -6356,19 +6359,19 @@
       </c>
     </row>
     <row r="749" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A749" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B749" s="7" t="s">
-        <v>3</v>
+      <c r="B749" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C749" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B750" s="3" t="s">
-        <v>4</v>
+      <c r="A750" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B750" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C750" s="5" t="s">
         <v>13</v>
@@ -6376,7 +6379,7 @@
     </row>
     <row r="751" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B751" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C751" s="5" t="s">
         <v>13</v>
@@ -6384,7 +6387,7 @@
     </row>
     <row r="752" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B752" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C752" s="5" t="s">
         <v>13</v>
@@ -6392,7 +6395,7 @@
     </row>
     <row r="753" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B753" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C753" s="5" t="s">
         <v>13</v>
@@ -6400,7 +6403,7 @@
     </row>
     <row r="754" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B754" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C754" s="5" t="s">
         <v>13</v>
@@ -6408,7 +6411,7 @@
     </row>
     <row r="755" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B755" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C755" s="5" t="s">
         <v>13</v>
@@ -6416,7 +6419,7 @@
     </row>
     <row r="756" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B756" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C756" s="5" t="s">
         <v>13</v>
@@ -6424,7 +6427,7 @@
     </row>
     <row r="757" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B757" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C757" s="5" t="s">
         <v>13</v>
@@ -6432,23 +6435,23 @@
     </row>
     <row r="758" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B758" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C758" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="759" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A759" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B759" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C759" s="5" t="s">
-        <v>13</v>
+      <c r="B759" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="760" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B760" s="3" t="s">
-        <v>4</v>
+      <c r="A760" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B760" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C760" s="5" t="s">
         <v>13</v>
@@ -6456,7 +6459,7 @@
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B761" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C761" s="5" t="s">
         <v>13</v>
@@ -6464,7 +6467,7 @@
     </row>
     <row r="762" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B762" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C762" s="5" t="s">
         <v>13</v>
@@ -6472,7 +6475,7 @@
     </row>
     <row r="763" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B763" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C763" s="5" t="s">
         <v>13</v>
@@ -6480,7 +6483,7 @@
     </row>
     <row r="764" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B764" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C764" s="5" t="s">
         <v>13</v>
@@ -6488,7 +6491,7 @@
     </row>
     <row r="765" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B765" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C765" s="5" t="s">
         <v>13</v>
@@ -6496,7 +6499,7 @@
     </row>
     <row r="766" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B766" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C766" s="5" t="s">
         <v>13</v>
@@ -6504,16 +6507,104 @@
     </row>
     <row r="767" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B767" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C767" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="768" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B768" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="769" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B769" s="3">
+        <v>11</v>
+      </c>
+      <c r="C768" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="769" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B769" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="770" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A770" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B770" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C770" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="771" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B771" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C771" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="772" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B772" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C772" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="773" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B773" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C773" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="774" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B774" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C774" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="775" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B775" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C775" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="776" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B776" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C776" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="777" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B777" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C777" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="778" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B778" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="779" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B779" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="780" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B780" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0414D08C-9C8A-409C-B51C-155BD2F6076A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6330C535-E6B5-4A14-A1CE-FEA09C0D394E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1446" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1468" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C780"/>
+  <dimension ref="A1:C791"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -650,7 +650,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -741,7 +741,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -832,7 +832,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -923,7 +923,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -1014,7 +1014,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1105,7 +1105,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1196,7 +1196,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1378,7 +1378,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1447,6 +1447,9 @@
       <c r="B120" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C120" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B121" s="3" t="s">
@@ -1466,7 +1469,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1535,9 +1538,6 @@
       <c r="B131" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C131" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B132" s="3" t="s">
@@ -1557,7 +1557,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1634,6 +1634,9 @@
       <c r="B143" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C143" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B144" s="3" t="s">
@@ -1645,7 +1648,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1714,6 +1717,9 @@
       <c r="B153" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C153" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B154" s="3" t="s">
@@ -1730,7 +1736,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1799,9 +1805,6 @@
       <c r="B164" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C164" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B165" s="3" t="s">
@@ -1818,7 +1821,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1887,6 +1890,9 @@
       <c r="B175" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C175" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B176" s="3" t="s">
@@ -1903,7 +1909,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1972,9 +1978,6 @@
       <c r="B186" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C186" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B187" s="3" t="s">
@@ -1991,7 +1994,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2079,7 +2082,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2167,7 +2170,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2236,6 +2239,9 @@
       <c r="B219" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C219" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B220" s="3" t="s">
@@ -2252,7 +2258,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2337,7 +2343,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2422,7 +2428,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2507,7 +2513,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2592,7 +2598,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2677,7 +2683,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2762,7 +2768,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2847,7 +2853,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2932,7 +2938,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3017,7 +3023,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3102,7 +3108,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3187,7 +3193,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3256,9 +3262,6 @@
       <c r="B351" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C351" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B352" s="3" t="s">
@@ -3275,7 +3278,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3344,6 +3347,9 @@
       <c r="B362" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C362" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B363" s="3" t="s">
@@ -3360,7 +3366,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3445,7 +3451,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3530,7 +3536,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3599,9 +3605,6 @@
       <c r="B395" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C395" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B396" s="3" t="s">
@@ -3618,7 +3621,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3706,7 +3709,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3775,6 +3778,9 @@
       <c r="B417" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C417" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B418" s="3" t="s">
@@ -3791,7 +3797,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3876,7 +3882,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3961,7 +3967,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4046,7 +4052,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4115,9 +4121,6 @@
       <c r="B461" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C461" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B462" s="3" t="s">
@@ -4134,7 +4137,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4222,7 +4225,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4299,9 +4302,6 @@
       <c r="B484" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C484" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B485" s="3" t="s">
@@ -4313,7 +4313,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4390,6 +4390,9 @@
       <c r="B495" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C495" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B496" s="3" t="s">
@@ -4401,7 +4404,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4489,7 +4492,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4577,7 +4580,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4665,7 +4668,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4753,7 +4756,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4822,6 +4825,9 @@
       <c r="B549" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C549" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B550" s="3" t="s">
@@ -4838,7 +4844,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4899,7 +4905,9 @@
       <c r="B559" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C559" s="6"/>
+      <c r="C559" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B560" s="3" t="s">
@@ -4915,10 +4923,13 @@
       <c r="B562" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C562" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -4979,17 +4990,12 @@
       <c r="B570" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C570" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C570" s="6"/>
     </row>
     <row r="571" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B571" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C571" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B572" s="3" t="s">
@@ -5000,13 +5006,10 @@
       <c r="B573" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C573" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5094,7 +5097,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5182,7 +5185,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5251,6 +5254,9 @@
       <c r="B604" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C604" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B605" s="3" t="s">
@@ -5267,7 +5273,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5352,7 +5358,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5426,9 +5432,6 @@
       <c r="B627" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C627" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B628" s="3" t="s">
@@ -5440,7 +5443,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5501,7 +5504,9 @@
       <c r="B636" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C636" s="6"/>
+      <c r="C636" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B637" s="3" t="s">
@@ -5512,15 +5517,21 @@
       <c r="B638" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C638" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B639" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C639" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5581,9 +5592,7 @@
       <c r="B647" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C647" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C647" s="6"/>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B648" s="3" t="s">
@@ -5599,13 +5608,10 @@
       <c r="B650" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C650" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5674,9 +5680,6 @@
       <c r="B659" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C659" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B660" s="3" t="s">
@@ -5693,7 +5696,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5762,6 +5765,9 @@
       <c r="B670" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C670" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="671" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B671" s="3" t="s">
@@ -5778,7 +5784,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5857,10 +5863,13 @@
       <c r="B683" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C683" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -5939,13 +5948,10 @@
       <c r="B694" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C694" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6014,9 +6020,6 @@
       <c r="B703" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C703" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="704" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B704" s="3" t="s">
@@ -6033,7 +6036,7 @@
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6054,19 +6057,25 @@
       <c r="B708" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C708" s="6"/>
+      <c r="C708" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="709" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B709" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C709" s="6"/>
+      <c r="C709" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="710" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B710" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C710" s="6"/>
+      <c r="C710" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="711" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B711" s="3" t="s">
@@ -6088,12 +6097,17 @@
       <c r="B713" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C713" s="6"/>
+      <c r="C713" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="714" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B714" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C714" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="715" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B715" s="3" t="s">
@@ -6104,10 +6118,13 @@
       <c r="B716" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C716" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6128,25 +6145,19 @@
       <c r="B719" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C719" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C719" s="6"/>
     </row>
     <row r="720" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B720" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C720" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C720" s="6"/>
     </row>
     <row r="721" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B721" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C721" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C721" s="6"/>
     </row>
     <row r="722" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B722" s="3" t="s">
@@ -6168,17 +6179,12 @@
       <c r="B724" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C724" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C724" s="6"/>
     </row>
     <row r="725" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B725" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C725" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="726" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B726" s="3" t="s">
@@ -6189,13 +6195,10 @@
       <c r="B727" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C727" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6283,7 +6286,7 @@
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6352,6 +6355,9 @@
       <c r="B747" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C747" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="748" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B748" s="3" t="s">
@@ -6368,7 +6374,7 @@
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6437,9 +6443,6 @@
       <c r="B758" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C758" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="759" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B759" s="3" t="s">
@@ -6447,19 +6450,19 @@
       </c>
     </row>
     <row r="760" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A760" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B760" s="7" t="s">
-        <v>3</v>
+      <c r="B760" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C760" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B761" s="3" t="s">
-        <v>4</v>
+      <c r="A761" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B761" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C761" s="5" t="s">
         <v>13</v>
@@ -6467,7 +6470,7 @@
     </row>
     <row r="762" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B762" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C762" s="5" t="s">
         <v>13</v>
@@ -6475,7 +6478,7 @@
     </row>
     <row r="763" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B763" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C763" s="5" t="s">
         <v>13</v>
@@ -6483,7 +6486,7 @@
     </row>
     <row r="764" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B764" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C764" s="5" t="s">
         <v>13</v>
@@ -6491,7 +6494,7 @@
     </row>
     <row r="765" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B765" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C765" s="5" t="s">
         <v>13</v>
@@ -6499,7 +6502,7 @@
     </row>
     <row r="766" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B766" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C766" s="5" t="s">
         <v>13</v>
@@ -6507,7 +6510,7 @@
     </row>
     <row r="767" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B767" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C767" s="5" t="s">
         <v>13</v>
@@ -6515,7 +6518,7 @@
     </row>
     <row r="768" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B768" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C768" s="5" t="s">
         <v>13</v>
@@ -6523,23 +6526,23 @@
     </row>
     <row r="769" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B769" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C769" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="770" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A770" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B770" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C770" s="5" t="s">
-        <v>13</v>
+      <c r="B770" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="771" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B771" s="3" t="s">
-        <v>4</v>
+      <c r="A771" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B771" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C771" s="5" t="s">
         <v>13</v>
@@ -6547,7 +6550,7 @@
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B772" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C772" s="5" t="s">
         <v>13</v>
@@ -6555,7 +6558,7 @@
     </row>
     <row r="773" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B773" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C773" s="5" t="s">
         <v>13</v>
@@ -6563,7 +6566,7 @@
     </row>
     <row r="774" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B774" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C774" s="5" t="s">
         <v>13</v>
@@ -6571,7 +6574,7 @@
     </row>
     <row r="775" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B775" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C775" s="5" t="s">
         <v>13</v>
@@ -6579,7 +6582,7 @@
     </row>
     <row r="776" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B776" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C776" s="5" t="s">
         <v>13</v>
@@ -6587,7 +6590,7 @@
     </row>
     <row r="777" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B777" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C777" s="5" t="s">
         <v>13</v>
@@ -6595,16 +6598,104 @@
     </row>
     <row r="778" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B778" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C778" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="779" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B779" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C779" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="780" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B780" s="3">
+      <c r="B780" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="781" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A781" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B781" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C781" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="782" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B782" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C782" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="783" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B783" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C783" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="784" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B784" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C784" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="785" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B785" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C785" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="786" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B786" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C786" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="787" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B787" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C787" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="788" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B788" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C788" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="789" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B789" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="790" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B790" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="791" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B791" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6330C535-E6B5-4A14-A1CE-FEA09C0D394E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15229970-7C39-4A58-9E2C-99975966B4AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1468" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1489" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C791"/>
+  <dimension ref="A1:C802"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -636,9 +636,6 @@
       <c r="B22" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B23" s="3" t="s">
@@ -650,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -741,7 +738,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -832,7 +829,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -923,7 +920,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -1014,7 +1011,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1105,7 +1102,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1196,7 +1193,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1287,7 +1284,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1378,7 +1375,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1469,7 +1466,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1538,6 +1535,9 @@
       <c r="B131" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C131" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B132" s="3" t="s">
@@ -1557,7 +1557,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1626,9 +1626,6 @@
       <c r="B142" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C142" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B143" s="3" t="s">
@@ -1648,7 +1645,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1725,6 +1722,9 @@
       <c r="B154" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C154" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B155" s="3" t="s">
@@ -1736,7 +1736,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1805,6 +1805,9 @@
       <c r="B164" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C164" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B165" s="3" t="s">
@@ -1821,7 +1824,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1890,9 +1893,6 @@
       <c r="B175" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C175" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B176" s="3" t="s">
@@ -1909,7 +1909,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1978,6 +1978,9 @@
       <c r="B186" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C186" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B187" s="3" t="s">
@@ -1994,7 +1997,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2063,9 +2066,6 @@
       <c r="B197" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C197" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B198" s="3" t="s">
@@ -2082,7 +2082,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2170,7 +2170,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2258,7 +2258,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2327,6 +2327,9 @@
       <c r="B230" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C230" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B231" s="3" t="s">
@@ -2343,7 +2346,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2428,7 +2431,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2513,7 +2516,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2598,7 +2601,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2683,7 +2686,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2768,7 +2771,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2853,7 +2856,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2938,7 +2941,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3023,7 +3026,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3108,7 +3111,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3193,7 +3196,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3278,7 +3281,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3347,9 +3350,6 @@
       <c r="B362" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C362" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B363" s="3" t="s">
@@ -3366,7 +3366,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3435,6 +3435,9 @@
       <c r="B373" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C373" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B374" s="3" t="s">
@@ -3451,7 +3454,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3536,7 +3539,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3621,7 +3624,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3690,9 +3693,6 @@
       <c r="B406" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C406" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B407" s="3" t="s">
@@ -3709,7 +3709,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3797,7 +3797,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3866,6 +3866,9 @@
       <c r="B428" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C428" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B429" s="3" t="s">
@@ -3882,7 +3885,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3967,7 +3970,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4052,7 +4055,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4137,7 +4140,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4206,9 +4209,6 @@
       <c r="B472" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C472" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B473" s="3" t="s">
@@ -4225,7 +4225,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4313,7 +4313,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4390,9 +4390,6 @@
       <c r="B495" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C495" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B496" s="3" t="s">
@@ -4404,7 +4401,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4481,6 +4478,9 @@
       <c r="B506" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C506" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B507" s="3" t="s">
@@ -4492,7 +4492,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4580,7 +4580,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4668,7 +4668,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4756,7 +4756,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4844,7 +4844,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4913,6 +4913,9 @@
       <c r="B560" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C560" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B561" s="3" t="s">
@@ -4929,7 +4932,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -4990,7 +4993,9 @@
       <c r="B570" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C570" s="6"/>
+      <c r="C570" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="571" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B571" s="3" t="s">
@@ -5006,10 +5011,13 @@
       <c r="B573" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C573" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5070,17 +5078,12 @@
       <c r="B581" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C581" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C581" s="6"/>
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B582" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C582" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B583" s="3" t="s">
@@ -5091,13 +5094,10 @@
       <c r="B584" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C584" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5185,7 +5185,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5273,7 +5273,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5342,6 +5342,9 @@
       <c r="B615" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C615" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B616" s="3" t="s">
@@ -5358,7 +5361,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5443,7 +5446,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5517,9 +5520,6 @@
       <c r="B638" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C638" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B639" s="3" t="s">
@@ -5531,7 +5531,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5592,7 +5592,9 @@
       <c r="B647" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C647" s="6"/>
+      <c r="C647" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B648" s="3" t="s">
@@ -5603,15 +5605,21 @@
       <c r="B649" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C649" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B650" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C650" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5672,9 +5680,7 @@
       <c r="B658" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C658" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C658" s="6"/>
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B659" s="3" t="s">
@@ -5690,13 +5696,10 @@
       <c r="B661" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C661" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5765,9 +5768,6 @@
       <c r="B670" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C670" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="671" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B671" s="3" t="s">
@@ -5784,7 +5784,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5853,6 +5853,9 @@
       <c r="B681" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C681" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="682" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B682" s="3" t="s">
@@ -5869,7 +5872,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -5948,10 +5951,13 @@
       <c r="B694" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C694" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6030,13 +6036,10 @@
       <c r="B705" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C705" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6105,9 +6108,6 @@
       <c r="B714" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C714" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="715" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B715" s="3" t="s">
@@ -6124,7 +6124,7 @@
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6145,19 +6145,25 @@
       <c r="B719" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C719" s="6"/>
+      <c r="C719" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="720" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B720" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C720" s="6"/>
+      <c r="C720" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="721" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B721" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C721" s="6"/>
+      <c r="C721" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="722" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B722" s="3" t="s">
@@ -6179,12 +6185,17 @@
       <c r="B724" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C724" s="6"/>
+      <c r="C724" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="725" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B725" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C725" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="726" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B726" s="3" t="s">
@@ -6195,10 +6206,13 @@
       <c r="B727" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C727" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6219,25 +6233,19 @@
       <c r="B730" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C730" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C730" s="6"/>
     </row>
     <row r="731" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B731" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C731" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C731" s="6"/>
     </row>
     <row r="732" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B732" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C732" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C732" s="6"/>
     </row>
     <row r="733" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B733" s="3" t="s">
@@ -6259,17 +6267,12 @@
       <c r="B735" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C735" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C735" s="6"/>
     </row>
     <row r="736" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B736" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C736" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="737" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B737" s="3" t="s">
@@ -6280,13 +6283,10 @@
       <c r="B738" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C738" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6374,7 +6374,7 @@
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6443,6 +6443,9 @@
       <c r="B758" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C758" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="759" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B759" s="3" t="s">
@@ -6459,7 +6462,7 @@
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6528,9 +6531,6 @@
       <c r="B769" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C769" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="770" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B770" s="3" t="s">
@@ -6538,19 +6538,19 @@
       </c>
     </row>
     <row r="771" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A771" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B771" s="7" t="s">
-        <v>3</v>
+      <c r="B771" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C771" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B772" s="3" t="s">
-        <v>4</v>
+      <c r="A772" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B772" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C772" s="5" t="s">
         <v>13</v>
@@ -6558,7 +6558,7 @@
     </row>
     <row r="773" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B773" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C773" s="5" t="s">
         <v>13</v>
@@ -6566,7 +6566,7 @@
     </row>
     <row r="774" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B774" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C774" s="5" t="s">
         <v>13</v>
@@ -6574,7 +6574,7 @@
     </row>
     <row r="775" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B775" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C775" s="5" t="s">
         <v>13</v>
@@ -6582,7 +6582,7 @@
     </row>
     <row r="776" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B776" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C776" s="5" t="s">
         <v>13</v>
@@ -6590,7 +6590,7 @@
     </row>
     <row r="777" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B777" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C777" s="5" t="s">
         <v>13</v>
@@ -6598,7 +6598,7 @@
     </row>
     <row r="778" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B778" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C778" s="5" t="s">
         <v>13</v>
@@ -6606,7 +6606,7 @@
     </row>
     <row r="779" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B779" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C779" s="5" t="s">
         <v>13</v>
@@ -6614,23 +6614,23 @@
     </row>
     <row r="780" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B780" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C780" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="781" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A781" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B781" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C781" s="5" t="s">
-        <v>13</v>
+      <c r="B781" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="782" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B782" s="3" t="s">
-        <v>4</v>
+      <c r="A782" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B782" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C782" s="5" t="s">
         <v>13</v>
@@ -6638,7 +6638,7 @@
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B783" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C783" s="5" t="s">
         <v>13</v>
@@ -6646,56 +6646,144 @@
     </row>
     <row r="784" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B784" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C784" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="785" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="785" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B785" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C785" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="786" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="786" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B786" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C786" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="787" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="787" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B787" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C787" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="788" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="788" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B788" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C788" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="789" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="789" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B789" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="790" spans="2:3" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="C789" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="790" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B790" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="791" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B791" s="3">
+        <v>11</v>
+      </c>
+      <c r="C790" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="791" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B791" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="792" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A792" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B792" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C792" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="793" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B793" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C793" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="794" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B794" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C794" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="795" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B795" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C795" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="796" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B796" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C796" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="797" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B797" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C797" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="798" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B798" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C798" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="799" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B799" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C799" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="800" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B800" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="801" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B801" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="802" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B802" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15229970-7C39-4A58-9E2C-99975966B4AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B30D5321-08EF-4117-8136-A55A2C1CB626}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1489" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1511" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C802"/>
+  <dimension ref="A1:C813"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -636,6 +636,9 @@
       <c r="B22" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C22" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B23" s="3" t="s">
@@ -647,7 +650,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -724,9 +727,6 @@
       <c r="B33" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C33" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B34" s="3" t="s">
@@ -738,7 +738,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -829,7 +829,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -920,7 +920,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -1011,7 +1011,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1102,7 +1102,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1193,7 +1193,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1284,7 +1284,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1375,7 +1375,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1557,7 +1557,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1626,6 +1626,9 @@
       <c r="B142" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C142" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B143" s="3" t="s">
@@ -1645,7 +1648,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1714,9 +1717,6 @@
       <c r="B153" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C153" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B154" s="3" t="s">
@@ -1736,7 +1736,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1813,6 +1813,9 @@
       <c r="B165" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C165" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B166" s="3" t="s">
@@ -1824,7 +1827,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1893,6 +1896,9 @@
       <c r="B175" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C175" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B176" s="3" t="s">
@@ -1909,7 +1915,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1978,9 +1984,6 @@
       <c r="B186" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C186" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B187" s="3" t="s">
@@ -1997,7 +2000,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2066,6 +2069,9 @@
       <c r="B197" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C197" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B198" s="3" t="s">
@@ -2082,7 +2088,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2151,9 +2157,6 @@
       <c r="B208" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C208" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B209" s="3" t="s">
@@ -2170,7 +2173,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2258,7 +2261,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2346,7 +2349,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2415,6 +2418,9 @@
       <c r="B241" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C241" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B242" s="3" t="s">
@@ -2431,7 +2437,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2516,7 +2522,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2601,7 +2607,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2686,7 +2692,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2771,7 +2777,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2856,7 +2862,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2941,7 +2947,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3026,7 +3032,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3111,7 +3117,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3196,7 +3202,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3281,7 +3287,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3366,7 +3372,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3435,9 +3441,6 @@
       <c r="B373" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C373" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B374" s="3" t="s">
@@ -3454,7 +3457,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3523,6 +3526,9 @@
       <c r="B384" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C384" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B385" s="3" t="s">
@@ -3539,7 +3545,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3624,7 +3630,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3709,7 +3715,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3778,9 +3784,6 @@
       <c r="B417" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C417" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B418" s="3" t="s">
@@ -3797,7 +3800,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3885,7 +3888,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3954,6 +3957,9 @@
       <c r="B439" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C439" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B440" s="3" t="s">
@@ -3970,7 +3976,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4055,7 +4061,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4140,7 +4146,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4225,7 +4231,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4294,9 +4300,6 @@
       <c r="B483" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C483" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B484" s="3" t="s">
@@ -4313,7 +4316,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4401,7 +4404,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4478,9 +4481,6 @@
       <c r="B506" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C506" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B507" s="3" t="s">
@@ -4492,7 +4492,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4569,6 +4569,9 @@
       <c r="B517" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C517" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B518" s="3" t="s">
@@ -4580,7 +4583,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4668,7 +4671,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4756,7 +4759,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4844,7 +4847,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4932,7 +4935,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5001,6 +5004,9 @@
       <c r="B571" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C571" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B572" s="3" t="s">
@@ -5017,7 +5023,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5078,7 +5084,9 @@
       <c r="B581" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C581" s="6"/>
+      <c r="C581" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B582" s="3" t="s">
@@ -5094,10 +5102,13 @@
       <c r="B584" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C584" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5158,17 +5169,12 @@
       <c r="B592" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C592" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C592" s="6"/>
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B593" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C593" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B594" s="3" t="s">
@@ -5179,13 +5185,10 @@
       <c r="B595" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C595" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5273,7 +5276,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5361,7 +5364,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5430,6 +5433,9 @@
       <c r="B626" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C626" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B627" s="3" t="s">
@@ -5446,7 +5452,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5531,7 +5537,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5605,9 +5611,6 @@
       <c r="B649" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C649" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B650" s="3" t="s">
@@ -5619,7 +5622,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5680,7 +5683,9 @@
       <c r="B658" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C658" s="6"/>
+      <c r="C658" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B659" s="3" t="s">
@@ -5691,15 +5696,21 @@
       <c r="B660" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C660" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B661" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C661" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5760,9 +5771,7 @@
       <c r="B669" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C669" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C669" s="6"/>
     </row>
     <row r="670" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B670" s="3" t="s">
@@ -5778,13 +5787,10 @@
       <c r="B672" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C672" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5853,9 +5859,6 @@
       <c r="B681" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C681" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="682" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B682" s="3" t="s">
@@ -5872,7 +5875,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -5941,6 +5944,9 @@
       <c r="B692" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C692" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="693" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B693" s="3" t="s">
@@ -5957,7 +5963,7 @@
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6036,10 +6042,13 @@
       <c r="B705" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C705" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6118,13 +6127,10 @@
       <c r="B716" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C716" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6193,9 +6199,6 @@
       <c r="B725" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C725" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="726" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B726" s="3" t="s">
@@ -6212,7 +6215,7 @@
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6233,19 +6236,25 @@
       <c r="B730" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C730" s="6"/>
+      <c r="C730" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="731" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B731" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C731" s="6"/>
+      <c r="C731" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="732" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B732" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C732" s="6"/>
+      <c r="C732" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="733" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B733" s="3" t="s">
@@ -6267,12 +6276,17 @@
       <c r="B735" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C735" s="6"/>
+      <c r="C735" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="736" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B736" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C736" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="737" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B737" s="3" t="s">
@@ -6283,10 +6297,13 @@
       <c r="B738" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C738" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6307,25 +6324,19 @@
       <c r="B741" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C741" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C741" s="6"/>
     </row>
     <row r="742" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B742" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C742" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C742" s="6"/>
     </row>
     <row r="743" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B743" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C743" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C743" s="6"/>
     </row>
     <row r="744" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B744" s="3" t="s">
@@ -6347,17 +6358,12 @@
       <c r="B746" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C746" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C746" s="6"/>
     </row>
     <row r="747" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B747" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C747" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="748" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B748" s="3" t="s">
@@ -6368,13 +6374,10 @@
       <c r="B749" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C749" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6462,7 +6465,7 @@
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6531,6 +6534,9 @@
       <c r="B769" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C769" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="770" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B770" s="3" t="s">
@@ -6547,7 +6553,7 @@
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3</v>
@@ -6616,9 +6622,6 @@
       <c r="B780" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C780" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="781" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B781" s="3" t="s">
@@ -6626,19 +6629,19 @@
       </c>
     </row>
     <row r="782" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A782" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B782" s="7" t="s">
-        <v>3</v>
+      <c r="B782" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C782" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B783" s="3" t="s">
-        <v>4</v>
+      <c r="A783" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B783" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C783" s="5" t="s">
         <v>13</v>
@@ -6646,7 +6649,7 @@
     </row>
     <row r="784" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B784" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C784" s="5" t="s">
         <v>13</v>
@@ -6654,7 +6657,7 @@
     </row>
     <row r="785" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B785" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C785" s="5" t="s">
         <v>13</v>
@@ -6662,7 +6665,7 @@
     </row>
     <row r="786" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B786" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C786" s="5" t="s">
         <v>13</v>
@@ -6670,7 +6673,7 @@
     </row>
     <row r="787" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B787" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C787" s="5" t="s">
         <v>13</v>
@@ -6678,7 +6681,7 @@
     </row>
     <row r="788" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B788" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C788" s="5" t="s">
         <v>13</v>
@@ -6686,7 +6689,7 @@
     </row>
     <row r="789" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B789" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C789" s="5" t="s">
         <v>13</v>
@@ -6694,7 +6697,7 @@
     </row>
     <row r="790" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B790" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C790" s="5" t="s">
         <v>13</v>
@@ -6702,23 +6705,23 @@
     </row>
     <row r="791" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B791" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C791" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="792" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A792" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B792" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C792" s="5" t="s">
-        <v>13</v>
+      <c r="B792" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="793" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B793" s="3" t="s">
-        <v>4</v>
+      <c r="A793" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B793" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C793" s="5" t="s">
         <v>13</v>
@@ -6726,7 +6729,7 @@
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B794" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C794" s="5" t="s">
         <v>13</v>
@@ -6734,7 +6737,7 @@
     </row>
     <row r="795" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B795" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C795" s="5" t="s">
         <v>13</v>
@@ -6742,7 +6745,7 @@
     </row>
     <row r="796" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B796" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C796" s="5" t="s">
         <v>13</v>
@@ -6750,7 +6753,7 @@
     </row>
     <row r="797" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B797" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C797" s="5" t="s">
         <v>13</v>
@@ -6758,7 +6761,7 @@
     </row>
     <row r="798" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B798" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C798" s="5" t="s">
         <v>13</v>
@@ -6766,7 +6769,7 @@
     </row>
     <row r="799" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B799" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C799" s="5" t="s">
         <v>13</v>
@@ -6774,16 +6777,104 @@
     </row>
     <row r="800" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B800" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="801" spans="2:2" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="C800" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="801" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B801" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="802" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B802" s="3">
+        <v>11</v>
+      </c>
+      <c r="C801" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="802" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B802" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="803" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A803" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B803" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C803" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="804" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B804" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C804" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="805" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B805" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C805" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="806" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B806" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C806" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="807" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B807" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C807" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="808" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B808" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C808" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="809" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B809" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C809" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="810" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B810" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C810" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="811" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B811" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="812" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B812" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="813" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B813" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B30D5321-08EF-4117-8136-A55A2C1CB626}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A8DA3FA-DF30-4CB2-A3FF-222E56FA7CB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1511" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1533" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C813"/>
+  <dimension ref="A1:C824"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -650,7 +650,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -727,6 +727,9 @@
       <c r="B33" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C33" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B34" s="3" t="s">
@@ -738,7 +741,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -815,9 +818,6 @@
       <c r="B44" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C44" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B45" s="3" t="s">
@@ -829,7 +829,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -920,7 +920,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -1011,7 +1011,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1102,7 +1102,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1193,7 +1193,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1284,7 +1284,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1375,7 +1375,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1557,7 +1557,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1648,7 +1648,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1717,6 +1717,9 @@
       <c r="B153" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C153" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B154" s="3" t="s">
@@ -1736,7 +1739,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1805,9 +1808,6 @@
       <c r="B164" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C164" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B165" s="3" t="s">
@@ -1827,7 +1827,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1904,6 +1904,9 @@
       <c r="B176" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C176" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B177" s="3" t="s">
@@ -1915,7 +1918,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1984,6 +1987,9 @@
       <c r="B186" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C186" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B187" s="3" t="s">
@@ -2000,7 +2006,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2069,9 +2075,6 @@
       <c r="B197" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C197" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B198" s="3" t="s">
@@ -2088,7 +2091,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2157,6 +2160,9 @@
       <c r="B208" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C208" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B209" s="3" t="s">
@@ -2173,7 +2179,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2242,9 +2248,6 @@
       <c r="B219" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C219" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B220" s="3" t="s">
@@ -2261,7 +2264,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2349,7 +2352,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2437,7 +2440,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2506,6 +2509,9 @@
       <c r="B252" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C252" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B253" s="3" t="s">
@@ -2522,7 +2528,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2607,7 +2613,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2692,7 +2698,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2777,7 +2783,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2862,7 +2868,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2947,7 +2953,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3032,7 +3038,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3117,7 +3123,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3202,7 +3208,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3287,7 +3293,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3372,7 +3378,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3457,7 +3463,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3526,9 +3532,6 @@
       <c r="B384" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C384" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B385" s="3" t="s">
@@ -3545,7 +3548,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3614,6 +3617,9 @@
       <c r="B395" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C395" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B396" s="3" t="s">
@@ -3630,7 +3636,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3715,7 +3721,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3800,7 +3806,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3869,9 +3875,6 @@
       <c r="B428" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C428" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B429" s="3" t="s">
@@ -3888,7 +3891,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3976,7 +3979,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4045,6 +4048,9 @@
       <c r="B450" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C450" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B451" s="3" t="s">
@@ -4061,7 +4067,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4146,7 +4152,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4231,7 +4237,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4316,7 +4322,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4385,9 +4391,6 @@
       <c r="B494" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C494" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B495" s="3" t="s">
@@ -4404,7 +4407,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4492,7 +4495,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4569,9 +4572,6 @@
       <c r="B517" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C517" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B518" s="3" t="s">
@@ -4583,7 +4583,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4660,6 +4660,9 @@
       <c r="B528" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C528" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B529" s="3" t="s">
@@ -4671,7 +4674,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4759,7 +4762,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4847,7 +4850,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4935,7 +4938,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5023,7 +5026,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5092,6 +5095,9 @@
       <c r="B582" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C582" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B583" s="3" t="s">
@@ -5108,7 +5114,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5169,7 +5175,9 @@
       <c r="B592" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C592" s="6"/>
+      <c r="C592" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B593" s="3" t="s">
@@ -5185,10 +5193,13 @@
       <c r="B595" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C595" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5249,17 +5260,12 @@
       <c r="B603" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C603" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C603" s="6"/>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B604" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C604" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B605" s="3" t="s">
@@ -5270,13 +5276,10 @@
       <c r="B606" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C606" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5364,7 +5367,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5452,7 +5455,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5521,6 +5524,9 @@
       <c r="B637" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C637" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B638" s="3" t="s">
@@ -5537,7 +5543,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5622,7 +5628,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5696,9 +5702,6 @@
       <c r="B660" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C660" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B661" s="3" t="s">
@@ -5710,7 +5713,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5771,7 +5774,9 @@
       <c r="B669" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C669" s="6"/>
+      <c r="C669" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="670" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B670" s="3" t="s">
@@ -5782,15 +5787,21 @@
       <c r="B671" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C671" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="672" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B672" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C672" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5851,9 +5862,7 @@
       <c r="B680" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C680" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C680" s="6"/>
     </row>
     <row r="681" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B681" s="3" t="s">
@@ -5869,13 +5878,10 @@
       <c r="B683" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C683" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -5944,9 +5950,6 @@
       <c r="B692" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C692" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="693" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B693" s="3" t="s">
@@ -5963,7 +5966,7 @@
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6032,6 +6035,9 @@
       <c r="B703" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C703" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="704" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B704" s="3" t="s">
@@ -6048,7 +6054,7 @@
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6127,10 +6133,13 @@
       <c r="B716" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C716" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6209,13 +6218,10 @@
       <c r="B727" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C727" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6284,9 +6290,6 @@
       <c r="B736" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C736" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="737" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B737" s="3" t="s">
@@ -6303,7 +6306,7 @@
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6324,19 +6327,25 @@
       <c r="B741" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C741" s="6"/>
+      <c r="C741" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="742" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B742" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C742" s="6"/>
+      <c r="C742" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="743" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B743" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C743" s="6"/>
+      <c r="C743" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="744" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B744" s="3" t="s">
@@ -6358,12 +6367,17 @@
       <c r="B746" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C746" s="6"/>
+      <c r="C746" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="747" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B747" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C747" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="748" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B748" s="3" t="s">
@@ -6374,10 +6388,13 @@
       <c r="B749" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C749" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6398,25 +6415,19 @@
       <c r="B752" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C752" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C752" s="6"/>
     </row>
     <row r="753" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B753" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C753" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C753" s="6"/>
     </row>
     <row r="754" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B754" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C754" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C754" s="6"/>
     </row>
     <row r="755" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B755" s="3" t="s">
@@ -6438,17 +6449,12 @@
       <c r="B757" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C757" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C757" s="6"/>
     </row>
     <row r="758" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B758" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C758" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="759" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B759" s="3" t="s">
@@ -6459,13 +6465,10 @@
       <c r="B760" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C760" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6553,7 +6556,7 @@
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3</v>
@@ -6622,6 +6625,9 @@
       <c r="B780" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C780" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="781" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B781" s="3" t="s">
@@ -6638,7 +6644,7 @@
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B783" s="7" t="s">
         <v>3</v>
@@ -6707,9 +6713,6 @@
       <c r="B791" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C791" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="792" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B792" s="3" t="s">
@@ -6717,19 +6720,19 @@
       </c>
     </row>
     <row r="793" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A793" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B793" s="7" t="s">
-        <v>3</v>
+      <c r="B793" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C793" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B794" s="3" t="s">
-        <v>4</v>
+      <c r="A794" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B794" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C794" s="5" t="s">
         <v>13</v>
@@ -6737,7 +6740,7 @@
     </row>
     <row r="795" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B795" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C795" s="5" t="s">
         <v>13</v>
@@ -6745,7 +6748,7 @@
     </row>
     <row r="796" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B796" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C796" s="5" t="s">
         <v>13</v>
@@ -6753,7 +6756,7 @@
     </row>
     <row r="797" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B797" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C797" s="5" t="s">
         <v>13</v>
@@ -6761,7 +6764,7 @@
     </row>
     <row r="798" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B798" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C798" s="5" t="s">
         <v>13</v>
@@ -6769,7 +6772,7 @@
     </row>
     <row r="799" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B799" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C799" s="5" t="s">
         <v>13</v>
@@ -6777,7 +6780,7 @@
     </row>
     <row r="800" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B800" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C800" s="5" t="s">
         <v>13</v>
@@ -6785,7 +6788,7 @@
     </row>
     <row r="801" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B801" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C801" s="5" t="s">
         <v>13</v>
@@ -6793,23 +6796,23 @@
     </row>
     <row r="802" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B802" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C802" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="803" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A803" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B803" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C803" s="5" t="s">
-        <v>13</v>
+      <c r="B803" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="804" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B804" s="3" t="s">
-        <v>4</v>
+      <c r="A804" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B804" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C804" s="5" t="s">
         <v>13</v>
@@ -6817,7 +6820,7 @@
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B805" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C805" s="5" t="s">
         <v>13</v>
@@ -6825,7 +6828,7 @@
     </row>
     <row r="806" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B806" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C806" s="5" t="s">
         <v>13</v>
@@ -6833,7 +6836,7 @@
     </row>
     <row r="807" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B807" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C807" s="5" t="s">
         <v>13</v>
@@ -6841,7 +6844,7 @@
     </row>
     <row r="808" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B808" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C808" s="5" t="s">
         <v>13</v>
@@ -6849,7 +6852,7 @@
     </row>
     <row r="809" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B809" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C809" s="5" t="s">
         <v>13</v>
@@ -6857,7 +6860,7 @@
     </row>
     <row r="810" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B810" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C810" s="5" t="s">
         <v>13</v>
@@ -6865,16 +6868,104 @@
     </row>
     <row r="811" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B811" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C811" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="812" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B812" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C812" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="813" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B813" s="3">
+      <c r="B813" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="814" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A814" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B814" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C814" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="815" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B815" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C815" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="816" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B816" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C816" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="817" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B817" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C817" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="818" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B818" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C818" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="819" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B819" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C819" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="820" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B820" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C820" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="821" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B821" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C821" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="822" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B822" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="823" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B823" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="824" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B824" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A8DA3FA-DF30-4CB2-A3FF-222E56FA7CB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15B18D2D-5501-4BA8-97D0-61B2FB32B468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1533" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1555" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C824"/>
+  <dimension ref="A1:C835"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -650,7 +650,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -741,7 +741,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -818,6 +818,9 @@
       <c r="B44" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C44" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B45" s="3" t="s">
@@ -829,7 +832,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -906,9 +909,6 @@
       <c r="B55" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C55" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B56" s="3" t="s">
@@ -920,7 +920,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -1011,7 +1011,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1102,7 +1102,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1193,7 +1193,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1284,7 +1284,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1375,7 +1375,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1557,7 +1557,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1648,7 +1648,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1739,7 +1739,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1808,6 +1808,9 @@
       <c r="B164" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C164" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B165" s="3" t="s">
@@ -1827,7 +1830,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1896,9 +1899,6 @@
       <c r="B175" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C175" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B176" s="3" t="s">
@@ -1918,7 +1918,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1995,6 +1995,9 @@
       <c r="B187" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C187" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B188" s="3" t="s">
@@ -2006,7 +2009,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2075,6 +2078,9 @@
       <c r="B197" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C197" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B198" s="3" t="s">
@@ -2091,7 +2097,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2160,9 +2166,6 @@
       <c r="B208" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C208" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B209" s="3" t="s">
@@ -2179,7 +2182,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2248,6 +2251,9 @@
       <c r="B219" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C219" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B220" s="3" t="s">
@@ -2264,7 +2270,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2333,9 +2339,6 @@
       <c r="B230" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C230" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B231" s="3" t="s">
@@ -2352,7 +2355,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2440,7 +2443,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2528,7 +2531,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2597,6 +2600,9 @@
       <c r="B263" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C263" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B264" s="3" t="s">
@@ -2613,7 +2619,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2698,7 +2704,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2783,7 +2789,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2868,7 +2874,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2953,7 +2959,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3038,7 +3044,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3123,7 +3129,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3208,7 +3214,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3293,7 +3299,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3378,7 +3384,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3463,7 +3469,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3548,7 +3554,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3617,9 +3623,6 @@
       <c r="B395" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C395" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B396" s="3" t="s">
@@ -3636,7 +3639,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3705,6 +3708,9 @@
       <c r="B406" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C406" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B407" s="3" t="s">
@@ -3721,7 +3727,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3806,7 +3812,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3891,7 +3897,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3960,9 +3966,6 @@
       <c r="B439" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C439" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B440" s="3" t="s">
@@ -3979,7 +3982,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4067,7 +4070,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4136,6 +4139,9 @@
       <c r="B461" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C461" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B462" s="3" t="s">
@@ -4152,7 +4158,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4237,7 +4243,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4322,7 +4328,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4407,7 +4413,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4476,9 +4482,6 @@
       <c r="B505" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C505" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B506" s="3" t="s">
@@ -4495,7 +4498,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4583,7 +4586,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4660,9 +4663,6 @@
       <c r="B528" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C528" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B529" s="3" t="s">
@@ -4674,7 +4674,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4751,6 +4751,9 @@
       <c r="B539" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C539" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B540" s="3" t="s">
@@ -4762,7 +4765,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4850,7 +4853,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4938,7 +4941,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5026,7 +5029,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5114,7 +5117,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5183,6 +5186,9 @@
       <c r="B593" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C593" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B594" s="3" t="s">
@@ -5199,7 +5205,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5260,7 +5266,9 @@
       <c r="B603" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C603" s="6"/>
+      <c r="C603" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B604" s="3" t="s">
@@ -5276,10 +5284,13 @@
       <c r="B606" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C606" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5340,17 +5351,12 @@
       <c r="B614" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C614" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C614" s="6"/>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B615" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C615" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B616" s="3" t="s">
@@ -5361,13 +5367,10 @@
       <c r="B617" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C617" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5455,7 +5458,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5543,7 +5546,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5612,6 +5615,9 @@
       <c r="B648" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C648" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B649" s="3" t="s">
@@ -5628,7 +5634,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5713,7 +5719,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5787,9 +5793,6 @@
       <c r="B671" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C671" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="672" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B672" s="3" t="s">
@@ -5801,7 +5804,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5862,7 +5865,9 @@
       <c r="B680" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C680" s="6"/>
+      <c r="C680" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="681" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B681" s="3" t="s">
@@ -5873,15 +5878,21 @@
       <c r="B682" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C682" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="683" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B683" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C683" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -5942,9 +5953,7 @@
       <c r="B691" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C691" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C691" s="6"/>
     </row>
     <row r="692" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B692" s="3" t="s">
@@ -5960,13 +5969,10 @@
       <c r="B694" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C694" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6035,9 +6041,6 @@
       <c r="B703" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C703" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="704" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B704" s="3" t="s">
@@ -6054,7 +6057,7 @@
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6123,6 +6126,9 @@
       <c r="B714" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C714" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="715" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B715" s="3" t="s">
@@ -6139,7 +6145,7 @@
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6218,10 +6224,13 @@
       <c r="B727" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C727" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6300,13 +6309,10 @@
       <c r="B738" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C738" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6375,9 +6381,6 @@
       <c r="B747" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C747" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="748" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B748" s="3" t="s">
@@ -6394,7 +6397,7 @@
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6415,19 +6418,25 @@
       <c r="B752" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C752" s="6"/>
+      <c r="C752" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="753" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B753" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C753" s="6"/>
+      <c r="C753" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="754" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B754" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C754" s="6"/>
+      <c r="C754" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="755" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B755" s="3" t="s">
@@ -6449,12 +6458,17 @@
       <c r="B757" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C757" s="6"/>
+      <c r="C757" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="758" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B758" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C758" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="759" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B759" s="3" t="s">
@@ -6465,10 +6479,13 @@
       <c r="B760" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C760" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6489,25 +6506,19 @@
       <c r="B763" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C763" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C763" s="6"/>
     </row>
     <row r="764" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B764" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C764" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C764" s="6"/>
     </row>
     <row r="765" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B765" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C765" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C765" s="6"/>
     </row>
     <row r="766" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B766" s="3" t="s">
@@ -6529,17 +6540,12 @@
       <c r="B768" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C768" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C768" s="6"/>
     </row>
     <row r="769" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B769" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C769" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="770" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B770" s="3" t="s">
@@ -6550,13 +6556,10 @@
       <c r="B771" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C771" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3</v>
@@ -6644,7 +6647,7 @@
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B783" s="7" t="s">
         <v>3</v>
@@ -6713,6 +6716,9 @@
       <c r="B791" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C791" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="792" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B792" s="3" t="s">
@@ -6729,7 +6735,7 @@
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A794" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B794" s="7" t="s">
         <v>3</v>
@@ -6798,9 +6804,6 @@
       <c r="B802" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C802" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="803" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B803" s="3" t="s">
@@ -6808,19 +6811,19 @@
       </c>
     </row>
     <row r="804" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A804" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B804" s="7" t="s">
-        <v>3</v>
+      <c r="B804" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C804" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B805" s="3" t="s">
-        <v>4</v>
+      <c r="A805" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B805" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C805" s="5" t="s">
         <v>13</v>
@@ -6828,7 +6831,7 @@
     </row>
     <row r="806" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B806" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C806" s="5" t="s">
         <v>13</v>
@@ -6836,7 +6839,7 @@
     </row>
     <row r="807" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B807" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C807" s="5" t="s">
         <v>13</v>
@@ -6844,7 +6847,7 @@
     </row>
     <row r="808" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B808" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C808" s="5" t="s">
         <v>13</v>
@@ -6852,7 +6855,7 @@
     </row>
     <row r="809" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B809" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C809" s="5" t="s">
         <v>13</v>
@@ -6860,7 +6863,7 @@
     </row>
     <row r="810" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B810" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C810" s="5" t="s">
         <v>13</v>
@@ -6868,7 +6871,7 @@
     </row>
     <row r="811" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B811" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C811" s="5" t="s">
         <v>13</v>
@@ -6876,7 +6879,7 @@
     </row>
     <row r="812" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B812" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C812" s="5" t="s">
         <v>13</v>
@@ -6884,23 +6887,23 @@
     </row>
     <row r="813" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B813" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C813" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="814" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A814" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B814" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C814" s="5" t="s">
-        <v>13</v>
+      <c r="B814" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="815" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B815" s="3" t="s">
-        <v>4</v>
+      <c r="A815" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B815" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C815" s="5" t="s">
         <v>13</v>
@@ -6908,64 +6911,152 @@
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B816" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C816" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="817" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="817" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B817" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C817" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="818" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="818" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B818" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C818" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="819" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="819" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B819" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C819" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="820" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="820" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B820" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C820" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="821" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="821" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B821" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C821" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="822" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="822" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B822" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="823" spans="2:3" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="C822" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="823" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B823" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="824" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B824" s="3">
+        <v>11</v>
+      </c>
+      <c r="C823" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="824" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B824" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="825" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A825" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B825" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C825" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="826" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B826" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C826" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="827" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B827" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C827" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="828" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B828" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C828" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="829" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B829" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C829" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="830" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B830" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C830" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="831" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B831" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C831" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="832" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B832" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C832" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="833" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B833" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="834" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B834" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="835" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B835" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15B18D2D-5501-4BA8-97D0-61B2FB32B468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFCC0A2F-68B9-47CD-9A89-8718734097A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1555" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1577" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C835"/>
+  <dimension ref="A1:C846"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -650,7 +650,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -741,7 +741,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -832,7 +832,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -909,6 +909,9 @@
       <c r="B55" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C55" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B56" s="3" t="s">
@@ -920,7 +923,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -997,9 +1000,6 @@
       <c r="B66" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C66" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B67" s="3" t="s">
@@ -1011,7 +1011,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1102,7 +1102,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1193,7 +1193,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1284,7 +1284,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1375,7 +1375,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1557,7 +1557,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1648,7 +1648,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1739,7 +1739,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1830,7 +1830,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1899,6 +1899,9 @@
       <c r="B175" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C175" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B176" s="3" t="s">
@@ -1918,7 +1921,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1987,9 +1990,6 @@
       <c r="B186" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C186" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B187" s="3" t="s">
@@ -2009,7 +2009,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2086,6 +2086,9 @@
       <c r="B198" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C198" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B199" s="3" t="s">
@@ -2097,7 +2100,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2166,6 +2169,9 @@
       <c r="B208" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C208" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B209" s="3" t="s">
@@ -2182,7 +2188,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2251,9 +2257,6 @@
       <c r="B219" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C219" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B220" s="3" t="s">
@@ -2270,7 +2273,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2339,6 +2342,9 @@
       <c r="B230" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C230" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B231" s="3" t="s">
@@ -2355,7 +2361,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2424,9 +2430,6 @@
       <c r="B241" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C241" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B242" s="3" t="s">
@@ -2443,7 +2446,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2531,7 +2534,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2619,7 +2622,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2688,6 +2691,9 @@
       <c r="B274" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C274" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B275" s="3" t="s">
@@ -2704,7 +2710,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2789,7 +2795,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2874,7 +2880,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2959,7 +2965,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3044,7 +3050,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3129,7 +3135,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3214,7 +3220,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3299,7 +3305,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3384,7 +3390,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3469,7 +3475,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3554,7 +3560,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3639,7 +3645,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3708,9 +3714,6 @@
       <c r="B406" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C406" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B407" s="3" t="s">
@@ -3727,7 +3730,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3796,6 +3799,9 @@
       <c r="B417" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C417" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B418" s="3" t="s">
@@ -3812,7 +3818,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3897,7 +3903,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3982,7 +3988,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4051,9 +4057,6 @@
       <c r="B450" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C450" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B451" s="3" t="s">
@@ -4070,7 +4073,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4158,7 +4161,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4227,6 +4230,9 @@
       <c r="B472" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C472" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B473" s="3" t="s">
@@ -4243,7 +4249,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4328,7 +4334,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4413,7 +4419,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4498,7 +4504,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4567,9 +4573,6 @@
       <c r="B516" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C516" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B517" s="3" t="s">
@@ -4586,7 +4589,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4674,7 +4677,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4751,9 +4754,6 @@
       <c r="B539" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C539" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B540" s="3" t="s">
@@ -4765,7 +4765,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4842,6 +4842,9 @@
       <c r="B550" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C550" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B551" s="3" t="s">
@@ -4853,7 +4856,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4941,7 +4944,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5029,7 +5032,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5117,7 +5120,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5205,7 +5208,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5274,6 +5277,9 @@
       <c r="B604" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C604" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B605" s="3" t="s">
@@ -5290,7 +5296,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5351,7 +5357,9 @@
       <c r="B614" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C614" s="6"/>
+      <c r="C614" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B615" s="3" t="s">
@@ -5367,10 +5375,13 @@
       <c r="B617" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C617" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5431,17 +5442,12 @@
       <c r="B625" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C625" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C625" s="6"/>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B626" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C626" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B627" s="3" t="s">
@@ -5452,13 +5458,10 @@
       <c r="B628" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C628" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5546,7 +5549,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5634,7 +5637,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5703,6 +5706,9 @@
       <c r="B659" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C659" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B660" s="3" t="s">
@@ -5719,7 +5725,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5804,7 +5810,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5878,9 +5884,6 @@
       <c r="B682" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C682" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="683" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B683" s="3" t="s">
@@ -5892,7 +5895,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -5953,7 +5956,9 @@
       <c r="B691" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C691" s="6"/>
+      <c r="C691" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="692" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B692" s="3" t="s">
@@ -5964,15 +5969,21 @@
       <c r="B693" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C693" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="694" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B694" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C694" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6033,9 +6044,7 @@
       <c r="B702" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C702" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C702" s="6"/>
     </row>
     <row r="703" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B703" s="3" t="s">
@@ -6051,13 +6060,10 @@
       <c r="B705" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C705" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6126,9 +6132,6 @@
       <c r="B714" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C714" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="715" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B715" s="3" t="s">
@@ -6145,7 +6148,7 @@
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6214,6 +6217,9 @@
       <c r="B725" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C725" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="726" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B726" s="3" t="s">
@@ -6230,7 +6236,7 @@
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6309,10 +6315,13 @@
       <c r="B738" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C738" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6391,13 +6400,10 @@
       <c r="B749" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C749" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6466,9 +6472,6 @@
       <c r="B758" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C758" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="759" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B759" s="3" t="s">
@@ -6485,7 +6488,7 @@
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6506,19 +6509,25 @@
       <c r="B763" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C763" s="6"/>
+      <c r="C763" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="764" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B764" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C764" s="6"/>
+      <c r="C764" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="765" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B765" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C765" s="6"/>
+      <c r="C765" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="766" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B766" s="3" t="s">
@@ -6540,12 +6549,17 @@
       <c r="B768" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C768" s="6"/>
+      <c r="C768" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="769" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B769" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C769" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="770" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B770" s="3" t="s">
@@ -6556,10 +6570,13 @@
       <c r="B771" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C771" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3</v>
@@ -6580,25 +6597,19 @@
       <c r="B774" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C774" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C774" s="6"/>
     </row>
     <row r="775" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B775" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C775" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C775" s="6"/>
     </row>
     <row r="776" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B776" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C776" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C776" s="6"/>
     </row>
     <row r="777" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B777" s="3" t="s">
@@ -6620,17 +6631,12 @@
       <c r="B779" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C779" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C779" s="6"/>
     </row>
     <row r="780" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B780" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C780" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="781" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B781" s="3" t="s">
@@ -6641,13 +6647,10 @@
       <c r="B782" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C782" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B783" s="7" t="s">
         <v>3</v>
@@ -6735,7 +6738,7 @@
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A794" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B794" s="7" t="s">
         <v>3</v>
@@ -6804,6 +6807,9 @@
       <c r="B802" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C802" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="803" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B803" s="3" t="s">
@@ -6820,7 +6826,7 @@
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A805" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B805" s="7" t="s">
         <v>3</v>
@@ -6889,9 +6895,6 @@
       <c r="B813" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C813" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="814" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B814" s="3" t="s">
@@ -6899,19 +6902,19 @@
       </c>
     </row>
     <row r="815" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A815" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B815" s="7" t="s">
-        <v>3</v>
+      <c r="B815" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C815" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B816" s="3" t="s">
-        <v>4</v>
+      <c r="A816" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B816" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C816" s="5" t="s">
         <v>13</v>
@@ -6919,7 +6922,7 @@
     </row>
     <row r="817" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B817" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C817" s="5" t="s">
         <v>13</v>
@@ -6927,7 +6930,7 @@
     </row>
     <row r="818" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B818" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C818" s="5" t="s">
         <v>13</v>
@@ -6935,7 +6938,7 @@
     </row>
     <row r="819" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B819" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C819" s="5" t="s">
         <v>13</v>
@@ -6943,7 +6946,7 @@
     </row>
     <row r="820" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B820" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C820" s="5" t="s">
         <v>13</v>
@@ -6951,7 +6954,7 @@
     </row>
     <row r="821" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B821" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C821" s="5" t="s">
         <v>13</v>
@@ -6959,7 +6962,7 @@
     </row>
     <row r="822" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B822" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C822" s="5" t="s">
         <v>13</v>
@@ -6967,7 +6970,7 @@
     </row>
     <row r="823" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B823" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C823" s="5" t="s">
         <v>13</v>
@@ -6975,23 +6978,23 @@
     </row>
     <row r="824" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B824" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C824" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="825" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A825" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B825" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C825" s="5" t="s">
-        <v>13</v>
+      <c r="B825" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="826" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B826" s="3" t="s">
-        <v>4</v>
+      <c r="A826" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B826" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C826" s="5" t="s">
         <v>13</v>
@@ -6999,7 +7002,7 @@
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B827" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C827" s="5" t="s">
         <v>13</v>
@@ -7007,7 +7010,7 @@
     </row>
     <row r="828" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B828" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C828" s="5" t="s">
         <v>13</v>
@@ -7015,7 +7018,7 @@
     </row>
     <row r="829" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B829" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C829" s="5" t="s">
         <v>13</v>
@@ -7023,7 +7026,7 @@
     </row>
     <row r="830" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B830" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C830" s="5" t="s">
         <v>13</v>
@@ -7031,7 +7034,7 @@
     </row>
     <row r="831" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B831" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C831" s="5" t="s">
         <v>13</v>
@@ -7039,24 +7042,112 @@
     </row>
     <row r="832" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B832" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C832" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="833" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="833" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B833" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="834" spans="2:2" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="C833" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="834" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B834" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="835" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B835" s="3">
+        <v>11</v>
+      </c>
+      <c r="C834" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="835" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B835" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="836" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A836" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B836" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C836" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="837" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B837" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C837" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="838" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B838" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C838" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="839" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B839" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C839" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="840" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B840" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C840" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="841" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B841" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C841" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="842" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B842" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C842" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="843" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B843" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C843" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="844" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B844" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="845" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B845" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="846" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B846" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFCC0A2F-68B9-47CD-9A89-8718734097A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBD712DE-B400-4D12-AB65-239851DAEFF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1577" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1599" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C846"/>
+  <dimension ref="A1:C857"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -650,7 +650,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -741,7 +741,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -832,7 +832,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -923,7 +923,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -1000,6 +1000,9 @@
       <c r="B66" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C66" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B67" s="3" t="s">
@@ -1011,7 +1014,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1088,9 +1091,6 @@
       <c r="B77" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C77" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B78" s="3" t="s">
@@ -1102,7 +1102,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1193,7 +1193,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1284,7 +1284,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1375,7 +1375,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1557,7 +1557,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1648,7 +1648,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1739,7 +1739,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1830,7 +1830,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1921,7 +1921,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1990,6 +1990,9 @@
       <c r="B186" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C186" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B187" s="3" t="s">
@@ -2009,7 +2012,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2078,9 +2081,6 @@
       <c r="B197" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C197" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B198" s="3" t="s">
@@ -2100,7 +2100,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2177,6 +2177,9 @@
       <c r="B209" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C209" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B210" s="3" t="s">
@@ -2188,7 +2191,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2257,6 +2260,9 @@
       <c r="B219" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C219" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B220" s="3" t="s">
@@ -2273,7 +2279,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2342,9 +2348,6 @@
       <c r="B230" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C230" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B231" s="3" t="s">
@@ -2361,7 +2364,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2430,6 +2433,9 @@
       <c r="B241" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C241" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B242" s="3" t="s">
@@ -2446,7 +2452,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2515,9 +2521,6 @@
       <c r="B252" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C252" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B253" s="3" t="s">
@@ -2534,7 +2537,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2622,7 +2625,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2710,7 +2713,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2779,6 +2782,9 @@
       <c r="B285" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C285" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B286" s="3" t="s">
@@ -2795,7 +2801,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2880,7 +2886,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2965,7 +2971,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3050,7 +3056,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3135,7 +3141,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3220,7 +3226,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3305,7 +3311,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3390,7 +3396,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3475,7 +3481,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3560,7 +3566,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3645,7 +3651,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3730,7 +3736,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3799,9 +3805,6 @@
       <c r="B417" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C417" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B418" s="3" t="s">
@@ -3818,7 +3821,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3887,6 +3890,9 @@
       <c r="B428" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C428" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B429" s="3" t="s">
@@ -3903,7 +3909,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3988,7 +3994,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4073,7 +4079,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4142,9 +4148,6 @@
       <c r="B461" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C461" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B462" s="3" t="s">
@@ -4161,7 +4164,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4249,7 +4252,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4318,6 +4321,9 @@
       <c r="B483" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C483" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B484" s="3" t="s">
@@ -4334,7 +4340,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4419,7 +4425,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4504,7 +4510,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4589,7 +4595,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4658,9 +4664,6 @@
       <c r="B527" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C527" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B528" s="3" t="s">
@@ -4677,7 +4680,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4765,7 +4768,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4842,9 +4845,6 @@
       <c r="B550" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C550" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B551" s="3" t="s">
@@ -4856,7 +4856,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4933,6 +4933,9 @@
       <c r="B561" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C561" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="562" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B562" s="3" t="s">
@@ -4944,7 +4947,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5032,7 +5035,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5120,7 +5123,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5208,7 +5211,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5296,7 +5299,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5365,6 +5368,9 @@
       <c r="B615" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C615" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B616" s="3" t="s">
@@ -5381,7 +5387,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5442,7 +5448,9 @@
       <c r="B625" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C625" s="6"/>
+      <c r="C625" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B626" s="3" t="s">
@@ -5458,10 +5466,13 @@
       <c r="B628" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C628" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5522,17 +5533,12 @@
       <c r="B636" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C636" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C636" s="6"/>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B637" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C637" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B638" s="3" t="s">
@@ -5543,13 +5549,10 @@
       <c r="B639" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C639" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5637,7 +5640,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5725,7 +5728,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5794,6 +5797,9 @@
       <c r="B670" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C670" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="671" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B671" s="3" t="s">
@@ -5810,7 +5816,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5895,7 +5901,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -5969,9 +5975,6 @@
       <c r="B693" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C693" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="694" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B694" s="3" t="s">
@@ -5983,7 +5986,7 @@
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6044,7 +6047,9 @@
       <c r="B702" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C702" s="6"/>
+      <c r="C702" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="703" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B703" s="3" t="s">
@@ -6055,15 +6060,21 @@
       <c r="B704" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C704" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="705" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B705" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C705" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6124,9 +6135,7 @@
       <c r="B713" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C713" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C713" s="6"/>
     </row>
     <row r="714" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B714" s="3" t="s">
@@ -6142,13 +6151,10 @@
       <c r="B716" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C716" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6217,9 +6223,6 @@
       <c r="B725" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C725" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="726" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B726" s="3" t="s">
@@ -6236,7 +6239,7 @@
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6305,6 +6308,9 @@
       <c r="B736" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C736" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="737" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B737" s="3" t="s">
@@ -6321,7 +6327,7 @@
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6400,10 +6406,13 @@
       <c r="B749" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C749" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6482,13 +6491,10 @@
       <c r="B760" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C760" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6557,9 +6563,6 @@
       <c r="B769" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C769" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="770" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B770" s="3" t="s">
@@ -6576,7 +6579,7 @@
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3</v>
@@ -6597,19 +6600,25 @@
       <c r="B774" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C774" s="6"/>
+      <c r="C774" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="775" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B775" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C775" s="6"/>
+      <c r="C775" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="776" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B776" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C776" s="6"/>
+      <c r="C776" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="777" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B777" s="3" t="s">
@@ -6631,12 +6640,17 @@
       <c r="B779" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C779" s="6"/>
+      <c r="C779" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="780" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B780" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C780" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="781" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B781" s="3" t="s">
@@ -6647,10 +6661,13 @@
       <c r="B782" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C782" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B783" s="7" t="s">
         <v>3</v>
@@ -6671,25 +6688,19 @@
       <c r="B785" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C785" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C785" s="6"/>
     </row>
     <row r="786" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B786" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C786" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C786" s="6"/>
     </row>
     <row r="787" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B787" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C787" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C787" s="6"/>
     </row>
     <row r="788" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B788" s="3" t="s">
@@ -6711,17 +6722,12 @@
       <c r="B790" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C790" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C790" s="6"/>
     </row>
     <row r="791" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B791" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C791" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="792" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B792" s="3" t="s">
@@ -6732,13 +6738,10 @@
       <c r="B793" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C793" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A794" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B794" s="7" t="s">
         <v>3</v>
@@ -6826,7 +6829,7 @@
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A805" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B805" s="7" t="s">
         <v>3</v>
@@ -6895,6 +6898,9 @@
       <c r="B813" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C813" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="814" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B814" s="3" t="s">
@@ -6911,7 +6917,7 @@
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A816" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B816" s="7" t="s">
         <v>3</v>
@@ -6980,9 +6986,6 @@
       <c r="B824" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C824" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="825" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B825" s="3" t="s">
@@ -6990,19 +6993,19 @@
       </c>
     </row>
     <row r="826" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A826" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B826" s="7" t="s">
-        <v>3</v>
+      <c r="B826" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C826" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B827" s="3" t="s">
-        <v>4</v>
+      <c r="A827" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B827" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C827" s="5" t="s">
         <v>13</v>
@@ -7010,7 +7013,7 @@
     </row>
     <row r="828" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B828" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C828" s="5" t="s">
         <v>13</v>
@@ -7018,7 +7021,7 @@
     </row>
     <row r="829" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B829" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C829" s="5" t="s">
         <v>13</v>
@@ -7026,7 +7029,7 @@
     </row>
     <row r="830" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B830" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C830" s="5" t="s">
         <v>13</v>
@@ -7034,7 +7037,7 @@
     </row>
     <row r="831" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B831" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C831" s="5" t="s">
         <v>13</v>
@@ -7042,7 +7045,7 @@
     </row>
     <row r="832" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B832" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C832" s="5" t="s">
         <v>13</v>
@@ -7050,7 +7053,7 @@
     </row>
     <row r="833" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B833" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C833" s="5" t="s">
         <v>13</v>
@@ -7058,7 +7061,7 @@
     </row>
     <row r="834" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B834" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C834" s="5" t="s">
         <v>13</v>
@@ -7066,23 +7069,23 @@
     </row>
     <row r="835" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B835" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C835" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="836" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A836" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B836" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C836" s="5" t="s">
-        <v>13</v>
+      <c r="B836" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="837" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B837" s="3" t="s">
-        <v>4</v>
+      <c r="A837" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B837" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C837" s="5" t="s">
         <v>13</v>
@@ -7090,7 +7093,7 @@
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B838" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C838" s="5" t="s">
         <v>13</v>
@@ -7098,7 +7101,7 @@
     </row>
     <row r="839" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B839" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C839" s="5" t="s">
         <v>13</v>
@@ -7106,7 +7109,7 @@
     </row>
     <row r="840" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B840" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C840" s="5" t="s">
         <v>13</v>
@@ -7114,7 +7117,7 @@
     </row>
     <row r="841" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B841" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C841" s="5" t="s">
         <v>13</v>
@@ -7122,7 +7125,7 @@
     </row>
     <row r="842" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B842" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C842" s="5" t="s">
         <v>13</v>
@@ -7130,7 +7133,7 @@
     </row>
     <row r="843" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B843" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C843" s="5" t="s">
         <v>13</v>
@@ -7138,16 +7141,104 @@
     </row>
     <row r="844" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B844" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C844" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="845" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B845" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C845" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="846" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B846" s="3">
+      <c r="B846" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="847" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A847" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B847" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C847" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="848" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B848" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C848" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="849" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B849" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C849" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="850" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B850" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C850" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="851" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B851" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C851" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="852" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B852" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C852" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="853" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B853" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C853" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="854" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B854" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C854" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="855" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B855" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="856" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B856" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="857" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B857" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBD712DE-B400-4D12-AB65-239851DAEFF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DECFB81-2D48-4D0D-A047-3B7C84ED2A4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1599" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C857"/>
+  <dimension ref="A1:C868"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -650,7 +650,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -741,7 +741,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -832,7 +832,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -923,7 +923,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -1014,7 +1014,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1091,6 +1091,9 @@
       <c r="B77" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C77" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B78" s="3" t="s">
@@ -1102,7 +1105,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1179,9 +1182,6 @@
       <c r="B88" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C88" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B89" s="3" t="s">
@@ -1193,7 +1193,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1284,7 +1284,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1375,7 +1375,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1557,7 +1557,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1648,7 +1648,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1739,7 +1739,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1830,7 +1830,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1921,7 +1921,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -2012,7 +2012,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2081,6 +2081,9 @@
       <c r="B197" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C197" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B198" s="3" t="s">
@@ -2100,7 +2103,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2169,9 +2172,6 @@
       <c r="B208" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C208" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B209" s="3" t="s">
@@ -2191,7 +2191,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2268,6 +2268,9 @@
       <c r="B220" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C220" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B221" s="3" t="s">
@@ -2279,7 +2282,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2348,6 +2351,9 @@
       <c r="B230" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C230" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B231" s="3" t="s">
@@ -2364,7 +2370,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2433,9 +2439,6 @@
       <c r="B241" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C241" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B242" s="3" t="s">
@@ -2452,7 +2455,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2521,6 +2524,9 @@
       <c r="B252" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C252" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B253" s="3" t="s">
@@ -2537,7 +2543,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2606,9 +2612,6 @@
       <c r="B263" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C263" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B264" s="3" t="s">
@@ -2625,7 +2628,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2713,7 +2716,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2801,7 +2804,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2870,6 +2873,9 @@
       <c r="B296" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C296" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B297" s="3" t="s">
@@ -2886,7 +2892,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2971,7 +2977,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3056,7 +3062,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3141,7 +3147,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3226,7 +3232,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3311,7 +3317,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3396,7 +3402,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3481,7 +3487,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3566,7 +3572,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3651,7 +3657,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3736,7 +3742,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3821,7 +3827,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3890,9 +3896,6 @@
       <c r="B428" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C428" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B429" s="3" t="s">
@@ -3909,7 +3912,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3978,6 +3981,9 @@
       <c r="B439" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C439" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B440" s="3" t="s">
@@ -3994,7 +4000,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4079,7 +4085,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4164,7 +4170,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4233,9 +4239,6 @@
       <c r="B472" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C472" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B473" s="3" t="s">
@@ -4252,7 +4255,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4340,7 +4343,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4409,6 +4412,9 @@
       <c r="B494" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C494" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B495" s="3" t="s">
@@ -4425,7 +4431,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4510,7 +4516,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4595,7 +4601,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4680,7 +4686,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4749,9 +4755,6 @@
       <c r="B538" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C538" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B539" s="3" t="s">
@@ -4768,7 +4771,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4856,7 +4859,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4933,9 +4936,6 @@
       <c r="B561" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C561" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="562" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B562" s="3" t="s">
@@ -4947,7 +4947,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5024,6 +5024,9 @@
       <c r="B572" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C572" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="573" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B573" s="3" t="s">
@@ -5035,7 +5038,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5123,7 +5126,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5211,7 +5214,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5299,7 +5302,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5387,7 +5390,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5456,6 +5459,9 @@
       <c r="B626" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C626" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B627" s="3" t="s">
@@ -5472,7 +5478,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5533,7 +5539,9 @@
       <c r="B636" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C636" s="6"/>
+      <c r="C636" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B637" s="3" t="s">
@@ -5549,10 +5557,13 @@
       <c r="B639" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C639" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5613,17 +5624,12 @@
       <c r="B647" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C647" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C647" s="6"/>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B648" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C648" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B649" s="3" t="s">
@@ -5634,13 +5640,10 @@
       <c r="B650" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C650" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5728,7 +5731,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5816,7 +5819,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5885,6 +5888,9 @@
       <c r="B681" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C681" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="682" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B682" s="3" t="s">
@@ -5901,7 +5907,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -5986,7 +5992,7 @@
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6060,9 +6066,6 @@
       <c r="B704" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C704" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="705" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B705" s="3" t="s">
@@ -6074,7 +6077,7 @@
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6135,7 +6138,9 @@
       <c r="B713" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C713" s="6"/>
+      <c r="C713" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="714" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B714" s="3" t="s">
@@ -6146,15 +6151,21 @@
       <c r="B715" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C715" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="716" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B716" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C716" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6215,9 +6226,7 @@
       <c r="B724" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C724" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C724" s="6"/>
     </row>
     <row r="725" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B725" s="3" t="s">
@@ -6233,13 +6242,10 @@
       <c r="B727" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C727" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6308,9 +6314,6 @@
       <c r="B736" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C736" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="737" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B737" s="3" t="s">
@@ -6327,7 +6330,7 @@
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6396,6 +6399,9 @@
       <c r="B747" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C747" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="748" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B748" s="3" t="s">
@@ -6412,7 +6418,7 @@
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6491,10 +6497,13 @@
       <c r="B760" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C760" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6573,13 +6582,10 @@
       <c r="B771" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C771" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3</v>
@@ -6648,9 +6654,6 @@
       <c r="B780" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C780" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="781" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B781" s="3" t="s">
@@ -6667,7 +6670,7 @@
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B783" s="7" t="s">
         <v>3</v>
@@ -6688,19 +6691,25 @@
       <c r="B785" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C785" s="6"/>
+      <c r="C785" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="786" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B786" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C786" s="6"/>
+      <c r="C786" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="787" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B787" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C787" s="6"/>
+      <c r="C787" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="788" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B788" s="3" t="s">
@@ -6722,12 +6731,17 @@
       <c r="B790" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C790" s="6"/>
+      <c r="C790" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="791" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B791" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C791" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="792" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B792" s="3" t="s">
@@ -6738,10 +6752,13 @@
       <c r="B793" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C793" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A794" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B794" s="7" t="s">
         <v>3</v>
@@ -6762,25 +6779,19 @@
       <c r="B796" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C796" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C796" s="6"/>
     </row>
     <row r="797" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B797" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C797" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C797" s="6"/>
     </row>
     <row r="798" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B798" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C798" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C798" s="6"/>
     </row>
     <row r="799" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B799" s="3" t="s">
@@ -6802,17 +6813,12 @@
       <c r="B801" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C801" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C801" s="6"/>
     </row>
     <row r="802" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B802" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C802" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="803" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B803" s="3" t="s">
@@ -6823,13 +6829,10 @@
       <c r="B804" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C804" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A805" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B805" s="7" t="s">
         <v>3</v>
@@ -6917,7 +6920,7 @@
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A816" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B816" s="7" t="s">
         <v>3</v>
@@ -6986,6 +6989,9 @@
       <c r="B824" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C824" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="825" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B825" s="3" t="s">
@@ -7002,7 +7008,7 @@
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A827" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B827" s="7" t="s">
         <v>3</v>
@@ -7071,9 +7077,6 @@
       <c r="B835" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C835" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="836" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B836" s="3" t="s">
@@ -7081,19 +7084,19 @@
       </c>
     </row>
     <row r="837" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A837" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B837" s="7" t="s">
-        <v>3</v>
+      <c r="B837" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C837" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B838" s="3" t="s">
-        <v>4</v>
+      <c r="A838" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B838" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C838" s="5" t="s">
         <v>13</v>
@@ -7101,7 +7104,7 @@
     </row>
     <row r="839" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B839" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C839" s="5" t="s">
         <v>13</v>
@@ -7109,7 +7112,7 @@
     </row>
     <row r="840" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B840" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C840" s="5" t="s">
         <v>13</v>
@@ -7117,7 +7120,7 @@
     </row>
     <row r="841" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B841" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C841" s="5" t="s">
         <v>13</v>
@@ -7125,7 +7128,7 @@
     </row>
     <row r="842" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B842" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C842" s="5" t="s">
         <v>13</v>
@@ -7133,7 +7136,7 @@
     </row>
     <row r="843" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B843" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C843" s="5" t="s">
         <v>13</v>
@@ -7141,7 +7144,7 @@
     </row>
     <row r="844" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B844" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C844" s="5" t="s">
         <v>13</v>
@@ -7149,7 +7152,7 @@
     </row>
     <row r="845" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B845" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C845" s="5" t="s">
         <v>13</v>
@@ -7157,88 +7160,176 @@
     </row>
     <row r="846" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B846" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C846" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="847" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A847" s="4">
+      <c r="B847" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="848" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A848" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B848" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C848" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="849" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B849" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C849" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="850" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B850" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C850" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="851" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B851" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C851" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="852" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B852" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C852" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="853" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B853" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C853" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="854" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B854" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C854" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="855" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B855" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C855" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="856" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B856" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C856" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="857" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B857" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="858" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A858" s="4">
         <v>46042</v>
       </c>
-      <c r="B847" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C847" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="848" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B848" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C848" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="849" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B849" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C849" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="850" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B850" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C850" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="851" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B851" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C851" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="852" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B852" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C852" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="853" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B853" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C853" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="854" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B854" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C854" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="855" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B855" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="856" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B856" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="857" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B857" s="3">
+      <c r="B858" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C858" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="859" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B859" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C859" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="860" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B860" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C860" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="861" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B861" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C861" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="862" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B862" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C862" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="863" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B863" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C863" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="864" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B864" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C864" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="865" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B865" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C865" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="866" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B866" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="867" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B867" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="868" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B868" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DECFB81-2D48-4D0D-A047-3B7C84ED2A4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36CF8122-BAD8-4A90-8B9D-3E5B7B1DB9C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1643" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C868"/>
+  <dimension ref="A1:C879"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -493,7 +493,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>3</v>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -650,7 +650,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -741,7 +741,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -832,7 +832,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -923,7 +923,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -1014,7 +1014,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1105,7 +1105,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1182,6 +1182,9 @@
       <c r="B88" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C88" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B89" s="3" t="s">
@@ -1193,7 +1196,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1270,9 +1273,6 @@
       <c r="B99" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C99" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B100" s="3" t="s">
@@ -1284,7 +1284,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1375,7 +1375,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1557,7 +1557,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1648,7 +1648,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1739,7 +1739,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1830,7 +1830,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1921,7 +1921,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -2012,7 +2012,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2103,7 +2103,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2172,6 +2172,9 @@
       <c r="B208" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C208" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B209" s="3" t="s">
@@ -2191,7 +2194,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2260,9 +2263,6 @@
       <c r="B219" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C219" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B220" s="3" t="s">
@@ -2282,7 +2282,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2359,6 +2359,9 @@
       <c r="B231" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C231" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B232" s="3" t="s">
@@ -2370,7 +2373,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2439,6 +2442,9 @@
       <c r="B241" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C241" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B242" s="3" t="s">
@@ -2455,7 +2461,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2524,9 +2530,6 @@
       <c r="B252" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C252" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B253" s="3" t="s">
@@ -2543,7 +2546,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2612,6 +2615,9 @@
       <c r="B263" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C263" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B264" s="3" t="s">
@@ -2628,7 +2634,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2697,9 +2703,6 @@
       <c r="B274" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C274" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B275" s="3" t="s">
@@ -2716,7 +2719,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2804,7 +2807,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2892,7 +2895,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2961,6 +2964,9 @@
       <c r="B307" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C307" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B308" s="3" t="s">
@@ -2977,7 +2983,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3062,7 +3068,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3147,7 +3153,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3232,7 +3238,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3317,7 +3323,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3402,7 +3408,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3487,7 +3493,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3572,7 +3578,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3657,7 +3663,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3742,7 +3748,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3827,7 +3833,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3912,7 +3918,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3981,9 +3987,6 @@
       <c r="B439" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C439" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B440" s="3" t="s">
@@ -4000,7 +4003,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4069,6 +4072,9 @@
       <c r="B450" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C450" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B451" s="3" t="s">
@@ -4085,7 +4091,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4170,7 +4176,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4255,7 +4261,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4324,9 +4330,6 @@
       <c r="B483" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C483" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B484" s="3" t="s">
@@ -4343,7 +4346,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4431,7 +4434,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4500,6 +4503,9 @@
       <c r="B505" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C505" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B506" s="3" t="s">
@@ -4516,7 +4522,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4601,7 +4607,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4686,7 +4692,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4771,7 +4777,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4840,9 +4846,6 @@
       <c r="B549" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C549" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B550" s="3" t="s">
@@ -4859,7 +4862,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4947,7 +4950,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5024,9 +5027,6 @@
       <c r="B572" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C572" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="573" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B573" s="3" t="s">
@@ -5038,7 +5038,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5115,6 +5115,9 @@
       <c r="B583" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C583" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B584" s="3" t="s">
@@ -5126,7 +5129,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5214,7 +5217,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5302,7 +5305,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5390,7 +5393,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5478,7 +5481,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5547,6 +5550,9 @@
       <c r="B637" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C637" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B638" s="3" t="s">
@@ -5563,7 +5569,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5624,7 +5630,9 @@
       <c r="B647" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C647" s="6"/>
+      <c r="C647" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B648" s="3" t="s">
@@ -5640,10 +5648,13 @@
       <c r="B650" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C650" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5704,17 +5715,12 @@
       <c r="B658" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C658" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C658" s="6"/>
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B659" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C659" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B660" s="3" t="s">
@@ -5725,13 +5731,10 @@
       <c r="B661" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C661" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5819,7 +5822,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5907,7 +5910,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -5976,6 +5979,9 @@
       <c r="B692" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C692" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="693" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B693" s="3" t="s">
@@ -5992,7 +5998,7 @@
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6077,7 +6083,7 @@
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6151,9 +6157,6 @@
       <c r="B715" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C715" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="716" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B716" s="3" t="s">
@@ -6165,7 +6168,7 @@
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6226,7 +6229,9 @@
       <c r="B724" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C724" s="6"/>
+      <c r="C724" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="725" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B725" s="3" t="s">
@@ -6237,15 +6242,21 @@
       <c r="B726" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C726" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="727" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B727" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C727" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6306,9 +6317,7 @@
       <c r="B735" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C735" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C735" s="6"/>
     </row>
     <row r="736" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B736" s="3" t="s">
@@ -6324,13 +6333,10 @@
       <c r="B738" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C738" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6399,9 +6405,6 @@
       <c r="B747" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C747" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="748" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B748" s="3" t="s">
@@ -6418,7 +6421,7 @@
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6487,6 +6490,9 @@
       <c r="B758" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C758" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="759" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B759" s="3" t="s">
@@ -6503,7 +6509,7 @@
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6582,10 +6588,13 @@
       <c r="B771" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C771" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3</v>
@@ -6664,13 +6673,10 @@
       <c r="B782" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C782" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B783" s="7" t="s">
         <v>3</v>
@@ -6739,9 +6745,6 @@
       <c r="B791" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C791" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="792" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B792" s="3" t="s">
@@ -6758,7 +6761,7 @@
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A794" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B794" s="7" t="s">
         <v>3</v>
@@ -6779,19 +6782,25 @@
       <c r="B796" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C796" s="6"/>
+      <c r="C796" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="797" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B797" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C797" s="6"/>
+      <c r="C797" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="798" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B798" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C798" s="6"/>
+      <c r="C798" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="799" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B799" s="3" t="s">
@@ -6813,12 +6822,17 @@
       <c r="B801" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C801" s="6"/>
+      <c r="C801" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="802" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B802" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C802" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="803" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B803" s="3" t="s">
@@ -6829,10 +6843,13 @@
       <c r="B804" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C804" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A805" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B805" s="7" t="s">
         <v>3</v>
@@ -6853,25 +6870,19 @@
       <c r="B807" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C807" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C807" s="6"/>
     </row>
     <row r="808" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B808" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C808" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C808" s="6"/>
     </row>
     <row r="809" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B809" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C809" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C809" s="6"/>
     </row>
     <row r="810" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B810" s="3" t="s">
@@ -6893,17 +6904,12 @@
       <c r="B812" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C812" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C812" s="6"/>
     </row>
     <row r="813" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B813" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C813" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="814" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B814" s="3" t="s">
@@ -6914,13 +6920,10 @@
       <c r="B815" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C815" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A816" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B816" s="7" t="s">
         <v>3</v>
@@ -7008,7 +7011,7 @@
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A827" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B827" s="7" t="s">
         <v>3</v>
@@ -7077,6 +7080,9 @@
       <c r="B835" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C835" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="836" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B836" s="3" t="s">
@@ -7093,7 +7099,7 @@
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A838" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B838" s="7" t="s">
         <v>3</v>
@@ -7162,9 +7168,6 @@
       <c r="B846" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C846" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="847" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B847" s="3" t="s">
@@ -7172,19 +7175,19 @@
       </c>
     </row>
     <row r="848" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A848" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B848" s="7" t="s">
-        <v>3</v>
+      <c r="B848" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C848" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B849" s="3" t="s">
-        <v>4</v>
+      <c r="A849" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B849" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C849" s="5" t="s">
         <v>13</v>
@@ -7192,7 +7195,7 @@
     </row>
     <row r="850" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B850" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C850" s="5" t="s">
         <v>13</v>
@@ -7200,7 +7203,7 @@
     </row>
     <row r="851" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B851" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C851" s="5" t="s">
         <v>13</v>
@@ -7208,7 +7211,7 @@
     </row>
     <row r="852" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B852" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C852" s="5" t="s">
         <v>13</v>
@@ -7216,7 +7219,7 @@
     </row>
     <row r="853" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B853" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C853" s="5" t="s">
         <v>13</v>
@@ -7224,7 +7227,7 @@
     </row>
     <row r="854" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B854" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C854" s="5" t="s">
         <v>13</v>
@@ -7232,7 +7235,7 @@
     </row>
     <row r="855" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B855" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C855" s="5" t="s">
         <v>13</v>
@@ -7240,7 +7243,7 @@
     </row>
     <row r="856" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B856" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C856" s="5" t="s">
         <v>13</v>
@@ -7248,23 +7251,23 @@
     </row>
     <row r="857" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B857" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C857" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="858" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A858" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B858" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C858" s="5" t="s">
-        <v>13</v>
+      <c r="B858" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="859" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B859" s="3" t="s">
-        <v>4</v>
+      <c r="A859" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B859" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C859" s="5" t="s">
         <v>13</v>
@@ -7272,7 +7275,7 @@
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B860" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C860" s="5" t="s">
         <v>13</v>
@@ -7280,7 +7283,7 @@
     </row>
     <row r="861" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B861" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C861" s="5" t="s">
         <v>13</v>
@@ -7288,7 +7291,7 @@
     </row>
     <row r="862" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B862" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C862" s="5" t="s">
         <v>13</v>
@@ -7296,7 +7299,7 @@
     </row>
     <row r="863" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B863" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C863" s="5" t="s">
         <v>13</v>
@@ -7304,32 +7307,120 @@
     </row>
     <row r="864" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B864" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C864" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="865" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="865" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B865" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C865" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="866" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="866" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B866" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="867" spans="2:3" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="C866" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="867" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B867" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="868" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B868" s="3">
+        <v>11</v>
+      </c>
+      <c r="C867" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="868" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B868" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="869" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A869" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B869" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C869" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="870" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B870" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C870" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="871" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B871" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C871" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="872" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B872" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C872" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="873" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B873" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C873" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="874" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B874" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C874" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="875" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B875" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C875" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="876" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B876" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C876" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="877" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B877" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="878" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B878" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="879" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B879" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36CF8122-BAD8-4A90-8B9D-3E5B7B1DB9C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBCDA07E-DFC0-4E22-83DB-7BC655E14744}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1643" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1665" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C879"/>
+  <dimension ref="A1:C890"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -650,7 +650,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -741,7 +741,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -832,7 +832,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -923,7 +923,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -1014,7 +1014,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1105,7 +1105,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1196,7 +1196,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1273,6 +1273,9 @@
       <c r="B99" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C99" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B100" s="3" t="s">
@@ -1284,7 +1287,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1361,9 +1364,6 @@
       <c r="B110" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C110" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B111" s="3" t="s">
@@ -1375,7 +1375,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1557,7 +1557,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1648,7 +1648,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1739,7 +1739,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1830,7 +1830,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1921,7 +1921,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -2012,7 +2012,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2103,7 +2103,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2194,7 +2194,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2263,6 +2263,9 @@
       <c r="B219" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C219" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B220" s="3" t="s">
@@ -2282,7 +2285,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2351,9 +2354,6 @@
       <c r="B230" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C230" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B231" s="3" t="s">
@@ -2373,7 +2373,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2450,6 +2450,9 @@
       <c r="B242" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C242" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B243" s="3" t="s">
@@ -2461,7 +2464,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2530,6 +2533,9 @@
       <c r="B252" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C252" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B253" s="3" t="s">
@@ -2546,7 +2552,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2615,9 +2621,6 @@
       <c r="B263" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C263" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B264" s="3" t="s">
@@ -2634,7 +2637,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2703,6 +2706,9 @@
       <c r="B274" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C274" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B275" s="3" t="s">
@@ -2719,7 +2725,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2788,9 +2794,6 @@
       <c r="B285" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C285" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B286" s="3" t="s">
@@ -2807,7 +2810,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2895,7 +2898,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2983,7 +2986,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3052,6 +3055,9 @@
       <c r="B318" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C318" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B319" s="3" t="s">
@@ -3068,7 +3074,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3153,7 +3159,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3238,7 +3244,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3323,7 +3329,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3408,7 +3414,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3493,7 +3499,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3578,7 +3584,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3663,7 +3669,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3748,7 +3754,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3833,7 +3839,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3918,7 +3924,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -4003,7 +4009,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4072,9 +4078,6 @@
       <c r="B450" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C450" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B451" s="3" t="s">
@@ -4091,7 +4094,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4160,6 +4163,9 @@
       <c r="B461" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C461" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B462" s="3" t="s">
@@ -4176,7 +4182,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4261,7 +4267,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4346,7 +4352,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4415,9 +4421,6 @@
       <c r="B494" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C494" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B495" s="3" t="s">
@@ -4434,7 +4437,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4522,7 +4525,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4591,6 +4594,9 @@
       <c r="B516" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C516" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B517" s="3" t="s">
@@ -4607,7 +4613,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4692,7 +4698,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4777,7 +4783,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4862,7 +4868,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4931,9 +4937,6 @@
       <c r="B560" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C560" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B561" s="3" t="s">
@@ -4950,7 +4953,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5038,7 +5041,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5115,9 +5118,6 @@
       <c r="B583" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C583" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B584" s="3" t="s">
@@ -5129,7 +5129,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5206,6 +5206,9 @@
       <c r="B594" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C594" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B595" s="3" t="s">
@@ -5217,7 +5220,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5305,7 +5308,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5393,7 +5396,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5481,7 +5484,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5569,7 +5572,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5638,6 +5641,9 @@
       <c r="B648" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C648" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B649" s="3" t="s">
@@ -5654,7 +5660,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5715,7 +5721,9 @@
       <c r="B658" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C658" s="6"/>
+      <c r="C658" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B659" s="3" t="s">
@@ -5731,10 +5739,13 @@
       <c r="B661" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C661" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5795,17 +5806,12 @@
       <c r="B669" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C669" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C669" s="6"/>
     </row>
     <row r="670" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B670" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C670" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="671" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B671" s="3" t="s">
@@ -5816,13 +5822,10 @@
       <c r="B672" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C672" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5910,7 +5913,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -5998,7 +6001,7 @@
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6067,6 +6070,9 @@
       <c r="B703" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C703" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="704" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B704" s="3" t="s">
@@ -6083,7 +6089,7 @@
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6168,7 +6174,7 @@
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6242,9 +6248,6 @@
       <c r="B726" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C726" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="727" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B727" s="3" t="s">
@@ -6256,7 +6259,7 @@
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6317,7 +6320,9 @@
       <c r="B735" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C735" s="6"/>
+      <c r="C735" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="736" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B736" s="3" t="s">
@@ -6328,15 +6333,21 @@
       <c r="B737" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C737" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="738" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B738" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C738" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6397,9 +6408,7 @@
       <c r="B746" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C746" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C746" s="6"/>
     </row>
     <row r="747" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B747" s="3" t="s">
@@ -6415,13 +6424,10 @@
       <c r="B749" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C749" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6490,9 +6496,6 @@
       <c r="B758" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C758" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="759" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B759" s="3" t="s">
@@ -6509,7 +6512,7 @@
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6578,6 +6581,9 @@
       <c r="B769" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C769" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="770" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B770" s="3" t="s">
@@ -6594,7 +6600,7 @@
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3</v>
@@ -6673,10 +6679,13 @@
       <c r="B782" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C782" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B783" s="7" t="s">
         <v>3</v>
@@ -6755,13 +6764,10 @@
       <c r="B793" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C793" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A794" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B794" s="7" t="s">
         <v>3</v>
@@ -6830,9 +6836,6 @@
       <c r="B802" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C802" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="803" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B803" s="3" t="s">
@@ -6849,7 +6852,7 @@
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A805" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B805" s="7" t="s">
         <v>3</v>
@@ -6870,19 +6873,25 @@
       <c r="B807" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C807" s="6"/>
+      <c r="C807" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="808" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B808" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C808" s="6"/>
+      <c r="C808" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="809" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B809" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C809" s="6"/>
+      <c r="C809" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="810" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B810" s="3" t="s">
@@ -6904,12 +6913,17 @@
       <c r="B812" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C812" s="6"/>
+      <c r="C812" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="813" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B813" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C813" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="814" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B814" s="3" t="s">
@@ -6920,10 +6934,13 @@
       <c r="B815" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C815" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A816" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B816" s="7" t="s">
         <v>3</v>
@@ -6944,25 +6961,19 @@
       <c r="B818" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C818" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C818" s="6"/>
     </row>
     <row r="819" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B819" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C819" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C819" s="6"/>
     </row>
     <row r="820" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B820" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C820" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C820" s="6"/>
     </row>
     <row r="821" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B821" s="3" t="s">
@@ -6984,17 +6995,12 @@
       <c r="B823" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C823" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C823" s="6"/>
     </row>
     <row r="824" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B824" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C824" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="825" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B825" s="3" t="s">
@@ -7005,13 +7011,10 @@
       <c r="B826" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C826" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A827" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B827" s="7" t="s">
         <v>3</v>
@@ -7099,7 +7102,7 @@
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A838" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B838" s="7" t="s">
         <v>3</v>
@@ -7168,6 +7171,9 @@
       <c r="B846" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C846" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="847" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B847" s="3" t="s">
@@ -7184,7 +7190,7 @@
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A849" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B849" s="7" t="s">
         <v>3</v>
@@ -7253,9 +7259,6 @@
       <c r="B857" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C857" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="858" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B858" s="3" t="s">
@@ -7263,19 +7266,19 @@
       </c>
     </row>
     <row r="859" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A859" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B859" s="7" t="s">
-        <v>3</v>
+      <c r="B859" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C859" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B860" s="3" t="s">
-        <v>4</v>
+      <c r="A860" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B860" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C860" s="5" t="s">
         <v>13</v>
@@ -7283,7 +7286,7 @@
     </row>
     <row r="861" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B861" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C861" s="5" t="s">
         <v>13</v>
@@ -7291,7 +7294,7 @@
     </row>
     <row r="862" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B862" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C862" s="5" t="s">
         <v>13</v>
@@ -7299,7 +7302,7 @@
     </row>
     <row r="863" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B863" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C863" s="5" t="s">
         <v>13</v>
@@ -7307,7 +7310,7 @@
     </row>
     <row r="864" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B864" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C864" s="5" t="s">
         <v>13</v>
@@ -7315,7 +7318,7 @@
     </row>
     <row r="865" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B865" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C865" s="5" t="s">
         <v>13</v>
@@ -7323,7 +7326,7 @@
     </row>
     <row r="866" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B866" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C866" s="5" t="s">
         <v>13</v>
@@ -7331,7 +7334,7 @@
     </row>
     <row r="867" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B867" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C867" s="5" t="s">
         <v>13</v>
@@ -7339,23 +7342,23 @@
     </row>
     <row r="868" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B868" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C868" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="869" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A869" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B869" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C869" s="5" t="s">
-        <v>13</v>
+      <c r="B869" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="870" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B870" s="3" t="s">
-        <v>4</v>
+      <c r="A870" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B870" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C870" s="5" t="s">
         <v>13</v>
@@ -7363,7 +7366,7 @@
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B871" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C871" s="5" t="s">
         <v>13</v>
@@ -7371,7 +7374,7 @@
     </row>
     <row r="872" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B872" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C872" s="5" t="s">
         <v>13</v>
@@ -7379,7 +7382,7 @@
     </row>
     <row r="873" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B873" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C873" s="5" t="s">
         <v>13</v>
@@ -7387,7 +7390,7 @@
     </row>
     <row r="874" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B874" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C874" s="5" t="s">
         <v>13</v>
@@ -7395,7 +7398,7 @@
     </row>
     <row r="875" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B875" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C875" s="5" t="s">
         <v>13</v>
@@ -7403,7 +7406,7 @@
     </row>
     <row r="876" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B876" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C876" s="5" t="s">
         <v>13</v>
@@ -7411,16 +7414,104 @@
     </row>
     <row r="877" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B877" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C877" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="878" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B878" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C878" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="879" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B879" s="3">
+      <c r="B879" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="880" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A880" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B880" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C880" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="881" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B881" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C881" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="882" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B882" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C882" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="883" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B883" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C883" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="884" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B884" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C884" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="885" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B885" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C885" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="886" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B886" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C886" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="887" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B887" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C887" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="888" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B888" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="889" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B889" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="890" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B890" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBCDA07E-DFC0-4E22-83DB-7BC655E14744}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADF721A1-26BF-4609-B2E6-DE664C93B98C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1665" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1687" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C890"/>
+  <dimension ref="A1:C901"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -650,7 +650,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -741,7 +741,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -832,7 +832,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -923,7 +923,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -1014,7 +1014,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1105,7 +1105,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1196,7 +1196,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1364,6 +1364,9 @@
       <c r="B110" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C110" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B111" s="3" t="s">
@@ -1375,7 +1378,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1452,9 +1455,6 @@
       <c r="B121" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C121" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B122" s="3" t="s">
@@ -1466,7 +1466,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1557,7 +1557,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1648,7 +1648,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1739,7 +1739,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1830,7 +1830,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1921,7 +1921,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -2012,7 +2012,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2103,7 +2103,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2194,7 +2194,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2285,7 +2285,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2354,6 +2354,9 @@
       <c r="B230" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C230" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B231" s="3" t="s">
@@ -2373,7 +2376,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2442,9 +2445,6 @@
       <c r="B241" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C241" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B242" s="3" t="s">
@@ -2464,7 +2464,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2541,6 +2541,9 @@
       <c r="B253" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C253" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B254" s="3" t="s">
@@ -2552,7 +2555,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2621,6 +2624,9 @@
       <c r="B263" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C263" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B264" s="3" t="s">
@@ -2637,7 +2643,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2706,9 +2712,6 @@
       <c r="B274" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C274" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B275" s="3" t="s">
@@ -2725,7 +2728,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2794,6 +2797,9 @@
       <c r="B285" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C285" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B286" s="3" t="s">
@@ -2810,7 +2816,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2879,9 +2885,6 @@
       <c r="B296" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C296" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B297" s="3" t="s">
@@ -2898,7 +2901,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2986,7 +2989,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3074,7 +3077,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3143,6 +3146,9 @@
       <c r="B329" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C329" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B330" s="3" t="s">
@@ -3159,7 +3165,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3244,7 +3250,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3329,7 +3335,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3414,7 +3420,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3499,7 +3505,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3584,7 +3590,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3669,7 +3675,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3754,7 +3760,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3839,7 +3845,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3924,7 +3930,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -4009,7 +4015,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4094,7 +4100,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4163,9 +4169,6 @@
       <c r="B461" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C461" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B462" s="3" t="s">
@@ -4182,7 +4185,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4251,6 +4254,9 @@
       <c r="B472" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C472" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B473" s="3" t="s">
@@ -4267,7 +4273,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4352,7 +4358,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4437,7 +4443,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4506,9 +4512,6 @@
       <c r="B505" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C505" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B506" s="3" t="s">
@@ -4525,7 +4528,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4613,7 +4616,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4682,6 +4685,9 @@
       <c r="B527" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C527" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B528" s="3" t="s">
@@ -4698,7 +4704,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4783,7 +4789,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4868,7 +4874,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4953,7 +4959,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5022,9 +5028,6 @@
       <c r="B571" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C571" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B572" s="3" t="s">
@@ -5041,7 +5044,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5129,7 +5132,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5206,9 +5209,6 @@
       <c r="B594" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C594" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B595" s="3" t="s">
@@ -5220,7 +5220,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5297,6 +5297,9 @@
       <c r="B605" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C605" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B606" s="3" t="s">
@@ -5308,7 +5311,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5396,7 +5399,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5484,7 +5487,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5572,7 +5575,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5660,7 +5663,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5729,6 +5732,9 @@
       <c r="B659" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C659" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B660" s="3" t="s">
@@ -5745,7 +5751,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5806,7 +5812,9 @@
       <c r="B669" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C669" s="6"/>
+      <c r="C669" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="670" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B670" s="3" t="s">
@@ -5822,10 +5830,13 @@
       <c r="B672" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C672" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5886,17 +5897,12 @@
       <c r="B680" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C680" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C680" s="6"/>
     </row>
     <row r="681" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B681" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C681" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="682" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B682" s="3" t="s">
@@ -5907,13 +5913,10 @@
       <c r="B683" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C683" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -6001,7 +6004,7 @@
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6089,7 +6092,7 @@
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6158,6 +6161,9 @@
       <c r="B714" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C714" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="715" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B715" s="3" t="s">
@@ -6174,7 +6180,7 @@
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6259,7 +6265,7 @@
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6333,9 +6339,6 @@
       <c r="B737" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C737" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="738" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B738" s="3" t="s">
@@ -6347,7 +6350,7 @@
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6408,7 +6411,9 @@
       <c r="B746" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C746" s="6"/>
+      <c r="C746" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="747" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B747" s="3" t="s">
@@ -6419,15 +6424,21 @@
       <c r="B748" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C748" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="749" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B749" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C749" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6488,9 +6499,7 @@
       <c r="B757" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C757" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C757" s="6"/>
     </row>
     <row r="758" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B758" s="3" t="s">
@@ -6506,13 +6515,10 @@
       <c r="B760" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C760" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6581,9 +6587,6 @@
       <c r="B769" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C769" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="770" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B770" s="3" t="s">
@@ -6600,7 +6603,7 @@
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3</v>
@@ -6669,6 +6672,9 @@
       <c r="B780" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C780" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="781" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B781" s="3" t="s">
@@ -6685,7 +6691,7 @@
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B783" s="7" t="s">
         <v>3</v>
@@ -6764,10 +6770,13 @@
       <c r="B793" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C793" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A794" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B794" s="7" t="s">
         <v>3</v>
@@ -6846,13 +6855,10 @@
       <c r="B804" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C804" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A805" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B805" s="7" t="s">
         <v>3</v>
@@ -6921,9 +6927,6 @@
       <c r="B813" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C813" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="814" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B814" s="3" t="s">
@@ -6940,7 +6943,7 @@
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A816" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B816" s="7" t="s">
         <v>3</v>
@@ -6961,19 +6964,25 @@
       <c r="B818" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C818" s="6"/>
+      <c r="C818" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="819" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B819" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C819" s="6"/>
+      <c r="C819" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="820" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B820" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C820" s="6"/>
+      <c r="C820" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="821" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B821" s="3" t="s">
@@ -6995,12 +7004,17 @@
       <c r="B823" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C823" s="6"/>
+      <c r="C823" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="824" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B824" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C824" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="825" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B825" s="3" t="s">
@@ -7011,10 +7025,13 @@
       <c r="B826" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C826" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A827" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B827" s="7" t="s">
         <v>3</v>
@@ -7035,25 +7052,19 @@
       <c r="B829" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C829" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C829" s="6"/>
     </row>
     <row r="830" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B830" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C830" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C830" s="6"/>
     </row>
     <row r="831" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B831" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C831" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C831" s="6"/>
     </row>
     <row r="832" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B832" s="3" t="s">
@@ -7075,17 +7086,12 @@
       <c r="B834" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C834" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C834" s="6"/>
     </row>
     <row r="835" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B835" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C835" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="836" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B836" s="3" t="s">
@@ -7096,13 +7102,10 @@
       <c r="B837" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C837" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A838" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B838" s="7" t="s">
         <v>3</v>
@@ -7190,7 +7193,7 @@
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A849" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B849" s="7" t="s">
         <v>3</v>
@@ -7259,6 +7262,9 @@
       <c r="B857" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C857" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="858" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B858" s="3" t="s">
@@ -7275,7 +7281,7 @@
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A860" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B860" s="7" t="s">
         <v>3</v>
@@ -7344,9 +7350,6 @@
       <c r="B868" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C868" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="869" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B869" s="3" t="s">
@@ -7354,19 +7357,19 @@
       </c>
     </row>
     <row r="870" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A870" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B870" s="7" t="s">
-        <v>3</v>
+      <c r="B870" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C870" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B871" s="3" t="s">
-        <v>4</v>
+      <c r="A871" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B871" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C871" s="5" t="s">
         <v>13</v>
@@ -7374,7 +7377,7 @@
     </row>
     <row r="872" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B872" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C872" s="5" t="s">
         <v>13</v>
@@ -7382,7 +7385,7 @@
     </row>
     <row r="873" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B873" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C873" s="5" t="s">
         <v>13</v>
@@ -7390,7 +7393,7 @@
     </row>
     <row r="874" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B874" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C874" s="5" t="s">
         <v>13</v>
@@ -7398,7 +7401,7 @@
     </row>
     <row r="875" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B875" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C875" s="5" t="s">
         <v>13</v>
@@ -7406,7 +7409,7 @@
     </row>
     <row r="876" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B876" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C876" s="5" t="s">
         <v>13</v>
@@ -7414,7 +7417,7 @@
     </row>
     <row r="877" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B877" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C877" s="5" t="s">
         <v>13</v>
@@ -7422,7 +7425,7 @@
     </row>
     <row r="878" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B878" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C878" s="5" t="s">
         <v>13</v>
@@ -7430,88 +7433,176 @@
     </row>
     <row r="879" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B879" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C879" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="880" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A880" s="4">
+      <c r="B880" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="881" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A881" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B881" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C881" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="882" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B882" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C882" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="883" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B883" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C883" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="884" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B884" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C884" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="885" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B885" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C885" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="886" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B886" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C886" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="887" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B887" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C887" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="888" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B888" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C888" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="889" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B889" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C889" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="890" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B890" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="891" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A891" s="4">
         <v>46042</v>
       </c>
-      <c r="B880" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C880" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="881" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B881" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C881" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="882" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B882" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C882" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="883" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B883" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C883" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="884" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B884" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C884" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="885" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B885" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C885" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="886" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B886" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C886" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="887" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B887" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C887" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="888" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B888" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="889" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B889" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="890" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B890" s="3">
+      <c r="B891" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C891" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="892" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B892" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C892" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="893" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B893" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C893" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="894" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B894" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C894" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="895" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B895" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C895" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="896" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B896" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C896" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="897" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B897" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C897" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="898" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B898" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C898" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="899" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B899" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="900" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B900" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="901" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B901" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADF721A1-26BF-4609-B2E6-DE664C93B98C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B138A9F3-FB66-46FD-991B-3F3A7A8B023A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1687" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1709" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C901"/>
+  <dimension ref="A1:C912"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -650,7 +650,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -741,7 +741,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -832,7 +832,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -923,7 +923,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -1014,7 +1014,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1105,7 +1105,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1196,7 +1196,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1378,7 +1378,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1455,6 +1455,9 @@
       <c r="B121" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C121" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B122" s="3" t="s">
@@ -1466,7 +1469,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1543,9 +1546,6 @@
       <c r="B132" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C132" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B133" s="3" t="s">
@@ -1557,7 +1557,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1648,7 +1648,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1739,7 +1739,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1830,7 +1830,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1921,7 +1921,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -2012,7 +2012,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2103,7 +2103,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2194,7 +2194,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2285,7 +2285,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2376,7 +2376,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2445,6 +2445,9 @@
       <c r="B241" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C241" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B242" s="3" t="s">
@@ -2464,7 +2467,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2533,9 +2536,6 @@
       <c r="B252" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C252" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B253" s="3" t="s">
@@ -2555,7 +2555,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2632,6 +2632,9 @@
       <c r="B264" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C264" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B265" s="3" t="s">
@@ -2643,7 +2646,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2712,6 +2715,9 @@
       <c r="B274" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C274" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B275" s="3" t="s">
@@ -2728,7 +2734,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2797,9 +2803,6 @@
       <c r="B285" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C285" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B286" s="3" t="s">
@@ -2816,7 +2819,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2885,6 +2888,9 @@
       <c r="B296" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C296" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B297" s="3" t="s">
@@ -2901,7 +2907,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2970,9 +2976,6 @@
       <c r="B307" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C307" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B308" s="3" t="s">
@@ -2989,7 +2992,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3077,7 +3080,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3165,7 +3168,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3234,6 +3237,9 @@
       <c r="B340" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C340" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B341" s="3" t="s">
@@ -3250,7 +3256,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3335,7 +3341,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3420,7 +3426,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3505,7 +3511,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3590,7 +3596,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3675,7 +3681,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3760,7 +3766,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3845,7 +3851,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3930,7 +3936,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -4015,7 +4021,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4100,7 +4106,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4185,7 +4191,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4254,9 +4260,6 @@
       <c r="B472" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C472" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B473" s="3" t="s">
@@ -4273,7 +4276,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4342,6 +4345,9 @@
       <c r="B483" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C483" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B484" s="3" t="s">
@@ -4358,7 +4364,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4443,7 +4449,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4528,7 +4534,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4597,9 +4603,6 @@
       <c r="B516" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C516" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B517" s="3" t="s">
@@ -4616,7 +4619,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4704,7 +4707,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4773,6 +4776,9 @@
       <c r="B538" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C538" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B539" s="3" t="s">
@@ -4789,7 +4795,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4874,7 +4880,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4959,7 +4965,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5044,7 +5050,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5113,9 +5119,6 @@
       <c r="B582" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C582" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B583" s="3" t="s">
@@ -5132,7 +5135,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5220,7 +5223,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5297,9 +5300,6 @@
       <c r="B605" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C605" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B606" s="3" t="s">
@@ -5311,7 +5311,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5388,6 +5388,9 @@
       <c r="B616" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C616" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B617" s="3" t="s">
@@ -5399,7 +5402,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5487,7 +5490,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5575,7 +5578,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5663,7 +5666,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5751,7 +5754,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5820,6 +5823,9 @@
       <c r="B670" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C670" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="671" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B671" s="3" t="s">
@@ -5836,7 +5842,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5897,7 +5903,9 @@
       <c r="B680" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C680" s="6"/>
+      <c r="C680" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="681" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B681" s="3" t="s">
@@ -5913,10 +5921,13 @@
       <c r="B683" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C683" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -5977,17 +5988,12 @@
       <c r="B691" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C691" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C691" s="6"/>
     </row>
     <row r="692" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B692" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C692" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="693" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B693" s="3" t="s">
@@ -5998,13 +6004,10 @@
       <c r="B694" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C694" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6092,7 +6095,7 @@
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6180,7 +6183,7 @@
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6249,6 +6252,9 @@
       <c r="B725" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C725" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="726" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B726" s="3" t="s">
@@ -6265,7 +6271,7 @@
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6350,7 +6356,7 @@
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6424,9 +6430,6 @@
       <c r="B748" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C748" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="749" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B749" s="3" t="s">
@@ -6438,7 +6441,7 @@
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6499,7 +6502,9 @@
       <c r="B757" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C757" s="6"/>
+      <c r="C757" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="758" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B758" s="3" t="s">
@@ -6510,15 +6515,21 @@
       <c r="B759" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C759" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="760" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B760" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C760" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6579,9 +6590,7 @@
       <c r="B768" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C768" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C768" s="6"/>
     </row>
     <row r="769" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B769" s="3" t="s">
@@ -6597,13 +6606,10 @@
       <c r="B771" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C771" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3</v>
@@ -6672,9 +6678,6 @@
       <c r="B780" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C780" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="781" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B781" s="3" t="s">
@@ -6691,7 +6694,7 @@
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B783" s="7" t="s">
         <v>3</v>
@@ -6760,6 +6763,9 @@
       <c r="B791" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C791" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="792" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B792" s="3" t="s">
@@ -6776,7 +6782,7 @@
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A794" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B794" s="7" t="s">
         <v>3</v>
@@ -6855,10 +6861,13 @@
       <c r="B804" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C804" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A805" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B805" s="7" t="s">
         <v>3</v>
@@ -6937,13 +6946,10 @@
       <c r="B815" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C815" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A816" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B816" s="7" t="s">
         <v>3</v>
@@ -7012,9 +7018,6 @@
       <c r="B824" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C824" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="825" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B825" s="3" t="s">
@@ -7031,7 +7034,7 @@
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A827" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B827" s="7" t="s">
         <v>3</v>
@@ -7052,19 +7055,25 @@
       <c r="B829" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C829" s="6"/>
+      <c r="C829" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="830" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B830" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C830" s="6"/>
+      <c r="C830" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="831" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B831" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C831" s="6"/>
+      <c r="C831" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="832" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B832" s="3" t="s">
@@ -7086,12 +7095,17 @@
       <c r="B834" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C834" s="6"/>
+      <c r="C834" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="835" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B835" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C835" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="836" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B836" s="3" t="s">
@@ -7102,10 +7116,13 @@
       <c r="B837" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C837" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A838" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B838" s="7" t="s">
         <v>3</v>
@@ -7126,25 +7143,19 @@
       <c r="B840" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C840" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C840" s="6"/>
     </row>
     <row r="841" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B841" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C841" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C841" s="6"/>
     </row>
     <row r="842" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B842" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C842" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C842" s="6"/>
     </row>
     <row r="843" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B843" s="3" t="s">
@@ -7166,17 +7177,12 @@
       <c r="B845" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C845" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C845" s="6"/>
     </row>
     <row r="846" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B846" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C846" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="847" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B847" s="3" t="s">
@@ -7187,13 +7193,10 @@
       <c r="B848" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C848" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A849" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B849" s="7" t="s">
         <v>3</v>
@@ -7281,7 +7284,7 @@
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A860" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B860" s="7" t="s">
         <v>3</v>
@@ -7350,6 +7353,9 @@
       <c r="B868" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C868" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="869" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B869" s="3" t="s">
@@ -7366,7 +7372,7 @@
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A871" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B871" s="7" t="s">
         <v>3</v>
@@ -7435,9 +7441,6 @@
       <c r="B879" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C879" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="880" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B880" s="3" t="s">
@@ -7445,19 +7448,19 @@
       </c>
     </row>
     <row r="881" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A881" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B881" s="7" t="s">
-        <v>3</v>
+      <c r="B881" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C881" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B882" s="3" t="s">
-        <v>4</v>
+      <c r="A882" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B882" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C882" s="5" t="s">
         <v>13</v>
@@ -7465,7 +7468,7 @@
     </row>
     <row r="883" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B883" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C883" s="5" t="s">
         <v>13</v>
@@ -7473,7 +7476,7 @@
     </row>
     <row r="884" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B884" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C884" s="5" t="s">
         <v>13</v>
@@ -7481,7 +7484,7 @@
     </row>
     <row r="885" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B885" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C885" s="5" t="s">
         <v>13</v>
@@ -7489,7 +7492,7 @@
     </row>
     <row r="886" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B886" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C886" s="5" t="s">
         <v>13</v>
@@ -7497,7 +7500,7 @@
     </row>
     <row r="887" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B887" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C887" s="5" t="s">
         <v>13</v>
@@ -7505,7 +7508,7 @@
     </row>
     <row r="888" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B888" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C888" s="5" t="s">
         <v>13</v>
@@ -7513,7 +7516,7 @@
     </row>
     <row r="889" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B889" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C889" s="5" t="s">
         <v>13</v>
@@ -7521,23 +7524,23 @@
     </row>
     <row r="890" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B890" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C890" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="891" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A891" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B891" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C891" s="5" t="s">
-        <v>13</v>
+      <c r="B891" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="892" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B892" s="3" t="s">
-        <v>4</v>
+      <c r="A892" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B892" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C892" s="5" t="s">
         <v>13</v>
@@ -7545,7 +7548,7 @@
     </row>
     <row r="893" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B893" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C893" s="5" t="s">
         <v>13</v>
@@ -7553,7 +7556,7 @@
     </row>
     <row r="894" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B894" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C894" s="5" t="s">
         <v>13</v>
@@ -7561,7 +7564,7 @@
     </row>
     <row r="895" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B895" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C895" s="5" t="s">
         <v>13</v>
@@ -7569,40 +7572,128 @@
     </row>
     <row r="896" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B896" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C896" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="897" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="897" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B897" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C897" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="898" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="898" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B898" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C898" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="899" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="899" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B899" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="900" spans="2:3" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="C899" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="900" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B900" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="901" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B901" s="3">
+        <v>11</v>
+      </c>
+      <c r="C900" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="901" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B901" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="902" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A902" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B902" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C902" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="903" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B903" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C903" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="904" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B904" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C904" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="905" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B905" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C905" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="906" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B906" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C906" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="907" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B907" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C907" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="908" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B908" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C908" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="909" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B909" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C909" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="910" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B910" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="911" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B911" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="912" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B912" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B138A9F3-FB66-46FD-991B-3F3A7A8B023A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59D1C7B5-3A6B-4B46-8818-9C07A2D81D5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1709" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1731" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C912"/>
+  <dimension ref="A1:C923"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -650,7 +650,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -741,7 +741,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -832,7 +832,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -923,7 +923,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -1014,7 +1014,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1105,7 +1105,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1196,7 +1196,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1378,7 +1378,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1469,7 +1469,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1546,6 +1546,9 @@
       <c r="B132" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C132" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B133" s="3" t="s">
@@ -1557,7 +1560,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1634,9 +1637,6 @@
       <c r="B143" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C143" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B144" s="3" t="s">
@@ -1648,7 +1648,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1739,7 +1739,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1830,7 +1830,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1921,7 +1921,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -2012,7 +2012,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2103,7 +2103,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2194,7 +2194,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2285,7 +2285,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2376,7 +2376,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2467,7 +2467,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2536,6 +2536,9 @@
       <c r="B252" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C252" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B253" s="3" t="s">
@@ -2555,7 +2558,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2624,9 +2627,6 @@
       <c r="B263" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C263" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B264" s="3" t="s">
@@ -2646,7 +2646,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2723,6 +2723,9 @@
       <c r="B275" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C275" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B276" s="3" t="s">
@@ -2734,7 +2737,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2803,6 +2806,9 @@
       <c r="B285" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C285" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B286" s="3" t="s">
@@ -2819,7 +2825,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2888,9 +2894,6 @@
       <c r="B296" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C296" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B297" s="3" t="s">
@@ -2907,7 +2910,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2976,6 +2979,9 @@
       <c r="B307" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C307" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B308" s="3" t="s">
@@ -2992,7 +2998,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3061,9 +3067,6 @@
       <c r="B318" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C318" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B319" s="3" t="s">
@@ -3080,7 +3083,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3168,7 +3171,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3256,7 +3259,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3325,6 +3328,9 @@
       <c r="B351" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C351" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B352" s="3" t="s">
@@ -3341,7 +3347,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3426,7 +3432,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3511,7 +3517,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3596,7 +3602,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3681,7 +3687,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3766,7 +3772,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3851,7 +3857,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3936,7 +3942,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -4021,7 +4027,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4106,7 +4112,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4191,7 +4197,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4276,7 +4282,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4345,9 +4351,6 @@
       <c r="B483" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C483" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B484" s="3" t="s">
@@ -4364,7 +4367,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4433,6 +4436,9 @@
       <c r="B494" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C494" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B495" s="3" t="s">
@@ -4449,7 +4455,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4534,7 +4540,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4619,7 +4625,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4688,9 +4694,6 @@
       <c r="B527" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C527" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B528" s="3" t="s">
@@ -4707,7 +4710,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4795,7 +4798,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4864,6 +4867,9 @@
       <c r="B549" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C549" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B550" s="3" t="s">
@@ -4880,7 +4886,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4965,7 +4971,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5050,7 +5056,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5135,7 +5141,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5204,9 +5210,6 @@
       <c r="B593" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C593" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B594" s="3" t="s">
@@ -5223,7 +5226,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5311,7 +5314,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5388,9 +5391,6 @@
       <c r="B616" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C616" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B617" s="3" t="s">
@@ -5402,7 +5402,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5479,6 +5479,9 @@
       <c r="B627" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C627" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B628" s="3" t="s">
@@ -5490,7 +5493,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5578,7 +5581,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5666,7 +5669,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5754,7 +5757,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5842,7 +5845,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5911,6 +5914,9 @@
       <c r="B681" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C681" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="682" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B682" s="3" t="s">
@@ -5927,7 +5933,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -5988,7 +5994,9 @@
       <c r="B691" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C691" s="6"/>
+      <c r="C691" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="692" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B692" s="3" t="s">
@@ -6004,10 +6012,13 @@
       <c r="B694" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C694" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6068,17 +6079,12 @@
       <c r="B702" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C702" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C702" s="6"/>
     </row>
     <row r="703" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B703" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C703" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="704" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B704" s="3" t="s">
@@ -6089,13 +6095,10 @@
       <c r="B705" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C705" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6183,7 +6186,7 @@
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6271,7 +6274,7 @@
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6340,6 +6343,9 @@
       <c r="B736" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C736" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="737" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B737" s="3" t="s">
@@ -6356,7 +6362,7 @@
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6441,7 +6447,7 @@
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6515,9 +6521,6 @@
       <c r="B759" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C759" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="760" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B760" s="3" t="s">
@@ -6529,7 +6532,7 @@
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6590,7 +6593,9 @@
       <c r="B768" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C768" s="6"/>
+      <c r="C768" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="769" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B769" s="3" t="s">
@@ -6601,15 +6606,21 @@
       <c r="B770" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C770" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="771" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B771" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C771" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3</v>
@@ -6670,9 +6681,7 @@
       <c r="B779" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C779" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C779" s="6"/>
     </row>
     <row r="780" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B780" s="3" t="s">
@@ -6688,13 +6697,10 @@
       <c r="B782" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C782" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B783" s="7" t="s">
         <v>3</v>
@@ -6763,9 +6769,6 @@
       <c r="B791" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C791" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="792" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B792" s="3" t="s">
@@ -6782,7 +6785,7 @@
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A794" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B794" s="7" t="s">
         <v>3</v>
@@ -6851,6 +6854,9 @@
       <c r="B802" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C802" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="803" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B803" s="3" t="s">
@@ -6867,7 +6873,7 @@
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A805" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B805" s="7" t="s">
         <v>3</v>
@@ -6946,10 +6952,13 @@
       <c r="B815" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C815" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A816" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B816" s="7" t="s">
         <v>3</v>
@@ -7028,13 +7037,10 @@
       <c r="B826" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C826" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A827" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B827" s="7" t="s">
         <v>3</v>
@@ -7103,9 +7109,6 @@
       <c r="B835" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C835" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="836" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B836" s="3" t="s">
@@ -7122,7 +7125,7 @@
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A838" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B838" s="7" t="s">
         <v>3</v>
@@ -7143,19 +7146,25 @@
       <c r="B840" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C840" s="6"/>
+      <c r="C840" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="841" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B841" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C841" s="6"/>
+      <c r="C841" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="842" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B842" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C842" s="6"/>
+      <c r="C842" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="843" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B843" s="3" t="s">
@@ -7177,12 +7186,17 @@
       <c r="B845" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C845" s="6"/>
+      <c r="C845" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="846" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B846" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C846" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="847" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B847" s="3" t="s">
@@ -7193,10 +7207,13 @@
       <c r="B848" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C848" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A849" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B849" s="7" t="s">
         <v>3</v>
@@ -7217,25 +7234,19 @@
       <c r="B851" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C851" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C851" s="6"/>
     </row>
     <row r="852" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B852" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C852" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C852" s="6"/>
     </row>
     <row r="853" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B853" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C853" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C853" s="6"/>
     </row>
     <row r="854" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B854" s="3" t="s">
@@ -7257,17 +7268,12 @@
       <c r="B856" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C856" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C856" s="6"/>
     </row>
     <row r="857" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B857" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C857" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="858" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B858" s="3" t="s">
@@ -7278,13 +7284,10 @@
       <c r="B859" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C859" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A860" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B860" s="7" t="s">
         <v>3</v>
@@ -7372,7 +7375,7 @@
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A871" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B871" s="7" t="s">
         <v>3</v>
@@ -7441,6 +7444,9 @@
       <c r="B879" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C879" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="880" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B880" s="3" t="s">
@@ -7457,7 +7463,7 @@
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A882" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B882" s="7" t="s">
         <v>3</v>
@@ -7526,9 +7532,6 @@
       <c r="B890" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C890" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="891" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B891" s="3" t="s">
@@ -7536,19 +7539,19 @@
       </c>
     </row>
     <row r="892" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A892" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B892" s="7" t="s">
-        <v>3</v>
+      <c r="B892" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C892" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="893" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B893" s="3" t="s">
-        <v>4</v>
+      <c r="A893" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B893" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C893" s="5" t="s">
         <v>13</v>
@@ -7556,7 +7559,7 @@
     </row>
     <row r="894" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B894" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C894" s="5" t="s">
         <v>13</v>
@@ -7564,7 +7567,7 @@
     </row>
     <row r="895" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B895" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C895" s="5" t="s">
         <v>13</v>
@@ -7572,7 +7575,7 @@
     </row>
     <row r="896" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B896" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C896" s="5" t="s">
         <v>13</v>
@@ -7580,7 +7583,7 @@
     </row>
     <row r="897" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B897" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C897" s="5" t="s">
         <v>13</v>
@@ -7588,7 +7591,7 @@
     </row>
     <row r="898" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B898" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C898" s="5" t="s">
         <v>13</v>
@@ -7596,7 +7599,7 @@
     </row>
     <row r="899" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B899" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C899" s="5" t="s">
         <v>13</v>
@@ -7604,7 +7607,7 @@
     </row>
     <row r="900" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B900" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C900" s="5" t="s">
         <v>13</v>
@@ -7612,23 +7615,23 @@
     </row>
     <row r="901" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B901" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C901" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="902" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A902" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B902" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C902" s="5" t="s">
-        <v>13</v>
+      <c r="B902" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="903" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B903" s="3" t="s">
-        <v>4</v>
+      <c r="A903" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B903" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C903" s="5" t="s">
         <v>13</v>
@@ -7636,7 +7639,7 @@
     </row>
     <row r="904" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B904" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C904" s="5" t="s">
         <v>13</v>
@@ -7644,7 +7647,7 @@
     </row>
     <row r="905" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B905" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C905" s="5" t="s">
         <v>13</v>
@@ -7652,7 +7655,7 @@
     </row>
     <row r="906" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B906" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C906" s="5" t="s">
         <v>13</v>
@@ -7660,7 +7663,7 @@
     </row>
     <row r="907" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B907" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C907" s="5" t="s">
         <v>13</v>
@@ -7668,7 +7671,7 @@
     </row>
     <row r="908" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B908" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C908" s="5" t="s">
         <v>13</v>
@@ -7676,7 +7679,7 @@
     </row>
     <row r="909" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B909" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C909" s="5" t="s">
         <v>13</v>
@@ -7684,16 +7687,104 @@
     </row>
     <row r="910" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B910" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C910" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="911" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B911" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C911" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="912" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B912" s="3">
+      <c r="B912" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="913" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A913" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B913" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C913" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="914" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B914" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C914" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="915" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B915" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C915" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="916" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B916" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C916" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="917" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B917" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C917" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="918" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B918" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C918" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="919" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B919" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C919" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="920" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B920" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C920" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="921" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B921" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="922" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B922" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="923" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B923" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59D1C7B5-3A6B-4B46-8818-9C07A2D81D5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CC3028C-A231-4BD1-AE57-5C64DEEC3B30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1731" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1753" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C923"/>
+  <dimension ref="A1:C934"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -650,7 +650,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -741,7 +741,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -832,7 +832,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -923,7 +923,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -1014,7 +1014,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1105,7 +1105,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1196,7 +1196,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1378,7 +1378,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1469,7 +1469,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1560,7 +1560,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1637,6 +1637,9 @@
       <c r="B143" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C143" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B144" s="3" t="s">
@@ -1648,7 +1651,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1725,9 +1728,6 @@
       <c r="B154" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C154" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B155" s="3" t="s">
@@ -1739,7 +1739,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1830,7 +1830,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1921,7 +1921,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -2012,7 +2012,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2103,7 +2103,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2194,7 +2194,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2285,7 +2285,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2376,7 +2376,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2467,7 +2467,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2558,7 +2558,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2627,6 +2627,9 @@
       <c r="B263" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C263" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B264" s="3" t="s">
@@ -2646,7 +2649,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2715,9 +2718,6 @@
       <c r="B274" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C274" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B275" s="3" t="s">
@@ -2737,7 +2737,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2814,6 +2814,9 @@
       <c r="B286" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C286" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B287" s="3" t="s">
@@ -2825,7 +2828,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2894,6 +2897,9 @@
       <c r="B296" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C296" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B297" s="3" t="s">
@@ -2910,7 +2916,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2979,9 +2985,6 @@
       <c r="B307" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C307" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B308" s="3" t="s">
@@ -2998,7 +3001,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3067,6 +3070,9 @@
       <c r="B318" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C318" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B319" s="3" t="s">
@@ -3083,7 +3089,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3152,9 +3158,6 @@
       <c r="B329" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C329" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B330" s="3" t="s">
@@ -3171,7 +3174,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3259,7 +3262,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3347,7 +3350,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3416,6 +3419,9 @@
       <c r="B362" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C362" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B363" s="3" t="s">
@@ -3432,7 +3438,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3517,7 +3523,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3602,7 +3608,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3687,7 +3693,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3772,7 +3778,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3857,7 +3863,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3942,7 +3948,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -4027,7 +4033,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4112,7 +4118,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4197,7 +4203,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4282,7 +4288,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4367,7 +4373,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4436,9 +4442,6 @@
       <c r="B494" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C494" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B495" s="3" t="s">
@@ -4455,7 +4458,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4524,6 +4527,9 @@
       <c r="B505" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C505" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B506" s="3" t="s">
@@ -4540,7 +4546,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4625,7 +4631,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4710,7 +4716,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4779,9 +4785,6 @@
       <c r="B538" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C538" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B539" s="3" t="s">
@@ -4798,7 +4801,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4886,7 +4889,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4955,6 +4958,9 @@
       <c r="B560" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C560" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B561" s="3" t="s">
@@ -4971,7 +4977,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5056,7 +5062,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5141,7 +5147,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5226,7 +5232,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5295,9 +5301,6 @@
       <c r="B604" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C604" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B605" s="3" t="s">
@@ -5314,7 +5317,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5402,7 +5405,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5479,9 +5482,6 @@
       <c r="B627" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C627" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B628" s="3" t="s">
@@ -5493,7 +5493,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5570,6 +5570,9 @@
       <c r="B638" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C638" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B639" s="3" t="s">
@@ -5581,7 +5584,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5669,7 +5672,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5757,7 +5760,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5845,7 +5848,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5933,7 +5936,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -6002,6 +6005,9 @@
       <c r="B692" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C692" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="693" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B693" s="3" t="s">
@@ -6018,7 +6024,7 @@
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6079,7 +6085,9 @@
       <c r="B702" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C702" s="6"/>
+      <c r="C702" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="703" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B703" s="3" t="s">
@@ -6095,10 +6103,13 @@
       <c r="B705" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C705" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6159,17 +6170,12 @@
       <c r="B713" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C713" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C713" s="6"/>
     </row>
     <row r="714" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B714" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C714" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="715" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B715" s="3" t="s">
@@ -6180,13 +6186,10 @@
       <c r="B716" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C716" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6274,7 +6277,7 @@
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6362,7 +6365,7 @@
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6431,6 +6434,9 @@
       <c r="B747" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C747" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="748" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B748" s="3" t="s">
@@ -6447,7 +6453,7 @@
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6532,7 +6538,7 @@
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6606,9 +6612,6 @@
       <c r="B770" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C770" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="771" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B771" s="3" t="s">
@@ -6620,7 +6623,7 @@
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3</v>
@@ -6681,7 +6684,9 @@
       <c r="B779" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C779" s="6"/>
+      <c r="C779" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="780" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B780" s="3" t="s">
@@ -6692,15 +6697,21 @@
       <c r="B781" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C781" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="782" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B782" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C782" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B783" s="7" t="s">
         <v>3</v>
@@ -6761,9 +6772,7 @@
       <c r="B790" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C790" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C790" s="6"/>
     </row>
     <row r="791" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B791" s="3" t="s">
@@ -6779,13 +6788,10 @@
       <c r="B793" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C793" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A794" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B794" s="7" t="s">
         <v>3</v>
@@ -6854,9 +6860,6 @@
       <c r="B802" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C802" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="803" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B803" s="3" t="s">
@@ -6873,7 +6876,7 @@
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A805" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B805" s="7" t="s">
         <v>3</v>
@@ -6942,6 +6945,9 @@
       <c r="B813" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C813" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="814" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B814" s="3" t="s">
@@ -6958,7 +6964,7 @@
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A816" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B816" s="7" t="s">
         <v>3</v>
@@ -7037,10 +7043,13 @@
       <c r="B826" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C826" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A827" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B827" s="7" t="s">
         <v>3</v>
@@ -7119,13 +7128,10 @@
       <c r="B837" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C837" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A838" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B838" s="7" t="s">
         <v>3</v>
@@ -7194,9 +7200,6 @@
       <c r="B846" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C846" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="847" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B847" s="3" t="s">
@@ -7213,7 +7216,7 @@
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A849" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B849" s="7" t="s">
         <v>3</v>
@@ -7234,19 +7237,25 @@
       <c r="B851" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C851" s="6"/>
+      <c r="C851" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="852" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B852" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C852" s="6"/>
+      <c r="C852" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="853" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B853" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C853" s="6"/>
+      <c r="C853" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="854" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B854" s="3" t="s">
@@ -7268,12 +7277,17 @@
       <c r="B856" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C856" s="6"/>
+      <c r="C856" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="857" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B857" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C857" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="858" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B858" s="3" t="s">
@@ -7284,10 +7298,13 @@
       <c r="B859" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C859" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A860" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B860" s="7" t="s">
         <v>3</v>
@@ -7308,25 +7325,19 @@
       <c r="B862" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C862" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C862" s="6"/>
     </row>
     <row r="863" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B863" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C863" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C863" s="6"/>
     </row>
     <row r="864" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B864" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C864" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C864" s="6"/>
     </row>
     <row r="865" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B865" s="3" t="s">
@@ -7348,17 +7359,12 @@
       <c r="B867" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C867" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C867" s="6"/>
     </row>
     <row r="868" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B868" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C868" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="869" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B869" s="3" t="s">
@@ -7369,13 +7375,10 @@
       <c r="B870" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C870" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A871" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B871" s="7" t="s">
         <v>3</v>
@@ -7463,7 +7466,7 @@
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A882" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B882" s="7" t="s">
         <v>3</v>
@@ -7532,6 +7535,9 @@
       <c r="B890" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C890" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="891" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B891" s="3" t="s">
@@ -7548,7 +7554,7 @@
     </row>
     <row r="893" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A893" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B893" s="7" t="s">
         <v>3</v>
@@ -7617,9 +7623,6 @@
       <c r="B901" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C901" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="902" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B902" s="3" t="s">
@@ -7627,19 +7630,19 @@
       </c>
     </row>
     <row r="903" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A903" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B903" s="7" t="s">
-        <v>3</v>
+      <c r="B903" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C903" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="904" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B904" s="3" t="s">
-        <v>4</v>
+      <c r="A904" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B904" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C904" s="5" t="s">
         <v>13</v>
@@ -7647,7 +7650,7 @@
     </row>
     <row r="905" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B905" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C905" s="5" t="s">
         <v>13</v>
@@ -7655,7 +7658,7 @@
     </row>
     <row r="906" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B906" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C906" s="5" t="s">
         <v>13</v>
@@ -7663,7 +7666,7 @@
     </row>
     <row r="907" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B907" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C907" s="5" t="s">
         <v>13</v>
@@ -7671,7 +7674,7 @@
     </row>
     <row r="908" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B908" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C908" s="5" t="s">
         <v>13</v>
@@ -7679,7 +7682,7 @@
     </row>
     <row r="909" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B909" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C909" s="5" t="s">
         <v>13</v>
@@ -7687,7 +7690,7 @@
     </row>
     <row r="910" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B910" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C910" s="5" t="s">
         <v>13</v>
@@ -7695,7 +7698,7 @@
     </row>
     <row r="911" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B911" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C911" s="5" t="s">
         <v>13</v>
@@ -7703,23 +7706,23 @@
     </row>
     <row r="912" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B912" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C912" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="913" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A913" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B913" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C913" s="5" t="s">
-        <v>13</v>
+      <c r="B913" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="914" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B914" s="3" t="s">
-        <v>4</v>
+      <c r="A914" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B914" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C914" s="5" t="s">
         <v>13</v>
@@ -7727,7 +7730,7 @@
     </row>
     <row r="915" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B915" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C915" s="5" t="s">
         <v>13</v>
@@ -7735,7 +7738,7 @@
     </row>
     <row r="916" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B916" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C916" s="5" t="s">
         <v>13</v>
@@ -7743,7 +7746,7 @@
     </row>
     <row r="917" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B917" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C917" s="5" t="s">
         <v>13</v>
@@ -7751,7 +7754,7 @@
     </row>
     <row r="918" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B918" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C918" s="5" t="s">
         <v>13</v>
@@ -7759,7 +7762,7 @@
     </row>
     <row r="919" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B919" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C919" s="5" t="s">
         <v>13</v>
@@ -7767,7 +7770,7 @@
     </row>
     <row r="920" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B920" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C920" s="5" t="s">
         <v>13</v>
@@ -7775,16 +7778,104 @@
     </row>
     <row r="921" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B921" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C921" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="922" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B922" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C922" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="923" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B923" s="3">
+      <c r="B923" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="924" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A924" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B924" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C924" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="925" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B925" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C925" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="926" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B926" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C926" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="927" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B927" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C927" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="928" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B928" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C928" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="929" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B929" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C929" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="930" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B930" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C930" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="931" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B931" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C931" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="932" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B932" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="933" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B933" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="934" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B934" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CC3028C-A231-4BD1-AE57-5C64DEEC3B30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7135BCC4-EA9F-4A42-8AF2-C28D92D412EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1753" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1775" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C934"/>
+  <dimension ref="A1:C945"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -650,7 +650,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -741,7 +741,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -832,7 +832,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -923,7 +923,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -1014,7 +1014,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1105,7 +1105,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1196,7 +1196,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1378,7 +1378,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1469,7 +1469,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1560,7 +1560,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1651,7 +1651,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1728,6 +1728,9 @@
       <c r="B154" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C154" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B155" s="3" t="s">
@@ -1739,7 +1742,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1816,9 +1819,6 @@
       <c r="B165" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C165" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B166" s="3" t="s">
@@ -1830,7 +1830,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1921,7 +1921,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -2012,7 +2012,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2103,7 +2103,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2194,7 +2194,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2285,7 +2285,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2376,7 +2376,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2467,7 +2467,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2558,7 +2558,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2649,7 +2649,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2718,6 +2718,9 @@
       <c r="B274" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C274" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B275" s="3" t="s">
@@ -2737,7 +2740,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2806,9 +2809,6 @@
       <c r="B285" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C285" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B286" s="3" t="s">
@@ -2828,7 +2828,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2905,6 +2905,9 @@
       <c r="B297" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C297" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B298" s="3" t="s">
@@ -2916,7 +2919,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2985,6 +2988,9 @@
       <c r="B307" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C307" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B308" s="3" t="s">
@@ -3001,7 +3007,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3070,9 +3076,6 @@
       <c r="B318" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C318" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B319" s="3" t="s">
@@ -3089,7 +3092,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3158,6 +3161,9 @@
       <c r="B329" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C329" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B330" s="3" t="s">
@@ -3174,7 +3180,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3243,9 +3249,6 @@
       <c r="B340" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C340" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B341" s="3" t="s">
@@ -3262,7 +3265,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3350,7 +3353,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3438,7 +3441,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3507,6 +3510,9 @@
       <c r="B373" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C373" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B374" s="3" t="s">
@@ -3523,7 +3529,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3608,7 +3614,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3693,7 +3699,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3778,7 +3784,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3863,7 +3869,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3948,7 +3954,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -4033,7 +4039,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4118,7 +4124,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4203,7 +4209,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4288,7 +4294,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4373,7 +4379,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4458,7 +4464,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4527,9 +4533,6 @@
       <c r="B505" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C505" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B506" s="3" t="s">
@@ -4546,7 +4549,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4615,6 +4618,9 @@
       <c r="B516" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C516" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B517" s="3" t="s">
@@ -4631,7 +4637,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4716,7 +4722,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4801,7 +4807,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4870,9 +4876,6 @@
       <c r="B549" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C549" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B550" s="3" t="s">
@@ -4889,7 +4892,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4977,7 +4980,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5046,6 +5049,9 @@
       <c r="B571" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C571" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B572" s="3" t="s">
@@ -5062,7 +5068,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5147,7 +5153,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5232,7 +5238,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5317,7 +5323,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5386,9 +5392,6 @@
       <c r="B615" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C615" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B616" s="3" t="s">
@@ -5405,7 +5408,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5493,7 +5496,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5570,9 +5573,6 @@
       <c r="B638" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C638" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B639" s="3" t="s">
@@ -5584,7 +5584,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5661,6 +5661,9 @@
       <c r="B649" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C649" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B650" s="3" t="s">
@@ -5672,7 +5675,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5760,7 +5763,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5848,7 +5851,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5936,7 +5939,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -6024,7 +6027,7 @@
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6093,6 +6096,9 @@
       <c r="B703" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C703" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="704" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B704" s="3" t="s">
@@ -6109,7 +6115,7 @@
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6170,7 +6176,9 @@
       <c r="B713" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C713" s="6"/>
+      <c r="C713" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="714" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B714" s="3" t="s">
@@ -6186,10 +6194,13 @@
       <c r="B716" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C716" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6250,17 +6261,12 @@
       <c r="B724" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C724" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C724" s="6"/>
     </row>
     <row r="725" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B725" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C725" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="726" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B726" s="3" t="s">
@@ -6271,13 +6277,10 @@
       <c r="B727" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C727" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6365,7 +6368,7 @@
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6453,7 +6456,7 @@
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6522,6 +6525,9 @@
       <c r="B758" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C758" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="759" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B759" s="3" t="s">
@@ -6538,7 +6544,7 @@
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6623,7 +6629,7 @@
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3</v>
@@ -6697,9 +6703,6 @@
       <c r="B781" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C781" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="782" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B782" s="3" t="s">
@@ -6711,7 +6714,7 @@
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B783" s="7" t="s">
         <v>3</v>
@@ -6772,7 +6775,9 @@
       <c r="B790" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C790" s="6"/>
+      <c r="C790" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="791" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B791" s="3" t="s">
@@ -6783,15 +6788,21 @@
       <c r="B792" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C792" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="793" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B793" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C793" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A794" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B794" s="7" t="s">
         <v>3</v>
@@ -6852,9 +6863,7 @@
       <c r="B801" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C801" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C801" s="6"/>
     </row>
     <row r="802" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B802" s="3" t="s">
@@ -6870,13 +6879,10 @@
       <c r="B804" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C804" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A805" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B805" s="7" t="s">
         <v>3</v>
@@ -6945,9 +6951,6 @@
       <c r="B813" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C813" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="814" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B814" s="3" t="s">
@@ -6964,7 +6967,7 @@
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A816" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B816" s="7" t="s">
         <v>3</v>
@@ -7033,6 +7036,9 @@
       <c r="B824" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C824" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="825" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B825" s="3" t="s">
@@ -7049,7 +7055,7 @@
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A827" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B827" s="7" t="s">
         <v>3</v>
@@ -7128,10 +7134,13 @@
       <c r="B837" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C837" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A838" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B838" s="7" t="s">
         <v>3</v>
@@ -7210,13 +7219,10 @@
       <c r="B848" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C848" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A849" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B849" s="7" t="s">
         <v>3</v>
@@ -7285,9 +7291,6 @@
       <c r="B857" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C857" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="858" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B858" s="3" t="s">
@@ -7304,7 +7307,7 @@
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A860" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B860" s="7" t="s">
         <v>3</v>
@@ -7325,19 +7328,25 @@
       <c r="B862" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C862" s="6"/>
+      <c r="C862" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="863" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B863" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C863" s="6"/>
+      <c r="C863" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="864" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B864" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C864" s="6"/>
+      <c r="C864" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="865" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B865" s="3" t="s">
@@ -7359,12 +7368,17 @@
       <c r="B867" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C867" s="6"/>
+      <c r="C867" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="868" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B868" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C868" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="869" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B869" s="3" t="s">
@@ -7375,10 +7389,13 @@
       <c r="B870" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C870" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A871" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B871" s="7" t="s">
         <v>3</v>
@@ -7399,25 +7416,19 @@
       <c r="B873" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C873" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C873" s="6"/>
     </row>
     <row r="874" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B874" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C874" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C874" s="6"/>
     </row>
     <row r="875" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B875" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C875" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C875" s="6"/>
     </row>
     <row r="876" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B876" s="3" t="s">
@@ -7439,17 +7450,12 @@
       <c r="B878" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C878" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C878" s="6"/>
     </row>
     <row r="879" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B879" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C879" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="880" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B880" s="3" t="s">
@@ -7460,13 +7466,10 @@
       <c r="B881" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C881" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A882" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B882" s="7" t="s">
         <v>3</v>
@@ -7554,7 +7557,7 @@
     </row>
     <row r="893" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A893" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B893" s="7" t="s">
         <v>3</v>
@@ -7623,6 +7626,9 @@
       <c r="B901" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C901" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="902" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B902" s="3" t="s">
@@ -7639,7 +7645,7 @@
     </row>
     <row r="904" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A904" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B904" s="7" t="s">
         <v>3</v>
@@ -7708,9 +7714,6 @@
       <c r="B912" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C912" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="913" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B913" s="3" t="s">
@@ -7718,19 +7721,19 @@
       </c>
     </row>
     <row r="914" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A914" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B914" s="7" t="s">
-        <v>3</v>
+      <c r="B914" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C914" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="915" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B915" s="3" t="s">
-        <v>4</v>
+      <c r="A915" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B915" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C915" s="5" t="s">
         <v>13</v>
@@ -7738,7 +7741,7 @@
     </row>
     <row r="916" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B916" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C916" s="5" t="s">
         <v>13</v>
@@ -7746,7 +7749,7 @@
     </row>
     <row r="917" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B917" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C917" s="5" t="s">
         <v>13</v>
@@ -7754,7 +7757,7 @@
     </row>
     <row r="918" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B918" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C918" s="5" t="s">
         <v>13</v>
@@ -7762,7 +7765,7 @@
     </row>
     <row r="919" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B919" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C919" s="5" t="s">
         <v>13</v>
@@ -7770,7 +7773,7 @@
     </row>
     <row r="920" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B920" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C920" s="5" t="s">
         <v>13</v>
@@ -7778,7 +7781,7 @@
     </row>
     <row r="921" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B921" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C921" s="5" t="s">
         <v>13</v>
@@ -7786,7 +7789,7 @@
     </row>
     <row r="922" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B922" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C922" s="5" t="s">
         <v>13</v>
@@ -7794,23 +7797,23 @@
     </row>
     <row r="923" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B923" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C923" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="924" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A924" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B924" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C924" s="5" t="s">
-        <v>13</v>
+      <c r="B924" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="925" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B925" s="3" t="s">
-        <v>4</v>
+      <c r="A925" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B925" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C925" s="5" t="s">
         <v>13</v>
@@ -7818,7 +7821,7 @@
     </row>
     <row r="926" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B926" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C926" s="5" t="s">
         <v>13</v>
@@ -7826,7 +7829,7 @@
     </row>
     <row r="927" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B927" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C927" s="5" t="s">
         <v>13</v>
@@ -7834,48 +7837,136 @@
     </row>
     <row r="928" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B928" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C928" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="929" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="929" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B929" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C929" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="930" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="930" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B930" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C930" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="931" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="931" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B931" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C931" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="932" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="932" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B932" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="933" spans="2:3" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="C932" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="933" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B933" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="934" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B934" s="3">
+        <v>11</v>
+      </c>
+      <c r="C933" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="934" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B934" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="935" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A935" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B935" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C935" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="936" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B936" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C936" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="937" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B937" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C937" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="938" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B938" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C938" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="939" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B939" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C939" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="940" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B940" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C940" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="941" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B941" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C941" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="942" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B942" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C942" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="943" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B943" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="944" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B944" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="945" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B945" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7135BCC4-EA9F-4A42-8AF2-C28D92D412EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2BC3889-142F-4863-859C-857BA1769836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1775" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C945"/>
+  <dimension ref="A1:C956"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -650,7 +650,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -741,7 +741,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -832,7 +832,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -923,7 +923,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -1014,7 +1014,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1105,7 +1105,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1196,7 +1196,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1378,7 +1378,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1469,7 +1469,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1560,7 +1560,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1651,7 +1651,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1742,7 +1742,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1819,6 +1819,9 @@
       <c r="B165" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C165" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B166" s="3" t="s">
@@ -1830,7 +1833,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1907,9 +1910,6 @@
       <c r="B176" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C176" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B177" s="3" t="s">
@@ -1921,7 +1921,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -2012,7 +2012,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2103,7 +2103,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2194,7 +2194,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2285,7 +2285,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2376,7 +2376,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2467,7 +2467,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2558,7 +2558,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2649,7 +2649,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2740,7 +2740,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2809,6 +2809,9 @@
       <c r="B285" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C285" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B286" s="3" t="s">
@@ -2828,7 +2831,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2897,9 +2900,6 @@
       <c r="B296" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C296" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B297" s="3" t="s">
@@ -2919,7 +2919,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2996,6 +2996,9 @@
       <c r="B308" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C308" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B309" s="3" t="s">
@@ -3007,7 +3010,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3076,6 +3079,9 @@
       <c r="B318" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C318" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B319" s="3" t="s">
@@ -3092,7 +3098,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3161,9 +3167,6 @@
       <c r="B329" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C329" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B330" s="3" t="s">
@@ -3180,7 +3183,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3249,6 +3252,9 @@
       <c r="B340" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C340" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B341" s="3" t="s">
@@ -3265,7 +3271,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3334,9 +3340,6 @@
       <c r="B351" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C351" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B352" s="3" t="s">
@@ -3353,7 +3356,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3441,7 +3444,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3529,7 +3532,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3598,6 +3601,9 @@
       <c r="B384" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C384" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B385" s="3" t="s">
@@ -3614,7 +3620,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3699,7 +3705,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3784,7 +3790,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3869,7 +3875,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3954,7 +3960,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -4039,7 +4045,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4124,7 +4130,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4209,7 +4215,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4294,7 +4300,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4379,7 +4385,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4464,7 +4470,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4549,7 +4555,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4618,9 +4624,6 @@
       <c r="B516" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C516" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B517" s="3" t="s">
@@ -4637,7 +4640,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4706,6 +4709,9 @@
       <c r="B527" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C527" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B528" s="3" t="s">
@@ -4722,7 +4728,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4807,7 +4813,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4892,7 +4898,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4961,9 +4967,6 @@
       <c r="B560" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C560" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B561" s="3" t="s">
@@ -4980,7 +4983,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5068,7 +5071,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5137,6 +5140,9 @@
       <c r="B582" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C582" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B583" s="3" t="s">
@@ -5153,7 +5159,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5238,7 +5244,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5323,7 +5329,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5408,7 +5414,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5477,9 +5483,6 @@
       <c r="B626" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C626" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B627" s="3" t="s">
@@ -5496,7 +5499,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5584,7 +5587,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5661,9 +5664,6 @@
       <c r="B649" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C649" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B650" s="3" t="s">
@@ -5675,7 +5675,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5752,6 +5752,9 @@
       <c r="B660" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C660" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B661" s="3" t="s">
@@ -5763,7 +5766,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5851,7 +5854,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5939,7 +5942,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -6027,7 +6030,7 @@
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6115,7 +6118,7 @@
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6184,6 +6187,9 @@
       <c r="B714" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C714" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="715" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B715" s="3" t="s">
@@ -6200,7 +6206,7 @@
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6261,7 +6267,9 @@
       <c r="B724" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C724" s="6"/>
+      <c r="C724" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="725" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B725" s="3" t="s">
@@ -6277,10 +6285,13 @@
       <c r="B727" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C727" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6341,17 +6352,12 @@
       <c r="B735" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C735" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C735" s="6"/>
     </row>
     <row r="736" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B736" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C736" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="737" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B737" s="3" t="s">
@@ -6362,13 +6368,10 @@
       <c r="B738" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C738" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6456,7 +6459,7 @@
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6544,7 +6547,7 @@
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6613,6 +6616,9 @@
       <c r="B769" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C769" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="770" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B770" s="3" t="s">
@@ -6629,7 +6635,7 @@
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3</v>
@@ -6714,7 +6720,7 @@
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B783" s="7" t="s">
         <v>3</v>
@@ -6788,9 +6794,6 @@
       <c r="B792" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C792" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="793" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B793" s="3" t="s">
@@ -6802,7 +6805,7 @@
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A794" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B794" s="7" t="s">
         <v>3</v>
@@ -6863,7 +6866,9 @@
       <c r="B801" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C801" s="6"/>
+      <c r="C801" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="802" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B802" s="3" t="s">
@@ -6874,15 +6879,21 @@
       <c r="B803" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C803" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="804" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B804" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C804" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A805" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B805" s="7" t="s">
         <v>3</v>
@@ -6943,9 +6954,7 @@
       <c r="B812" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C812" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C812" s="6"/>
     </row>
     <row r="813" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B813" s="3" t="s">
@@ -6961,13 +6970,10 @@
       <c r="B815" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C815" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A816" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B816" s="7" t="s">
         <v>3</v>
@@ -7036,9 +7042,6 @@
       <c r="B824" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C824" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="825" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B825" s="3" t="s">
@@ -7055,7 +7058,7 @@
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A827" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B827" s="7" t="s">
         <v>3</v>
@@ -7124,6 +7127,9 @@
       <c r="B835" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C835" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="836" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B836" s="3" t="s">
@@ -7140,7 +7146,7 @@
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A838" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B838" s="7" t="s">
         <v>3</v>
@@ -7219,10 +7225,13 @@
       <c r="B848" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C848" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A849" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B849" s="7" t="s">
         <v>3</v>
@@ -7301,13 +7310,10 @@
       <c r="B859" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C859" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A860" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B860" s="7" t="s">
         <v>3</v>
@@ -7376,9 +7382,6 @@
       <c r="B868" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C868" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="869" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B869" s="3" t="s">
@@ -7395,7 +7398,7 @@
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A871" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B871" s="7" t="s">
         <v>3</v>
@@ -7416,19 +7419,25 @@
       <c r="B873" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C873" s="6"/>
+      <c r="C873" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="874" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B874" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C874" s="6"/>
+      <c r="C874" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="875" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B875" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C875" s="6"/>
+      <c r="C875" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="876" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B876" s="3" t="s">
@@ -7450,12 +7459,17 @@
       <c r="B878" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C878" s="6"/>
+      <c r="C878" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="879" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B879" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C879" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="880" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B880" s="3" t="s">
@@ -7466,10 +7480,13 @@
       <c r="B881" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C881" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A882" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B882" s="7" t="s">
         <v>3</v>
@@ -7490,25 +7507,19 @@
       <c r="B884" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C884" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C884" s="6"/>
     </row>
     <row r="885" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B885" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C885" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C885" s="6"/>
     </row>
     <row r="886" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B886" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C886" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C886" s="6"/>
     </row>
     <row r="887" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B887" s="3" t="s">
@@ -7530,17 +7541,12 @@
       <c r="B889" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C889" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C889" s="6"/>
     </row>
     <row r="890" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B890" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C890" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="891" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B891" s="3" t="s">
@@ -7551,13 +7557,10 @@
       <c r="B892" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C892" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="893" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A893" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B893" s="7" t="s">
         <v>3</v>
@@ -7645,7 +7648,7 @@
     </row>
     <row r="904" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A904" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B904" s="7" t="s">
         <v>3</v>
@@ -7714,6 +7717,9 @@
       <c r="B912" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C912" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="913" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B913" s="3" t="s">
@@ -7730,7 +7736,7 @@
     </row>
     <row r="915" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A915" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B915" s="7" t="s">
         <v>3</v>
@@ -7799,9 +7805,6 @@
       <c r="B923" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C923" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="924" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B924" s="3" t="s">
@@ -7809,19 +7812,19 @@
       </c>
     </row>
     <row r="925" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A925" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B925" s="7" t="s">
-        <v>3</v>
+      <c r="B925" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C925" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="926" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B926" s="3" t="s">
-        <v>4</v>
+      <c r="A926" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B926" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C926" s="5" t="s">
         <v>13</v>
@@ -7829,7 +7832,7 @@
     </row>
     <row r="927" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B927" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C927" s="5" t="s">
         <v>13</v>
@@ -7837,7 +7840,7 @@
     </row>
     <row r="928" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B928" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C928" s="5" t="s">
         <v>13</v>
@@ -7845,7 +7848,7 @@
     </row>
     <row r="929" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B929" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C929" s="5" t="s">
         <v>13</v>
@@ -7853,7 +7856,7 @@
     </row>
     <row r="930" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B930" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C930" s="5" t="s">
         <v>13</v>
@@ -7861,7 +7864,7 @@
     </row>
     <row r="931" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B931" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C931" s="5" t="s">
         <v>13</v>
@@ -7869,7 +7872,7 @@
     </row>
     <row r="932" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B932" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C932" s="5" t="s">
         <v>13</v>
@@ -7877,7 +7880,7 @@
     </row>
     <row r="933" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B933" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C933" s="5" t="s">
         <v>13</v>
@@ -7885,23 +7888,23 @@
     </row>
     <row r="934" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B934" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C934" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="935" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A935" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B935" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C935" s="5" t="s">
-        <v>13</v>
+      <c r="B935" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="936" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B936" s="3" t="s">
-        <v>4</v>
+      <c r="A936" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B936" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C936" s="5" t="s">
         <v>13</v>
@@ -7909,7 +7912,7 @@
     </row>
     <row r="937" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B937" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C937" s="5" t="s">
         <v>13</v>
@@ -7917,7 +7920,7 @@
     </row>
     <row r="938" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B938" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C938" s="5" t="s">
         <v>13</v>
@@ -7925,7 +7928,7 @@
     </row>
     <row r="939" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B939" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C939" s="5" t="s">
         <v>13</v>
@@ -7933,7 +7936,7 @@
     </row>
     <row r="940" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B940" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C940" s="5" t="s">
         <v>13</v>
@@ -7941,7 +7944,7 @@
     </row>
     <row r="941" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B941" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C941" s="5" t="s">
         <v>13</v>
@@ -7949,7 +7952,7 @@
     </row>
     <row r="942" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B942" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C942" s="5" t="s">
         <v>13</v>
@@ -7957,16 +7960,104 @@
     </row>
     <row r="943" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B943" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C943" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="944" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B944" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="945" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B945" s="3">
+        <v>11</v>
+      </c>
+      <c r="C944" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="945" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B945" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="946" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A946" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B946" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C946" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="947" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B947" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C947" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="948" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B948" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C948" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="949" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B949" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C949" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="950" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B950" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C950" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="951" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B951" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C951" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="952" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B952" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C952" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="953" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B953" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C953" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="954" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B954" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="955" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B955" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="956" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B956" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2BC3889-142F-4863-859C-857BA1769836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52F32291-334C-463E-AF2B-C714779052E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1819" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C956"/>
+  <dimension ref="A1:C967"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -650,7 +650,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -741,7 +741,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -832,7 +832,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -923,7 +923,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -1014,7 +1014,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1105,7 +1105,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1196,7 +1196,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1378,7 +1378,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1469,7 +1469,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1560,7 +1560,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1651,7 +1651,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1742,7 +1742,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1833,7 +1833,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1910,6 +1910,9 @@
       <c r="B176" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C176" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B177" s="3" t="s">
@@ -1921,7 +1924,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1998,9 +2001,6 @@
       <c r="B187" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C187" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B188" s="3" t="s">
@@ -2012,7 +2012,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2103,7 +2103,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2194,7 +2194,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2285,7 +2285,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2376,7 +2376,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2467,7 +2467,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2558,7 +2558,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2649,7 +2649,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2740,7 +2740,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2831,7 +2831,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2900,6 +2900,9 @@
       <c r="B296" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C296" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B297" s="3" t="s">
@@ -2919,7 +2922,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2988,9 +2991,6 @@
       <c r="B307" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C307" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B308" s="3" t="s">
@@ -3010,7 +3010,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3087,6 +3087,9 @@
       <c r="B319" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C319" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B320" s="3" t="s">
@@ -3098,7 +3101,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3167,6 +3170,9 @@
       <c r="B329" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C329" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B330" s="3" t="s">
@@ -3183,7 +3189,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3252,9 +3258,6 @@
       <c r="B340" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C340" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B341" s="3" t="s">
@@ -3271,7 +3274,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3340,6 +3343,9 @@
       <c r="B351" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C351" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B352" s="3" t="s">
@@ -3356,7 +3362,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3425,9 +3431,6 @@
       <c r="B362" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C362" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B363" s="3" t="s">
@@ -3444,7 +3447,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3532,7 +3535,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3620,7 +3623,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3689,6 +3692,9 @@
       <c r="B395" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C395" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B396" s="3" t="s">
@@ -3705,7 +3711,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3790,7 +3796,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3875,7 +3881,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3960,7 +3966,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -4045,7 +4051,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4130,7 +4136,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4215,7 +4221,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4300,7 +4306,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4385,7 +4391,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4470,7 +4476,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4555,7 +4561,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4640,7 +4646,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4709,9 +4715,6 @@
       <c r="B527" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C527" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B528" s="3" t="s">
@@ -4728,7 +4731,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4797,6 +4800,9 @@
       <c r="B538" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C538" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B539" s="3" t="s">
@@ -4813,7 +4819,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4898,7 +4904,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4983,7 +4989,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5052,9 +5058,6 @@
       <c r="B571" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C571" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B572" s="3" t="s">
@@ -5071,7 +5074,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5159,7 +5162,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5228,6 +5231,9 @@
       <c r="B593" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C593" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B594" s="3" t="s">
@@ -5244,7 +5250,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5329,7 +5335,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5414,7 +5420,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5499,7 +5505,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5568,9 +5574,6 @@
       <c r="B637" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C637" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B638" s="3" t="s">
@@ -5587,7 +5590,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5675,7 +5678,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5752,9 +5755,6 @@
       <c r="B660" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C660" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B661" s="3" t="s">
@@ -5766,7 +5766,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5843,6 +5843,9 @@
       <c r="B671" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C671" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="672" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B672" s="3" t="s">
@@ -5854,7 +5857,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5942,7 +5945,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -6030,7 +6033,7 @@
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6118,7 +6121,7 @@
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6206,7 +6209,7 @@
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6275,6 +6278,9 @@
       <c r="B725" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C725" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="726" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B726" s="3" t="s">
@@ -6291,7 +6297,7 @@
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6352,7 +6358,9 @@
       <c r="B735" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C735" s="6"/>
+      <c r="C735" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="736" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B736" s="3" t="s">
@@ -6368,10 +6376,13 @@
       <c r="B738" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C738" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6432,17 +6443,12 @@
       <c r="B746" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C746" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C746" s="6"/>
     </row>
     <row r="747" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B747" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C747" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="748" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B748" s="3" t="s">
@@ -6453,13 +6459,10 @@
       <c r="B749" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C749" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6547,7 +6550,7 @@
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6635,7 +6638,7 @@
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3</v>
@@ -6704,6 +6707,9 @@
       <c r="B780" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C780" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="781" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B781" s="3" t="s">
@@ -6720,7 +6726,7 @@
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B783" s="7" t="s">
         <v>3</v>
@@ -6805,7 +6811,7 @@
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A794" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B794" s="7" t="s">
         <v>3</v>
@@ -6879,9 +6885,6 @@
       <c r="B803" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C803" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="804" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B804" s="3" t="s">
@@ -6893,7 +6896,7 @@
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A805" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B805" s="7" t="s">
         <v>3</v>
@@ -6954,7 +6957,9 @@
       <c r="B812" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C812" s="6"/>
+      <c r="C812" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="813" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B813" s="3" t="s">
@@ -6965,15 +6970,21 @@
       <c r="B814" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C814" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="815" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B815" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C815" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A816" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B816" s="7" t="s">
         <v>3</v>
@@ -7034,9 +7045,7 @@
       <c r="B823" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C823" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C823" s="6"/>
     </row>
     <row r="824" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B824" s="3" t="s">
@@ -7052,13 +7061,10 @@
       <c r="B826" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C826" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A827" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B827" s="7" t="s">
         <v>3</v>
@@ -7127,9 +7133,6 @@
       <c r="B835" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C835" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="836" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B836" s="3" t="s">
@@ -7146,7 +7149,7 @@
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A838" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B838" s="7" t="s">
         <v>3</v>
@@ -7215,6 +7218,9 @@
       <c r="B846" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C846" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="847" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B847" s="3" t="s">
@@ -7231,7 +7237,7 @@
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A849" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B849" s="7" t="s">
         <v>3</v>
@@ -7310,10 +7316,13 @@
       <c r="B859" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C859" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A860" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B860" s="7" t="s">
         <v>3</v>
@@ -7392,13 +7401,10 @@
       <c r="B870" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C870" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A871" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B871" s="7" t="s">
         <v>3</v>
@@ -7467,9 +7473,6 @@
       <c r="B879" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C879" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="880" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B880" s="3" t="s">
@@ -7486,7 +7489,7 @@
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A882" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B882" s="7" t="s">
         <v>3</v>
@@ -7507,19 +7510,25 @@
       <c r="B884" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C884" s="6"/>
+      <c r="C884" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="885" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B885" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C885" s="6"/>
+      <c r="C885" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="886" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B886" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C886" s="6"/>
+      <c r="C886" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="887" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B887" s="3" t="s">
@@ -7541,12 +7550,17 @@
       <c r="B889" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C889" s="6"/>
+      <c r="C889" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="890" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B890" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C890" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="891" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B891" s="3" t="s">
@@ -7557,10 +7571,13 @@
       <c r="B892" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C892" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="893" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A893" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B893" s="7" t="s">
         <v>3</v>
@@ -7581,25 +7598,19 @@
       <c r="B895" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C895" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C895" s="6"/>
     </row>
     <row r="896" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B896" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C896" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C896" s="6"/>
     </row>
     <row r="897" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B897" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C897" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C897" s="6"/>
     </row>
     <row r="898" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B898" s="3" t="s">
@@ -7621,17 +7632,12 @@
       <c r="B900" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C900" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C900" s="6"/>
     </row>
     <row r="901" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B901" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C901" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="902" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B902" s="3" t="s">
@@ -7642,13 +7648,10 @@
       <c r="B903" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C903" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="904" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A904" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B904" s="7" t="s">
         <v>3</v>
@@ -7736,7 +7739,7 @@
     </row>
     <row r="915" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A915" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B915" s="7" t="s">
         <v>3</v>
@@ -7805,6 +7808,9 @@
       <c r="B923" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C923" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="924" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B924" s="3" t="s">
@@ -7821,7 +7827,7 @@
     </row>
     <row r="926" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A926" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B926" s="7" t="s">
         <v>3</v>
@@ -7890,9 +7896,6 @@
       <c r="B934" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C934" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="935" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B935" s="3" t="s">
@@ -7900,19 +7903,19 @@
       </c>
     </row>
     <row r="936" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A936" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B936" s="7" t="s">
-        <v>3</v>
+      <c r="B936" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C936" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="937" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B937" s="3" t="s">
-        <v>4</v>
+      <c r="A937" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B937" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C937" s="5" t="s">
         <v>13</v>
@@ -7920,7 +7923,7 @@
     </row>
     <row r="938" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B938" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C938" s="5" t="s">
         <v>13</v>
@@ -7928,7 +7931,7 @@
     </row>
     <row r="939" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B939" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C939" s="5" t="s">
         <v>13</v>
@@ -7936,7 +7939,7 @@
     </row>
     <row r="940" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B940" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C940" s="5" t="s">
         <v>13</v>
@@ -7944,7 +7947,7 @@
     </row>
     <row r="941" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B941" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C941" s="5" t="s">
         <v>13</v>
@@ -7952,7 +7955,7 @@
     </row>
     <row r="942" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B942" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C942" s="5" t="s">
         <v>13</v>
@@ -7960,7 +7963,7 @@
     </row>
     <row r="943" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B943" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C943" s="5" t="s">
         <v>13</v>
@@ -7968,7 +7971,7 @@
     </row>
     <row r="944" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B944" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C944" s="5" t="s">
         <v>13</v>
@@ -7976,23 +7979,23 @@
     </row>
     <row r="945" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B945" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C945" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="946" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A946" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B946" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C946" s="5" t="s">
-        <v>13</v>
+      <c r="B946" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="947" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B947" s="3" t="s">
-        <v>4</v>
+      <c r="A947" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B947" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C947" s="5" t="s">
         <v>13</v>
@@ -8000,7 +8003,7 @@
     </row>
     <row r="948" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B948" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C948" s="5" t="s">
         <v>13</v>
@@ -8008,7 +8011,7 @@
     </row>
     <row r="949" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B949" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C949" s="5" t="s">
         <v>13</v>
@@ -8016,7 +8019,7 @@
     </row>
     <row r="950" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B950" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C950" s="5" t="s">
         <v>13</v>
@@ -8024,7 +8027,7 @@
     </row>
     <row r="951" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B951" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C951" s="5" t="s">
         <v>13</v>
@@ -8032,7 +8035,7 @@
     </row>
     <row r="952" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B952" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C952" s="5" t="s">
         <v>13</v>
@@ -8040,7 +8043,7 @@
     </row>
     <row r="953" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B953" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C953" s="5" t="s">
         <v>13</v>
@@ -8048,16 +8051,104 @@
     </row>
     <row r="954" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B954" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C954" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="955" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B955" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C955" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="956" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B956" s="3">
+      <c r="B956" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="957" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A957" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B957" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C957" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="958" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B958" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C958" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="959" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B959" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C959" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="960" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B960" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C960" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="961" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B961" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C961" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="962" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B962" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C962" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="963" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B963" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C963" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="964" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B964" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C964" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="965" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B965" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="966" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B966" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="967" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B967" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52F32291-334C-463E-AF2B-C714779052E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41038163-5C92-4324-B9B3-FBF0F05AB44C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1819" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1841" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C967"/>
+  <dimension ref="A1:C978"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -650,7 +650,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -741,7 +741,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -832,7 +832,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -923,7 +923,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -1014,7 +1014,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1105,7 +1105,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1196,7 +1196,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1378,7 +1378,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1469,7 +1469,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1560,7 +1560,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1651,7 +1651,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1742,7 +1742,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1833,7 +1833,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1924,7 +1924,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -2001,6 +2001,9 @@
       <c r="B187" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C187" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B188" s="3" t="s">
@@ -2012,7 +2015,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2089,9 +2092,6 @@
       <c r="B198" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C198" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B199" s="3" t="s">
@@ -2103,7 +2103,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2194,7 +2194,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2285,7 +2285,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2376,7 +2376,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2467,7 +2467,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2558,7 +2558,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2649,7 +2649,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2740,7 +2740,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2831,7 +2831,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2922,7 +2922,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2991,6 +2991,9 @@
       <c r="B307" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C307" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B308" s="3" t="s">
@@ -3010,7 +3013,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3079,9 +3082,6 @@
       <c r="B318" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C318" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B319" s="3" t="s">
@@ -3101,7 +3101,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3178,6 +3178,9 @@
       <c r="B330" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C330" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B331" s="3" t="s">
@@ -3189,7 +3192,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3258,6 +3261,9 @@
       <c r="B340" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C340" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B341" s="3" t="s">
@@ -3274,7 +3280,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3343,9 +3349,6 @@
       <c r="B351" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C351" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B352" s="3" t="s">
@@ -3362,7 +3365,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3431,6 +3434,9 @@
       <c r="B362" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C362" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B363" s="3" t="s">
@@ -3447,7 +3453,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3516,9 +3522,6 @@
       <c r="B373" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C373" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B374" s="3" t="s">
@@ -3535,7 +3538,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3623,7 +3626,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3711,7 +3714,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3780,6 +3783,9 @@
       <c r="B406" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C406" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B407" s="3" t="s">
@@ -3796,7 +3802,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3881,7 +3887,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3966,7 +3972,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -4051,7 +4057,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4136,7 +4142,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4221,7 +4227,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4306,7 +4312,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4391,7 +4397,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4476,7 +4482,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4561,7 +4567,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4646,7 +4652,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4731,7 +4737,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4800,9 +4806,6 @@
       <c r="B538" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C538" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B539" s="3" t="s">
@@ -4819,7 +4822,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4888,6 +4891,9 @@
       <c r="B549" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C549" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B550" s="3" t="s">
@@ -4904,7 +4910,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4989,7 +4995,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5074,7 +5080,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5143,9 +5149,6 @@
       <c r="B582" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C582" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B583" s="3" t="s">
@@ -5162,7 +5165,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5250,7 +5253,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5319,6 +5322,9 @@
       <c r="B604" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C604" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B605" s="3" t="s">
@@ -5335,7 +5341,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5420,7 +5426,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5505,7 +5511,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5590,7 +5596,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5659,9 +5665,6 @@
       <c r="B648" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C648" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B649" s="3" t="s">
@@ -5678,7 +5681,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5766,7 +5769,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5843,9 +5846,6 @@
       <c r="B671" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C671" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="672" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B672" s="3" t="s">
@@ -5857,7 +5857,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5934,6 +5934,9 @@
       <c r="B682" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C682" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="683" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B683" s="3" t="s">
@@ -5945,7 +5948,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -6033,7 +6036,7 @@
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6121,7 +6124,7 @@
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6209,7 +6212,7 @@
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6297,7 +6300,7 @@
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6366,6 +6369,9 @@
       <c r="B736" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C736" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="737" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B737" s="3" t="s">
@@ -6382,7 +6388,7 @@
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6443,7 +6449,9 @@
       <c r="B746" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C746" s="6"/>
+      <c r="C746" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="747" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B747" s="3" t="s">
@@ -6459,10 +6467,13 @@
       <c r="B749" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C749" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6523,17 +6534,12 @@
       <c r="B757" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C757" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C757" s="6"/>
     </row>
     <row r="758" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B758" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C758" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="759" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B759" s="3" t="s">
@@ -6544,13 +6550,10 @@
       <c r="B760" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C760" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6638,7 +6641,7 @@
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3</v>
@@ -6726,7 +6729,7 @@
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B783" s="7" t="s">
         <v>3</v>
@@ -6795,6 +6798,9 @@
       <c r="B791" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C791" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="792" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B792" s="3" t="s">
@@ -6811,7 +6817,7 @@
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A794" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B794" s="7" t="s">
         <v>3</v>
@@ -6896,7 +6902,7 @@
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A805" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B805" s="7" t="s">
         <v>3</v>
@@ -6970,9 +6976,6 @@
       <c r="B814" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C814" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="815" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B815" s="3" t="s">
@@ -6984,7 +6987,7 @@
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A816" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B816" s="7" t="s">
         <v>3</v>
@@ -7045,7 +7048,9 @@
       <c r="B823" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C823" s="6"/>
+      <c r="C823" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="824" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B824" s="3" t="s">
@@ -7056,15 +7061,21 @@
       <c r="B825" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C825" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="826" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B826" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C826" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A827" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B827" s="7" t="s">
         <v>3</v>
@@ -7125,9 +7136,7 @@
       <c r="B834" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C834" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C834" s="6"/>
     </row>
     <row r="835" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B835" s="3" t="s">
@@ -7143,13 +7152,10 @@
       <c r="B837" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C837" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A838" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B838" s="7" t="s">
         <v>3</v>
@@ -7218,9 +7224,6 @@
       <c r="B846" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C846" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="847" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B847" s="3" t="s">
@@ -7237,7 +7240,7 @@
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A849" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B849" s="7" t="s">
         <v>3</v>
@@ -7306,6 +7309,9 @@
       <c r="B857" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C857" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="858" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B858" s="3" t="s">
@@ -7322,7 +7328,7 @@
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A860" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B860" s="7" t="s">
         <v>3</v>
@@ -7401,10 +7407,13 @@
       <c r="B870" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C870" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A871" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B871" s="7" t="s">
         <v>3</v>
@@ -7483,13 +7492,10 @@
       <c r="B881" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C881" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A882" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B882" s="7" t="s">
         <v>3</v>
@@ -7558,9 +7564,6 @@
       <c r="B890" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C890" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="891" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B891" s="3" t="s">
@@ -7577,7 +7580,7 @@
     </row>
     <row r="893" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A893" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B893" s="7" t="s">
         <v>3</v>
@@ -7598,19 +7601,25 @@
       <c r="B895" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C895" s="6"/>
+      <c r="C895" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="896" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B896" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C896" s="6"/>
+      <c r="C896" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="897" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B897" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C897" s="6"/>
+      <c r="C897" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="898" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B898" s="3" t="s">
@@ -7632,12 +7641,17 @@
       <c r="B900" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C900" s="6"/>
+      <c r="C900" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="901" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B901" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C901" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="902" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B902" s="3" t="s">
@@ -7648,10 +7662,13 @@
       <c r="B903" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C903" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="904" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A904" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B904" s="7" t="s">
         <v>3</v>
@@ -7672,25 +7689,19 @@
       <c r="B906" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C906" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C906" s="6"/>
     </row>
     <row r="907" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B907" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C907" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C907" s="6"/>
     </row>
     <row r="908" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B908" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C908" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C908" s="6"/>
     </row>
     <row r="909" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B909" s="3" t="s">
@@ -7712,17 +7723,12 @@
       <c r="B911" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C911" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C911" s="6"/>
     </row>
     <row r="912" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B912" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C912" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="913" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B913" s="3" t="s">
@@ -7733,13 +7739,10 @@
       <c r="B914" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C914" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="915" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A915" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B915" s="7" t="s">
         <v>3</v>
@@ -7827,7 +7830,7 @@
     </row>
     <row r="926" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A926" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B926" s="7" t="s">
         <v>3</v>
@@ -7896,6 +7899,9 @@
       <c r="B934" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C934" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="935" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B935" s="3" t="s">
@@ -7912,7 +7918,7 @@
     </row>
     <row r="937" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A937" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B937" s="7" t="s">
         <v>3</v>
@@ -7981,9 +7987,6 @@
       <c r="B945" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C945" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="946" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B946" s="3" t="s">
@@ -7991,19 +7994,19 @@
       </c>
     </row>
     <row r="947" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A947" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B947" s="7" t="s">
-        <v>3</v>
+      <c r="B947" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C947" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="948" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B948" s="3" t="s">
-        <v>4</v>
+      <c r="A948" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B948" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C948" s="5" t="s">
         <v>13</v>
@@ -8011,7 +8014,7 @@
     </row>
     <row r="949" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B949" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C949" s="5" t="s">
         <v>13</v>
@@ -8019,7 +8022,7 @@
     </row>
     <row r="950" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B950" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C950" s="5" t="s">
         <v>13</v>
@@ -8027,7 +8030,7 @@
     </row>
     <row r="951" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B951" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C951" s="5" t="s">
         <v>13</v>
@@ -8035,7 +8038,7 @@
     </row>
     <row r="952" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B952" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C952" s="5" t="s">
         <v>13</v>
@@ -8043,7 +8046,7 @@
     </row>
     <row r="953" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B953" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C953" s="5" t="s">
         <v>13</v>
@@ -8051,7 +8054,7 @@
     </row>
     <row r="954" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B954" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C954" s="5" t="s">
         <v>13</v>
@@ -8059,7 +8062,7 @@
     </row>
     <row r="955" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B955" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C955" s="5" t="s">
         <v>13</v>
@@ -8067,23 +8070,23 @@
     </row>
     <row r="956" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B956" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C956" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="957" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A957" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B957" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C957" s="5" t="s">
-        <v>13</v>
+      <c r="B957" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="958" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B958" s="3" t="s">
-        <v>4</v>
+      <c r="A958" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B958" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C958" s="5" t="s">
         <v>13</v>
@@ -8091,7 +8094,7 @@
     </row>
     <row r="959" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B959" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C959" s="5" t="s">
         <v>13</v>
@@ -8099,56 +8102,144 @@
     </row>
     <row r="960" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B960" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C960" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="961" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="961" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B961" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C961" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="962" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="962" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B962" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C962" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="963" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="963" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B963" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C963" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="964" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="964" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B964" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C964" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="965" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="965" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B965" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="966" spans="2:3" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="C965" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="966" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B966" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="967" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B967" s="3">
+        <v>11</v>
+      </c>
+      <c r="C966" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="967" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B967" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="968" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A968" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B968" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C968" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="969" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B969" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C969" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="970" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B970" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C970" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="971" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B971" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C971" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="972" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B972" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C972" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="973" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B973" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C973" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="974" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B974" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C974" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="975" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B975" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C975" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="976" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B976" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="977" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B977" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="978" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B978" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41038163-5C92-4324-B9B3-FBF0F05AB44C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C799B20-DC60-4F1C-8B95-0BE25CCF52D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1841" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1863" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C978"/>
+  <dimension ref="A1:C989"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -650,7 +650,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -741,7 +741,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -832,7 +832,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -923,7 +923,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -1014,7 +1014,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1105,7 +1105,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1196,7 +1196,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1378,7 +1378,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1469,7 +1469,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1560,7 +1560,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1651,7 +1651,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1742,7 +1742,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1833,7 +1833,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1924,7 +1924,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -2015,7 +2015,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2092,6 +2092,9 @@
       <c r="B198" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C198" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B199" s="3" t="s">
@@ -2103,7 +2106,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2180,9 +2183,6 @@
       <c r="B209" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C209" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B210" s="3" t="s">
@@ -2194,7 +2194,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2285,7 +2285,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2376,7 +2376,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2467,7 +2467,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2558,7 +2558,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2649,7 +2649,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2740,7 +2740,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2831,7 +2831,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2922,7 +2922,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -3013,7 +3013,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3082,6 +3082,9 @@
       <c r="B318" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C318" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B319" s="3" t="s">
@@ -3101,7 +3104,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3170,9 +3173,6 @@
       <c r="B329" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C329" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B330" s="3" t="s">
@@ -3192,7 +3192,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3269,6 +3269,9 @@
       <c r="B341" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C341" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B342" s="3" t="s">
@@ -3280,7 +3283,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3349,6 +3352,9 @@
       <c r="B351" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C351" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B352" s="3" t="s">
@@ -3365,7 +3371,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3434,9 +3440,6 @@
       <c r="B362" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C362" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B363" s="3" t="s">
@@ -3453,7 +3456,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3522,6 +3525,9 @@
       <c r="B373" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C373" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B374" s="3" t="s">
@@ -3538,7 +3544,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3607,9 +3613,6 @@
       <c r="B384" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C384" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B385" s="3" t="s">
@@ -3626,7 +3629,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3714,7 +3717,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3802,7 +3805,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3871,6 +3874,9 @@
       <c r="B417" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C417" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B418" s="3" t="s">
@@ -3887,7 +3893,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3972,7 +3978,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -4057,7 +4063,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4142,7 +4148,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4227,7 +4233,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4312,7 +4318,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4397,7 +4403,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4482,7 +4488,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4567,7 +4573,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4652,7 +4658,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4737,7 +4743,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4822,7 +4828,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4891,9 +4897,6 @@
       <c r="B549" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C549" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B550" s="3" t="s">
@@ -4910,7 +4913,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4979,6 +4982,9 @@
       <c r="B560" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C560" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B561" s="3" t="s">
@@ -4995,7 +5001,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5080,7 +5086,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5165,7 +5171,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5234,9 +5240,6 @@
       <c r="B593" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C593" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B594" s="3" t="s">
@@ -5253,7 +5256,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5341,7 +5344,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5410,6 +5413,9 @@
       <c r="B615" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C615" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B616" s="3" t="s">
@@ -5426,7 +5432,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5511,7 +5517,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5596,7 +5602,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5681,7 +5687,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5750,9 +5756,6 @@
       <c r="B659" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C659" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B660" s="3" t="s">
@@ -5769,7 +5772,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5857,7 +5860,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5934,9 +5937,6 @@
       <c r="B682" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C682" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="683" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B683" s="3" t="s">
@@ -5948,7 +5948,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -6025,6 +6025,9 @@
       <c r="B693" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C693" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="694" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B694" s="3" t="s">
@@ -6036,7 +6039,7 @@
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6124,7 +6127,7 @@
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6212,7 +6215,7 @@
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6300,7 +6303,7 @@
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6388,7 +6391,7 @@
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6457,6 +6460,9 @@
       <c r="B747" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C747" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="748" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B748" s="3" t="s">
@@ -6473,7 +6479,7 @@
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6534,7 +6540,9 @@
       <c r="B757" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C757" s="6"/>
+      <c r="C757" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="758" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B758" s="3" t="s">
@@ -6550,10 +6558,13 @@
       <c r="B760" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C760" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6614,17 +6625,12 @@
       <c r="B768" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C768" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C768" s="6"/>
     </row>
     <row r="769" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B769" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C769" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="770" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B770" s="3" t="s">
@@ -6635,13 +6641,10 @@
       <c r="B771" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C771" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3</v>
@@ -6729,7 +6732,7 @@
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B783" s="7" t="s">
         <v>3</v>
@@ -6817,7 +6820,7 @@
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A794" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B794" s="7" t="s">
         <v>3</v>
@@ -6886,6 +6889,9 @@
       <c r="B802" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C802" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="803" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B803" s="3" t="s">
@@ -6902,7 +6908,7 @@
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A805" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B805" s="7" t="s">
         <v>3</v>
@@ -6987,7 +6993,7 @@
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A816" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B816" s="7" t="s">
         <v>3</v>
@@ -7061,9 +7067,6 @@
       <c r="B825" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C825" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="826" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B826" s="3" t="s">
@@ -7075,7 +7078,7 @@
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A827" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B827" s="7" t="s">
         <v>3</v>
@@ -7136,7 +7139,9 @@
       <c r="B834" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C834" s="6"/>
+      <c r="C834" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="835" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B835" s="3" t="s">
@@ -7147,15 +7152,21 @@
       <c r="B836" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C836" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="837" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B837" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C837" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A838" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B838" s="7" t="s">
         <v>3</v>
@@ -7216,9 +7227,7 @@
       <c r="B845" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C845" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C845" s="6"/>
     </row>
     <row r="846" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B846" s="3" t="s">
@@ -7234,13 +7243,10 @@
       <c r="B848" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C848" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A849" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B849" s="7" t="s">
         <v>3</v>
@@ -7309,9 +7315,6 @@
       <c r="B857" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C857" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="858" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B858" s="3" t="s">
@@ -7328,7 +7331,7 @@
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A860" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B860" s="7" t="s">
         <v>3</v>
@@ -7397,6 +7400,9 @@
       <c r="B868" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C868" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="869" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B869" s="3" t="s">
@@ -7413,7 +7419,7 @@
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A871" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B871" s="7" t="s">
         <v>3</v>
@@ -7492,10 +7498,13 @@
       <c r="B881" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C881" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A882" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B882" s="7" t="s">
         <v>3</v>
@@ -7574,13 +7583,10 @@
       <c r="B892" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C892" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="893" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A893" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B893" s="7" t="s">
         <v>3</v>
@@ -7649,9 +7655,6 @@
       <c r="B901" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C901" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="902" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B902" s="3" t="s">
@@ -7668,7 +7671,7 @@
     </row>
     <row r="904" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A904" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B904" s="7" t="s">
         <v>3</v>
@@ -7689,19 +7692,25 @@
       <c r="B906" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C906" s="6"/>
+      <c r="C906" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="907" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B907" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C907" s="6"/>
+      <c r="C907" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="908" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B908" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C908" s="6"/>
+      <c r="C908" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="909" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B909" s="3" t="s">
@@ -7723,12 +7732,17 @@
       <c r="B911" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C911" s="6"/>
+      <c r="C911" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="912" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B912" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C912" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="913" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B913" s="3" t="s">
@@ -7739,10 +7753,13 @@
       <c r="B914" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C914" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="915" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A915" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B915" s="7" t="s">
         <v>3</v>
@@ -7763,25 +7780,19 @@
       <c r="B917" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C917" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C917" s="6"/>
     </row>
     <row r="918" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B918" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C918" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C918" s="6"/>
     </row>
     <row r="919" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B919" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C919" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C919" s="6"/>
     </row>
     <row r="920" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B920" s="3" t="s">
@@ -7803,17 +7814,12 @@
       <c r="B922" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C922" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C922" s="6"/>
     </row>
     <row r="923" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B923" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C923" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="924" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B924" s="3" t="s">
@@ -7824,13 +7830,10 @@
       <c r="B925" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C925" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="926" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A926" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B926" s="7" t="s">
         <v>3</v>
@@ -7918,7 +7921,7 @@
     </row>
     <row r="937" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A937" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B937" s="7" t="s">
         <v>3</v>
@@ -7987,6 +7990,9 @@
       <c r="B945" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C945" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="946" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B946" s="3" t="s">
@@ -8003,7 +8009,7 @@
     </row>
     <row r="948" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A948" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B948" s="7" t="s">
         <v>3</v>
@@ -8072,9 +8078,6 @@
       <c r="B956" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C956" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="957" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B957" s="3" t="s">
@@ -8082,19 +8085,19 @@
       </c>
     </row>
     <row r="958" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A958" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B958" s="7" t="s">
-        <v>3</v>
+      <c r="B958" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C958" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="959" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B959" s="3" t="s">
-        <v>4</v>
+      <c r="A959" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B959" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C959" s="5" t="s">
         <v>13</v>
@@ -8102,7 +8105,7 @@
     </row>
     <row r="960" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B960" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C960" s="5" t="s">
         <v>13</v>
@@ -8110,7 +8113,7 @@
     </row>
     <row r="961" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B961" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C961" s="5" t="s">
         <v>13</v>
@@ -8118,7 +8121,7 @@
     </row>
     <row r="962" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B962" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C962" s="5" t="s">
         <v>13</v>
@@ -8126,7 +8129,7 @@
     </row>
     <row r="963" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B963" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C963" s="5" t="s">
         <v>13</v>
@@ -8134,7 +8137,7 @@
     </row>
     <row r="964" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B964" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C964" s="5" t="s">
         <v>13</v>
@@ -8142,7 +8145,7 @@
     </row>
     <row r="965" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B965" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C965" s="5" t="s">
         <v>13</v>
@@ -8150,7 +8153,7 @@
     </row>
     <row r="966" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B966" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C966" s="5" t="s">
         <v>13</v>
@@ -8158,23 +8161,23 @@
     </row>
     <row r="967" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B967" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C967" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="968" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A968" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B968" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C968" s="5" t="s">
-        <v>13</v>
+      <c r="B968" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="969" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B969" s="3" t="s">
-        <v>4</v>
+      <c r="A969" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B969" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C969" s="5" t="s">
         <v>13</v>
@@ -8182,7 +8185,7 @@
     </row>
     <row r="970" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B970" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C970" s="5" t="s">
         <v>13</v>
@@ -8190,7 +8193,7 @@
     </row>
     <row r="971" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B971" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C971" s="5" t="s">
         <v>13</v>
@@ -8198,7 +8201,7 @@
     </row>
     <row r="972" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B972" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C972" s="5" t="s">
         <v>13</v>
@@ -8206,7 +8209,7 @@
     </row>
     <row r="973" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B973" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C973" s="5" t="s">
         <v>13</v>
@@ -8214,7 +8217,7 @@
     </row>
     <row r="974" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B974" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C974" s="5" t="s">
         <v>13</v>
@@ -8222,7 +8225,7 @@
     </row>
     <row r="975" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B975" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C975" s="5" t="s">
         <v>13</v>
@@ -8230,16 +8233,104 @@
     </row>
     <row r="976" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B976" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="977" spans="2:2" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="C976" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="977" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B977" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="978" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B978" s="3">
+        <v>11</v>
+      </c>
+      <c r="C977" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="978" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B978" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="979" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A979" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B979" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C979" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="980" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B980" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C980" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="981" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B981" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C981" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="982" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B982" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C982" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="983" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B983" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C983" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="984" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B984" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C984" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="985" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B985" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C985" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="986" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B986" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C986" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="987" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B987" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="988" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B988" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="989" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B989" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C799B20-DC60-4F1C-8B95-0BE25CCF52D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1240E4FF-A0D4-4866-B384-7E189D08F04E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1863" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1885" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C989"/>
+  <dimension ref="A1:C1000"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -650,7 +650,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -741,7 +741,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -832,7 +832,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -923,7 +923,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -1014,7 +1014,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1105,7 +1105,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1196,7 +1196,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1378,7 +1378,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1469,7 +1469,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1560,7 +1560,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1651,7 +1651,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1742,7 +1742,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1833,7 +1833,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1924,7 +1924,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -2015,7 +2015,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2106,7 +2106,7 @@